--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544274330139</t>
+    <t xml:space="preserve">1.12615501880646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1254426240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.09552574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11831951141357</t>
+    <t xml:space="preserve">1.11831963062286</t>
   </si>
   <si>
     <t xml:space="preserve">1.0962381362915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09695029258728</t>
+    <t xml:space="preserve">1.09695041179657</t>
   </si>
   <si>
     <t xml:space="preserve">1.10407328605652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09053957462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412873744965</t>
+    <t xml:space="preserve">1.0905396938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412885665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.00007677078247</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">0.925996959209442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993665993213654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925371170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01004898548126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0185968875885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492436885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213059902191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711664676666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02571988105774</t>
+    <t xml:space="preserve">0.993666112422943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925347328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01004922389984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492424964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0321307182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02571976184845</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495203495026</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">0.947366237640381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900354146957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024804115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530968666077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
+    <t xml:space="preserve">0.900354027748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435581684113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530909061432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830664634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160007476807</t>
   </si>
   <si>
     <t xml:space="preserve">0.961612284183502</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">0.962324559688568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00435054302216</t>
+    <t xml:space="preserve">1.00435066223145</t>
   </si>
   <si>
     <t xml:space="preserve">0.997939884662628</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">0.991529166698456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979420065879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990817070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967550754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227549552917</t>
+    <t xml:space="preserve">0.979419887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990816950798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967610359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227489948273</t>
   </si>
   <si>
     <t xml:space="preserve">1.01717209815979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01503539085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078904628754</t>
+    <t xml:space="preserve">1.0150351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078916549683</t>
   </si>
   <si>
     <t xml:space="preserve">1.02215826511383</t>
@@ -194,46 +194,46 @@
     <t xml:space="preserve">1.00791203975677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03284275531769</t>
+    <t xml:space="preserve">1.03284299373627</t>
   </si>
   <si>
     <t xml:space="preserve">1.01930904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979951381683</t>
+    <t xml:space="preserve">1.03996598720551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979963302612</t>
   </si>
   <si>
     <t xml:space="preserve">1.1005117893219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.084841132164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982741832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18171489238739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185322284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968873023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15393495559692</t>
+    <t xml:space="preserve">1.08484125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1817147731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818082332611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185334205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968884944916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15393459796906</t>
   </si>
   <si>
     <t xml:space="preserve">1.11689484119415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09766268730164</t>
+    <t xml:space="preserve">1.09766256809235</t>
   </si>
   <si>
     <t xml:space="preserve">1.16105794906616</t>
@@ -251,58 +251,58 @@
     <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12900400161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316699028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17031800746918</t>
+    <t xml:space="preserve">1.12900412082672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467489719391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316710948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17031788825989</t>
   </si>
   <si>
     <t xml:space="preserve">1.18100237846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19738554954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21091938018799</t>
+    <t xml:space="preserve">1.197385430336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2109192609787</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163141727448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20593309402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302842140198</t>
+    <t xml:space="preserve">1.20593297481537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302830219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089147567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596076011658</t>
+    <t xml:space="preserve">1.19596087932587</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548460006714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22670149803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937349319458</t>
+    <t xml:space="preserve">1.22670161724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937361240387</t>
   </si>
   <si>
     <t xml:space="preserve">1.18790972232819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1630243062973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16595196723938</t>
+    <t xml:space="preserve">1.16302418708801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16595208644867</t>
   </si>
   <si>
     <t xml:space="preserve">1.16229236125946</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">1.15570497512817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14911770820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424144268036</t>
+    <t xml:space="preserve">1.14911794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424132347107</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
@@ -326,28 +326,28 @@
     <t xml:space="preserve">1.11837697029114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10154271125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10520243644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934711456299</t>
+    <t xml:space="preserve">1.10154294967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10520267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934687614441</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1293557882309</t>
+    <t xml:space="preserve">1.12935590744019</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203657627106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12716007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07226598262787</t>
+    <t xml:space="preserve">1.12715995311737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07226574420929</t>
   </si>
   <si>
     <t xml:space="preserve">1.06860637664795</t>
@@ -356,34 +356,34 @@
     <t xml:space="preserve">1.13081955909729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423264980316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15716898441315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18717777729034</t>
+    <t xml:space="preserve">1.12423276901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15716886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18717765808105</t>
   </si>
   <si>
     <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20767164230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17839455604553</t>
+    <t xml:space="preserve">1.20767152309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17839467525482</t>
   </si>
   <si>
     <t xml:space="preserve">1.20401191711426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18351817131042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20474374294281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1747350692749</t>
+    <t xml:space="preserve">1.18351793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20474398136139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17473495006561</t>
   </si>
   <si>
     <t xml:space="preserve">1.18571388721466</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">1.1930330991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20035243034363</t>
+    <t xml:space="preserve">1.20035219192505</t>
   </si>
   <si>
     <t xml:space="preserve">1.19888854026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21499073505402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693981647491</t>
+    <t xml:space="preserve">1.21499085426331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693945884705</t>
   </si>
   <si>
     <t xml:space="preserve">1.21425902843475</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">1.22230982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2296290397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2332888841629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22450578212738</t>
+    <t xml:space="preserve">1.22962927818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23328876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22450566291809</t>
   </si>
   <si>
     <t xml:space="preserve">1.25524652004242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28232753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745994091034</t>
+    <t xml:space="preserve">1.28232765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745982170105</t>
   </si>
   <si>
     <t xml:space="preserve">1.30208945274353</t>
@@ -437,79 +437,79 @@
     <t xml:space="preserve">1.29550218582153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29184257984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866780757904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24426782131195</t>
+    <t xml:space="preserve">1.2918426990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
     <t xml:space="preserve">1.25890624523163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27354443073273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963795185089</t>
+    <t xml:space="preserve">1.27354454994202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25963807106018</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183378696442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26256573200226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26915311813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694849014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24719536304474</t>
+    <t xml:space="preserve">1.26256561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26915299892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694860935211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109304904938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402962207794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24719512462616</t>
   </si>
   <si>
     <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21938240528107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19962048530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669270515442</t>
+    <t xml:space="preserve">1.21938228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962024688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669282436371</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376504421234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766261100769</t>
+    <t xml:space="preserve">1.17766273021698</t>
   </si>
   <si>
     <t xml:space="preserve">1.19742465019226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20620775222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230103492737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522002220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15643692016602</t>
+    <t xml:space="preserve">1.20620763301849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230115413666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522014141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15643703937531</t>
   </si>
   <si>
     <t xml:space="preserve">1.16887974739075</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">1.17693078517914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19522881507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985856533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498206138611</t>
+    <t xml:space="preserve">1.19522905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985844612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498182296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.17400312423706</t>
@@ -542,40 +542,40 @@
     <t xml:space="preserve">1.14326238632202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11252176761627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1344792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325371265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593438148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1227685213089</t>
+    <t xml:space="preserve">1.11252164840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13447940349579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984074115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593450069427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007894039154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12276864051819</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032593250275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1161812543869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13960289955139</t>
+    <t xml:space="preserve">1.11618137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1396027803421</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14399421215057</t>
+    <t xml:space="preserve">1.14399433135986</t>
   </si>
   <si>
     <t xml:space="preserve">1.14179849624634</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">1.13813889026642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14253044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19449698925018</t>
+    <t xml:space="preserve">1.14253056049347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19449687004089</t>
   </si>
   <si>
     <t xml:space="preserve">1.1813223361969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17253947257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912638187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887107372284</t>
+    <t xml:space="preserve">1.17253935337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912662029266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887083530426</t>
   </si>
   <si>
     <t xml:space="preserve">1.13374745845795</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">1.12350046634674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12569630146027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11910879611969</t>
+    <t xml:space="preserve">1.12569618225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11910891532898</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496447563171</t>
@@ -623,34 +623,34 @@
     <t xml:space="preserve">1.12642824649811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15936481952667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277743339539</t>
+    <t xml:space="preserve">1.15936470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1527773141861</t>
   </si>
   <si>
     <t xml:space="preserve">1.16741585731506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22377383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596943378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25671029090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792742729187</t>
+    <t xml:space="preserve">1.22377395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596955299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2567104101181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792730808258</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26622533798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26842105388641</t>
+    <t xml:space="preserve">1.26622521877289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2684211730957</t>
   </si>
   <si>
     <t xml:space="preserve">1.29769802093506</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">1.30867671966553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29403829574585</t>
+    <t xml:space="preserve">1.29403841495514</t>
   </si>
   <si>
     <t xml:space="preserve">1.3247789144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32404708862305</t>
+    <t xml:space="preserve">1.32404720783234</t>
   </si>
   <si>
     <t xml:space="preserve">1.31014060974121</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">1.3284387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29037857055664</t>
+    <t xml:space="preserve">1.29037880897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135762691498</t>
@@ -683,37 +683,37 @@
     <t xml:space="preserve">1.30282139778137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31526410579681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32624280452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137521266937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941745758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34673678874969</t>
+    <t xml:space="preserve">1.3152642250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32624292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137533187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941769599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34673690795898</t>
   </si>
   <si>
     <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36869442462921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772439956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35991144180298</t>
+    <t xml:space="preserve">1.3686945438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772451877594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3599112033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.37454986572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40529048442841</t>
+    <t xml:space="preserve">1.40529036521912</t>
   </si>
   <si>
     <t xml:space="preserve">1.39065206050873</t>
@@ -722,37 +722,37 @@
     <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114580631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38186919689178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37162208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927766799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45009875297546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046503543854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53654825687408</t>
+    <t xml:space="preserve">1.41114592552185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38186895847321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162220478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38845610618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927754878998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45009863376617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046491622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53654837608337</t>
   </si>
   <si>
     <t xml:space="preserve">1.56361079216003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58616268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60570812225342</t>
+    <t xml:space="preserve">1.58616292476654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60570800304413</t>
   </si>
   <si>
     <t xml:space="preserve">1.51700305938721</t>
@@ -764,40 +764,40 @@
     <t xml:space="preserve">1.48693382740021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47866451740265</t>
+    <t xml:space="preserve">1.47866463661194</t>
   </si>
   <si>
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814048290253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964395046234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44333302974701</t>
+    <t xml:space="preserve">1.46814024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964383125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44333291053772</t>
   </si>
   <si>
     <t xml:space="preserve">1.44483661651611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43882262706757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43205690383911</t>
+    <t xml:space="preserve">1.43882274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4320570230484</t>
   </si>
   <si>
     <t xml:space="preserve">1.43581557273865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574622154236</t>
+    <t xml:space="preserve">1.40574634075165</t>
   </si>
   <si>
     <t xml:space="preserve">1.45836782455444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45911955833435</t>
+    <t xml:space="preserve">1.45911931991577</t>
   </si>
   <si>
     <t xml:space="preserve">1.47189903259277</t>
@@ -806,28 +806,28 @@
     <t xml:space="preserve">1.4531055688858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42829823493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41852569580078</t>
+    <t xml:space="preserve">1.42829835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41852581501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4207808971405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42604315280914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41702222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42529141902924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44408476352692</t>
+    <t xml:space="preserve">1.42078101634979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42604291439056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41702234745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42529153823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44408488273621</t>
   </si>
   <si>
     <t xml:space="preserve">1.47716116905212</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">1.49219584465027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46663677692413</t>
+    <t xml:space="preserve">1.46663689613342</t>
   </si>
   <si>
     <t xml:space="preserve">1.46588516235352</t>
@@ -845,166 +845,166 @@
     <t xml:space="preserve">1.49144411087036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48843705654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850664615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948560237885</t>
+    <t xml:space="preserve">1.48843729496002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948572158813</t>
   </si>
   <si>
     <t xml:space="preserve">1.50347197055817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48167169094086</t>
+    <t xml:space="preserve">1.48167145252228</t>
   </si>
   <si>
     <t xml:space="preserve">1.49595463275909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51249289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497543811798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151370048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49369919300079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49896144866943</t>
+    <t xml:space="preserve">1.51249277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497555732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151358127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369931221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49896132946014</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602410316467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49670648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5079824924469</t>
+    <t xml:space="preserve">1.496706366539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798237323761</t>
   </si>
   <si>
     <t xml:space="preserve">1.54857611656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48242342472076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039544582367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941637039185</t>
+    <t xml:space="preserve">1.48242330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941648960114</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903091907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51399624347687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158293247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511437892914</t>
+    <t xml:space="preserve">1.52903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51399636268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158281326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511425971985</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609345436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126718997955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682601928711</t>
+    <t xml:space="preserve">1.63126707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637121677399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6568261384964</t>
   </si>
   <si>
     <t xml:space="preserve">1.69140601158142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70644056797028</t>
+    <t xml:space="preserve">1.70644044876099</t>
   </si>
   <si>
     <t xml:space="preserve">1.71997201442719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65381932258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937803268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735053062439</t>
+    <t xml:space="preserve">1.65381920337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937791347504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735017299652</t>
   </si>
   <si>
     <t xml:space="preserve">1.66885387897491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67787456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186081409454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839907646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983307361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6463018655777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7440277338028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115962028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318688392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213833808899</t>
+    <t xml:space="preserve">1.67787480354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6883989572525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68689525127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983283519745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878452777863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64630162715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402725696564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318736076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213869571686</t>
   </si>
   <si>
     <t xml:space="preserve">1.79965591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84175312519073</t>
+    <t xml:space="preserve">1.84175300598145</t>
   </si>
   <si>
     <t xml:space="preserve">1.86430525779724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83874595165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657950878143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245455741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206910610199</t>
+    <t xml:space="preserve">1.83874642848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71245443820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133666038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7620689868927</t>
   </si>
   <si>
     <t xml:space="preserve">1.77560031414032</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">1.80566990375519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82220780849457</t>
+    <t xml:space="preserve">1.82220804691315</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899270057678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7410204410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598588466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75154483318329</t>
+    <t xml:space="preserve">1.74102079868317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598564624786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.751544713974</t>
   </si>
   <si>
     <t xml:space="preserve">1.72297883033752</t>
@@ -1037,79 +1037,79 @@
     <t xml:space="preserve">1.70193028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69441294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388855457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434335708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72448229789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71846878528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755870342255</t>
+    <t xml:space="preserve">1.69441282749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388867378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728106021881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434359550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72448194026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846854686737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755894184113</t>
   </si>
   <si>
     <t xml:space="preserve">1.73500657081604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73951685428619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73651003837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71395790576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161418437958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906205177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920111179352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82671844959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416631698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87934005260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664885997772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913176059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927046298981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701057434082</t>
+    <t xml:space="preserve">1.73951721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73651015758514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71395778656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161382675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906217098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416619777679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87933969497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88685715198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168353557587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7966490983963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409684658051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913152217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8492705821991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870108127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.89468145370483</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">1.84865689277649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86399829387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797361373901</t>
+    <t xml:space="preserve">1.86399805545807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797349452972</t>
   </si>
   <si>
     <t xml:space="preserve">1.81030285358429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90235209465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331525325775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8026317358017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660741329193</t>
+    <t xml:space="preserve">1.90235221385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263221263885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660753250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.70291197299957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76427829265594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67989981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524157047272</t>
+    <t xml:space="preserve">1.76427805423737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989945411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524133205414</t>
   </si>
   <si>
     <t xml:space="preserve">1.67222905158997</t>
@@ -1157,52 +1157,52 @@
     <t xml:space="preserve">1.7489367723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65688753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154601097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5801796913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455841064453</t>
+    <t xml:space="preserve">1.65688765048981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154589176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58017957210541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455829143524</t>
   </si>
   <si>
     <t xml:space="preserve">1.62620413303375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57250881195068</t>
+    <t xml:space="preserve">1.57250893115997</t>
   </si>
   <si>
     <t xml:space="preserve">1.51497805118561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53031957149506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48813045024872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4152580499649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41142272949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3730685710907</t>
+    <t xml:space="preserve">1.53031945228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48813033103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41525793075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4114226102829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
     <t xml:space="preserve">1.35005629062653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38073933124542</t>
+    <t xml:space="preserve">1.38073945045471</t>
   </si>
   <si>
     <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36923313140869</t>
+    <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
     <t xml:space="preserve">1.39991652965546</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">1.35772716999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35389184951782</t>
+    <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.34238564968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30403172969818</t>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101933002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26951336860657</t>
+    <t xml:space="preserve">1.26951324939728</t>
   </si>
   <si>
     <t xml:space="preserve">1.25417172908783</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">1.24650096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25800728797913</t>
+    <t xml:space="preserve">1.25800693035126</t>
   </si>
   <si>
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869032859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019664764404</t>
+    <t xml:space="preserve">1.28869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019640922546</t>
   </si>
   <si>
     <t xml:space="preserve">1.29252552986145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31937325000763</t>
+    <t xml:space="preserve">1.31937336921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.30786716938019</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">1.33087956905365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33855009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471477031708</t>
+    <t xml:space="preserve">1.33855032920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471488952637</t>
   </si>
   <si>
     <t xml:space="preserve">1.31553792953491</t>
@@ -1268,43 +1268,43 @@
     <t xml:space="preserve">1.39608108997345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38457489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40375185012817</t>
+    <t xml:space="preserve">1.38457477092743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40375173091888</t>
   </si>
   <si>
     <t xml:space="preserve">1.36156260967255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36539793014526</t>
+    <t xml:space="preserve">1.36539804935455</t>
   </si>
   <si>
     <t xml:space="preserve">1.43443500995636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37690412998199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38841021060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3462210893631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704389095306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320868968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706005573273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3890346288681</t>
+    <t xml:space="preserve">1.37690401077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38841032981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34622097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334868907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320857048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38903474807739</t>
   </si>
   <si>
     <t xml:space="preserve">1.3610942363739</t>
@@ -1316,37 +1316,37 @@
     <t xml:space="preserve">1.35311138629913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34512829780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508584022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39701747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41298341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40100908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40899193286896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41697490215302</t>
+    <t xml:space="preserve">1.34512841701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508595943451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39701759815216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41298353672028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4010089635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40899205207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4169750213623</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886432170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49680459499359</t>
+    <t xml:space="preserve">1.4968044757843</t>
   </si>
   <si>
     <t xml:space="preserve">1.50877904891968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51277053356171</t>
+    <t xml:space="preserve">1.51277041435242</t>
   </si>
   <si>
     <t xml:space="preserve">1.49281311035156</t>
@@ -1355,43 +1355,43 @@
     <t xml:space="preserve">1.46487271785736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50079607963562</t>
+    <t xml:space="preserve">1.50079596042633</t>
   </si>
   <si>
     <t xml:space="preserve">1.44491529464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45289838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693244457245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495787143707</t>
+    <t xml:space="preserve">1.45289826393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495799064636</t>
   </si>
   <si>
     <t xml:space="preserve">1.42096638679504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40500056743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39302599430084</t>
+    <t xml:space="preserve">1.40500044822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39302611351013</t>
   </si>
   <si>
     <t xml:space="preserve">1.38504314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42894923686981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306869029999</t>
+    <t xml:space="preserve">1.4289493560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306880950928</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35710299015045</t>
+    <t xml:space="preserve">1.35710275173187</t>
   </si>
   <si>
     <t xml:space="preserve">1.3491199016571</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">1.4848301410675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47684717178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46088135242462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48882150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075326442719</t>
+    <t xml:space="preserve">1.47684705257416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46088123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48882162570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075350284576</t>
   </si>
   <si>
     <t xml:space="preserve">1.51676201820374</t>
@@ -1418,22 +1418,22 @@
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659147262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5646595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54071068763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53272771835327</t>
+    <t xml:space="preserve">1.59659135341644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56465971469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54071080684662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
     <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58860850334167</t>
+    <t xml:space="preserve">1.58860874176025</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
@@ -1442,22 +1442,22 @@
     <t xml:space="preserve">1.54869377613068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5367192029953</t>
+    <t xml:space="preserve">1.53671932220459</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470217227936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55268526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52474498748779</t>
+    <t xml:space="preserve">1.55268537998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52474474906921</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264268398285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642104625702</t>
+    <t xml:space="preserve">1.67642092704773</t>
   </si>
   <si>
     <t xml:space="preserve">1.86801207065582</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">1.9478417634964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15539860725403</t>
+    <t xml:space="preserve">2.15539836883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.05960297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16338133811951</t>
+    <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
     <t xml:space="preserve">2.20329642295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926236152649</t>
+    <t xml:space="preserve">2.21926212310791</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">2.17934727668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23522806167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11548376083374</t>
+    <t xml:space="preserve">2.23522782325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11548352241516</t>
   </si>
   <si>
     <t xml:space="preserve">1.9877564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011437416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91590976715088</t>
+    <t xml:space="preserve">1.82011449337006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809746265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91591000556946</t>
   </si>
   <si>
     <t xml:space="preserve">1.86002898216248</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">1.62852334976196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64448928833008</t>
+    <t xml:space="preserve">1.6444890499115</t>
   </si>
   <si>
     <t xml:space="preserve">1.68440401554108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60457456111908</t>
+    <t xml:space="preserve">1.60457444190979</t>
   </si>
   <si>
     <t xml:space="preserve">1.66045522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65247213840485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826776981354</t>
+    <t xml:space="preserve">1.65247225761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826753139496</t>
   </si>
   <si>
     <t xml:space="preserve">1.71633589267731</t>
@@ -1550,40 +1550,40 @@
     <t xml:space="preserve">1.62054038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843819618225</t>
+    <t xml:space="preserve">1.66843783855438</t>
   </si>
   <si>
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238698482513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75625097751617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76423370838165</t>
+    <t xml:space="preserve">1.69238686561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625061988831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
     <t xml:space="preserve">1.90792691707611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95582485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92389297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757211208344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456258296967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679543018341</t>
+    <t xml:space="preserve">1.95582461357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389273643494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757223129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9145622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679519176483</t>
   </si>
   <si>
     <t xml:space="preserve">1.84029054641724</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">1.81553339958191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79077613353729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75776660442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902851581573</t>
+    <t xml:space="preserve">1.790776014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75776636600494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902839660645</t>
   </si>
   <si>
     <t xml:space="preserve">1.77427124977112</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">1.76601886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74126136302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252387046814</t>
+    <t xml:space="preserve">1.74126148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252375125885</t>
   </si>
   <si>
     <t xml:space="preserve">1.73300898075104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7495139837265</t>
+    <t xml:space="preserve">1.74951374530792</t>
   </si>
   <si>
     <t xml:space="preserve">1.71650421619415</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">1.66698956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174695014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72475671768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048480033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985396385193</t>
+    <t xml:space="preserve">1.65873718261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174706935883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7247565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048491954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398015499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572765350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985384464264</t>
   </si>
   <si>
     <t xml:space="preserve">1.60922276973724</t>
@@ -1664,91 +1664,94 @@
     <t xml:space="preserve">1.89805746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95582461357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660105705261</t>
+    <t xml:space="preserve">1.95582437515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
     <t xml:space="preserve">1.9640771150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9393196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330031394958</t>
+    <t xml:space="preserve">1.93931972980499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8733001947403</t>
   </si>
   <si>
     <t xml:space="preserve">1.88155269622803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88980519771576</t>
+    <t xml:space="preserve">1.88980531692505</t>
   </si>
   <si>
     <t xml:space="preserve">1.86504793167114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92281472682953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106722831726</t>
+    <t xml:space="preserve">1.92281484603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106734752655</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883450031281</t>
+    <t xml:space="preserve">1.98883414268494</t>
   </si>
   <si>
     <t xml:space="preserve">1.97232949733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98058199882507</t>
+    <t xml:space="preserve">1.98058176040649</t>
   </si>
   <si>
     <t xml:space="preserve">2.0631058216095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19514513015747</t>
+    <t xml:space="preserve">2.19514489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17864012718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17038774490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563012123108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566035270691</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17038774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213488578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715023994446</t>
+    <t xml:space="preserve">2.18715000152588</t>
   </si>
   <si>
     <t xml:space="preserve">2.15310907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11906766891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08502674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09353685379028</t>
+    <t xml:space="preserve">2.11906790733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08502650260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09353709220886</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396487236023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02545428276062</t>
+    <t xml:space="preserve">2.03396463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254545211792</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
@@ -1760,22 +1763,22 @@
     <t xml:space="preserve">1.91482019424438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93184101581573</t>
+    <t xml:space="preserve">1.93184065818787</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290276527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11055731773376</t>
+    <t xml:space="preserve">1.98290252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439229488373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0765163898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
     <t xml:space="preserve">2.05949568748474</t>
@@ -1790,10 +1793,10 @@
     <t xml:space="preserve">2.00843358039856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01694393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204720497131</t>
+    <t xml:space="preserve">2.01694369316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204696655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
@@ -1802,7 +1805,7 @@
     <t xml:space="preserve">2.14459872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16161918640137</t>
+    <t xml:space="preserve">2.16161942481995</t>
   </si>
   <si>
     <t xml:space="preserve">2.13608837127686</t>
@@ -1811,25 +1814,22 @@
     <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94035124778748</t>
+    <t xml:space="preserve">1.94035112857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.89779961109161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90631008148193</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.8722687959671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92333042621613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94886159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07243394851685</t>
+    <t xml:space="preserve">1.92333054542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94886147975922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07243418693542</t>
   </si>
   <si>
     <t xml:space="preserve">2.08129048347473</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">2.05472087860107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04586458206177</t>
+    <t xml:space="preserve">2.04586434364319</t>
   </si>
   <si>
     <t xml:space="preserve">2.00158166885376</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958580493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9750120639801</t>
+    <t xml:space="preserve">1.93958556652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97501194477081</t>
   </si>
   <si>
     <t xml:space="preserve">1.99272501468658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95729899406433</t>
+    <t xml:space="preserve">1.95729887485504</t>
   </si>
   <si>
     <t xml:space="preserve">1.94844233989716</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">1.8687332868576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92187285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91301620006561</t>
+    <t xml:space="preserve">1.92187261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9130163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775897026062</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90415954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89530313014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8244503736496</t>
+    <t xml:space="preserve">1.96615540981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90415966510773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89530301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82445049285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">1.79788088798523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70045876502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70488703250885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131116390228</t>
+    <t xml:space="preserve">1.70045864582062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70488691329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131128311157</t>
   </si>
   <si>
     <t xml:space="preserve">1.815593957901</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">1.74474155902863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85102021694183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016781806946</t>
+    <t xml:space="preserve">1.85102009773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84216368198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016769886017</t>
   </si>
   <si>
     <t xml:space="preserve">1.85987663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75802648067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76245450973511</t>
+    <t xml:space="preserve">1.75802636146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76245474815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">1.71817195415497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7093151807785</t>
+    <t xml:space="preserve">1.70931529998779</t>
   </si>
   <si>
     <t xml:space="preserve">1.72702848911285</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295209407806</t>
+    <t xml:space="preserve">1.88295221328735</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988074302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142035007477</t>
+    <t xml:space="preserve">1.79988086223602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142046928406</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526966571808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988884449005</t>
+    <t xml:space="preserve">1.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757925510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66142845153809</t>
+    <t xml:space="preserve">1.6614283323288</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9752539396286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833291530609</t>
+    <t xml:space="preserve">1.97525370121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833303451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526180267334</t>
+    <t xml:space="preserve">1.81372606754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526168346405</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89218235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910301685333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064262390137</t>
+    <t xml:space="preserve">1.8921822309494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910277843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064250469208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371409416199</t>
+    <t xml:space="preserve">1.99371421337128</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -38672,7 +38672,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38698,7 +38698,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38724,7 +38724,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38776,7 +38776,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38802,7 +38802,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38828,7 +38828,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38854,7 +38854,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38880,7 +38880,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38906,7 +38906,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38932,7 +38932,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38958,7 +38958,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38984,7 +38984,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39010,7 +39010,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39036,7 +39036,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39062,7 +39062,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39088,7 +39088,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39114,7 +39114,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39140,7 +39140,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39166,7 +39166,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39192,7 +39192,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39218,7 +39218,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39244,7 +39244,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39270,7 +39270,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39296,7 +39296,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39322,7 +39322,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39348,7 +39348,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39374,7 +39374,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39400,7 +39400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39426,7 +39426,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39452,7 +39452,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39478,7 +39478,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39504,7 +39504,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39530,7 +39530,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39556,7 +39556,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39582,7 +39582,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39608,7 +39608,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39634,7 +39634,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39660,7 +39660,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39686,7 +39686,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39712,7 +39712,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39738,7 +39738,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39764,7 +39764,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39790,7 +39790,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39816,7 +39816,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39842,7 +39842,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39868,7 +39868,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39894,7 +39894,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39920,7 +39920,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39946,7 +39946,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39972,7 +39972,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39998,7 +39998,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40024,7 +40024,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40050,7 +40050,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40076,7 +40076,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40102,7 +40102,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40128,7 +40128,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40154,7 +40154,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40180,7 +40180,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40206,7 +40206,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40232,7 +40232,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40258,7 +40258,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40284,7 +40284,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40310,7 +40310,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40336,7 +40336,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40362,7 +40362,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40388,7 +40388,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40414,7 +40414,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40440,7 +40440,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40466,7 +40466,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40492,7 +40492,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40518,7 +40518,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40544,7 +40544,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40570,7 +40570,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40596,7 +40596,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40622,7 +40622,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40648,7 +40648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40674,7 +40674,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40700,7 +40700,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40726,7 +40726,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40752,7 +40752,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40778,7 +40778,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40804,7 +40804,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40830,7 +40830,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40856,7 +40856,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40882,7 +40882,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40908,7 +40908,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40934,7 +40934,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40960,7 +40960,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40986,7 +40986,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41012,7 +41012,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41038,7 +41038,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41064,7 +41064,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41090,7 +41090,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41116,7 +41116,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41142,7 +41142,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41168,7 +41168,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41194,7 +41194,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41220,7 +41220,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41246,7 +41246,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41272,7 +41272,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41298,7 +41298,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41324,7 +41324,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41350,7 +41350,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41376,7 +41376,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41402,7 +41402,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41428,7 +41428,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41454,7 +41454,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41480,7 +41480,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41506,7 +41506,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41532,7 +41532,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41558,7 +41558,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41584,7 +41584,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41610,7 +41610,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41636,7 +41636,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41662,7 +41662,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41688,7 +41688,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41714,7 +41714,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41740,7 +41740,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41766,7 +41766,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41792,7 +41792,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41818,7 +41818,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41844,7 +41844,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41870,7 +41870,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41896,7 +41896,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41922,7 +41922,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41948,7 +41948,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41974,7 +41974,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42000,7 +42000,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42026,7 +42026,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42052,7 +42052,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42078,7 +42078,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42104,7 +42104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42130,7 +42130,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42156,7 +42156,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42182,7 +42182,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42208,7 +42208,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42234,7 +42234,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42260,7 +42260,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42286,7 +42286,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42312,7 +42312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42338,7 +42338,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42364,7 +42364,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42390,7 +42390,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42416,7 +42416,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42442,7 +42442,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42468,7 +42468,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42494,7 +42494,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42520,7 +42520,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42546,7 +42546,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42572,7 +42572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42598,7 +42598,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42624,7 +42624,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42650,7 +42650,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42676,7 +42676,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42702,7 +42702,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42728,7 +42728,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42754,7 +42754,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42780,7 +42780,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42806,7 +42806,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42832,7 +42832,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42858,7 +42858,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42884,7 +42884,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42910,7 +42910,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42936,7 +42936,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42962,7 +42962,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42988,7 +42988,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43014,7 +43014,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43040,7 +43040,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43066,7 +43066,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43092,7 +43092,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43118,7 +43118,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43144,7 +43144,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43170,7 +43170,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43196,7 +43196,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43222,7 +43222,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43248,7 +43248,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43274,7 +43274,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43300,7 +43300,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43326,7 +43326,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43352,7 +43352,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>601</v>
+        <v>522</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43482,7 +43482,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43508,7 +43508,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43534,7 +43534,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43560,7 +43560,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43586,7 +43586,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43612,7 +43612,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43638,7 +43638,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43664,7 +43664,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43690,7 +43690,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43716,7 +43716,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43742,7 +43742,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43768,7 +43768,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43794,7 +43794,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43820,7 +43820,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43846,7 +43846,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43872,7 +43872,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43898,7 +43898,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43924,7 +43924,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43950,7 +43950,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43976,7 +43976,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44002,7 +44002,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44028,7 +44028,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44054,7 +44054,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44080,7 +44080,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44106,7 +44106,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44132,7 +44132,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44158,7 +44158,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44184,7 +44184,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44210,7 +44210,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44236,7 +44236,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44262,7 +44262,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44418,7 +44418,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44444,7 +44444,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44470,7 +44470,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44496,7 +44496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44548,7 +44548,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44574,7 +44574,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44600,7 +44600,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44626,7 +44626,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44652,7 +44652,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44678,7 +44678,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44704,7 +44704,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44730,7 +44730,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44756,7 +44756,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44782,7 +44782,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44808,7 +44808,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44834,7 +44834,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44860,7 +44860,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44886,7 +44886,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44912,7 +44912,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44938,7 +44938,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44964,7 +44964,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44990,7 +44990,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45016,7 +45016,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45042,7 +45042,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45068,7 +45068,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45094,7 +45094,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45120,7 +45120,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45146,7 +45146,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45172,7 +45172,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45198,7 +45198,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45224,7 +45224,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45250,7 +45250,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45276,7 +45276,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -67202,7 +67202,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6444212963</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>8791</v>
@@ -67223,6 +67223,32 @@
         <v>726</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.555162037</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>2248</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">1.12615489959717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12544238567352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552562236786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831951141357</t>
+    <t xml:space="preserve">1.12544274330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831963062286</t>
   </si>
   <si>
     <t xml:space="preserve">1.0962381362915</t>
@@ -62,37 +62,37 @@
     <t xml:space="preserve">1.09695041179657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407328605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0905396938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412897586823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007688999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943804740905762</t>
+    <t xml:space="preserve">1.10407340526581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09053957462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412885665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007677078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943804800510406</t>
   </si>
   <si>
     <t xml:space="preserve">0.925997078418732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993665874004364</t>
+    <t xml:space="preserve">0.993666052818298</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925359249115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004922389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859676837921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492448806763</t>
+    <t xml:space="preserve">1.01004910469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0185968875885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492436885834</t>
   </si>
   <si>
     <t xml:space="preserve">1.03213059902191</t>
@@ -107,64 +107,64 @@
     <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643215656281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366178035736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354027748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91602486371994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435522079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530789852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830724239349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159888267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612224578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00435078144073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997939825057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392161369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529107093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419887065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990816831588745</t>
+    <t xml:space="preserve">1.02643227577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0207337141037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366297245026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354206562042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024744510651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435462474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530849456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830664634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324500083923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00435054302216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997940003871918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392340183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529047489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979420065879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990816950798035</t>
   </si>
   <si>
     <t xml:space="preserve">0.987967669963837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997227549552917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0171719789505</t>
+    <t xml:space="preserve">0.997227609157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717221736908</t>
   </si>
   <si>
     <t xml:space="preserve">1.0150351524353</t>
@@ -173,37 +173,37 @@
     <t xml:space="preserve">1.00078916549683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02215814590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577533245087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648760795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076138019562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00221371650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984406113624573</t>
+    <t xml:space="preserve">1.02215826511383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577521324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648748874664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0107616186142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00221395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984406054019928</t>
   </si>
   <si>
     <t xml:space="preserve">1.00791215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03284299373627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01930904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996598720551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979963302612</t>
+    <t xml:space="preserve">1.03284275531769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01930916309357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996586799622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979975223541</t>
   </si>
   <si>
     <t xml:space="preserve">1.10051190853119</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">1.084841132164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08982729911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1817147731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16818106174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185322284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15393471717834</t>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18171465396881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1681809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185334205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968861103058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15393483638763</t>
   </si>
   <si>
     <t xml:space="preserve">1.11689484119415</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">1.09766256809235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16105782985687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15963327884674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14752388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683950901031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612723350525</t>
+    <t xml:space="preserve">1.16105771064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15963339805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612735271454</t>
   </si>
   <si>
     <t xml:space="preserve">1.12900412082672</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">1.1703177690506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18100225925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19738566875458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21091938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163153648376</t>
+    <t xml:space="preserve">1.18100249767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.197385430336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163165569305</t>
   </si>
   <si>
     <t xml:space="preserve">1.20593297481537</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">1.19596087932587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23548448085785</t>
+    <t xml:space="preserve">1.23548460006714</t>
   </si>
   <si>
     <t xml:space="preserve">1.22670137882233</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">1.18937349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1879096031189</t>
+    <t xml:space="preserve">1.18790948390961</t>
   </si>
   <si>
     <t xml:space="preserve">1.1630243062973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16595208644867</t>
+    <t xml:space="preserve">1.16595184803009</t>
   </si>
   <si>
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375625133514</t>
+    <t xml:space="preserve">1.16375613212585</t>
   </si>
   <si>
     <t xml:space="preserve">1.15570497512817</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">1.14911782741547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15424120426178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14106667041779</t>
+    <t xml:space="preserve">1.15424108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1410665512085</t>
   </si>
   <si>
     <t xml:space="preserve">1.11837708950043</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">1.10154283046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520231723785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545810222626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1293557882309</t>
+    <t xml:space="preserve">1.10520255565643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0993469953537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12935590744019</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203669548035</t>
@@ -347,70 +347,70 @@
     <t xml:space="preserve">1.12716019153595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07226586341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860637664795</t>
+    <t xml:space="preserve">1.07226598262787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860625743866</t>
   </si>
   <si>
     <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423241138458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15716886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18717765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205428123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20767152309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17839467525482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401191711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18351805210114</t>
+    <t xml:space="preserve">1.12423253059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15716898441315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18717777729034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205416202545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20767164230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17839455604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401179790497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18351817131042</t>
   </si>
   <si>
     <t xml:space="preserve">1.2047438621521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1747350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571376800537</t>
+    <t xml:space="preserve">1.17473495006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571388721466</t>
   </si>
   <si>
     <t xml:space="preserve">1.17546689510345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1930330991745</t>
+    <t xml:space="preserve">1.19303297996521</t>
   </si>
   <si>
     <t xml:space="preserve">1.20035231113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19888865947723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693957805634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21425890922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22231006622314</t>
+    <t xml:space="preserve">1.19888854026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499073505402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693981647491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21425879001617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22230970859528</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962915897369</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22450578212738</t>
+    <t xml:space="preserve">1.22450590133667</t>
   </si>
   <si>
     <t xml:space="preserve">1.25524652004242</t>
@@ -428,118 +428,118 @@
     <t xml:space="preserve">1.28232765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31745970249176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208945274353</t>
+    <t xml:space="preserve">1.31745982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208957195282</t>
   </si>
   <si>
     <t xml:space="preserve">1.29550218582153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29184246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24426770210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25890600681305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354454994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2596378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26183378696442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26256585121155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26915287971497</t>
+    <t xml:space="preserve">1.2918426990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866780757904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24426758289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25890612602234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354443073273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25963807106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26183390617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26256561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26915311813354</t>
   </si>
   <si>
     <t xml:space="preserve">1.23694837093353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23109316825867</t>
+    <t xml:space="preserve">1.23109304904938</t>
   </si>
   <si>
     <t xml:space="preserve">1.26402950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24719536304474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22304177284241</t>
+    <t xml:space="preserve">1.24719524383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
     <t xml:space="preserve">1.21938228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19962060451508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669258594513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376504421234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17766273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742465019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20620763301849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059062957764</t>
+    <t xml:space="preserve">1.19962048530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669282436371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17766284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742476940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20620775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230103492737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059051036835</t>
   </si>
   <si>
     <t xml:space="preserve">1.16522002220154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15643692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16887962818146</t>
+    <t xml:space="preserve">1.15643715858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16887950897217</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693078517914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19522893428802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985856533051</t>
+    <t xml:space="preserve">1.19522881507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985832691193</t>
   </si>
   <si>
     <t xml:space="preserve">1.18498182296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17400300502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107546329498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16814792156219</t>
+    <t xml:space="preserve">1.17400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107534408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16814768314362</t>
   </si>
   <si>
     <t xml:space="preserve">1.1461900472641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14326226711273</t>
+    <t xml:space="preserve">1.14326250553131</t>
   </si>
   <si>
     <t xml:space="preserve">1.11252164840698</t>
@@ -548,40 +548,40 @@
     <t xml:space="preserve">1.1344792842865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11984086036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325359344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593438148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007894039154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276864051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1161812543869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13960301876068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1278920173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14399445056915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14179861545563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13521111011505</t>
+    <t xml:space="preserve">1.11984074115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325371265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593450069427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007905960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12276887893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032593250275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11618137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12789189815521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14399421215057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14179837703705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13521122932434</t>
   </si>
   <si>
     <t xml:space="preserve">1.13813889026642</t>
@@ -602,49 +602,49 @@
     <t xml:space="preserve">1.17912650108337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13887095451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13374745845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350046634674</t>
+    <t xml:space="preserve">1.13887107372284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13374733924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350034713745</t>
   </si>
   <si>
     <t xml:space="preserve">1.12569630146027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11910915374756</t>
+    <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12642812728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936458110809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1527773141861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741585731506</t>
+    <t xml:space="preserve">1.12642824649811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936481952667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15277743339539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741597652435</t>
   </si>
   <si>
     <t xml:space="preserve">1.22377395629883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22596955299377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25671052932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792730808258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24060809612274</t>
+    <t xml:space="preserve">1.22596967220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25671029090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24060821533203</t>
   </si>
   <si>
     <t xml:space="preserve">1.26622533798218</t>
@@ -653,40 +653,40 @@
     <t xml:space="preserve">1.26842105388641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29769814014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477915287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404720783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31014049053192</t>
+    <t xml:space="preserve">1.29769802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867683887482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403841495514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3101407289505</t>
   </si>
   <si>
     <t xml:space="preserve">1.32843887805939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29037868976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135750770569</t>
+    <t xml:space="preserve">1.29037857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135762691498</t>
   </si>
   <si>
     <t xml:space="preserve">1.30282127857208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3152642250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32624304294586</t>
+    <t xml:space="preserve">1.31526410579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32624316215515</t>
   </si>
   <si>
     <t xml:space="preserve">1.36137521266937</t>
@@ -698,43 +698,43 @@
     <t xml:space="preserve">1.34673678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38699245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36869442462921</t>
+    <t xml:space="preserve">1.38699233531952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3686945438385</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772439956665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35991144180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37454974651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40529036521912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39065194129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39650738239288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114592552185</t>
+    <t xml:space="preserve">1.35991132259369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37454986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40529048442841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39065206050873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39650750160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114604473114</t>
   </si>
   <si>
     <t xml:space="preserve">1.38186895847321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.371621966362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845646381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927742958069</t>
+    <t xml:space="preserve">1.37162208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3884562253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927754878998</t>
   </si>
   <si>
     <t xml:space="preserve">1.45009875297546</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53654813766479</t>
+    <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
     <t xml:space="preserve">1.56361067295074</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">1.58616280555725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60570776462555</t>
+    <t xml:space="preserve">1.60570788383484</t>
   </si>
   <si>
     <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51098930835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693382740021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866463661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49069249629974</t>
+    <t xml:space="preserve">1.51098906993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866475582123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49069261550903</t>
   </si>
   <si>
     <t xml:space="preserve">1.46814024448395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46964395046234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44333291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882262706757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4320570230484</t>
+    <t xml:space="preserve">1.46964371204376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44333302974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483649730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43205714225769</t>
   </si>
   <si>
     <t xml:space="preserve">1.43581569194794</t>
@@ -797,67 +797,67 @@
     <t xml:space="preserve">1.45836782455444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45911967754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4531055688858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42829823493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41852557659149</t>
+    <t xml:space="preserve">1.45911955833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189891338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45310568809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42829835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41852581501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4207808971405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42604327201843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41702234745026</t>
+    <t xml:space="preserve">1.42078077793121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42604315280914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41702222824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.42529141902924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44408476352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716116905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219596385956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46663665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46588528156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144423007965</t>
+    <t xml:space="preserve">1.44408488273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716128826141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219608306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46663689613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144411087036</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843717575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850664615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347197055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167157173157</t>
+    <t xml:space="preserve">1.51850652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948560237885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167169094086</t>
   </si>
   <si>
     <t xml:space="preserve">1.49595439434052</t>
@@ -866,43 +866,43 @@
     <t xml:space="preserve">1.51249277591705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497543811798</t>
+    <t xml:space="preserve">1.50497531890869</t>
   </si>
   <si>
     <t xml:space="preserve">1.52151346206665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49369931221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49896144866943</t>
+    <t xml:space="preserve">1.49369943141937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49896132946014</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602398395538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.496706366539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5079824924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54857587814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039544582367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941637039185</t>
+    <t xml:space="preserve">1.49670648574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54857611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242342472076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941625118256</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203785419464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5290310382843</t>
+    <t xml:space="preserve">1.52903079986572</t>
   </si>
   <si>
     <t xml:space="preserve">1.51399624347687</t>
@@ -917,52 +917,52 @@
     <t xml:space="preserve">1.55609345436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126707077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67637133598328</t>
+    <t xml:space="preserve">1.63126730918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6763710975647</t>
   </si>
   <si>
     <t xml:space="preserve">1.65682601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69140589237213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644068717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7199718952179</t>
+    <t xml:space="preserve">1.69140565395355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644044876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997201442719</t>
   </si>
   <si>
     <t xml:space="preserve">1.65381908416748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67937791347504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735029220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66885387897491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035710811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186081409454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839907646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983283519745</t>
+    <t xml:space="preserve">1.67937803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6673504114151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67787492275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035722732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186057567596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6883989572525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6868953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983295440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.63878428936005</t>
@@ -977,61 +977,61 @@
     <t xml:space="preserve">1.80115926265717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81318700313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213857650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175312519073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430513858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8387463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657962799072</t>
+    <t xml:space="preserve">1.81318688392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213845729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430537700653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874642848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657950878143</t>
   </si>
   <si>
     <t xml:space="preserve">1.71245455741882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66133654117584</t>
+    <t xml:space="preserve">1.66133642196655</t>
   </si>
   <si>
     <t xml:space="preserve">1.76206910610199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77560019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83423590660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80567002296448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220804691315</t>
+    <t xml:space="preserve">1.77560043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83423578739166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566990375519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220792770386</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899258136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7410204410553</t>
+    <t xml:space="preserve">1.74102056026459</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598564624786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75154483318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297871112823</t>
+    <t xml:space="preserve">1.751544713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
     <t xml:space="preserve">1.70193016529083</t>
@@ -1040,55 +1040,55 @@
     <t xml:space="preserve">1.69441270828247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68388843536377</t>
+    <t xml:space="preserve">1.68388867378235</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434347629547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72448229789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71846866607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755858421326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500669002533</t>
+    <t xml:space="preserve">1.66434359550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72448205947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846830844879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755870342255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500657081604</t>
   </si>
   <si>
     <t xml:space="preserve">1.73951697349548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73650991916656</t>
+    <t xml:space="preserve">1.73651003837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395802497864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78161418437958</t>
+    <t xml:space="preserve">1.78161442279816</t>
   </si>
   <si>
     <t xml:space="preserve">1.75906193256378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81920123100281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8267183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416619777679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87933957576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685727119446</t>
+    <t xml:space="preserve">1.81920099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416643619537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87934005260468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88685739040375</t>
   </si>
   <si>
     <t xml:space="preserve">1.81168365478516</t>
@@ -1103,85 +1103,85 @@
     <t xml:space="preserve">1.78913164138794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8492705821991</t>
+    <t xml:space="preserve">1.85678803920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927046298981</t>
   </si>
   <si>
     <t xml:space="preserve">1.8870108127594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87933993339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468121528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399829387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797361373901</t>
+    <t xml:space="preserve">1.8793398141861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468157291412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486567735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179737329483</t>
   </si>
   <si>
     <t xml:space="preserve">1.81030285358429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90235221385956</t>
+    <t xml:space="preserve">1.90235233306885</t>
   </si>
   <si>
     <t xml:space="preserve">1.83331537246704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80263233184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660753250122</t>
+    <t xml:space="preserve">1.80263209342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660729408264</t>
   </si>
   <si>
     <t xml:space="preserve">1.70291209220886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76427817344666</t>
+    <t xml:space="preserve">1.76427805423737</t>
   </si>
   <si>
     <t xml:space="preserve">1.6798996925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69524121284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74893689155579</t>
+    <t xml:space="preserve">1.69524133205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222893238068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7489367723465</t>
   </si>
   <si>
     <t xml:space="preserve">1.65688741207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64154589176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58017945289612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455817222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620425224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250893115997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031969070435</t>
+    <t xml:space="preserve">1.64154613018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5801796913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620437145233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5149781703949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031957149506</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813045024872</t>
@@ -1190,19 +1190,19 @@
     <t xml:space="preserve">1.41525793075562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4114226102829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3730685710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35005629062653</t>
+    <t xml:space="preserve">1.41142272949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306880950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35005617141724</t>
   </si>
   <si>
     <t xml:space="preserve">1.38073933124542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39224576950073</t>
+    <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923325061798</t>
@@ -1217,46 +1217,46 @@
     <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3423855304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403172969818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28101944923401</t>
+    <t xml:space="preserve">1.34238564968109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28101921081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.26951313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25417160987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24650096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25800704956055</t>
+    <t xml:space="preserve">1.25417172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24650084972382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25800716876984</t>
   </si>
   <si>
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869020938873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019640922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252552986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937325000763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786716938019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087933063507</t>
+    <t xml:space="preserve">1.28869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019652843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252564907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937336921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3078670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087956905365</t>
   </si>
   <si>
     <t xml:space="preserve">1.33855020999908</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">1.31553792953491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39608097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
+    <t xml:space="preserve">1.39608108997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457477092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.40375185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36156237125397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539781093597</t>
+    <t xml:space="preserve">1.36156260967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539793014526</t>
   </si>
   <si>
     <t xml:space="preserve">1.43443500995636</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">1.37690412998199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38841021060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34622085094452</t>
+    <t xml:space="preserve">1.38841032981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34622097015381</t>
   </si>
   <si>
     <t xml:space="preserve">1.32704412937164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320880889893</t>
+    <t xml:space="preserve">1.27334868907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320857048035</t>
   </si>
   <si>
     <t xml:space="preserve">1.37706017494202</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">1.32916235923767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311138629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34512829780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508572101593</t>
+    <t xml:space="preserve">1.35311150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34512841701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508584022522</t>
   </si>
   <si>
     <t xml:space="preserve">1.39701759815216</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">1.40100908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40899193286896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41697490215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46886420249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4968044757843</t>
+    <t xml:space="preserve">1.40899205207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41697514057159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46886432170868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49680459499359</t>
   </si>
   <si>
     <t xml:space="preserve">1.50877892971039</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">1.51277041435242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49281322956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487271785736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50079596042633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44491529464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45289838314056</t>
+    <t xml:space="preserve">1.49281311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487295627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50079607963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44491541385651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45289814472198</t>
   </si>
   <si>
     <t xml:space="preserve">1.43693232536316</t>
@@ -1379,55 +1379,55 @@
     <t xml:space="preserve">1.40500044822693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39302599430084</t>
+    <t xml:space="preserve">1.39302623271942</t>
   </si>
   <si>
     <t xml:space="preserve">1.38504314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4289493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306869029999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907732486725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35710275173187</t>
+    <t xml:space="preserve">1.42894947528839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306892871857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35710287094116</t>
   </si>
   <si>
     <t xml:space="preserve">1.3491199016571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4848301410675</t>
+    <t xml:space="preserve">1.48483026027679</t>
   </si>
   <si>
     <t xml:space="preserve">1.47684729099274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46088135242462</t>
+    <t xml:space="preserve">1.46088123321533</t>
   </si>
   <si>
     <t xml:space="preserve">1.48882162570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52075338363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51676189899445</t>
+    <t xml:space="preserve">1.52075350284576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51676201820374</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659159183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56465983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54071068763733</t>
+    <t xml:space="preserve">1.59659147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56465971469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54071080684662</t>
   </si>
   <si>
     <t xml:space="preserve">1.53272783756256</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58860838413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55667686462402</t>
+    <t xml:space="preserve">1.58860862255096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55667674541473</t>
   </si>
   <si>
     <t xml:space="preserve">1.54869389533997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5367192029953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54470229148865</t>
+    <t xml:space="preserve">1.53671956062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54470217227936</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268537998199</t>
@@ -1457,25 +1457,25 @@
     <t xml:space="preserve">1.5247448682785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264256477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801183223724</t>
+    <t xml:space="preserve">1.57264268398285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801195144653</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397800922394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94784152507782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05960321426392</t>
+    <t xml:space="preserve">1.94784200191498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539860725403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05960297584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338157653809</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">2.20329618453979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926236152649</t>
+    <t xml:space="preserve">2.21926212310791</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">1.9877564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011437416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91590976715088</t>
+    <t xml:space="preserve">1.82011449337006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91591000556946</t>
   </si>
   <si>
     <t xml:space="preserve">1.86002922058105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63650631904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890689849854</t>
+    <t xml:space="preserve">1.63650619983673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890701770782</t>
   </si>
   <si>
     <t xml:space="preserve">1.59260010719299</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">1.72431886196136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62852323055267</t>
+    <t xml:space="preserve">1.62852334976196</t>
   </si>
   <si>
     <t xml:space="preserve">1.64448916912079</t>
@@ -1535,25 +1535,25 @@
     <t xml:space="preserve">1.68440389633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60457444190979</t>
+    <t xml:space="preserve">1.60457456111908</t>
   </si>
   <si>
     <t xml:space="preserve">1.66045522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65247213840485</t>
+    <t xml:space="preserve">1.65247225761414</t>
   </si>
   <si>
     <t xml:space="preserve">1.74826765060425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7163360118866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054038047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843807697296</t>
+    <t xml:space="preserve">1.71633589267731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054049968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843795776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.61255741119385</t>
@@ -1562,40 +1562,40 @@
     <t xml:space="preserve">1.69238698482513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75625061988831</t>
+    <t xml:space="preserve">1.7562507390976</t>
   </si>
   <si>
     <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792691707611</t>
+    <t xml:space="preserve">1.9079270362854</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582461357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92389249801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757211208344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9145622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679543018341</t>
+    <t xml:space="preserve">1.92389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757199287415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456258296967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630996227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8567955493927</t>
   </si>
   <si>
     <t xml:space="preserve">1.84029054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81553339958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79077613353729</t>
+    <t xml:space="preserve">1.81553328037262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.790776014328</t>
   </si>
   <si>
     <t xml:space="preserve">1.75776648521423</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">1.79902851581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7742714881897</t>
+    <t xml:space="preserve">1.77427136898041</t>
   </si>
   <si>
     <t xml:space="preserve">1.76601886749268</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">1.78252375125885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73300898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7495139837265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69999933242798</t>
+    <t xml:space="preserve">1.73300909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74951386451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69999945163727</t>
   </si>
   <si>
     <t xml:space="preserve">1.6834944486618</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825159549713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174695014954</t>
+    <t xml:space="preserve">1.65873742103577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174706935883</t>
   </si>
   <si>
     <t xml:space="preserve">1.72475671768188</t>
@@ -1652,37 +1652,37 @@
     <t xml:space="preserve">1.65048480033875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63397991657257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
+    <t xml:space="preserve">1.63398003578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572777271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.62985384464264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60922288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805746078491</t>
+    <t xml:space="preserve">1.60922276973724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805734157562</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582437515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04660129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96407723426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93931972980499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155293464661</t>
+    <t xml:space="preserve">2.04660153388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9640771150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931949138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330007553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155281543732</t>
   </si>
   <si>
     <t xml:space="preserve">1.88980507850647</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">1.92281484603882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93106698989868</t>
+    <t xml:space="preserve">1.93106710910797</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359152793884</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">1.97232949733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98058187961578</t>
+    <t xml:space="preserve">1.98058199882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.06310606002808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19514465332031</t>
+    <t xml:space="preserve">2.19514489173889</t>
   </si>
   <si>
     <t xml:space="preserve">2.17864060401917</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563035964966</t>
+    <t xml:space="preserve">2.16213488578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563012123108</t>
   </si>
   <si>
     <t xml:space="preserve">2.19566059112549</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18715023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310883522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906766891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08502650260925</t>
+    <t xml:space="preserve">2.18715000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906790733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08502674102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.09353685379028</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396487236023</t>
+    <t xml:space="preserve">2.03396463394165</t>
   </si>
   <si>
     <t xml:space="preserve">2.0254545211792</t>
@@ -1763,16 +1763,16 @@
     <t xml:space="preserve">2.05098509788513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91482043266296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184089660645</t>
+    <t xml:space="preserve">1.91482031345367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184065818787</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290264606476</t>
+    <t xml:space="preserve">1.98290252685547</t>
   </si>
   <si>
     <t xml:space="preserve">1.97439253330231</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949544906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992346763611</t>
+    <t xml:space="preserve">2.05949592590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992334842682</t>
   </si>
   <si>
     <t xml:space="preserve">1.9914128780365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00843381881714</t>
+    <t xml:space="preserve">2.00843358039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.01694393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10204720497131</t>
+    <t xml:space="preserve">2.10204696655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
@@ -1808,28 +1808,28 @@
     <t xml:space="preserve">2.14459872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16161918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13608860969543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96588206291199</t>
+    <t xml:space="preserve">2.16161894798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13608837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.94035112857819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89779961109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226867675781</t>
+    <t xml:space="preserve">1.8977997303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722687959671</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94886147975922</t>
+    <t xml:space="preserve">1.94886159896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.07243394851685</t>
@@ -67361,7 +67361,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.3940856481</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>2177</v>
@@ -67382,6 +67382,32 @@
         <v>727</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.5134143519</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>525</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1254426240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552562236786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831951141357</t>
+    <t xml:space="preserve">1.12615478038788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12544250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831963062286</t>
   </si>
   <si>
     <t xml:space="preserve">1.09623801708221</t>
@@ -65,52 +65,52 @@
     <t xml:space="preserve">1.10407328605652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09053957462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412873744965</t>
+    <t xml:space="preserve">1.0905396938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412897586823</t>
   </si>
   <si>
     <t xml:space="preserve">1.00007688999176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943804800510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925996780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666112422943</t>
+    <t xml:space="preserve">0.943804621696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925997078418732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993665933609009</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925359249115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004922389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859652996063</t>
+    <t xml:space="preserve">1.01004910469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0185968875885</t>
   </si>
   <si>
     <t xml:space="preserve">1.05492424964905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0321307182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711676597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02572000026703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495203495026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02643215656281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0207337141037</t>
+    <t xml:space="preserve">1.03213047981262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711664676666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02571976184845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495215415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02643203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073359489441</t>
   </si>
   <si>
     <t xml:space="preserve">0.947366297245026</t>
@@ -122,49 +122,49 @@
     <t xml:space="preserve">0.916024744510651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530849456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98583060503006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612284183502</t>
+    <t xml:space="preserve">0.922435522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530968666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970159888267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612343788147</t>
   </si>
   <si>
     <t xml:space="preserve">0.962324559688568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00435054302216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997939765453339</t>
+    <t xml:space="preserve">1.00435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997939884662628</t>
   </si>
   <si>
     <t xml:space="preserve">0.989392340183258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991529107093811</t>
+    <t xml:space="preserve">0.991529166698456</t>
   </si>
   <si>
     <t xml:space="preserve">0.979419946670532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99081689119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967610359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717209815979</t>
+    <t xml:space="preserve">0.9908167719841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967789173126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227489948273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717221736908</t>
   </si>
   <si>
     <t xml:space="preserve">1.01503527164459</t>
@@ -173,34 +173,34 @@
     <t xml:space="preserve">1.00078916549683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02215838432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577533245087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648748874664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076138019562</t>
+    <t xml:space="preserve">1.02215826511383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577521324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648725032806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076149940491</t>
   </si>
   <si>
     <t xml:space="preserve">1.00221383571625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984406113624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00791215896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03284299373627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01930892467499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996598720551</t>
+    <t xml:space="preserve">0.984405934810638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00791203975677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0328426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01930904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996610641479</t>
   </si>
   <si>
     <t xml:space="preserve">1.09979963302612</t>
@@ -209,61 +209,61 @@
     <t xml:space="preserve">1.10051202774048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.084841132164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982729911804</t>
+    <t xml:space="preserve">1.08484125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
   </si>
   <si>
     <t xml:space="preserve">1.1817147731781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16818082332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185334205627</t>
+    <t xml:space="preserve">1.1681809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185322284698</t>
   </si>
   <si>
     <t xml:space="preserve">1.13968873023987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15393471717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11689496040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09766268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16105794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15963327884674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683950901031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612711429596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12900412082672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467489719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316722869873</t>
+    <t xml:space="preserve">1.15393495559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11689484119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09766256809235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16105771064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15963315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14752388000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612723350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12900424003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316687107086</t>
   </si>
   <si>
     <t xml:space="preserve">1.17031788825989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18100237846375</t>
+    <t xml:space="preserve">1.18100249767303</t>
   </si>
   <si>
     <t xml:space="preserve">1.19738554954529</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">1.21091938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163153648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20593297481537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302842140198</t>
+    <t xml:space="preserve">1.21163165569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20593309402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302830219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089159488678</t>
@@ -287,43 +287,43 @@
     <t xml:space="preserve">1.19596076011658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23548448085785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22670149803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937337398529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790972232819</t>
+    <t xml:space="preserve">1.23548436164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22670161724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18790984153748</t>
   </si>
   <si>
     <t xml:space="preserve">1.16302418708801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16595208644867</t>
+    <t xml:space="preserve">1.16595196723938</t>
   </si>
   <si>
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375625133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570509433746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911758899689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424132347107</t>
+    <t xml:space="preserve">1.16375637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570497512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911782741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424120426178</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11837708950043</t>
+    <t xml:space="preserve">1.11837685108185</t>
   </si>
   <si>
     <t xml:space="preserve">1.10154271125793</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">1.10520243644714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0993469953537</t>
+    <t xml:space="preserve">1.09934711456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12935590744019</t>
+    <t xml:space="preserve">1.1293557882309</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203669548035</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">1.12716007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07226610183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860625743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13081967830658</t>
+    <t xml:space="preserve">1.07226598262787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860649585724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13081991672516</t>
   </si>
   <si>
     <t xml:space="preserve">1.12423241138458</t>
@@ -362,61 +362,61 @@
     <t xml:space="preserve">1.15716886520386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18717753887177</t>
+    <t xml:space="preserve">1.18717777729034</t>
   </si>
   <si>
     <t xml:space="preserve">1.18205428123474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20767140388489</t>
+    <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
     <t xml:space="preserve">1.17839455604553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20401203632355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18351829051971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20474362373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1747350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571376800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546677589417</t>
+    <t xml:space="preserve">1.20401191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18351805210114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2047438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17473518848419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546701431274</t>
   </si>
   <si>
     <t xml:space="preserve">1.19303297996521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20035243034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888830184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21425879001617</t>
+    <t xml:space="preserve">1.20035231113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888854026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499085426331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693957805634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21425890922546</t>
   </si>
   <si>
     <t xml:space="preserve">1.22230982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962927818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23328876495361</t>
+    <t xml:space="preserve">1.22962915897369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23328852653503</t>
   </si>
   <si>
     <t xml:space="preserve">1.22450578212738</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">1.25524652004242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28232753276825</t>
+    <t xml:space="preserve">1.28232765197754</t>
   </si>
   <si>
     <t xml:space="preserve">1.31745994091034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30208969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184246063232</t>
+    <t xml:space="preserve">1.30208957195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550218582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2918426990509</t>
   </si>
   <si>
     <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24426770210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25890612602234</t>
+    <t xml:space="preserve">1.24426782131195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25890624523163</t>
   </si>
   <si>
     <t xml:space="preserve">1.27354454994202</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">1.26256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915299892426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694849014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109316825867</t>
+    <t xml:space="preserve">1.26915287971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694837093353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109328746796</t>
   </si>
   <si>
     <t xml:space="preserve">1.26402962207794</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">1.24719536304474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22304201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21938228607178</t>
+    <t xml:space="preserve">1.2230418920517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21938216686249</t>
   </si>
   <si>
     <t xml:space="preserve">1.19962048530579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19669282436371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376516342163</t>
+    <t xml:space="preserve">1.19669270515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376492500305</t>
   </si>
   <si>
     <t xml:space="preserve">1.17766273021698</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">1.19742465019226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20620787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230103492737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522014141083</t>
+    <t xml:space="preserve">1.20620763301849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230091571808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059051036835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522002220154</t>
   </si>
   <si>
     <t xml:space="preserve">1.15643692016602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16887950897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693102359772</t>
+    <t xml:space="preserve">1.16887962818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693090438843</t>
   </si>
   <si>
     <t xml:space="preserve">1.19522881507874</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">1.17985844612122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18498206138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17400300502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107558250427</t>
+    <t xml:space="preserve">1.18498194217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107546329498</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814768314362</t>
@@ -539,22 +539,22 @@
     <t xml:space="preserve">1.1461900472641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14326238632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11252176761627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1344792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
+    <t xml:space="preserve">1.14326250553131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11252164840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13447916507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984074115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.11325371265411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10593450069427</t>
+    <t xml:space="preserve">1.10593438148499</t>
   </si>
   <si>
     <t xml:space="preserve">1.10007905960083</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">1.12276864051819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11032569408417</t>
+    <t xml:space="preserve">1.11032605171204</t>
   </si>
   <si>
     <t xml:space="preserve">1.1161812543869</t>
@@ -572,34 +572,34 @@
     <t xml:space="preserve">1.13960266113281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1278920173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14399433135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14179849624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13521122932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.138139128685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14253056049347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19449687004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18132221698761</t>
+    <t xml:space="preserve">1.12789189815521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14399445056915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14179861545563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13521111011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14253044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19449698925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18132245540619</t>
   </si>
   <si>
     <t xml:space="preserve">1.17253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17912662029266</t>
+    <t xml:space="preserve">1.17912638187408</t>
   </si>
   <si>
     <t xml:space="preserve">1.13887083530426</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12350034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11910915374756</t>
+    <t xml:space="preserve">1.12350058555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569630146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496435642242</t>
@@ -623,19 +623,19 @@
     <t xml:space="preserve">1.12642812728882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15936470031738</t>
+    <t xml:space="preserve">1.15936481952667</t>
   </si>
   <si>
     <t xml:space="preserve">1.15277755260468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16741597652435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22377383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596955299377</t>
+    <t xml:space="preserve">1.16741585731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22377371788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596967220306</t>
   </si>
   <si>
     <t xml:space="preserve">1.25671017169952</t>
@@ -650,70 +650,70 @@
     <t xml:space="preserve">1.26622521877289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26842093467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29769790172577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867683887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477915287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404720783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31014049053192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32843863964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037892818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135750770569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30282127857208</t>
+    <t xml:space="preserve">1.2684211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29769802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867695808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403841495514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3101407289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3284387588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037868976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135762691498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30282139778137</t>
   </si>
   <si>
     <t xml:space="preserve">1.3152642250061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32624292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137521266937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941733837128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34673678874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38699233531952</t>
+    <t xml:space="preserve">1.32624304294586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137533187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34673690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.36869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38772428035736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35991132259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37454986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40529036521912</t>
+    <t xml:space="preserve">1.38772451877594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35991144180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37454998493195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4052906036377</t>
   </si>
   <si>
     <t xml:space="preserve">1.39065206050873</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114580631256</t>
+    <t xml:space="preserve">1.41114592552185</t>
   </si>
   <si>
     <t xml:space="preserve">1.38186895847321</t>
@@ -731,43 +731,43 @@
     <t xml:space="preserve">1.37162208557129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38845658302307</t>
+    <t xml:space="preserve">1.38845634460449</t>
   </si>
   <si>
     <t xml:space="preserve">1.41927742958069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45009863376617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046515464783</t>
+    <t xml:space="preserve">1.45009875297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046491622925</t>
   </si>
   <si>
     <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56361079216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58616268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60570800304413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51700294017792</t>
+    <t xml:space="preserve">1.56361067295074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58616292476654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60570812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.51098918914795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48693382740021</t>
+    <t xml:space="preserve">1.4869339466095</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49069249629974</t>
+    <t xml:space="preserve">1.49069237709045</t>
   </si>
   <si>
     <t xml:space="preserve">1.46814036369324</t>
@@ -779,22 +779,22 @@
     <t xml:space="preserve">1.44333302974701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882262706757</t>
+    <t xml:space="preserve">1.44483649730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882274627686</t>
   </si>
   <si>
     <t xml:space="preserve">1.4320570230484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43581557273865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40574622154236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836758613586</t>
+    <t xml:space="preserve">1.43581569194794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40574610233307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836782455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.45911955833435</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">1.47189891338348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45310568809509</t>
+    <t xml:space="preserve">1.4531055688858</t>
   </si>
   <si>
     <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41852581501007</t>
+    <t xml:space="preserve">1.41852557659149</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980170249939</t>
@@ -818,25 +818,25 @@
     <t xml:space="preserve">1.4207808971405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42604339122772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41702234745026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42529129981995</t>
+    <t xml:space="preserve">1.42604315280914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41702222824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42529153823853</t>
   </si>
   <si>
     <t xml:space="preserve">1.44408476352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47716128826141</t>
+    <t xml:space="preserve">1.47716116905212</t>
   </si>
   <si>
     <t xml:space="preserve">1.49219584465027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46663689613342</t>
+    <t xml:space="preserve">1.46663677692413</t>
   </si>
   <si>
     <t xml:space="preserve">1.46588516235352</t>
@@ -848,25 +848,25 @@
     <t xml:space="preserve">1.48843717575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5185067653656</t>
+    <t xml:space="preserve">1.51850664615631</t>
   </si>
   <si>
     <t xml:space="preserve">1.50948584079742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50347197055817</t>
+    <t xml:space="preserve">1.50347185134888</t>
   </si>
   <si>
     <t xml:space="preserve">1.48167145252228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4959545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51249289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497531890869</t>
+    <t xml:space="preserve">1.49595463275909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51249277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497555732727</t>
   </si>
   <si>
     <t xml:space="preserve">1.52151346206665</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">1.49369931221008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49896144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602386474609</t>
+    <t xml:space="preserve">1.49896156787872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602398395538</t>
   </si>
   <si>
     <t xml:space="preserve">1.496706366539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50798237323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5485759973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242342472076</t>
+    <t xml:space="preserve">1.5079824924469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54857587814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242330551147</t>
   </si>
   <si>
     <t xml:space="preserve">1.47039544582367</t>
@@ -902,43 +902,43 @@
     <t xml:space="preserve">1.53203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51399624347687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158293247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511414051056</t>
+    <t xml:space="preserve">1.52903091907501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51399612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158305168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511437892914</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609333515167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126695156097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682578086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69140577316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644080638885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7199718952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381932258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937803268433</t>
+    <t xml:space="preserve">1.63126718997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637133598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65682590007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69140589237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644068717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997201442719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937827110291</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735029220581</t>
@@ -947,85 +947,85 @@
     <t xml:space="preserve">1.66885375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778746843338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035734653473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186081409454</t>
+    <t xml:space="preserve">1.67787480354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035722732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186069488525</t>
   </si>
   <si>
     <t xml:space="preserve">1.6883989572525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6868953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6463018655777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74402749538422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115950107574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318724155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213869571686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175300598145</t>
+    <t xml:space="preserve">1.68689548969269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983307361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878452777863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64630162715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402737617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115902423859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213857650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965579509735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175312519073</t>
   </si>
   <si>
     <t xml:space="preserve">1.86430525779724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8387463092804</t>
+    <t xml:space="preserve">1.83874619007111</t>
   </si>
   <si>
     <t xml:space="preserve">1.76657938957214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206910610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77560007572174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83423578739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80566942691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220804691315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72899281978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74102067947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598600387573</t>
+    <t xml:space="preserve">1.71245455741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133654117584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206922531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77560031414032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83423590660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566990375519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220780849457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72899258136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74102056026459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598564624786</t>
   </si>
   <si>
     <t xml:space="preserve">1.751544713974</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">1.72297894954681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70193016529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388843536377</t>
+    <t xml:space="preserve">1.70193028450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441282749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388867378235</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">1.66434347629547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72448229789734</t>
+    <t xml:space="preserve">1.72448241710663</t>
   </si>
   <si>
     <t xml:space="preserve">1.71846854686737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75755882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500669002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951685428619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73651003837585</t>
+    <t xml:space="preserve">1.75755870342255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951709270477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73650991916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395802497864</t>
@@ -1073,22 +1073,22 @@
     <t xml:space="preserve">1.78161418437958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75906229019165</t>
+    <t xml:space="preserve">1.75906217098236</t>
   </si>
   <si>
     <t xml:space="preserve">1.81920099258423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82671844959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416643619537</t>
+    <t xml:space="preserve">1.82671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416619777679</t>
   </si>
   <si>
     <t xml:space="preserve">1.87934005260468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685715198517</t>
+    <t xml:space="preserve">1.88685691356659</t>
   </si>
   <si>
     <t xml:space="preserve">1.81168377399445</t>
@@ -1097,40 +1097,43 @@
     <t xml:space="preserve">1.7966490983963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77409672737122</t>
+    <t xml:space="preserve">1.77409684658051</t>
   </si>
   <si>
     <t xml:space="preserve">1.78913187980652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85678780078888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8492705821991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701069355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486567735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399829387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179737329483</t>
+    <t xml:space="preserve">1.8567875623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927070140839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88701093196869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87933993339539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468109607697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865689277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797361373901</t>
   </si>
   <si>
     <t xml:space="preserve">1.810302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90235233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331525325775</t>
+    <t xml:space="preserve">1.90235221385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331537246704</t>
   </si>
   <si>
     <t xml:space="preserve">1.80263197422028</t>
@@ -1139,37 +1142,37 @@
     <t xml:space="preserve">1.75660765171051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427805423737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67989981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524121284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222893238068</t>
+    <t xml:space="preserve">1.70291197299957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427817344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6798996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524133205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222905158997</t>
   </si>
   <si>
     <t xml:space="preserve">1.74893665313721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65688753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154601097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5801796913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455805301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620413303375</t>
+    <t xml:space="preserve">1.65688741207123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58017945289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455817222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620425224304</t>
   </si>
   <si>
     <t xml:space="preserve">1.57250893115997</t>
@@ -1184,37 +1187,37 @@
     <t xml:space="preserve">1.48813045024872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41525816917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41142249107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306869029999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35005640983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38073933124542</t>
+    <t xml:space="preserve">1.41525781154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41142272949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306880950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35005629062653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.380739569664</t>
   </si>
   <si>
     <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36923336982727</t>
+    <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
     <t xml:space="preserve">1.39991641044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35772716999054</t>
+    <t xml:space="preserve">1.35772705078125</t>
   </si>
   <si>
     <t xml:space="preserve">1.35389184951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34238564968109</t>
+    <t xml:space="preserve">1.34238576889038</t>
   </si>
   <si>
     <t xml:space="preserve">1.30403184890747</t>
@@ -1223,40 +1226,40 @@
     <t xml:space="preserve">1.28101933002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26951313018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25417160987854</t>
+    <t xml:space="preserve">1.26951324939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25417172908783</t>
   </si>
   <si>
     <t xml:space="preserve">1.24650096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25800716876984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29636108875275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869009017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019629001617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252552986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937336921692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786728858948</t>
+    <t xml:space="preserve">1.25800704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29636096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28869020938873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019652843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252541065216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937348842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786716938019</t>
   </si>
   <si>
     <t xml:space="preserve">1.33087944984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33855032920837</t>
+    <t xml:space="preserve">1.33855009078979</t>
   </si>
   <si>
     <t xml:space="preserve">1.33471488952637</t>
@@ -1268,22 +1271,22 @@
     <t xml:space="preserve">1.39608108997345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38457489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40375185012817</t>
+    <t xml:space="preserve">1.38457477092743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40375173091888</t>
   </si>
   <si>
     <t xml:space="preserve">1.36156249046326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36539804935455</t>
+    <t xml:space="preserve">1.36539793014526</t>
   </si>
   <si>
     <t xml:space="preserve">1.43443489074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37690412998199</t>
+    <t xml:space="preserve">1.37690401077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.38841021060944</t>
@@ -1292,10 +1295,10 @@
     <t xml:space="preserve">1.34622097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32704412937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334868907928</t>
+    <t xml:space="preserve">1.32704401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334880828857</t>
   </si>
   <si>
     <t xml:space="preserve">1.32320868968964</t>
@@ -1307,25 +1310,25 @@
     <t xml:space="preserve">1.3890346288681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36109447479248</t>
+    <t xml:space="preserve">1.3610942363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916235923767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311126708984</t>
+    <t xml:space="preserve">1.35311138629913</t>
   </si>
   <si>
     <t xml:space="preserve">1.34512829780579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36508572101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39701759815216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41298353672028</t>
+    <t xml:space="preserve">1.36508584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39701771736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41298341751099</t>
   </si>
   <si>
     <t xml:space="preserve">1.4010089635849</t>
@@ -1334,25 +1337,25 @@
     <t xml:space="preserve">1.40899205207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41697490215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4688640832901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49680459499359</t>
+    <t xml:space="preserve">1.4169750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46886420249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4968044757843</t>
   </si>
   <si>
     <t xml:space="preserve">1.50877904891968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51277053356171</t>
+    <t xml:space="preserve">1.51277041435242</t>
   </si>
   <si>
     <t xml:space="preserve">1.49281299114227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46487271785736</t>
+    <t xml:space="preserve">1.46487283706665</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079596042633</t>
@@ -1364,10 +1367,10 @@
     <t xml:space="preserve">1.45289826393127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43693220615387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495799064636</t>
+    <t xml:space="preserve">1.43693232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495787143707</t>
   </si>
   <si>
     <t xml:space="preserve">1.42096650600433</t>
@@ -1376,7 +1379,7 @@
     <t xml:space="preserve">1.40500056743622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39302623271942</t>
+    <t xml:space="preserve">1.39302611351013</t>
   </si>
   <si>
     <t xml:space="preserve">1.38504314422607</t>
@@ -1385,22 +1388,19 @@
     <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37306880950928</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
     <t xml:space="preserve">1.35710287094116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3491199016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48483002185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47684729099274</t>
+    <t xml:space="preserve">1.34911978244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4848301410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47684717178345</t>
   </si>
   <si>
     <t xml:space="preserve">1.46088123321533</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">1.52075338363647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51676177978516</t>
+    <t xml:space="preserve">1.51676189899445</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066834926605</t>
@@ -1424,28 +1424,28 @@
     <t xml:space="preserve">1.56465971469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54071080684662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53272771835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52873635292053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58860850334167</t>
+    <t xml:space="preserve">1.54071068763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53272783756256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52873623371124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58860862255096</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54869389533997</t>
+    <t xml:space="preserve">1.54869401454926</t>
   </si>
   <si>
     <t xml:space="preserve">1.53671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470217227936</t>
+    <t xml:space="preserve">1.54470229148865</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268526077271</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">1.52474498748779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264280319214</t>
+    <t xml:space="preserve">1.57264268398285</t>
   </si>
   <si>
     <t xml:space="preserve">1.67642104625702</t>
@@ -1463,28 +1463,28 @@
     <t xml:space="preserve">1.86801207065582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88397777080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784140586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05960321426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16338181495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20329642295837</t>
+    <t xml:space="preserve">1.88397789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784164428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539860725403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05960273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16338157653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20329666137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.21926212310791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22724533081055</t>
+    <t xml:space="preserve">2.22724509239197</t>
   </si>
   <si>
     <t xml:space="preserve">2.1793475151062</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">2.11548376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98775625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82011425495148</t>
+    <t xml:space="preserve">1.98775672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82011437416077</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809746265411</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">1.91590988636017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86002898216248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650631904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890677928925</t>
+    <t xml:space="preserve">1.86002910137177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650619983673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890689849854</t>
   </si>
   <si>
     <t xml:space="preserve">1.59260010719299</t>
@@ -1523,37 +1523,37 @@
     <t xml:space="preserve">1.72431898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62852323055267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68440401554108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457468032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66045498847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65247225761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826776981354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7163360118866</t>
+    <t xml:space="preserve">1.62852346897125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64448916912079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68440413475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457444190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604551076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65247213840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633589267731</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054026126862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843819618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61255741119385</t>
+    <t xml:space="preserve">1.66843795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61255729198456</t>
   </si>
   <si>
     <t xml:space="preserve">1.69238686561584</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792691707611</t>
+    <t xml:space="preserve">1.90792715549469</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582473278046</t>
@@ -1583,34 +1583,34 @@
     <t xml:space="preserve">1.90630984306335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8567955493927</t>
+    <t xml:space="preserve">1.85679543018341</t>
   </si>
   <si>
     <t xml:space="preserve">1.84029066562653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81553339958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.790776014328</t>
+    <t xml:space="preserve">1.81553328037262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077613353729</t>
   </si>
   <si>
     <t xml:space="preserve">1.75776648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79902851581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427136898041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76601886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126136302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252375125885</t>
+    <t xml:space="preserve">1.79902863502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427124977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76601874828339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252387046814</t>
   </si>
   <si>
     <t xml:space="preserve">1.73300909996033</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">1.74951386451721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71650409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69999945163727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68349432945251</t>
+    <t xml:space="preserve">1.71650421619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69999921321869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6834944486618</t>
   </si>
   <si>
     <t xml:space="preserve">1.67524218559265</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873730182648</t>
+    <t xml:space="preserve">1.65873718261719</t>
   </si>
   <si>
     <t xml:space="preserve">1.70825171470642</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">1.69174695014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72475671768188</t>
+    <t xml:space="preserve">1.7247565984726</t>
   </si>
   <si>
     <t xml:space="preserve">1.65048491954803</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">1.63398003578186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62572765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985372543335</t>
+    <t xml:space="preserve">1.62572753429413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985384464264</t>
   </si>
   <si>
     <t xml:space="preserve">1.60922265052795</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">1.9640771150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9393196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330007553101</t>
+    <t xml:space="preserve">1.93931949138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330031394958</t>
   </si>
   <si>
     <t xml:space="preserve">1.88155269622803</t>
@@ -1688,16 +1688,16 @@
     <t xml:space="preserve">1.86504781246185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92281460762024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106710910797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883414268494</t>
+    <t xml:space="preserve">1.92281484603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106734752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.97232937812805</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">2.17864036560059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17038774490356</t>
+    <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.16213512420654</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">2.14563012123108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19566059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864012718201</t>
+    <t xml:space="preserve">2.19566035270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
     <t xml:space="preserve">2.18715000152588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15310907363892</t>
+    <t xml:space="preserve">2.15310883522034</t>
   </si>
   <si>
     <t xml:space="preserve">2.11906790733337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08502674102783</t>
+    <t xml:space="preserve">2.08502650260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.09353685379028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800580024719</t>
+    <t xml:space="preserve">2.06800603866577</t>
   </si>
   <si>
     <t xml:space="preserve">2.03396463394165</t>
@@ -1757,37 +1757,37 @@
     <t xml:space="preserve">2.04247498512268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05098509788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482031345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184065818787</t>
+    <t xml:space="preserve">2.05098533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184089660645</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290252685547</t>
+    <t xml:space="preserve">1.98290276527405</t>
   </si>
   <si>
     <t xml:space="preserve">1.97439253330231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07651615142822</t>
+    <t xml:space="preserve">2.0765163898468</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992334842682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9914128780365</t>
+    <t xml:space="preserve">2.05949544906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992311000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99141311645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.00843358039856</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14459872245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16161894798279</t>
+    <t xml:space="preserve">2.14459848403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16161942481995</t>
   </si>
   <si>
     <t xml:space="preserve">2.13608837127686</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">1.8977997303009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90630996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722687959671</t>
+    <t xml:space="preserve">1.90631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87226867675781</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">1.94886159896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07243394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08129072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05472111701965</t>
+    <t xml:space="preserve">2.07243418693542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08129048347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05472087860107</t>
   </si>
   <si>
     <t xml:space="preserve">2.04586434364319</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958580493927</t>
+    <t xml:space="preserve">1.93958556652069</t>
   </si>
   <si>
     <t xml:space="preserve">1.97501194477081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99272525310516</t>
+    <t xml:space="preserve">1.99272501468658</t>
   </si>
   <si>
     <t xml:space="preserve">1.95729887485504</t>
@@ -1868,19 +1868,19 @@
     <t xml:space="preserve">1.94844233989716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86873304843903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92187285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91301620006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87758982181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072915077209</t>
+    <t xml:space="preserve">1.8687332868576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92187261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9130163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775897026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072926998138</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">1.96615540981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90415978431702</t>
+    <t xml:space="preserve">1.90415966510773</t>
   </si>
   <si>
     <t xml:space="preserve">1.89530301094055</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673730373383</t>
+    <t xml:space="preserve">1.80673742294312</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">1.74474155902863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85102021694183</t>
+    <t xml:space="preserve">1.85102009773254</t>
   </si>
   <si>
     <t xml:space="preserve">1.84216368198395</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">1.75802636146545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7624546289444</t>
+    <t xml:space="preserve">1.76245474815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">1.7535982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71817183494568</t>
+    <t xml:space="preserve">1.71817195415497</t>
   </si>
   <si>
     <t xml:space="preserve">1.70931529998779</t>
@@ -19025,7 +19025,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G634" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19051,7 +19051,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G635" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19077,7 +19077,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G636" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19103,7 +19103,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19129,7 +19129,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19233,7 +19233,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G642" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19259,7 +19259,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19311,7 +19311,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G645" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19337,7 +19337,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G646" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19363,7 +19363,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G647" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19389,7 +19389,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G648" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19415,7 +19415,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G649" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19441,7 +19441,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G650" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19467,7 +19467,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G651" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19519,7 +19519,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G653" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19545,7 +19545,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G654" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19701,7 +19701,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G660" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19727,7 +19727,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G661" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19753,7 +19753,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G662" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19805,7 +19805,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G664" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19831,7 +19831,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G665" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -19935,7 +19935,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G669" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -19987,7 +19987,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20169,7 +20169,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G678" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20299,7 +20299,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20325,7 +20325,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G684" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20351,7 +20351,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G685" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20377,7 +20377,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G686" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20403,7 +20403,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G687" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20611,7 +20611,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G695" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20637,7 +20637,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G696" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20845,7 +20845,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G708" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -20975,7 +20975,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21131,7 +21131,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G715" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21157,7 +21157,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G716" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21183,7 +21183,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21209,7 +21209,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G718" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21235,7 +21235,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G719" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21261,7 +21261,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G720" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21287,7 +21287,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G721" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21313,7 +21313,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G722" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21339,7 +21339,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G723" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21365,7 +21365,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21391,7 +21391,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G725" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21417,7 +21417,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21443,7 +21443,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G727" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21469,7 +21469,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G728" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21495,7 +21495,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G729" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21521,7 +21521,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G730" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21547,7 +21547,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21573,7 +21573,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G732" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21599,7 +21599,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21625,7 +21625,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21651,7 +21651,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G735" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21677,7 +21677,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G736" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21703,7 +21703,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G737" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21729,7 +21729,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G738" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21755,7 +21755,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G739" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21781,7 +21781,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G740" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21807,7 +21807,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G741" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21833,7 +21833,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G742" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -21859,7 +21859,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G743" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21885,7 +21885,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G744" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21911,7 +21911,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21937,7 +21937,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G746" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21963,7 +21963,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G747" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21989,7 +21989,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G748" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22015,7 +22015,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G749" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22041,7 +22041,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22067,7 +22067,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G751" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22093,7 +22093,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G752" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22119,7 +22119,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G753" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22145,7 +22145,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G754" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22171,7 +22171,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G755" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22197,7 +22197,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G756" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22223,7 +22223,7 @@
         <v>1.75</v>
       </c>
       <c r="G757" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22249,7 +22249,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G758" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22275,7 +22275,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G759" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22301,7 +22301,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G760" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22327,7 +22327,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G761" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22353,7 +22353,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G762" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22379,7 +22379,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22405,7 +22405,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G764" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22431,7 +22431,7 @@
         <v>1.625</v>
       </c>
       <c r="G765" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22457,7 +22457,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G766" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22483,7 +22483,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G767" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22509,7 +22509,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G768" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22535,7 +22535,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G769" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22561,7 +22561,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G770" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22587,7 +22587,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G771" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22613,7 +22613,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G772" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22639,7 +22639,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G773" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22665,7 +22665,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G774" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22691,7 +22691,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G775" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22717,7 +22717,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22743,7 +22743,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G777" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22769,7 +22769,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G778" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22795,7 +22795,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G779" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22821,7 +22821,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G780" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22847,7 +22847,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G781" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22873,7 +22873,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G782" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22899,7 +22899,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G783" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22925,7 +22925,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G784" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22951,7 +22951,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G785" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22977,7 +22977,7 @@
         <v>1.75</v>
       </c>
       <c r="G786" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23003,7 +23003,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G787" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23029,7 +23029,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G788" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23055,7 +23055,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G789" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23081,7 +23081,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G790" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23107,7 +23107,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G791" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23133,7 +23133,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G792" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23159,7 +23159,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G793" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23185,7 +23185,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G794" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G795" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23237,7 +23237,7 @@
         <v>1.75</v>
       </c>
       <c r="G796" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23263,7 +23263,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G797" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23289,7 +23289,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G798" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23315,7 +23315,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G799" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23341,7 +23341,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G800" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23367,7 +23367,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G801" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23393,7 +23393,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G802" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23419,7 +23419,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G803" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23445,7 +23445,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G804" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23471,7 +23471,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G805" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23497,7 +23497,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G806" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23523,7 +23523,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G807" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23549,7 +23549,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G808" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23575,7 +23575,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G809" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23601,7 +23601,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G810" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23627,7 +23627,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G811" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23653,7 +23653,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23679,7 +23679,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G813" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23705,7 +23705,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23731,7 +23731,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G815" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23757,7 +23757,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G816" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G817" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23809,7 +23809,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G818" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23835,7 +23835,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G819" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23861,7 +23861,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G820" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23887,7 +23887,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23939,7 +23939,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G823" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23965,7 +23965,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G824" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23991,7 +23991,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G825" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24017,7 +24017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24043,7 +24043,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24069,7 +24069,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G828" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24095,7 +24095,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24121,7 +24121,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G830" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24147,7 +24147,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G831" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24173,7 +24173,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G832" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24199,7 +24199,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G833" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24225,7 +24225,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G834" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24251,7 +24251,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G835" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24277,7 +24277,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G836" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24303,7 +24303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G837" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24329,7 +24329,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G838" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24355,7 +24355,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G839" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24381,7 +24381,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G840" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24407,7 +24407,7 @@
         <v>1.75</v>
       </c>
       <c r="G841" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24433,7 +24433,7 @@
         <v>1.75</v>
       </c>
       <c r="G842" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24459,7 +24459,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G843" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24485,7 +24485,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24511,7 +24511,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24537,7 +24537,7 @@
         <v>1.75</v>
       </c>
       <c r="G846" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24563,7 +24563,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G847" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24589,7 +24589,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G848" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24615,7 +24615,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G849" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24641,7 +24641,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G850" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G851" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G852" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G853" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G854" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G856" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G858" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G859" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G860" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G861" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G862" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G863" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G864" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G865" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G866" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G867" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G868" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G869" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G870" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G872" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G873" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G875" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G876" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G877" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G878" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G879" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G880" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G881" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G882" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G888" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G889" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G890" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>1.75</v>
       </c>
       <c r="G892" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G893" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>1.75</v>
       </c>
       <c r="G894" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G895" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>1.75</v>
       </c>
       <c r="G896" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G897" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G898" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G899" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G900" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G901" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G902" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G903" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>1.875</v>
       </c>
       <c r="G904" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G905" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G906" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G907" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G908" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G909" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G910" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G912" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26279,7 +26279,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G913" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G914" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G915" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G916" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G917" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G918" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G919" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G920" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>1.75</v>
       </c>
       <c r="G921" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G922" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G923" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G924" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G925" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G926" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G927" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G928" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G929" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G931" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G932" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G933" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G935" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G936" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>1.75</v>
       </c>
       <c r="G937" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>1.75</v>
       </c>
       <c r="G938" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G939" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G940" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>1.75</v>
       </c>
       <c r="G941" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G942" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>1.75</v>
       </c>
       <c r="G943" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27085,7 +27085,7 @@
         <v>1.75</v>
       </c>
       <c r="G944" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27137,7 +27137,7 @@
         <v>1.75</v>
       </c>
       <c r="G946" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>1.75</v>
       </c>
       <c r="G947" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27189,7 +27189,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G948" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27215,7 +27215,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G951" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G955" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27527,7 +27527,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G961" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G973" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G975" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27995,7 +27995,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G979" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G983" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G984" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G985" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G989" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G994" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G997" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1002" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1004" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1005" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1008" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1013" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1019" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>1.75</v>
       </c>
       <c r="G1063" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1064" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1068" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1072" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1074" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1075" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>1.75</v>
       </c>
       <c r="G1078" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1079" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1080" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -67653,19 +67653,19 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911805556</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>1729</v>
+        <v>1791</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.29999995231628</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.25999999046326</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.29999995231628</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="F2505" t="n">
         <v>2.27999997138977</v>
@@ -67674,6 +67674,84 @@
         <v>732</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>7775</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>1729</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6446296296</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.12615478038788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12544250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552562236786</t>
+    <t xml:space="preserve">1.1254426240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552586078644</t>
   </si>
   <si>
     <t xml:space="preserve">1.11831951141357</t>
@@ -59,34 +59,34 @@
     <t xml:space="preserve">1.0962381362915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09695029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407340526581</t>
+    <t xml:space="preserve">1.09695041179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407328605652</t>
   </si>
   <si>
     <t xml:space="preserve">1.09053957462311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08412885665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943804502487183</t>
+    <t xml:space="preserve">1.08412873744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007688999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943804681301117</t>
   </si>
   <si>
     <t xml:space="preserve">0.925997078418732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993666172027588</t>
+    <t xml:space="preserve">0.993665993213654</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925359249115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004910469055</t>
+    <t xml:space="preserve">1.01004898548126</t>
   </si>
   <si>
     <t xml:space="preserve">1.01859664916992</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">1.03213059902191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03711688518524</t>
+    <t xml:space="preserve">1.03711664676666</t>
   </si>
   <si>
     <t xml:space="preserve">1.02572000026703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495191574097</t>
+    <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
     <t xml:space="preserve">1.02643215656281</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">1.0207337141037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947366237640381</t>
+    <t xml:space="preserve">0.947366178035736</t>
   </si>
   <si>
     <t xml:space="preserve">0.900354146957397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91602486371994</t>
+    <t xml:space="preserve">0.916024625301361</t>
   </si>
   <si>
     <t xml:space="preserve">0.922435402870178</t>
@@ -128,61 +128,61 @@
     <t xml:space="preserve">0.939530968666077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985830664634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612522602081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00435078144073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997939884662628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392399787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529047489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979420065879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990816831588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967550754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227430343628</t>
+    <t xml:space="preserve">0.985830724239349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160067081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612284183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324559688568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00435054302216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997940003871918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392220973969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529107093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990817010402679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967610359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227668762207</t>
   </si>
   <si>
     <t xml:space="preserve">1.01717221736908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01503527164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078904628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02215826511383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577521324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648748874664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076138019562</t>
+    <t xml:space="preserve">1.0150351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02215838432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577533245087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076149940491</t>
   </si>
   <si>
     <t xml:space="preserve">1.00221371650696</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">0.984405994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00791215896606</t>
+    <t xml:space="preserve">1.00791227817535</t>
   </si>
   <si>
     <t xml:space="preserve">1.03284287452698</t>
@@ -200,43 +200,43 @@
     <t xml:space="preserve">1.01930916309357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996598720551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979951381683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1005117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982753753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18171489238739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16818106174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185334205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968861103058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15393483638763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11689496040344</t>
+    <t xml:space="preserve">1.03996586799622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979963302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10051190853119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084841132164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982729911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1817147731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1681809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185322284698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15393471717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11689484119415</t>
   </si>
   <si>
     <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16105782985687</t>
+    <t xml:space="preserve">1.16105794906616</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963315963745</t>
@@ -248,67 +248,67 @@
     <t xml:space="preserve">1.13683938980103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612711429596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12900412082672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316687107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1703177690506</t>
+    <t xml:space="preserve">1.13612723350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12900424003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467489719391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316710948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17031764984131</t>
   </si>
   <si>
     <t xml:space="preserve">1.18100249767303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19738531112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2109192609787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163165569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20593309402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302842140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22089147567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19596087932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23548460006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22670149803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937337398529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790972232819</t>
+    <t xml:space="preserve">1.19738554954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163153648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20593297481537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302830219269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22089159488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19596076011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23548448085785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22670161724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1879096031189</t>
   </si>
   <si>
     <t xml:space="preserve">1.1630243062973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16595208644867</t>
+    <t xml:space="preserve">1.16595196723938</t>
   </si>
   <si>
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375625133514</t>
+    <t xml:space="preserve">1.16375613212585</t>
   </si>
   <si>
     <t xml:space="preserve">1.15570497512817</t>
@@ -323,31 +323,31 @@
     <t xml:space="preserve">1.14106667041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11837685108185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10154271125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10520231723785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934723377228</t>
+    <t xml:space="preserve">1.11837708950043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10154283046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10520255565643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934711456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1293557882309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12203645706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12716007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07226610183716</t>
+    <t xml:space="preserve">1.12935590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12203657627106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12716019153595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07226598262787</t>
   </si>
   <si>
     <t xml:space="preserve">1.06860637664795</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423241138458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15716874599457</t>
+    <t xml:space="preserve">1.12423229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15716886520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.18717777729034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18205440044403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20767164230347</t>
+    <t xml:space="preserve">1.18205428123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20767140388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.17839467525482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20401203632355</t>
+    <t xml:space="preserve">1.20401179790497</t>
   </si>
   <si>
     <t xml:space="preserve">1.18351817131042</t>
@@ -389,130 +389,130 @@
     <t xml:space="preserve">1.18571388721466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17546689510345</t>
+    <t xml:space="preserve">1.17546701431274</t>
   </si>
   <si>
     <t xml:space="preserve">1.1930330991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20035254955292</t>
+    <t xml:space="preserve">1.20035219192505</t>
   </si>
   <si>
     <t xml:space="preserve">1.19888842105865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21499073505402</t>
+    <t xml:space="preserve">1.21499061584473</t>
   </si>
   <si>
     <t xml:space="preserve">1.20693969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21425902843475</t>
+    <t xml:space="preserve">1.21425890922546</t>
   </si>
   <si>
     <t xml:space="preserve">1.22230982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962915897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23328876495361</t>
+    <t xml:space="preserve">1.22962927818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23328864574432</t>
   </si>
   <si>
     <t xml:space="preserve">1.22450578212738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25524652004242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232741355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745982170105</t>
+    <t xml:space="preserve">1.25524640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232753276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745994091034</t>
   </si>
   <si>
     <t xml:space="preserve">1.30208945274353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29550206661224</t>
+    <t xml:space="preserve">1.29550218582153</t>
   </si>
   <si>
     <t xml:space="preserve">1.29184257984161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27866792678833</t>
+    <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890624523163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354454994202</t>
+    <t xml:space="preserve">1.25890600681305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354443073273</t>
   </si>
   <si>
     <t xml:space="preserve">1.25963807106018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26183366775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26256585121155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26915287971497</t>
+    <t xml:space="preserve">1.26183378696442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26256561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26915299892426</t>
   </si>
   <si>
     <t xml:space="preserve">1.23694837093353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23109328746796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402950286865</t>
+    <t xml:space="preserve">1.23109316825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402938365936</t>
   </si>
   <si>
     <t xml:space="preserve">1.24719536304474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22304177284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21938228607178</t>
+    <t xml:space="preserve">1.22304201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21938252449036</t>
   </si>
   <si>
     <t xml:space="preserve">1.19962048530579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19669270515442</t>
+    <t xml:space="preserve">1.19669258594513</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376516342163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766261100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742476940155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20620775222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522026062012</t>
+    <t xml:space="preserve">1.17766273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742465019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20620763301849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230103492737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059051036835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522002220154</t>
   </si>
   <si>
     <t xml:space="preserve">1.15643692016602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16887974739075</t>
+    <t xml:space="preserve">1.16887950897217</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693090438843</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">1.19522881507874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17985856533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498182296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17400300502777</t>
+    <t xml:space="preserve">1.17985844612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498206138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17400312423706</t>
   </si>
   <si>
     <t xml:space="preserve">1.17107534408569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16814768314362</t>
+    <t xml:space="preserve">1.16814780235291</t>
   </si>
   <si>
     <t xml:space="preserve">1.1461900472641</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">1.13447940349579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1198410987854</t>
+    <t xml:space="preserve">1.11984086036682</t>
   </si>
   <si>
     <t xml:space="preserve">1.11325359344482</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">1.10593450069427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10007905960083</t>
+    <t xml:space="preserve">1.10007894039154</t>
   </si>
   <si>
     <t xml:space="preserve">1.1227685213089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11032593250275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11618137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1396027803421</t>
+    <t xml:space="preserve">1.11032569408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11618113517761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13960289955139</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278920173645</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">1.13521122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13813889026642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14253032207489</t>
+    <t xml:space="preserve">1.13813900947571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14253044128418</t>
   </si>
   <si>
     <t xml:space="preserve">1.19449698925018</t>
@@ -596,25 +596,25 @@
     <t xml:space="preserve">1.18132221698761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17253923416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912650108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887083530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13374757766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11910891532898</t>
+    <t xml:space="preserve">1.17253947257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912662029266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13374745845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350058555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569630146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496435642242</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">1.15936470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15277755260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741573810577</t>
+    <t xml:space="preserve">1.15277743339539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741561889648</t>
   </si>
   <si>
     <t xml:space="preserve">1.22377395629883</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">1.25671029090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24792742729187</t>
+    <t xml:space="preserve">1.24792718887329</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060809612274</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26842105388641</t>
+    <t xml:space="preserve">1.2684211730957</t>
   </si>
   <si>
     <t xml:space="preserve">1.29769790172577</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">1.30867683887482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29403853416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477915287018</t>
+    <t xml:space="preserve">1.29403829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477903366089</t>
   </si>
   <si>
     <t xml:space="preserve">1.32404720783234</t>
@@ -671,49 +671,49 @@
     <t xml:space="preserve">1.31014049053192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3284387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037892818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135762691498</t>
+    <t xml:space="preserve">1.32843863964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037868976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135750770569</t>
   </si>
   <si>
     <t xml:space="preserve">1.30282127857208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31526410579681</t>
+    <t xml:space="preserve">1.31526398658752</t>
   </si>
   <si>
     <t xml:space="preserve">1.32624292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36137509346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941757678986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34673678874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38699233531952</t>
+    <t xml:space="preserve">1.36137533187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34673690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.36869442462921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38772451877594</t>
+    <t xml:space="preserve">1.38772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">1.35991144180298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37455010414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4052906036377</t>
+    <t xml:space="preserve">1.37454974651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40529048442841</t>
   </si>
   <si>
     <t xml:space="preserve">1.39065206050873</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114592552185</t>
+    <t xml:space="preserve">1.41114580631256</t>
   </si>
   <si>
     <t xml:space="preserve">1.38186895847321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.371621966362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927754878998</t>
+    <t xml:space="preserve">1.37162208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3884562253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927742958069</t>
   </si>
   <si>
     <t xml:space="preserve">1.45009875297546</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">1.58616280555725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60570800304413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51700305938721</t>
+    <t xml:space="preserve">1.60570812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51700294017792</t>
   </si>
   <si>
     <t xml:space="preserve">1.51098930835724</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">1.47866463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49069237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46814036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964371204376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4433331489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882262706757</t>
+    <t xml:space="preserve">1.49069249629974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46814024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964383125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44333302974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483649730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882274627686</t>
   </si>
   <si>
     <t xml:space="preserve">1.43205690383911</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574622154236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836770534515</t>
+    <t xml:space="preserve">1.40574645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836794376373</t>
   </si>
   <si>
     <t xml:space="preserve">1.45911943912506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189915180206</t>
+    <t xml:space="preserve">1.47189891338348</t>
   </si>
   <si>
     <t xml:space="preserve">1.45310568809509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42829823493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41852569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42980194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42078113555908</t>
+    <t xml:space="preserve">1.42829835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41852581501007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4298015832901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42078101634979</t>
   </si>
   <si>
     <t xml:space="preserve">1.42604315280914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702234745026</t>
+    <t xml:space="preserve">1.41702222824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.42529153823853</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">1.47716116905212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49219596385956</t>
+    <t xml:space="preserve">1.49219608306885</t>
   </si>
   <si>
     <t xml:space="preserve">1.46663677692413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46588504314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144411087036</t>
+    <t xml:space="preserve">1.46588528156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144423007965</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843717575073</t>
@@ -851,31 +851,31 @@
     <t xml:space="preserve">1.51850664615631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948560237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347197055817</t>
+    <t xml:space="preserve">1.50948572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347208976746</t>
   </si>
   <si>
     <t xml:space="preserve">1.48167157173157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49595475196838</t>
+    <t xml:space="preserve">1.49595463275909</t>
   </si>
   <si>
     <t xml:space="preserve">1.51249265670776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151370048523</t>
+    <t xml:space="preserve">1.50497543811798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151346206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.49369943141937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49896156787872</t>
+    <t xml:space="preserve">1.49896144866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602398395538</t>
@@ -899,76 +899,76 @@
     <t xml:space="preserve">1.47941637039185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53203809261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52903079986572</t>
+    <t xml:space="preserve">1.53203785419464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52903091907501</t>
   </si>
   <si>
     <t xml:space="preserve">1.51399612426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55158293247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511425971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55609345436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126718997955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67637133598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682601928711</t>
+    <t xml:space="preserve">1.55158305168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511414051056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55609333515167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637121677399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65682625770569</t>
   </si>
   <si>
     <t xml:space="preserve">1.69140589237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70644056797028</t>
+    <t xml:space="preserve">1.70644068717957</t>
   </si>
   <si>
     <t xml:space="preserve">1.71997177600861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65381920337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937803268433</t>
+    <t xml:space="preserve">1.65381932258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937827110291</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735029220581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66885387897491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787492275238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035710811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186057567596</t>
+    <t xml:space="preserve">1.66885411739349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6778746843338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035734653473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186093330383</t>
   </si>
   <si>
     <t xml:space="preserve">1.6883989572525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68689525127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983307361603</t>
+    <t xml:space="preserve">1.6868953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983295440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.63878452777863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64630198478699</t>
+    <t xml:space="preserve">1.64630162715912</t>
   </si>
   <si>
     <t xml:space="preserve">1.74402737617493</t>
@@ -977,178 +977,178 @@
     <t xml:space="preserve">1.80115926265717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81318724155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213833808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965567588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175312519073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430537700653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83874642848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657950878143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133666038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206934452057</t>
+    <t xml:space="preserve">1.81318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213845729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965579509735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175324440002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430525779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8387463092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71245467662811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133654117584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206910610199</t>
   </si>
   <si>
     <t xml:space="preserve">1.77560019493103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83423578739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8056697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220816612244</t>
+    <t xml:space="preserve">1.83423566818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566942691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220768928528</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899258136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74102067947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598588466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.751544713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297871112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70193028450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441258907318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388843536377</t>
+    <t xml:space="preserve">1.7410204410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598576545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75154483318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7229790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70193016529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441282749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388855457306</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434347629547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72448217868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7184681892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500657081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951709270477</t>
+    <t xml:space="preserve">1.66434359550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72448205947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846854686737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755894184113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500669002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951685428619</t>
   </si>
   <si>
     <t xml:space="preserve">1.73651003837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71395814418793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906205177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920099258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82671844959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416655540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87933969497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685750961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168377399445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7966490983963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409684658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913176059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8567875623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927046298981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701045513153</t>
+    <t xml:space="preserve">1.71395802497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161442279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906217098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920111179352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82671809196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416631698608</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
+    <t xml:space="preserve">1.88685727119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168389320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409672737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678791999817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8492705821991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870108127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87934005260468</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.89468145370483</t>
   </si>
   <si>
     <t xml:space="preserve">1.84865701198578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86399841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797361373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81030297279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235245227814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263197422028</t>
+    <t xml:space="preserve">1.86399805545807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797385215759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81030285358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331525325775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263209342957</t>
   </si>
   <si>
     <t xml:space="preserve">1.75660741329193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427817344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6798996925354</t>
+    <t xml:space="preserve">1.70291221141815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427805423737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989957332611</t>
   </si>
   <si>
     <t xml:space="preserve">1.69524133205414</t>
@@ -1157,31 +1157,31 @@
     <t xml:space="preserve">1.67222905158997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74893665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688729286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154601097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58017957210541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455829143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620401382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250881195068</t>
+    <t xml:space="preserve">1.7489367723465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688741207123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154613018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5801796913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455817222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620425224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250893115997</t>
   </si>
   <si>
     <t xml:space="preserve">1.51497805118561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53031945228577</t>
+    <t xml:space="preserve">1.53031957149506</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813045024872</t>
@@ -1190,49 +1190,49 @@
     <t xml:space="preserve">1.4152580499649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4114226102829</t>
+    <t xml:space="preserve">1.41142272949219</t>
   </si>
   <si>
     <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35005640983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38073933124542</t>
+    <t xml:space="preserve">1.35005629062653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.380739569664</t>
   </si>
   <si>
     <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36923325061798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39991652965546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35772716999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35389184951782</t>
+    <t xml:space="preserve">1.36923313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39991629123688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35772705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.34238564968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30403172969818</t>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101933002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26951336860657</t>
+    <t xml:space="preserve">1.26951313018799</t>
   </si>
   <si>
     <t xml:space="preserve">1.25417160987854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24650084972382</t>
+    <t xml:space="preserve">1.24650096893311</t>
   </si>
   <si>
     <t xml:space="preserve">1.25800716876984</t>
@@ -1241,76 +1241,76 @@
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869009017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019640922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252552986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937348842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786728858948</t>
+    <t xml:space="preserve">1.28869020938873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019629001617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252541065216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937325000763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3078670501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.33087944984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33855020999908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471477031708</t>
+    <t xml:space="preserve">1.33855009078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471488952637</t>
   </si>
   <si>
     <t xml:space="preserve">1.31553792953491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39608097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
+    <t xml:space="preserve">1.39608108997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457477092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.40375185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36156260967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539793014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443500995636</t>
+    <t xml:space="preserve">1.36156249046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539781093597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443512916565</t>
   </si>
   <si>
     <t xml:space="preserve">1.37690401077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38841032981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34622085094452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334880828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320880889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706029415131</t>
+    <t xml:space="preserve">1.38841021060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34622097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704412937164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320857048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706005573273</t>
   </si>
   <si>
     <t xml:space="preserve">1.3890346288681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36109435558319</t>
+    <t xml:space="preserve">1.3610942363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916235923767</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">1.39701759815216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41298353672028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40100908279419</t>
+    <t xml:space="preserve">1.41298341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4010089635849</t>
   </si>
   <si>
     <t xml:space="preserve">1.40899193286896</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">1.41697490215302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46886420249939</t>
+    <t xml:space="preserve">1.46886432170868</t>
   </si>
   <si>
     <t xml:space="preserve">1.49680459499359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50877892971039</t>
+    <t xml:space="preserve">1.50877904891968</t>
   </si>
   <si>
     <t xml:space="preserve">1.51277041435242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49281311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487259864807</t>
+    <t xml:space="preserve">1.49281322956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487271785736</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079607963562</t>
@@ -1367,25 +1367,25 @@
     <t xml:space="preserve">1.45289838314056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43693232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096650600433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500056743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39302611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504326343536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894947528839</t>
+    <t xml:space="preserve">1.43693244457245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096626758575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500044822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39302599430084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907720565796</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.34911978244781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4848301410675</t>
+    <t xml:space="preserve">1.48483026027679</t>
   </si>
   <si>
     <t xml:space="preserve">1.47684717178345</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">1.48882162570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52075338363647</t>
+    <t xml:space="preserve">1.52075326442719</t>
   </si>
   <si>
     <t xml:space="preserve">1.51676189899445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56066811084747</t>
+    <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659159183502</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">1.56465971469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54071080684662</t>
+    <t xml:space="preserve">1.54071092605591</t>
   </si>
   <si>
     <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52873635292053</t>
+    <t xml:space="preserve">1.52873647212982</t>
   </si>
   <si>
     <t xml:space="preserve">1.58860862255096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55667674541473</t>
+    <t xml:space="preserve">1.55667686462402</t>
   </si>
   <si>
     <t xml:space="preserve">1.54869389533997</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470217227936</t>
+    <t xml:space="preserve">1.54470229148865</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247448682785</t>
+    <t xml:space="preserve">1.52474498748779</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264268398285</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">1.67642104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801195144653</t>
+    <t xml:space="preserve">1.86801207065582</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397789001465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9478417634964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539884567261</t>
+    <t xml:space="preserve">1.94784152507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539860725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.05960297584534</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">2.20329618453979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926212310791</t>
+    <t xml:space="preserve">2.21926236152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1793475151062</t>
+    <t xml:space="preserve">2.17934727668762</t>
   </si>
   <si>
     <t xml:space="preserve">2.23522806167603</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">1.9877564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011425495148</t>
+    <t xml:space="preserve">1.82011437416077</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809722423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91591000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002886295319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650619983673</t>
+    <t xml:space="preserve">1.91590976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650631904602</t>
   </si>
   <si>
     <t xml:space="preserve">1.44890677928925</t>
@@ -1523,148 +1523,151 @@
     <t xml:space="preserve">1.72431886196136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62852323055267</t>
+    <t xml:space="preserve">1.62852334976196</t>
   </si>
   <si>
     <t xml:space="preserve">1.64448928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68440389633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457444190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6604551076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65247225761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7163360118866</t>
+    <t xml:space="preserve">1.68440401554108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457456111908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66045522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65247213840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826753139496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633589267731</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843807697296</t>
+    <t xml:space="preserve">1.66843819618225</t>
   </si>
   <si>
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238686561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75625061988831</t>
+    <t xml:space="preserve">1.69238698482513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625085830688</t>
   </si>
   <si>
     <t xml:space="preserve">1.76423370838165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9079270362854</t>
+    <t xml:space="preserve">1.90792691707611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757211208344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456234455109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679543018341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84029078483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81553339958191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077613353729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75776660442352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902851581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427124977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76601898670197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252375125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74951386451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650421619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69999933242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6834944486618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67524206638336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66698956489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825171470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174695014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72475671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048480033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398015499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572753429413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985384464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60922276973724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805746078491</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582461357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92389297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757211208344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456246376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8567955493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84029054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81553339958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79077613353729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75776636600494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902851581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427136898041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76601886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74951386451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69999933242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6834944486618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67524218559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66698968410492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174695014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7247565984726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63397991657257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985384464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60922276973724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660129547119</t>
+    <t xml:space="preserve">2.04660105705261</t>
   </si>
   <si>
     <t xml:space="preserve">1.9640771150589</t>
@@ -1673,10 +1676,10 @@
     <t xml:space="preserve">1.93931972980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87330007553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155257701874</t>
+    <t xml:space="preserve">1.87330031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155269622803</t>
   </si>
   <si>
     <t xml:space="preserve">1.88980507850647</t>
@@ -1685,16 +1688,16 @@
     <t xml:space="preserve">1.86504793167114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92281448841095</t>
+    <t xml:space="preserve">1.92281496524811</t>
   </si>
   <si>
     <t xml:space="preserve">1.93106722831726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883426189423</t>
+    <t xml:space="preserve">2.01359152793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883450031281</t>
   </si>
   <si>
     <t xml:space="preserve">1.97232949733734</t>
@@ -1703,31 +1706,28 @@
     <t xml:space="preserve">1.98058199882507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06310606002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19514513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864012718201</t>
+    <t xml:space="preserve">2.0631058216095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19514489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
     <t xml:space="preserve">2.17038774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563012123108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566035270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863988876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715000152588</t>
+    <t xml:space="preserve">2.16213488578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18715023994446</t>
   </si>
   <si>
     <t xml:space="preserve">2.15310883522034</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">2.11906766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08502650260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09353685379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06800603866577</t>
+    <t xml:space="preserve">2.08502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09353709220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
     <t xml:space="preserve">2.03396487236023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0254545211792</t>
+    <t xml:space="preserve">2.02545428276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">1.98290300369263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651615142822</t>
+    <t xml:space="preserve">1.97439229488373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07651591300964</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055731773376</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">2.05949568748474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99992311000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9914128780365</t>
+    <t xml:space="preserve">1.99992334842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99141311645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.00843358039856</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">2.01694393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10204720497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1275782585144</t>
+    <t xml:space="preserve">2.10204744338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
     <t xml:space="preserve">2.14459848403931</t>
@@ -1805,22 +1805,22 @@
     <t xml:space="preserve">2.16161918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13608837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96588218212128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9403510093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9233306646347</t>
+    <t xml:space="preserve">2.13608860969543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9658819437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94035124778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89779984951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722687959671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92333042621613</t>
   </si>
   <si>
     <t xml:space="preserve">1.94886136054993</t>
@@ -35113,7 +35113,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35139,7 +35139,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35191,7 +35191,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1256" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35217,7 +35217,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35269,7 +35269,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35295,7 +35295,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1260" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35373,7 +35373,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35399,7 +35399,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35425,7 +35425,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35451,7 +35451,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35477,7 +35477,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35503,7 +35503,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35529,7 +35529,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1269" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35555,7 +35555,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1270" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35581,7 +35581,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1271" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35607,7 +35607,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35633,7 +35633,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35659,7 +35659,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1274" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35685,7 +35685,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35737,7 +35737,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1277" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35945,7 +35945,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35971,7 +35971,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1286" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35997,7 +35997,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1287" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36023,7 +36023,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1288" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36049,7 +36049,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36075,7 +36075,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36153,7 +36153,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36205,7 +36205,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36257,7 +36257,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36309,7 +36309,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36335,7 +36335,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36361,7 +36361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36465,7 +36465,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36569,7 +36569,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36751,7 +36751,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36777,7 +36777,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36803,7 +36803,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36829,7 +36829,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36855,7 +36855,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1320" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36881,7 +36881,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1321" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36907,7 +36907,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1322" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37011,7 +37011,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1326" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37037,7 +37037,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37063,7 +37063,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1328" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37089,7 +37089,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37115,7 +37115,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1330" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37141,7 +37141,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1331" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37167,7 +37167,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37193,7 +37193,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37297,7 +37297,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37323,7 +37323,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37505,7 +37505,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37583,7 +37583,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37635,7 +37635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1350" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37713,7 +37713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37739,7 +37739,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37765,7 +37765,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37791,7 +37791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1356" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37843,7 +37843,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1358" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37869,7 +37869,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1359" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37895,7 +37895,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1360" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37921,7 +37921,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1361" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37947,7 +37947,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37973,7 +37973,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1363" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38025,7 +38025,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1365" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38051,7 +38051,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38077,7 +38077,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1367" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38103,7 +38103,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1368" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38129,7 +38129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38155,7 +38155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38181,7 +38181,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38207,7 +38207,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1372" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38233,7 +38233,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38259,7 +38259,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1374" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38285,7 +38285,7 @@
         <v>2.5</v>
       </c>
       <c r="G1375" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38311,7 +38311,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38337,7 +38337,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1377" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38363,7 +38363,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38389,7 +38389,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38415,7 +38415,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38441,7 +38441,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1381" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38467,7 +38467,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1382" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38493,7 +38493,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1383" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38519,7 +38519,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1384" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38545,7 +38545,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38571,7 +38571,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38597,7 +38597,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1387" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38623,7 +38623,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38649,7 +38649,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1389" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38675,7 +38675,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38701,7 +38701,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38753,7 +38753,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -67751,7 +67751,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6910185185</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>3571</v>
@@ -67772,6 +67772,32 @@
         <v>730</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.490625</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>631</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681160449982</t>
+    <t xml:space="preserve">1.14681172370911</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615478038788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544274330139</t>
+    <t xml:space="preserve">1.12615501880646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1254426240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.09552586078644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11831974983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09623801708221</t>
+    <t xml:space="preserve">1.11831939220428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09623825550079</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695029258728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407340526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0905396938324</t>
+    <t xml:space="preserve">1.10407328605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09053957462311</t>
   </si>
   <si>
     <t xml:space="preserve">1.08412885665894</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">1.00007688999176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943804860115051</t>
+    <t xml:space="preserve">0.943804800510406</t>
   </si>
   <si>
     <t xml:space="preserve">0.925997018814087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993666052818298</t>
+    <t xml:space="preserve">0.993665993213654</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004922389984</t>
+    <t xml:space="preserve">1.01004898548126</t>
   </si>
   <si>
     <t xml:space="preserve">1.01859664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05492436885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213047981262</t>
+    <t xml:space="preserve">1.05492424964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213059902191</t>
   </si>
   <si>
     <t xml:space="preserve">1.03711676597595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02572000026703</t>
+    <t xml:space="preserve">1.02571988105774</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495215415955</t>
@@ -110,76 +110,76 @@
     <t xml:space="preserve">1.02643215656281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0207337141037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366118431091</t>
+    <t xml:space="preserve">1.02073347568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366237640381</t>
   </si>
   <si>
     <t xml:space="preserve">0.900354146957397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916024923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830664634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970160067081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00435078144073</t>
+    <t xml:space="preserve">0.916024804115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435581684113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530730247498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160126686096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612284183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324559688568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00435054302216</t>
   </si>
   <si>
     <t xml:space="preserve">0.997940003871918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989392340183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529107093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419946670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990816950798035</t>
+    <t xml:space="preserve">0.989392280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529285907745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9908167719841</t>
   </si>
   <si>
     <t xml:space="preserve">0.987967610359192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997227668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717209815979</t>
+    <t xml:space="preserve">0.997227609157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717221736908</t>
   </si>
   <si>
     <t xml:space="preserve">1.01503527164459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00078904628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02215850353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577533245087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648772716522</t>
+    <t xml:space="preserve">1.00078916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02215802669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577521324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648736953735</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076149940491</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">1.00221371650696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984406054019928</t>
+    <t xml:space="preserve">0.984406113624573</t>
   </si>
   <si>
     <t xml:space="preserve">1.00791203975677</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">1.03996598720551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09979951381683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10051190853119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982729911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1817147731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16818106174469</t>
+    <t xml:space="preserve">1.09979963302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10051202774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084841132164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18171465396881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1681809425354</t>
   </si>
   <si>
     <t xml:space="preserve">1.13185322284698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13968861103058</t>
+    <t xml:space="preserve">1.13968873023987</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393483638763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689496040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09766280651093</t>
+    <t xml:space="preserve">1.11689484119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
     <t xml:space="preserve">1.16105771064758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15963327884674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14752399921417</t>
+    <t xml:space="preserve">1.15963315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14752388000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.1368396282196</t>
@@ -251,103 +251,103 @@
     <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12900412082672</t>
+    <t xml:space="preserve">1.12900424003601</t>
   </si>
   <si>
     <t xml:space="preserve">1.14467477798462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17316710948944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1703177690506</t>
+    <t xml:space="preserve">1.17316687107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17031788825989</t>
   </si>
   <si>
     <t xml:space="preserve">1.18100237846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19738554954529</t>
+    <t xml:space="preserve">1.19738531112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.21091914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163165569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20593297481537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302854061127</t>
+    <t xml:space="preserve">1.21163141727448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20593309402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302842140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089159488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596087932587</t>
+    <t xml:space="preserve">1.19596076011658</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548448085785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22670149803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937361240387</t>
+    <t xml:space="preserve">1.22670161724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937349319458</t>
   </si>
   <si>
     <t xml:space="preserve">1.18790972232819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16302442550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16595208644867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16229236125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16375625133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570521354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911806583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424120426178</t>
+    <t xml:space="preserve">1.1630243062973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16595196723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16229248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16375613212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570509433746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911782741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424132347107</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11837697029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10154283046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10520231723785</t>
+    <t xml:space="preserve">1.11837708950043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10154294967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10520255565643</t>
   </si>
   <si>
     <t xml:space="preserve">1.0993469953537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14545822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1293557882309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12203681468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12716019153595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07226586341858</t>
+    <t xml:space="preserve">1.14545834064484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12935590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12203657627106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12716007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07226610183716</t>
   </si>
   <si>
     <t xml:space="preserve">1.06860637664795</t>
@@ -359,37 +359,37 @@
     <t xml:space="preserve">1.12423253059387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15716886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18717765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205440044403</t>
+    <t xml:space="preserve">1.15716898441315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18717777729034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839467525482</t>
+    <t xml:space="preserve">1.17839455604553</t>
   </si>
   <si>
     <t xml:space="preserve">1.20401191711426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18351817131042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20474398136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1747350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546689510345</t>
+    <t xml:space="preserve">1.18351829051971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20474410057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17473495006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571388721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546701431274</t>
   </si>
   <si>
     <t xml:space="preserve">1.19303297996521</t>
@@ -398,61 +398,61 @@
     <t xml:space="preserve">1.20035231113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19888842105865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499073505402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693981647491</t>
+    <t xml:space="preserve">1.19888854026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693957805634</t>
   </si>
   <si>
     <t xml:space="preserve">1.21425890922546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22231018543243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962915897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2332888841629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22450578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524652004242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232765197754</t>
+    <t xml:space="preserve">1.22230982780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962939739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23328876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22450566291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232753276825</t>
   </si>
   <si>
     <t xml:space="preserve">1.31745994091034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30208957195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184257984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866816520691</t>
+    <t xml:space="preserve">1.30208969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550218582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29184246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866792678833</t>
   </si>
   <si>
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890600681305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354466915131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963807106018</t>
+    <t xml:space="preserve">1.25890624523163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354454994202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25963795185089</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183378696442</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.26256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915287971497</t>
+    <t xml:space="preserve">1.26915311813354</t>
   </si>
   <si>
     <t xml:space="preserve">1.23694849014282</t>
@@ -470,31 +470,31 @@
     <t xml:space="preserve">1.23109316825867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26402962207794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24719548225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2230418920517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21938228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19962048530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669270515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376504421234</t>
+    <t xml:space="preserve">1.26402950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24719524383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22304177284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21938240528107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962060451508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669282436371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376492500305</t>
   </si>
   <si>
     <t xml:space="preserve">1.17766273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19742465019226</t>
+    <t xml:space="preserve">1.19742488861084</t>
   </si>
   <si>
     <t xml:space="preserve">1.20620763301849</t>
@@ -503,40 +503,40 @@
     <t xml:space="preserve">1.19230115413666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18059062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522014141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15643715858459</t>
+    <t xml:space="preserve">1.18059039115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522002220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15643703937531</t>
   </si>
   <si>
     <t xml:space="preserve">1.16887962818146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693078517914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19522905349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498194217682</t>
+    <t xml:space="preserve">1.17693090438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19522869586945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985832691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498206138611</t>
   </si>
   <si>
     <t xml:space="preserve">1.17400312423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17107534408569</t>
+    <t xml:space="preserve">1.17107546329498</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814780235291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1461900472641</t>
+    <t xml:space="preserve">1.14619016647339</t>
   </si>
   <si>
     <t xml:space="preserve">1.14326250553131</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">1.11984074115753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11325359344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593450069427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007917881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276864051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032593250275</t>
+    <t xml:space="preserve">1.11325371265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593438148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007905960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12276840209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032581329346</t>
   </si>
   <si>
     <t xml:space="preserve">1.1161812543869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13960289955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1278920173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14399433135986</t>
+    <t xml:space="preserve">1.1396027803421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12789213657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14399445056915</t>
   </si>
   <si>
     <t xml:space="preserve">1.14179849624634</t>
@@ -587,49 +587,49 @@
     <t xml:space="preserve">1.13813889026642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14253056049347</t>
+    <t xml:space="preserve">1.14253044128418</t>
   </si>
   <si>
     <t xml:space="preserve">1.19449687004089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1813223361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17253935337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912650108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887107372284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13374757766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350058555603</t>
+    <t xml:space="preserve">1.18132221698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17253947257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912638187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887083530426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13374745845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350034713745</t>
   </si>
   <si>
     <t xml:space="preserve">1.12569630146027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11910891532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12496423721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12642812728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936481952667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277755260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741573810577</t>
+    <t xml:space="preserve">1.11910915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12496435642242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1264283657074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15277743339539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741585731506</t>
   </si>
   <si>
     <t xml:space="preserve">1.22377383708954</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">1.2567104101181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24792742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24060809612274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26622533798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2684211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29769790172577</t>
+    <t xml:space="preserve">1.24792730808258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24060821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26622521877289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26842105388641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29769814014435</t>
   </si>
   <si>
     <t xml:space="preserve">1.30867671966553</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">1.29403829574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3247789144516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404720783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3101407289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3284387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037892818451</t>
+    <t xml:space="preserve">1.32477903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32843887805939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037868976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135762691498</t>
@@ -683,55 +683,55 @@
     <t xml:space="preserve">1.30282151699066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31526398658752</t>
+    <t xml:space="preserve">1.3152642250061</t>
   </si>
   <si>
     <t xml:space="preserve">1.32624304294586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36137521266937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941769599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34673690795898</t>
+    <t xml:space="preserve">1.36137509346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941757678986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34673678874969</t>
   </si>
   <si>
     <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36869466304779</t>
+    <t xml:space="preserve">1.3686945438385</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772451877594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35991144180298</t>
+    <t xml:space="preserve">1.35991132259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.37454986572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4052906036377</t>
+    <t xml:space="preserve">1.40529036521912</t>
   </si>
   <si>
     <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39650750160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114604473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3818690776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37162208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845634460449</t>
+    <t xml:space="preserve">1.39650738239288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114580631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38186895847321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162220478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38845646381378</t>
   </si>
   <si>
     <t xml:space="preserve">1.41927754878998</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">1.45009863376617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50046503543854</t>
+    <t xml:space="preserve">1.50046515464783</t>
   </si>
   <si>
     <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56361067295074</t>
+    <t xml:space="preserve">1.56361079216003</t>
   </si>
   <si>
     <t xml:space="preserve">1.58616268634796</t>
@@ -755,55 +755,55 @@
     <t xml:space="preserve">1.60570788383484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5170031785965</t>
+    <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.51098942756653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4869339466095</t>
+    <t xml:space="preserve">1.48693370819092</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49069249629974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46814024448395</t>
+    <t xml:space="preserve">1.49069237709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46814036369324</t>
   </si>
   <si>
     <t xml:space="preserve">1.46964383125305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4433331489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882274627686</t>
+    <t xml:space="preserve">1.44333291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483649730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882262706757</t>
   </si>
   <si>
     <t xml:space="preserve">1.4320570230484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43581581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40574645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836782455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45911955833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45310568809509</t>
+    <t xml:space="preserve">1.43581569194794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40574634075165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836770534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45911943912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189891338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45310580730438</t>
   </si>
   <si>
     <t xml:space="preserve">1.42829835414886</t>
@@ -812,37 +812,37 @@
     <t xml:space="preserve">1.41852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42980182170868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42078077793121</t>
+    <t xml:space="preserve">1.42980170249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42078101634979</t>
   </si>
   <si>
     <t xml:space="preserve">1.42604315280914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702234745026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42529153823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44408488273621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716128826141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219596385956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46663689613342</t>
+    <t xml:space="preserve">1.41702210903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42529141902924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44408464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716104984283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219572544098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46663701534271</t>
   </si>
   <si>
     <t xml:space="preserve">1.46588516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49144423007965</t>
+    <t xml:space="preserve">1.49144399166107</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843717575073</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347208976746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167169094086</t>
+    <t xml:space="preserve">1.50948560237885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347197055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167157173157</t>
   </si>
   <si>
     <t xml:space="preserve">1.4959545135498</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">1.51249289512634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497555732727</t>
+    <t xml:space="preserve">1.50497543811798</t>
   </si>
   <si>
     <t xml:space="preserve">1.52151346206665</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">1.49369943141937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49896156787872</t>
+    <t xml:space="preserve">1.49896144866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602410316467</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">1.54857611656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48242330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039568424225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941648960114</t>
+    <t xml:space="preserve">1.48242354393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941637039185</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203785419464</t>
@@ -905,46 +905,46 @@
     <t xml:space="preserve">1.52903091907501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51399624347687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158305168152</t>
+    <t xml:space="preserve">1.51399636268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158281326294</t>
   </si>
   <si>
     <t xml:space="preserve">1.56511425971985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55609333515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126718997955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67637121677399</t>
+    <t xml:space="preserve">1.55609357357025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126730918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6763710975647</t>
   </si>
   <si>
     <t xml:space="preserve">1.65682601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69140589237213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644056797028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997201442719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937803268433</t>
+    <t xml:space="preserve">1.69140577316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644044876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381932258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937791347504</t>
   </si>
   <si>
     <t xml:space="preserve">1.6673504114151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6688539981842</t>
+    <t xml:space="preserve">1.66885387897491</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778746843338</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">1.68689548969269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65983283519745</t>
+    <t xml:space="preserve">1.65983295440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.63878440856934</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">1.74402737617493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80115938186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318688392639</t>
+    <t xml:space="preserve">1.80115926265717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318724155426</t>
   </si>
   <si>
     <t xml:space="preserve">1.79213857650757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79965627193451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175324440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430525779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8387463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245455741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133642196655</t>
+    <t xml:space="preserve">1.79965579509735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175336360931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430537700653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874619007111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133654117584</t>
   </si>
   <si>
     <t xml:space="preserve">1.76206910610199</t>
@@ -1010,55 +1010,55 @@
     <t xml:space="preserve">1.77560031414032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83423590660095</t>
+    <t xml:space="preserve">1.83423566818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.8056697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82220828533173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72899258136749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74102056026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598588466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.751544713974</t>
+    <t xml:space="preserve">1.82220792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72899270057678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7410204410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598600387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75154495239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70193016529083</t>
+    <t xml:space="preserve">1.70193004608154</t>
   </si>
   <si>
     <t xml:space="preserve">1.69441294670105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68388843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434347629547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72448229789734</t>
+    <t xml:space="preserve">1.68388855457306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728106021881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434359550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72448241710663</t>
   </si>
   <si>
     <t xml:space="preserve">1.71846854686737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75755882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500680923462</t>
+    <t xml:space="preserve">1.75755870342255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500645160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.73951685428619</t>
@@ -1067,61 +1067,61 @@
     <t xml:space="preserve">1.73651003837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71395814418793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161406517029</t>
+    <t xml:space="preserve">1.71395790576935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161430358887</t>
   </si>
   <si>
     <t xml:space="preserve">1.75906217098236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81920123100281</t>
+    <t xml:space="preserve">1.81920099258423</t>
   </si>
   <si>
     <t xml:space="preserve">1.82671844959259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416643619537</t>
+    <t xml:space="preserve">1.80416631698608</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685750961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168365478516</t>
+    <t xml:space="preserve">1.88685727119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168401241302</t>
   </si>
   <si>
     <t xml:space="preserve">1.7966490983963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77409684658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913199901581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8492705821991</t>
+    <t xml:space="preserve">1.77409672737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927070140839</t>
   </si>
   <si>
     <t xml:space="preserve">1.88701057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89468133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865665435791</t>
+    <t xml:space="preserve">1.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486567735672</t>
   </si>
   <si>
     <t xml:space="preserve">1.86399817466736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81797349452972</t>
+    <t xml:space="preserve">1.81797361373901</t>
   </si>
   <si>
     <t xml:space="preserve">1.81030285358429</t>
@@ -1130,64 +1130,64 @@
     <t xml:space="preserve">1.90235233306885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83331537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263221263885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660753250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291221141815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427793502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6798996925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524109363556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74893689155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688753128052</t>
+    <t xml:space="preserve">1.83331525325775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263209342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660741329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291197299957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427805423737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989981174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524145126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222905158997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7489367723465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688741207123</t>
   </si>
   <si>
     <t xml:space="preserve">1.64154601097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58017957210541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455829143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620437145233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250893115997</t>
+    <t xml:space="preserve">1.5801796913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620425224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250905036926</t>
   </si>
   <si>
     <t xml:space="preserve">1.5149781703949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53031969070435</t>
+    <t xml:space="preserve">1.53031957149506</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813045024872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4152580499649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4114226102829</t>
+    <t xml:space="preserve">1.41525781154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41142272949219</t>
   </si>
   <si>
     <t xml:space="preserve">1.37306869029999</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">1.35005629062653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38073933124542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39224576950073</t>
+    <t xml:space="preserve">1.38073945045471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923325061798</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34238576889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403172969818</t>
+    <t xml:space="preserve">1.3423855304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101933002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26951313018799</t>
+    <t xml:space="preserve">1.26951324939728</t>
   </si>
   <si>
     <t xml:space="preserve">1.25417172908783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24650096893311</t>
+    <t xml:space="preserve">1.24650084972382</t>
   </si>
   <si>
     <t xml:space="preserve">1.25800704956055</t>
@@ -1238,52 +1238,52 @@
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869009017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019640922546</t>
+    <t xml:space="preserve">1.28869020938873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019652843475</t>
   </si>
   <si>
     <t xml:space="preserve">1.29252564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31937336921692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786716938019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087956905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855009078979</t>
+    <t xml:space="preserve">1.31937348842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786728858948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855020999908</t>
   </si>
   <si>
     <t xml:space="preserve">1.33471477031708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3155380487442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39608108997345</t>
+    <t xml:space="preserve">1.31553792953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39608097076416</t>
   </si>
   <si>
     <t xml:space="preserve">1.38457489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40375185012817</t>
+    <t xml:space="preserve">1.40375173091888</t>
   </si>
   <si>
     <t xml:space="preserve">1.36156249046326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36539804935455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443500995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37690412998199</t>
+    <t xml:space="preserve">1.36539793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37690401077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.38841021060944</t>
@@ -1292,43 +1292,43 @@
     <t xml:space="preserve">1.34622097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32704412937164</t>
+    <t xml:space="preserve">1.32704401016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.27334868907928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32320868968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706029415131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3890346288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36109435558319</t>
+    <t xml:space="preserve">1.32320857048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38903450965881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916247844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311126708984</t>
+    <t xml:space="preserve">1.35311150550842</t>
   </si>
   <si>
     <t xml:space="preserve">1.34512841701508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36508572101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39701759815216</t>
+    <t xml:space="preserve">1.36508584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39701747894287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41298353672028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40100908279419</t>
+    <t xml:space="preserve">1.4010089635849</t>
   </si>
   <si>
     <t xml:space="preserve">1.40899193286896</t>
@@ -1340,46 +1340,46 @@
     <t xml:space="preserve">1.46886432170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49680459499359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5087788105011</t>
+    <t xml:space="preserve">1.49680471420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877904891968</t>
   </si>
   <si>
     <t xml:space="preserve">1.51277053356171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49281311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487283706665</t>
+    <t xml:space="preserve">1.49281299114227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487271785736</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079607963562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44491517543793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45289838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693220615387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495799064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096650600433</t>
+    <t xml:space="preserve">1.44491529464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45289814472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495787143707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096638679504</t>
   </si>
   <si>
     <t xml:space="preserve">1.40500044822693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39302599430084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504314422607</t>
+    <t xml:space="preserve">1.39302611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504302501678</t>
   </si>
   <si>
     <t xml:space="preserve">1.4289493560791</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35710275173187</t>
+    <t xml:space="preserve">1.35710287094116</t>
   </si>
   <si>
     <t xml:space="preserve">1.3491199016571</t>
@@ -1406,31 +1406,31 @@
     <t xml:space="preserve">1.46088123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48882150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075350284576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51676201820374</t>
+    <t xml:space="preserve">1.48882162570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075338363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51676189899445</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659159183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56465983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54071068763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53272783756256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52873635292053</t>
+    <t xml:space="preserve">1.59659147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56465971469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54071056842804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53272771835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52873647212982</t>
   </si>
   <si>
     <t xml:space="preserve">1.58860850334167</t>
@@ -1445,34 +1445,34 @@
     <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470229148865</t>
+    <t xml:space="preserve">1.54470217227936</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247448682785</t>
+    <t xml:space="preserve">1.52474474906921</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264268398285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801183223724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88397777080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784200191498</t>
+    <t xml:space="preserve">1.67642092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801207065582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88397789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478417634964</t>
   </si>
   <si>
     <t xml:space="preserve">2.15539836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05960321426392</t>
+    <t xml:space="preserve">2.05960297584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338157653809</t>
@@ -1481,43 +1481,43 @@
     <t xml:space="preserve">2.20329642295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926212310791</t>
+    <t xml:space="preserve">2.21926188468933</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724485397339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1793475151062</t>
+    <t xml:space="preserve">2.17934775352478</t>
   </si>
   <si>
     <t xml:space="preserve">2.23522806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11548376083374</t>
+    <t xml:space="preserve">2.11548352241516</t>
   </si>
   <si>
     <t xml:space="preserve">1.9877564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011461257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91590976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650631904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890701770782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260010719299</t>
+    <t xml:space="preserve">1.82011437416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91590988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002910137177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650643825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5925999879837</t>
   </si>
   <si>
     <t xml:space="preserve">1.72431898117065</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">1.62852323055267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64448916912079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6844037771225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457444190979</t>
+    <t xml:space="preserve">1.64448928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68440401554108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457456111908</t>
   </si>
   <si>
     <t xml:space="preserve">1.66045498847961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65247213840485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7163360118866</t>
+    <t xml:space="preserve">1.65247225761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826776981354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633589267731</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054038047791</t>
@@ -1556,271 +1556,271 @@
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238710403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7562507390976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76423346996307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9079270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582485198975</t>
+    <t xml:space="preserve">1.69238698482513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625085830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76423370838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90792691707611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582461357117</t>
   </si>
   <si>
     <t xml:space="preserve">1.92389273643494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94757199287415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456234455109</t>
+    <t xml:space="preserve">1.94757223129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456246376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679543018341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84029066562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81553363800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077625274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75776648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902851581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427124977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76601886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126136302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252375125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495139837265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69999933242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68349456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67524218559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66698968410492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873742103577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174695014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7247565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048480033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398003578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572753429413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985384464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60922276973724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582437515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9640771150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931972980499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87329995632172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88980531692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92281460762024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106710910797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232949733734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98058199882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06310606002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19514489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17864012718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17038774490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566035270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18715023994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906790733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09353685379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06800580024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03396463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254545211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247498512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05098533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482031345367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184065818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95737171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98290252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439253330231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0765163898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11055755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05949592590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992334842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9914128780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843358039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01694393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204696655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12757802009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14459872245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16161918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13608837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9658819437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94035112857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977997303009</t>
   </si>
   <si>
     <t xml:space="preserve">1.90630996227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8567955493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84029042720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81553339958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79077613353729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75776648521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427136898041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76601886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126136302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300909996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7495139837265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69999933242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6834944486618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67524218559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66698968410492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174706935883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7247565984726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63397991657257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985384464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60922276973724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805734157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582437515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96407735347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93931972980499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330007553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8815530538559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88980507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86504793167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92281484603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106710910797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883414268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232949733734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98058176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0631058216095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19514465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17038750648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563012123108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864012718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906790733337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08502674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09353685379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06800580024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03396463394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0254545211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247498512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05098509788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482031345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184065818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95737171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439253330231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11055755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05949592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992334842682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9914128780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843358039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01694393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204696655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12757802009583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14459872245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16161894798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13608837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9658819437027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94035112857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722687959671</t>
+    <t xml:space="preserve">1.87226891517639</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>522</v>
+        <v>601</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -67806,7 +67806,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.5037152778</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>3107</v>
@@ -67827,6 +67827,32 @@
         <v>726</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6912037037</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>5348</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615501880646</t>
+    <t xml:space="preserve">1.12615478038788</t>
   </si>
   <si>
     <t xml:space="preserve">1.1254426240921</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">1.09552586078644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11831939220428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09623825550079</t>
+    <t xml:space="preserve">1.11831951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09623801708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695029258728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407328605652</t>
+    <t xml:space="preserve">1.10407340526581</t>
   </si>
   <si>
     <t xml:space="preserve">1.09053957462311</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">0.925997018814087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993665993213654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925371170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01004898548126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492424964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213059902191</t>
+    <t xml:space="preserve">0.993666112422943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925359249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01004922389984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859676837921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492436885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0321307182312</t>
   </si>
   <si>
     <t xml:space="preserve">1.03711676597595</t>
@@ -104,67 +104,67 @@
     <t xml:space="preserve">1.02571988105774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495215415955</t>
+    <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
     <t xml:space="preserve">1.02643215656281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02073347568512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354146957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024804115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435581684113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530730247498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970160126686096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324559688568</t>
+    <t xml:space="preserve">1.0207337141037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366416454315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354087352753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024744510651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530909061432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830724239349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970159947872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612403392792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324678897858</t>
   </si>
   <si>
     <t xml:space="preserve">1.00435054302216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997940003871918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529285907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419887065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9908167719841</t>
+    <t xml:space="preserve">0.997939765453339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392220973969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529107093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979420065879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99081689119339</t>
   </si>
   <si>
     <t xml:space="preserve">0.987967610359192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997227609157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717221736908</t>
+    <t xml:space="preserve">0.997227668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717209815979</t>
   </si>
   <si>
     <t xml:space="preserve">1.01503527164459</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">1.00078916549683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02215802669525</t>
+    <t xml:space="preserve">1.02215838432312</t>
   </si>
   <si>
     <t xml:space="preserve">1.00577521324158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00648736953735</t>
+    <t xml:space="preserve">1.00648760795593</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076149940491</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">1.00221371650696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984406113624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00791203975677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03284287452698</t>
+    <t xml:space="preserve">0.984406232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00791227817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03284311294556</t>
   </si>
   <si>
     <t xml:space="preserve">1.01930904388428</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">1.09979963302612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10051202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084841132164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982717990875</t>
+    <t xml:space="preserve">1.1005117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982741832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.18171465396881</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">1.13185322284698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13968873023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15393483638763</t>
+    <t xml:space="preserve">1.13968884944916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15393471717834</t>
   </si>
   <si>
     <t xml:space="preserve">1.11689484119415</t>
@@ -236,67 +236,67 @@
     <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16105771064758</t>
+    <t xml:space="preserve">1.16105794906616</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14752388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1368396282196</t>
+    <t xml:space="preserve">1.14752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683938980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12900424003601</t>
+    <t xml:space="preserve">1.12900412082672</t>
   </si>
   <si>
     <t xml:space="preserve">1.14467477798462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17316687107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17031788825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18100237846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19738531112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21091914176941</t>
+    <t xml:space="preserve">1.17316710948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1703177690506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18100249767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19738554954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2109192609787</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163141727448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20593309402466</t>
+    <t xml:space="preserve">1.20593297481537</t>
   </si>
   <si>
     <t xml:space="preserve">1.22302842140198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22089159488678</t>
+    <t xml:space="preserve">1.22089147567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.19596076011658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23548448085785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22670161724091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790972232819</t>
+    <t xml:space="preserve">1.23548460006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22670149803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937361240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18790984153748</t>
   </si>
   <si>
     <t xml:space="preserve">1.1630243062973</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">1.16229248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375613212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570509433746</t>
+    <t xml:space="preserve">1.16375637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570521354675</t>
   </si>
   <si>
     <t xml:space="preserve">1.14911782741547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15424132347107</t>
+    <t xml:space="preserve">1.15424120426178</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
@@ -326,19 +326,19 @@
     <t xml:space="preserve">1.11837708950043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10154294967651</t>
+    <t xml:space="preserve">1.10154283046722</t>
   </si>
   <si>
     <t xml:space="preserve">1.10520255565643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0993469953537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545834064484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12935590744019</t>
+    <t xml:space="preserve">1.09934711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545810222626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12935602664948</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203657627106</t>
@@ -347,88 +347,88 @@
     <t xml:space="preserve">1.12716007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07226610183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13081979751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12423253059387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15716898441315</t>
+    <t xml:space="preserve">1.07226598262787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860649585724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13081955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12423241138458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15716886520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.18717777729034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18205416202545</t>
+    <t xml:space="preserve">1.18205440044403</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839455604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401191711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18351829051971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20474410057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17473495006561</t>
+    <t xml:space="preserve">1.17839467525482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401179790497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18351817131042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2047438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1747350692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.18571388721466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17546701431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19303297996521</t>
+    <t xml:space="preserve">1.17546689510345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1930330991745</t>
   </si>
   <si>
     <t xml:space="preserve">1.20035231113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19888854026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693957805634</t>
+    <t xml:space="preserve">1.19888830184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499073505402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693981647491</t>
   </si>
   <si>
     <t xml:space="preserve">1.21425890922546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22230982780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962939739227</t>
+    <t xml:space="preserve">1.22230994701385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962915897369</t>
   </si>
   <si>
     <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22450566291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524640083313</t>
+    <t xml:space="preserve">1.22450590133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524652004242</t>
   </si>
   <si>
     <t xml:space="preserve">1.28232753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31745994091034</t>
+    <t xml:space="preserve">1.31745970249176</t>
   </si>
   <si>
     <t xml:space="preserve">1.30208969116211</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">1.27866792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24426770210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25890624523163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354454994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963795185089</t>
+    <t xml:space="preserve">1.24426782131195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25890612602234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354466915131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2596378326416</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183378696442</t>
@@ -461,52 +461,52 @@
     <t xml:space="preserve">1.26256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915311813354</t>
+    <t xml:space="preserve">1.26915287971497</t>
   </si>
   <si>
     <t xml:space="preserve">1.23694849014282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23109316825867</t>
+    <t xml:space="preserve">1.23109292984009</t>
   </si>
   <si>
     <t xml:space="preserve">1.26402950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22304177284241</t>
+    <t xml:space="preserve">1.24719548225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
     <t xml:space="preserve">1.21938240528107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19962060451508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669282436371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376492500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17766273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20620763301849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230115413666</t>
+    <t xml:space="preserve">1.19962048530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669258594513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17766261100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742476940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20620775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230103492737</t>
   </si>
   <si>
     <t xml:space="preserve">1.18059039115906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16522002220154</t>
+    <t xml:space="preserve">1.16522014141083</t>
   </si>
   <si>
     <t xml:space="preserve">1.15643703937531</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">1.16887962818146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693090438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19522869586945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985832691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498206138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17400312423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107546329498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16814780235291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14619016647339</t>
+    <t xml:space="preserve">1.17693066596985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19522893428802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985856533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498194217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17400300502777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107558250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16814768314362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1461900472641</t>
   </si>
   <si>
     <t xml:space="preserve">1.14326250553131</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">1.1344792842865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11984074115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325371265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593438148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276840209961</t>
+    <t xml:space="preserve">1.11984086036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593450069427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007917881012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12276864051819</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032581329346</t>
@@ -569,25 +569,25 @@
     <t xml:space="preserve">1.1161812543869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1396027803421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12789213657379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14399445056915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14179849624634</t>
+    <t xml:space="preserve">1.13960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12789189815521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14399433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14179861545563</t>
   </si>
   <si>
     <t xml:space="preserve">1.13521122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13813889026642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14253044128418</t>
+    <t xml:space="preserve">1.138139128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14253056049347</t>
   </si>
   <si>
     <t xml:space="preserve">1.19449687004089</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">1.18132221698761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17253947257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912638187408</t>
+    <t xml:space="preserve">1.17253911495209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912650108337</t>
   </si>
   <si>
     <t xml:space="preserve">1.13887083530426</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12350034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569630146027</t>
+    <t xml:space="preserve">1.12350046634674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569642066956</t>
   </si>
   <si>
     <t xml:space="preserve">1.11910915374756</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">1.12496435642242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1264283657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936470031738</t>
+    <t xml:space="preserve">1.12642812728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936481952667</t>
   </si>
   <si>
     <t xml:space="preserve">1.15277743339539</t>
@@ -632,37 +632,37 @@
     <t xml:space="preserve">1.16741585731506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22377383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596955299377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2567104101181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792730808258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24060821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26622521877289</t>
+    <t xml:space="preserve">1.22377395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596967220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25671029090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24060785770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
     <t xml:space="preserve">1.26842105388641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29769814014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477903366089</t>
+    <t xml:space="preserve">1.29769778251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867695808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403841495514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3247789144516</t>
   </si>
   <si>
     <t xml:space="preserve">1.32404708862305</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">1.31014060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32843887805939</t>
+    <t xml:space="preserve">1.32843863964081</t>
   </si>
   <si>
     <t xml:space="preserve">1.29037868976593</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">1.30135762691498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30282151699066</t>
+    <t xml:space="preserve">1.30282139778137</t>
   </si>
   <si>
     <t xml:space="preserve">1.3152642250061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32624304294586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137509346008</t>
+    <t xml:space="preserve">1.32624292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137521266937</t>
   </si>
   <si>
     <t xml:space="preserve">1.33941757678986</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">1.34673678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38699245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3686945438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772451877594</t>
+    <t xml:space="preserve">1.38699233531952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36869430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772428035736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35991132259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37454986572266</t>
+    <t xml:space="preserve">1.37454974651337</t>
   </si>
   <si>
     <t xml:space="preserve">1.40529036521912</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39650738239288</t>
+    <t xml:space="preserve">1.39650750160217</t>
   </si>
   <si>
     <t xml:space="preserve">1.41114580631256</t>
@@ -731,79 +731,79 @@
     <t xml:space="preserve">1.37162220478058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38845646381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927754878998</t>
+    <t xml:space="preserve">1.38845634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4192773103714</t>
   </si>
   <si>
     <t xml:space="preserve">1.45009863376617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50046515464783</t>
+    <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
     <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56361079216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58616268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60570788383484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51700305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51098942756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866463661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49069237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46814036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964383125305</t>
+    <t xml:space="preserve">1.56361067295074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58616292476654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60570800304413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5170031785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51098930835724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693382740021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866475582123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49069249629974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46814024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964371204376</t>
   </si>
   <si>
     <t xml:space="preserve">1.44333291053772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483649730682</t>
+    <t xml:space="preserve">1.44483661651611</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882262706757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4320570230484</t>
+    <t xml:space="preserve">1.43205690383911</t>
   </si>
   <si>
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574634075165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836770534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45911943912506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189891338348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45310580730438</t>
+    <t xml:space="preserve">1.40574622154236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836782455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45911955833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45310568809509</t>
   </si>
   <si>
     <t xml:space="preserve">1.42829835414886</t>
@@ -815,52 +815,52 @@
     <t xml:space="preserve">1.42980170249939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42078101634979</t>
+    <t xml:space="preserve">1.4207808971405</t>
   </si>
   <si>
     <t xml:space="preserve">1.42604315280914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702210903168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42529141902924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44408464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716104984283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219572544098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46663701534271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46588516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144399166107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48843717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850652694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948560237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347197055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167157173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4959545135498</t>
+    <t xml:space="preserve">1.41702222824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42529129981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44408476352692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716116905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219596385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46663689613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46588528156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144423007965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48843705654144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5185067653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948584079742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167145252228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49595475196838</t>
   </si>
   <si>
     <t xml:space="preserve">1.51249289512634</t>
@@ -872,43 +872,43 @@
     <t xml:space="preserve">1.52151346206665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49369943141937</t>
+    <t xml:space="preserve">1.49369931221008</t>
   </si>
   <si>
     <t xml:space="preserve">1.49896144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602410316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49670648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50798237323761</t>
+    <t xml:space="preserve">1.52602398395538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.496706366539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798225402832</t>
   </si>
   <si>
     <t xml:space="preserve">1.54857611656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48242354393005</t>
+    <t xml:space="preserve">1.48242330551147</t>
   </si>
   <si>
     <t xml:space="preserve">1.47039556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47941637039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53203785419464</t>
+    <t xml:space="preserve">1.47941648960114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53203809261322</t>
   </si>
   <si>
     <t xml:space="preserve">1.52903091907501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51399636268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158281326294</t>
+    <t xml:space="preserve">1.51399624347687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158305168152</t>
   </si>
   <si>
     <t xml:space="preserve">1.56511425971985</t>
@@ -917,91 +917,91 @@
     <t xml:space="preserve">1.55609357357025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126730918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
+    <t xml:space="preserve">1.63126695156097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637133598328</t>
   </si>
   <si>
     <t xml:space="preserve">1.65682601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69140577316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644044876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381932258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937791347504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6673504114151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66885387897491</t>
+    <t xml:space="preserve">1.69140589237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644056797028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997201442719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735029220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885375976562</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778746843338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67035722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839907646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
+    <t xml:space="preserve">1.67035710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186081409454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6883989572525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6868953704834</t>
   </si>
   <si>
     <t xml:space="preserve">1.65983295440674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63878440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64630174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74402737617493</t>
+    <t xml:space="preserve">1.63878452777863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64630198478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402713775635</t>
   </si>
   <si>
     <t xml:space="preserve">1.80115926265717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81318724155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213857650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965579509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175336360931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430537700653</t>
+    <t xml:space="preserve">1.81318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213869571686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965603351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175324440002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430501937866</t>
   </si>
   <si>
     <t xml:space="preserve">1.83874619007111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76657938957214</t>
+    <t xml:space="preserve">1.76657950878143</t>
   </si>
   <si>
     <t xml:space="preserve">1.7124547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66133654117584</t>
+    <t xml:space="preserve">1.66133642196655</t>
   </si>
   <si>
     <t xml:space="preserve">1.76206910610199</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">1.77560031414032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83423566818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8056697845459</t>
+    <t xml:space="preserve">1.83423578739166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566966533661</t>
   </si>
   <si>
     <t xml:space="preserve">1.82220792770386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72899270057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7410204410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598600387573</t>
+    <t xml:space="preserve">1.72899281978607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74102067947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598576545715</t>
   </si>
   <si>
     <t xml:space="preserve">1.75154495239258</t>
@@ -1034,106 +1034,106 @@
     <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70193004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388855457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728106021881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434359550476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72448241710663</t>
+    <t xml:space="preserve">1.70193028450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441282749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434347629547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72448205947876</t>
   </si>
   <si>
     <t xml:space="preserve">1.71846854686737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75755870342255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500645160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951685428619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73651003837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71395790576935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161430358887</t>
+    <t xml:space="preserve">1.75755882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951709270477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73650991916656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71395802497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161418437958</t>
   </si>
   <si>
     <t xml:space="preserve">1.75906217098236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81920099258423</t>
+    <t xml:space="preserve">1.81920123100281</t>
   </si>
   <si>
     <t xml:space="preserve">1.82671844959259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416631698608</t>
+    <t xml:space="preserve">1.80416655540466</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168401241302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7966490983963</t>
+    <t xml:space="preserve">1.88685715198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664897918701</t>
   </si>
   <si>
     <t xml:space="preserve">1.77409672737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78913164138794</t>
+    <t xml:space="preserve">1.78913152217865</t>
   </si>
   <si>
     <t xml:space="preserve">1.85678780078888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84927070140839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486567735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399817466736</t>
+    <t xml:space="preserve">1.84927034378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88701069355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468133449554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865701198578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399841308594</t>
   </si>
   <si>
     <t xml:space="preserve">1.81797361373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81030285358429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235233306885</t>
+    <t xml:space="preserve">1.81030309200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235209465027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83331525325775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80263209342957</t>
+    <t xml:space="preserve">1.80263221263885</t>
   </si>
   <si>
     <t xml:space="preserve">1.75660741329193</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">1.70291197299957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76427805423737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67989981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524145126343</t>
+    <t xml:space="preserve">1.76427793502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989993095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524133205414</t>
   </si>
   <si>
     <t xml:space="preserve">1.67222905158997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7489367723465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688741207123</t>
+    <t xml:space="preserve">1.74893665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688753128052</t>
   </si>
   <si>
     <t xml:space="preserve">1.64154601097107</t>
@@ -1166,34 +1166,34 @@
     <t xml:space="preserve">1.5801796913147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66455841064453</t>
+    <t xml:space="preserve">1.66455817222595</t>
   </si>
   <si>
     <t xml:space="preserve">1.62620425224304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57250905036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5149781703949</t>
+    <t xml:space="preserve">1.57250881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51497805118561</t>
   </si>
   <si>
     <t xml:space="preserve">1.53031957149506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48813045024872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41525781154633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41142272949219</t>
+    <t xml:space="preserve">1.48813033103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4152580499649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4114226102829</t>
   </si>
   <si>
     <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35005629062653</t>
+    <t xml:space="preserve">1.35005640983582</t>
   </si>
   <si>
     <t xml:space="preserve">1.38073945045471</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39991652965546</t>
+    <t xml:space="preserve">1.39991641044617</t>
   </si>
   <si>
     <t xml:space="preserve">1.35772716999054</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3423855304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403184890747</t>
+    <t xml:space="preserve">1.34238564968109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403172969818</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101933002472</t>
@@ -1226,61 +1226,61 @@
     <t xml:space="preserve">1.26951324939728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25417172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24650084972382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25800704956055</t>
+    <t xml:space="preserve">1.25417184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24650096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25800716876984</t>
   </si>
   <si>
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869020938873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019652843475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252564907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937348842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786728858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087944984436</t>
+    <t xml:space="preserve">1.28868997097015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019640922546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252552986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786716938019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087956905365</t>
   </si>
   <si>
     <t xml:space="preserve">1.33855020999908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33471477031708</t>
+    <t xml:space="preserve">1.33471488952637</t>
   </si>
   <si>
     <t xml:space="preserve">1.31553792953491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39608097076416</t>
+    <t xml:space="preserve">1.39608108997345</t>
   </si>
   <si>
     <t xml:space="preserve">1.38457489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40375173091888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36156249046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539793014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443489074707</t>
+    <t xml:space="preserve">1.40375196933746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36156260967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539804935455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443512916565</t>
   </si>
   <si>
     <t xml:space="preserve">1.37690401077271</t>
@@ -1289,46 +1289,46 @@
     <t xml:space="preserve">1.38841021060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34622097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704401016235</t>
+    <t xml:space="preserve">1.3462210893631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704412937164</t>
   </si>
   <si>
     <t xml:space="preserve">1.27334868907928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32320857048035</t>
+    <t xml:space="preserve">1.32320868968964</t>
   </si>
   <si>
     <t xml:space="preserve">1.37706017494202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38903450965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36109447479248</t>
+    <t xml:space="preserve">1.3890346288681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36109435558319</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916247844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34512841701508</t>
+    <t xml:space="preserve">1.35311138629913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34512829780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.36508584022522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39701747894287</t>
+    <t xml:space="preserve">1.39701759815216</t>
   </si>
   <si>
     <t xml:space="preserve">1.41298353672028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4010089635849</t>
+    <t xml:space="preserve">1.40100908279419</t>
   </si>
   <si>
     <t xml:space="preserve">1.40899193286896</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">1.4169750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46886432170868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49680471420288</t>
+    <t xml:space="preserve">1.46886420249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49680459499359</t>
   </si>
   <si>
     <t xml:space="preserve">1.50877904891968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51277053356171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49281299114227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487271785736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50079607963562</t>
+    <t xml:space="preserve">1.51277041435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49281322956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487259864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50079619884491</t>
   </si>
   <si>
     <t xml:space="preserve">1.44491529464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45289814472198</t>
+    <t xml:space="preserve">1.45289826393127</t>
   </si>
   <si>
     <t xml:space="preserve">1.43693232536316</t>
@@ -1370,136 +1370,136 @@
     <t xml:space="preserve">1.42495787143707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42096638679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500044822693</t>
+    <t xml:space="preserve">1.42096650600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500056743622</t>
   </si>
   <si>
     <t xml:space="preserve">1.39302611351013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38504302501678</t>
+    <t xml:space="preserve">1.38504326343536</t>
   </si>
   <si>
     <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37306880950928</t>
+    <t xml:space="preserve">1.3730685710907</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35710287094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3491199016571</t>
+    <t xml:space="preserve">1.35710275173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34911978244781</t>
   </si>
   <si>
     <t xml:space="preserve">1.4848301410675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47684717178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46088123321533</t>
+    <t xml:space="preserve">1.47684729099274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46088135242462</t>
   </si>
   <si>
     <t xml:space="preserve">1.48882162570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52075338363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51676189899445</t>
+    <t xml:space="preserve">1.52075350284576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51676201820374</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659147262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56465971469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54071056842804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53272771835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52873647212982</t>
+    <t xml:space="preserve">1.59659159183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5646595954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54071068763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53272783756256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
     <t xml:space="preserve">1.58860850334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55667662620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54869389533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5367192029953</t>
+    <t xml:space="preserve">1.55667674541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54869377613068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53671932220459</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470217227936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55268526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52474474906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264268398285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801207065582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88397789001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478417634964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05960297584534</t>
+    <t xml:space="preserve">1.55268537998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5247448682785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264256477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88397812843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94784152507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05960273742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329642295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926188468933</t>
+    <t xml:space="preserve">2.20329618453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926236152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724485397339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17934775352478</t>
+    <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
     <t xml:space="preserve">2.23522806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11548352241516</t>
+    <t xml:space="preserve">2.11548399925232</t>
   </si>
   <si>
     <t xml:space="preserve">1.9877564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011437416077</t>
+    <t xml:space="preserve">1.82011425495148</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809722423553</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">1.91590988636017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86002910137177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650643825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890689849854</t>
+    <t xml:space="preserve">1.86002898216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650619983673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890677928925</t>
   </si>
   <si>
     <t xml:space="preserve">1.5925999879837</t>
@@ -1523,43 +1523,43 @@
     <t xml:space="preserve">1.72431898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62852323055267</t>
+    <t xml:space="preserve">1.62852334976196</t>
   </si>
   <si>
     <t xml:space="preserve">1.64448928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68440401554108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457456111908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66045498847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65247225761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826776981354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633589267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054038047791</t>
+    <t xml:space="preserve">1.68440389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457444190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604551076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65247213840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826788902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7163360118866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054026126862</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843807697296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61255741119385</t>
+    <t xml:space="preserve">1.61255753040314</t>
   </si>
   <si>
     <t xml:space="preserve">1.69238698482513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75625085830688</t>
+    <t xml:space="preserve">1.7562507390976</t>
   </si>
   <si>
     <t xml:space="preserve">1.76423370838165</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">1.95582461357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92389273643494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757223129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456246376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630984306335</t>
+    <t xml:space="preserve">1.92389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757235050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9145622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630972385406</t>
   </si>
   <si>
     <t xml:space="preserve">1.85679543018341</t>
@@ -1589,55 +1589,55 @@
     <t xml:space="preserve">1.84029066562653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81553363800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79077625274658</t>
+    <t xml:space="preserve">1.8155335187912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077613353729</t>
   </si>
   <si>
     <t xml:space="preserve">1.75776648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79902851581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427124977112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76601886749268</t>
+    <t xml:space="preserve">1.79902863502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427136898041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76601898670197</t>
   </si>
   <si>
     <t xml:space="preserve">1.74126136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78252375125885</t>
+    <t xml:space="preserve">1.78252387046814</t>
   </si>
   <si>
     <t xml:space="preserve">1.73300909996033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7495139837265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650409698486</t>
+    <t xml:space="preserve">1.74951386451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650421619415</t>
   </si>
   <si>
     <t xml:space="preserve">1.69999933242798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68349456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67524218559265</t>
+    <t xml:space="preserve">1.6834944486618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67524206638336</t>
   </si>
   <si>
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873742103577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825183391571</t>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825171470642</t>
   </si>
   <si>
     <t xml:space="preserve">1.69174695014954</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">1.65048480033875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63398003578186</t>
+    <t xml:space="preserve">1.63397991657257</t>
   </si>
   <si>
     <t xml:space="preserve">1.62572753429413</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">1.60922276973724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89805746078491</t>
+    <t xml:space="preserve">1.89805734157562</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582437515259</t>
@@ -1670,31 +1670,31 @@
     <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9640771150589</t>
+    <t xml:space="preserve">1.96407723426819</t>
   </si>
   <si>
     <t xml:space="preserve">1.93931972980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87329995632172</t>
+    <t xml:space="preserve">1.8733001947403</t>
   </si>
   <si>
     <t xml:space="preserve">1.88155269622803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88980531692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86504793167114</t>
+    <t xml:space="preserve">1.88980507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86504781246185</t>
   </si>
   <si>
     <t xml:space="preserve">1.92281460762024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93106710910797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359176635742</t>
+    <t xml:space="preserve">1.93106746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359128952026</t>
   </si>
   <si>
     <t xml:space="preserve">1.98883438110352</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">1.97232949733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98058199882507</t>
+    <t xml:space="preserve">1.98058187961578</t>
   </si>
   <si>
     <t xml:space="preserve">2.06310606002808</t>
@@ -1712,31 +1712,34 @@
     <t xml:space="preserve">2.19514489173889</t>
   </si>
   <si>
+    <t xml:space="preserve">2.17864036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17038798332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563012123108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566035270691</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17038774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566035270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906790733337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08502674102783</t>
+    <t xml:space="preserve">2.18715000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310883522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906766891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08502650260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.09353685379028</t>
@@ -1748,7 +1751,7 @@
     <t xml:space="preserve">2.03396463394165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0254545211792</t>
+    <t xml:space="preserve">2.02545428276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
@@ -1760,28 +1763,28 @@
     <t xml:space="preserve">1.91482031345367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93184065818787</t>
+    <t xml:space="preserve">1.93184089660645</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439253330231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0765163898468</t>
+    <t xml:space="preserve">1.98290288448334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439229488373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07651615142822</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992334842682</t>
+    <t xml:space="preserve">2.05949568748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.9914128780365</t>
@@ -1793,7 +1796,7 @@
     <t xml:space="preserve">2.01694393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10204696655273</t>
+    <t xml:space="preserve">2.10204720497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
@@ -1808,7 +1811,7 @@
     <t xml:space="preserve">2.13608837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9658819437027</t>
+    <t xml:space="preserve">1.96588206291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.94035112857819</t>
@@ -1817,25 +1820,22 @@
     <t xml:space="preserve">1.8977997303009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90630996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226891517639</t>
+    <t xml:space="preserve">1.87226855754852</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94886159896851</t>
+    <t xml:space="preserve">1.94886147975922</t>
   </si>
   <si>
     <t xml:space="preserve">2.07243394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08129072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05472111701965</t>
+    <t xml:space="preserve">2.08129048347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05472087860107</t>
   </si>
   <si>
     <t xml:space="preserve">2.04586434364319</t>
@@ -1850,49 +1850,49 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958580493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97501194477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99272525310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95729887485504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94844233989716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86873304843903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92187285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91301620006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87758982181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072915077209</t>
+    <t xml:space="preserve">1.93958568572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9750120639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99272513389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95729875564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94844222068787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86873316764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92187261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91301608085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775897026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072938919067</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615540981293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90415978431702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89530301094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82445049285889</t>
+    <t xml:space="preserve">1.96615552902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90415954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89530313014984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8244503736496</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">1.70488691329956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77131128311157</t>
+    <t xml:space="preserve">1.77131116390228</t>
   </si>
   <si>
     <t xml:space="preserve">1.815593957901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74474155902863</t>
+    <t xml:space="preserve">1.74474143981934</t>
   </si>
   <si>
     <t xml:space="preserve">1.85102021694183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84216368198395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016769886017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85987663269043</t>
+    <t xml:space="preserve">1.84216356277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016781806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85987651348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.75802636146545</t>
@@ -1940,22 +1940,22 @@
     <t xml:space="preserve">1.73588502407074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7535982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71817183494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70931529998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72702848911285</t>
+    <t xml:space="preserve">1.75359809398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71817195415497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7093151807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72702836990356</t>
   </si>
   <si>
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295221328735</t>
+    <t xml:space="preserve">1.88295209407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988086223602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142046928406</t>
+    <t xml:space="preserve">1.79988074302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142035007477</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757925510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988872528076</t>
+    <t xml:space="preserve">1.73526966571808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757913589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988884449005</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6614283323288</t>
+    <t xml:space="preserve">1.66142845153809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97525370121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833303451538</t>
+    <t xml:space="preserve">1.9752539396286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833291530609</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372606754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526168346405</t>
+    <t xml:space="preserve">1.81372594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526180267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8921822309494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910277843475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064250469208</t>
+    <t xml:space="preserve">1.89218235015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910301685333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371421337128</t>
+    <t xml:space="preserve">1.99371409416199</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>601</v>
+        <v>522</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -67832,7 +67832,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6912037037</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>5348</v>
@@ -67853,6 +67853,32 @@
         <v>726</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.5913888889</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>1321</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1468118429184</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615501880646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544274330139</t>
+    <t xml:space="preserve">1.12615478038788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12544250488281</t>
   </si>
   <si>
     <t xml:space="preserve">1.09552574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11831974983215</t>
+    <t xml:space="preserve">1.11831951141357</t>
   </si>
   <si>
     <t xml:space="preserve">1.0962381362915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09695053100586</t>
+    <t xml:space="preserve">1.09695041179657</t>
   </si>
   <si>
     <t xml:space="preserve">1.10407340526581</t>
@@ -71,226 +71,226 @@
     <t xml:space="preserve">1.08412885665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00007700920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943804800510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925997018814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666231632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925371170044</t>
+    <t xml:space="preserve">1.00007688999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943804621696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925996899604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993665933609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925347328186</t>
   </si>
   <si>
     <t xml:space="preserve">1.01004910469055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492424964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213047981262</t>
+    <t xml:space="preserve">1.01859676837921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492436885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213059902191</t>
   </si>
   <si>
     <t xml:space="preserve">1.03711688518524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02572000026703</t>
+    <t xml:space="preserve">1.02571988105774</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0207337141037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354087352753</t>
+    <t xml:space="preserve">1.02643215656281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073383331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366178035736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354146957397</t>
   </si>
   <si>
     <t xml:space="preserve">0.91602486371994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922435581684113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830664634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970160007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612462997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00435054302216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997940063476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392340183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529166698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419887065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99081689119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967789173126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717221736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01503527164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078892707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02215814590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577533245087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648736953735</t>
+    <t xml:space="preserve">0.922435462474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530968666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830843448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970159888267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612403392792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324678897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997939944267273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991528987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419827461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990816950798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967669963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227489948273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01503503322601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078904628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02215826511383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577509403229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648760795593</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076149940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00221383571625</t>
+    <t xml:space="preserve">1.00221395492554</t>
   </si>
   <si>
     <t xml:space="preserve">0.984405994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00791215896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03284299373627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01930916309357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996598720551</t>
+    <t xml:space="preserve">1.00791203975677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03284287452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01930904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996586799622</t>
   </si>
   <si>
     <t xml:space="preserve">1.09979963302612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10051202774048</t>
+    <t xml:space="preserve">1.10051190853119</t>
   </si>
   <si>
     <t xml:space="preserve">1.08484125137329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08982741832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1817147731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185346126556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968873023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15393483638763</t>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18171465396881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818082332611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185334205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968861103058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15393471717834</t>
   </si>
   <si>
     <t xml:space="preserve">1.11689496040344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09766256809235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16105782985687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15963339805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683950901031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612723350525</t>
+    <t xml:space="preserve">1.09766268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16105771064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15963315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14752411842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612711429596</t>
   </si>
   <si>
     <t xml:space="preserve">1.12900412082672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14467489719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316699028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17031788825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18100249767303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19738554954529</t>
+    <t xml:space="preserve">1.14467477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316710948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17031764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18100237846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.197385430336</t>
   </si>
   <si>
     <t xml:space="preserve">1.21091938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163153648376</t>
+    <t xml:space="preserve">1.21163165569305</t>
   </si>
   <si>
     <t xml:space="preserve">1.20593309402466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22302842140198</t>
+    <t xml:space="preserve">1.22302854061127</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089159488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596087932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23548460006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22670161724091</t>
+    <t xml:space="preserve">1.19596076011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23548471927643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22670149803162</t>
   </si>
   <si>
     <t xml:space="preserve">1.18937349319458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">1.1879096031189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16302442550659</t>
+    <t xml:space="preserve">1.1630243062973</t>
   </si>
   <si>
     <t xml:space="preserve">1.16595208644867</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">1.15570497512817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14911794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424120426178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14106678962708</t>
+    <t xml:space="preserve">1.14911770820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424132347107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1410665512085</t>
   </si>
   <si>
     <t xml:space="preserve">1.11837708950043</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">1.10154283046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520243644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545810222626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12935602664948</t>
+    <t xml:space="preserve">1.10520231723785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934687614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545798301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1293557882309</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203669548035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12716019153595</t>
+    <t xml:space="preserve">1.12716007232666</t>
   </si>
   <si>
     <t xml:space="preserve">1.07226598262787</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">1.06860637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13081979751587</t>
+    <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
     <t xml:space="preserve">1.12423241138458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15716910362244</t>
+    <t xml:space="preserve">1.15716874599457</t>
   </si>
   <si>
     <t xml:space="preserve">1.18717777729034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18205416202545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20767164230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17839479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401203632355</t>
+    <t xml:space="preserve">1.18205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20767152309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17839455604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401191711426</t>
   </si>
   <si>
     <t xml:space="preserve">1.18351805210114</t>
@@ -392,25 +392,25 @@
     <t xml:space="preserve">1.17546689510345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1930330991745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035243034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888865947723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499073505402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21425890922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22231018543243</t>
+    <t xml:space="preserve">1.19303297996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035231113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888842105865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693957805634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21425879001617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22230994701385</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962927818298</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">1.27866792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24426770210266</t>
+    <t xml:space="preserve">1.24426782131195</t>
   </si>
   <si>
     <t xml:space="preserve">1.25890612602234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27354454994202</t>
+    <t xml:space="preserve">1.27354466915131</t>
   </si>
   <si>
     <t xml:space="preserve">1.25963795185089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26183378696442</t>
+    <t xml:space="preserve">1.26183390617371</t>
   </si>
   <si>
     <t xml:space="preserve">1.26256573200226</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">1.26915299892426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23694849014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109304904938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24719524383545</t>
+    <t xml:space="preserve">1.23694837093353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109292984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402962207794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24719548225403</t>
   </si>
   <si>
     <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21938228607178</t>
+    <t xml:space="preserve">1.21938216686249</t>
   </si>
   <si>
     <t xml:space="preserve">1.19962048530579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19669282436371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376516342163</t>
+    <t xml:space="preserve">1.19669270515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376504421234</t>
   </si>
   <si>
     <t xml:space="preserve">1.17766284942627</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">1.19742465019226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20620787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230115413666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059062957764</t>
+    <t xml:space="preserve">1.20620775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230127334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059039115906</t>
   </si>
   <si>
     <t xml:space="preserve">1.16522014141083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15643715858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16887974739075</t>
+    <t xml:space="preserve">1.15643703937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16887962818146</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693090438843</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">1.19522893428802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17985844612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1849821805954</t>
+    <t xml:space="preserve">1.17985856533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498194217682</t>
   </si>
   <si>
     <t xml:space="preserve">1.17400312423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17107558250427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16814780235291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14619016647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14326250553131</t>
+    <t xml:space="preserve">1.17107546329498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16814768314362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1461900472641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14326238632202</t>
   </si>
   <si>
     <t xml:space="preserve">1.11252164840698</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">1.13447940349579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11984097957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1132538318634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593438148499</t>
+    <t xml:space="preserve">1.11984086036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593450069427</t>
   </si>
   <si>
     <t xml:space="preserve">1.10007894039154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12276864051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032593250275</t>
+    <t xml:space="preserve">1.12276875972748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032581329346</t>
   </si>
   <si>
     <t xml:space="preserve">1.11618113517761</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">1.13960289955139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1278920173645</t>
+    <t xml:space="preserve">1.12789213657379</t>
   </si>
   <si>
     <t xml:space="preserve">1.14399433135986</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">1.14179849624634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13521122932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13813889026642</t>
+    <t xml:space="preserve">1.13521111011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13813877105713</t>
   </si>
   <si>
     <t xml:space="preserve">1.14253056049347</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">1.19449687004089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1813223361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17253935337067</t>
+    <t xml:space="preserve">1.18132245540619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17253911495209</t>
   </si>
   <si>
     <t xml:space="preserve">1.17912650108337</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">1.13887095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13374745845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569630146027</t>
+    <t xml:space="preserve">1.13374733924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569618225098</t>
   </si>
   <si>
     <t xml:space="preserve">1.11910903453827</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">1.12496435642242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1264283657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936470031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277755260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741585731506</t>
+    <t xml:space="preserve">1.12642824649811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936481952667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1527773141861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741573810577</t>
   </si>
   <si>
     <t xml:space="preserve">1.22377395629883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22596967220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25671029090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792730808258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24060809612274</t>
+    <t xml:space="preserve">1.22596955299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2567104101181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24060797691345</t>
   </si>
   <si>
     <t xml:space="preserve">1.26622533798218</t>
@@ -656,49 +656,49 @@
     <t xml:space="preserve">1.29769802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30867671966553</t>
+    <t xml:space="preserve">1.30867683887482</t>
   </si>
   <si>
     <t xml:space="preserve">1.29403841495514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32477903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404720783234</t>
+    <t xml:space="preserve">1.32477915287018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404708862305</t>
   </si>
   <si>
     <t xml:space="preserve">1.31014060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3284387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037868976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135750770569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30282139778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31526398658752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32624292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137533187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941757678986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34673666954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38699233531952</t>
+    <t xml:space="preserve">1.32843887805939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037892818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135774612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30282151699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31526410579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32624304294586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137521266937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34673690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.36869442462921</t>
@@ -710,100 +710,100 @@
     <t xml:space="preserve">1.35991132259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37454962730408</t>
+    <t xml:space="preserve">1.37454974651337</t>
   </si>
   <si>
     <t xml:space="preserve">1.40529048442841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39065206050873</t>
+    <t xml:space="preserve">1.39065229892731</t>
   </si>
   <si>
     <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114580631256</t>
+    <t xml:space="preserve">1.41114592552185</t>
   </si>
   <si>
     <t xml:space="preserve">1.38186883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37162208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845610618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927742958069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45009887218475</t>
+    <t xml:space="preserve">1.37162220478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3884562253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927754878998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45009875297546</t>
   </si>
   <si>
     <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53654813766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56361091136932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58616268634796</t>
+    <t xml:space="preserve">1.53654837608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56361079216003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58616280555725</t>
   </si>
   <si>
     <t xml:space="preserve">1.60570800304413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51700294017792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51098930835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693370819092</t>
+    <t xml:space="preserve">1.51700305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51098906993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693382740021</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866475582123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49069249629974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46814024448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964395046234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44333291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483649730682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882250785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4320570230484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43581557273865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40574622154236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836770534515</t>
+    <t xml:space="preserve">1.49069237709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46814036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964383125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44333302974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483661651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43205690383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43581569194794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40574634075165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836794376373</t>
   </si>
   <si>
     <t xml:space="preserve">1.45911955833435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45310544967651</t>
+    <t xml:space="preserve">1.47189891338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4531055688858</t>
   </si>
   <si>
     <t xml:space="preserve">1.42829835414886</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">1.42604303359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42529141902924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44408476352692</t>
+    <t xml:space="preserve">1.41702234745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42529153823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44408488273621</t>
   </si>
   <si>
     <t xml:space="preserve">1.47716116905212</t>
@@ -836,235 +836,235 @@
     <t xml:space="preserve">1.49219596385956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46663677692413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46588528156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144423007965</t>
+    <t xml:space="preserve">1.46663689613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144399166107</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843717575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850664615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948560237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347197055817</t>
+    <t xml:space="preserve">1.51850652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347220897675</t>
   </si>
   <si>
     <t xml:space="preserve">1.48167169094086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4959545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51249289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497555732727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151370048523</t>
+    <t xml:space="preserve">1.49595463275909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51249277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497543811798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151358127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.49369931221008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49896144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602398395538</t>
+    <t xml:space="preserve">1.49896156787872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602410316467</t>
   </si>
   <si>
     <t xml:space="preserve">1.496706366539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50798225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5485759973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242342472076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039544582367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941648960114</t>
+    <t xml:space="preserve">1.50798237323761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54857611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941637039185</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203809261322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903091907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51399612426758</t>
+    <t xml:space="preserve">1.52903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51399624347687</t>
   </si>
   <si>
     <t xml:space="preserve">1.55158305168152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56511425971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55609333515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126730918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
+    <t xml:space="preserve">1.56511437892914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55609321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126695156097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637121677399</t>
   </si>
   <si>
     <t xml:space="preserve">1.65682590007782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69140589237213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644068717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997201442719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381920337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937803268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735029220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6688539981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778746843338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186093330383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6883989572525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64630162715912</t>
+    <t xml:space="preserve">1.69140577316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644044876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937815189362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735017299652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67787492275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186081409454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839907646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6868953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983307361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878464698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64630150794983</t>
   </si>
   <si>
     <t xml:space="preserve">1.74402737617493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80115914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8131867647171</t>
+    <t xml:space="preserve">1.80115938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318724155426</t>
   </si>
   <si>
     <t xml:space="preserve">1.79213869571686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79965603351593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430525779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8387463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657950878143</t>
+    <t xml:space="preserve">1.79965579509735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175288677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430513858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874619007111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657938957214</t>
   </si>
   <si>
     <t xml:space="preserve">1.71245455741882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66133654117584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206910610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77560043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83423554897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80566966533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220804691315</t>
+    <t xml:space="preserve">1.66133666038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206886768341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7756005525589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83423590660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8056697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220780849457</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899258136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74102032184601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598564624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75154483318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297894954681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70193028450012</t>
+    <t xml:space="preserve">1.7410204410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598588466644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75154447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72297871112823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70193004608154</t>
   </si>
   <si>
     <t xml:space="preserve">1.69441294670105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68388831615448</t>
+    <t xml:space="preserve">1.68388867378235</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434335708618</t>
+    <t xml:space="preserve">1.66434347629547</t>
   </si>
   <si>
     <t xml:space="preserve">1.72448217868805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71846830844879</t>
+    <t xml:space="preserve">1.71846842765808</t>
   </si>
   <si>
     <t xml:space="preserve">1.75755882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73500680923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951697349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73650991916656</t>
+    <t xml:space="preserve">1.73500669002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951709270477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73651003837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395790576935</t>
@@ -1073,37 +1073,37 @@
     <t xml:space="preserve">1.78161406517029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75906193256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920111179352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82671844959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416643619537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87933993339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685727119446</t>
+    <t xml:space="preserve">1.75906240940094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920087337494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8267183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8793398141861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88685715198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.81168377399445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79664885997772</t>
+    <t xml:space="preserve">1.7966490983963</t>
   </si>
   <si>
     <t xml:space="preserve">1.77409684658051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78913164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678791999817</t>
+    <t xml:space="preserve">1.78913187980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">1.8492705821991</t>
@@ -1115,40 +1115,40 @@
     <t xml:space="preserve">1.87933969497681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865689277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797361373901</t>
+    <t xml:space="preserve">1.89468121528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486567735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399829387665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797349452972</t>
   </si>
   <si>
     <t xml:space="preserve">1.81030285358429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90235233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331513404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263197422028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660729408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291221141815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427805423737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6798996925354</t>
+    <t xml:space="preserve">1.90235221385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331525325775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263209342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660741329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291197299957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427817344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989945411682</t>
   </si>
   <si>
     <t xml:space="preserve">1.69524133205414</t>
@@ -1160,124 +1160,124 @@
     <t xml:space="preserve">1.74893665313721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65688741207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154613018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58017957210541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620413303375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250893115997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031969070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48813033103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41525793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41142249107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306869029999</t>
+    <t xml:space="preserve">1.65688765048981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154589176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5801796913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455817222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620425224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5149781703949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031945228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48813056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41525781154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4114226102829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306880950928</t>
   </si>
   <si>
     <t xml:space="preserve">1.35005640983582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.380739569664</t>
+    <t xml:space="preserve">1.38073945045471</t>
   </si>
   <si>
     <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36923336982727</t>
+    <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
     <t xml:space="preserve">1.39991641044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35772728919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35389173030853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34238576889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403196811676</t>
+    <t xml:space="preserve">1.35772716999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35389184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34238564968109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101933002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26951324939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25417184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24650084972382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25800716876984</t>
+    <t xml:space="preserve">1.26951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25417160987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24650096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25800704956055</t>
   </si>
   <si>
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869020938873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019640922546</t>
+    <t xml:space="preserve">1.28869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019629001617</t>
   </si>
   <si>
     <t xml:space="preserve">1.29252552986145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31937325000763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786728858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087956905365</t>
+    <t xml:space="preserve">1.31937336921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786716938019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087944984436</t>
   </si>
   <si>
     <t xml:space="preserve">1.33855020999908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33471477031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31553781032562</t>
+    <t xml:space="preserve">1.33471488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3155380487442</t>
   </si>
   <si>
     <t xml:space="preserve">1.39608108997345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38457489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40375196933746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36156272888184</t>
+    <t xml:space="preserve">1.38457477092743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40375173091888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36156260967255</t>
   </si>
   <si>
     <t xml:space="preserve">1.36539793014526</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">1.37690412998199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38841032981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34622097015381</t>
+    <t xml:space="preserve">1.38841021060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34622085094452</t>
   </si>
   <si>
     <t xml:space="preserve">1.32704412937164</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">1.27334856987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32320892810822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706029415131</t>
+    <t xml:space="preserve">1.32320868968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706017494202</t>
   </si>
   <si>
     <t xml:space="preserve">1.3890346288681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36109435558319</t>
+    <t xml:space="preserve">1.3610942363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916235923767</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">1.35311126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3451281785965</t>
+    <t xml:space="preserve">1.34512829780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.36508584022522</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">1.39701759815216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41298353672028</t>
+    <t xml:space="preserve">1.41298341751099</t>
   </si>
   <si>
     <t xml:space="preserve">1.40100884437561</t>
@@ -1340,55 +1340,55 @@
     <t xml:space="preserve">1.41697490215302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46886432170868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4968044757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877892971039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51277029514313</t>
+    <t xml:space="preserve">1.46886420249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49680459499359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877904891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51277053356171</t>
   </si>
   <si>
     <t xml:space="preserve">1.49281311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46487271785736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50079607963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44491517543793</t>
+    <t xml:space="preserve">1.46487259864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50079596042633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44491529464722</t>
   </si>
   <si>
     <t xml:space="preserve">1.45289838314056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43693244457245</t>
+    <t xml:space="preserve">1.43693232536316</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495787143707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42096650600433</t>
+    <t xml:space="preserve">1.42096638679504</t>
   </si>
   <si>
     <t xml:space="preserve">1.40500056743622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39302623271942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4289493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907720565796</t>
+    <t xml:space="preserve">1.39302599430084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504302501678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894947528839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907732486725</t>
   </si>
   <si>
     <t xml:space="preserve">1.35710287094116</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">1.3491199016571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4848301410675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47684717178345</t>
+    <t xml:space="preserve">1.48483002185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47684729099274</t>
   </si>
   <si>
     <t xml:space="preserve">1.46088123321533</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">1.48882162570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52075350284576</t>
+    <t xml:space="preserve">1.52075338363647</t>
   </si>
   <si>
     <t xml:space="preserve">1.51676189899445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56066823005676</t>
+    <t xml:space="preserve">1.56066834926605</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659159183502</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">1.56465971469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54071068763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53272783756256</t>
+    <t xml:space="preserve">1.54071080684662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53272771835327</t>
   </si>
   <si>
     <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58860850334167</t>
+    <t xml:space="preserve">1.58860862255096</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470229148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55268537998199</t>
+    <t xml:space="preserve">1.54470217227936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55268514156342</t>
   </si>
   <si>
     <t xml:space="preserve">1.52474498748779</t>
@@ -1460,28 +1460,28 @@
     <t xml:space="preserve">1.67642092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801195144653</t>
+    <t xml:space="preserve">1.8680123090744</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397800922394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9478417634964</t>
+    <t xml:space="preserve">1.94784164428711</t>
   </si>
   <si>
     <t xml:space="preserve">2.15539860725403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05960273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16338133811951</t>
+    <t xml:space="preserve">2.05960321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
     <t xml:space="preserve">2.20329642295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926236152649</t>
+    <t xml:space="preserve">2.21926188468933</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
@@ -1490,103 +1490,103 @@
     <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2352283000946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11548376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98775637149811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82011461257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91591000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002922058105</t>
+    <t xml:space="preserve">2.23522806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11548352241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9877564907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82011425495148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91590988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002886295319</t>
   </si>
   <si>
     <t xml:space="preserve">1.63650631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59259986877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72431886196136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62852334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68440389633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457444190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66045522689819</t>
+    <t xml:space="preserve">1.44890677928925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5925999879837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72431910037994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62852323055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64448916912079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68440401554108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6045743227005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604551076889</t>
   </si>
   <si>
     <t xml:space="preserve">1.65247213840485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74826765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633577346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054026126862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843819618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61255753040314</t>
+    <t xml:space="preserve">1.74826741218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7163360118866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054049968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843807697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61255729198456</t>
   </si>
   <si>
     <t xml:space="preserve">1.69238698482513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75625085830688</t>
+    <t xml:space="preserve">1.7562507390976</t>
   </si>
   <si>
     <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792679786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582461357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92389285564423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757223129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456246376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630972385406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679543018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84029066562653</t>
+    <t xml:space="preserve">1.90792691707611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582437515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389261722565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757211208344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456234455109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679531097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84029054641724</t>
   </si>
   <si>
     <t xml:space="preserve">1.81553339958191</t>
@@ -1595,46 +1595,46 @@
     <t xml:space="preserve">1.790776014328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75776660442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902851581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427113056183</t>
+    <t xml:space="preserve">1.75776648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902863502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427136898041</t>
   </si>
   <si>
     <t xml:space="preserve">1.76601886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74126136302948</t>
+    <t xml:space="preserve">1.74126148223877</t>
   </si>
   <si>
     <t xml:space="preserve">1.78252387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73300909996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7495139837265</t>
+    <t xml:space="preserve">1.73300898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74951386451721</t>
   </si>
   <si>
     <t xml:space="preserve">1.71650421619415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69999945163727</t>
+    <t xml:space="preserve">1.69999933242798</t>
   </si>
   <si>
     <t xml:space="preserve">1.6834944486618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67524206638336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66698980331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873730182648</t>
+    <t xml:space="preserve">1.67524218559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66698956489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873718261719</t>
   </si>
   <si>
     <t xml:space="preserve">1.70825171470642</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">1.69174695014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72475671768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048480033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398015499115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
+    <t xml:space="preserve">1.7247565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048491954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398003578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572765350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.62985384464264</t>
@@ -1661,55 +1661,52 @@
     <t xml:space="preserve">1.60922276973724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89805746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582437515259</t>
+    <t xml:space="preserve">1.8980575799942</t>
   </si>
   <si>
     <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96407699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9393196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8733001947403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155293464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88980519771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86504781246185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92281496524811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106710910797</t>
+    <t xml:space="preserve">1.96407723426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931949138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330007553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88980507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92281460762024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106746673584</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359152793884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883450031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232937812805</t>
+    <t xml:space="preserve">1.98883414268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232949733734</t>
   </si>
   <si>
     <t xml:space="preserve">1.98058187961578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06310629844666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19514465332031</t>
+    <t xml:space="preserve">2.06310606002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19514489173889</t>
   </si>
   <si>
     <t xml:space="preserve">2.17864036560059</t>
@@ -1718,10 +1715,10 @@
     <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16213488578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563035964966</t>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563012123108</t>
   </si>
   <si>
     <t xml:space="preserve">2.19566059112549</t>
@@ -1739,7 +1736,7 @@
     <t xml:space="preserve">2.11906766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08502650260925</t>
+    <t xml:space="preserve">2.08502626419067</t>
   </si>
   <si>
     <t xml:space="preserve">2.09353685379028</t>
@@ -1748,55 +1745,55 @@
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396463394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02545428276062</t>
+    <t xml:space="preserve">2.03396487236023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254545211792</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05098533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482031345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184101581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95737183094025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98290276527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651615142822</t>
+    <t xml:space="preserve">2.05098509788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184065818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95737171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98290264606476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439229488373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0765163898468</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949568748474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992334842682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99141299724579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843358039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01694393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204720497131</t>
+    <t xml:space="preserve">2.05949544906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99141311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843381881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01694369316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204696655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
@@ -1811,25 +1808,28 @@
     <t xml:space="preserve">2.13608837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96588218212128</t>
+    <t xml:space="preserve">1.96588206291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.94035112857819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226855754852</t>
+    <t xml:space="preserve">1.89779961109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87226867675781</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94886159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07243394851685</t>
+    <t xml:space="preserve">1.94886147975922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07243418693542</t>
   </si>
   <si>
     <t xml:space="preserve">2.08129048347473</t>
@@ -1850,55 +1850,55 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9750120639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99272513389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95729875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94844222068787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86873316764832</t>
+    <t xml:space="preserve">1.93958556652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97501194477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99272501468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95729887485504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94844233989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8687332868576</t>
   </si>
   <si>
     <t xml:space="preserve">1.92187261581421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91301608085632</t>
+    <t xml:space="preserve">1.9130163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775897026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93072938919067</t>
+    <t xml:space="preserve">1.93072926998138</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90415954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89530313014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8244503736496</t>
+    <t xml:space="preserve">1.96615540981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90415966510773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89530301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82445049285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673730373383</t>
+    <t xml:space="preserve">1.80673742294312</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
@@ -1910,52 +1910,52 @@
     <t xml:space="preserve">1.70488691329956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77131116390228</t>
+    <t xml:space="preserve">1.77131128311157</t>
   </si>
   <si>
     <t xml:space="preserve">1.815593957901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74474143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85102021694183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016781806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85987651348114</t>
+    <t xml:space="preserve">1.74474155902863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85102009773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84216368198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016769886017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85987663269043</t>
   </si>
   <si>
     <t xml:space="preserve">1.75802636146545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7624546289444</t>
+    <t xml:space="preserve">1.76245474815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75359809398651</t>
+    <t xml:space="preserve">1.7535982131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.71817195415497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7093151807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72702836990356</t>
+    <t xml:space="preserve">1.70931529998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72702848911285</t>
   </si>
   <si>
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295209407806</t>
+    <t xml:space="preserve">1.88295221328735</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988074302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142035007477</t>
+    <t xml:space="preserve">1.79988086223602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142046928406</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526966571808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988884449005</t>
+    <t xml:space="preserve">1.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757925510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66142845153809</t>
+    <t xml:space="preserve">1.6614283323288</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9752539396286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833291530609</t>
+    <t xml:space="preserve">1.97525370121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833303451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526180267334</t>
+    <t xml:space="preserve">1.81372606754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526168346405</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89218235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910301685333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064262390137</t>
+    <t xml:space="preserve">1.8921822309494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910277843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064250469208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371409416199</t>
+    <t xml:space="preserve">1.99371421337128</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -35116,7 +35116,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35142,7 +35142,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1256" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35220,7 +35220,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35272,7 +35272,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35298,7 +35298,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1260" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35376,7 +35376,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35402,7 +35402,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35428,7 +35428,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35454,7 +35454,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35480,7 +35480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35506,7 +35506,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1268" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35532,7 +35532,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1269" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35558,7 +35558,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1270" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35584,7 +35584,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1271" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35610,7 +35610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35636,7 +35636,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35662,7 +35662,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1274" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35688,7 +35688,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35740,7 +35740,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1277" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35948,7 +35948,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35974,7 +35974,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1286" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36000,7 +36000,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1287" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36026,7 +36026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1288" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36052,7 +36052,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36078,7 +36078,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36156,7 +36156,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36208,7 +36208,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36260,7 +36260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36312,7 +36312,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36338,7 +36338,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36468,7 +36468,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36572,7 +36572,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36754,7 +36754,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36780,7 +36780,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36806,7 +36806,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36832,7 +36832,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36858,7 +36858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1320" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36884,7 +36884,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1321" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36910,7 +36910,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1322" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37014,7 +37014,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1326" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37040,7 +37040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37066,7 +37066,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1328" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37092,7 +37092,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37118,7 +37118,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1330" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37144,7 +37144,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1331" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37170,7 +37170,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37196,7 +37196,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37300,7 +37300,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37326,7 +37326,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37508,7 +37508,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37586,7 +37586,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37638,7 +37638,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1350" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37794,7 +37794,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1356" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37846,7 +37846,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1358" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37872,7 +37872,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1359" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37898,7 +37898,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1360" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37924,7 +37924,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1361" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37976,7 +37976,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1363" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38028,7 +38028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1365" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38080,7 +38080,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1367" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38106,7 +38106,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1368" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38184,7 +38184,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38210,7 +38210,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1372" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38236,7 +38236,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38262,7 +38262,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1374" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38288,7 +38288,7 @@
         <v>2.5</v>
       </c>
       <c r="G1375" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38314,7 +38314,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38340,7 +38340,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1377" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38366,7 +38366,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38392,7 +38392,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38418,7 +38418,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38444,7 +38444,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1381" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38470,7 +38470,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1382" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38496,7 +38496,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1383" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38522,7 +38522,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1384" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38548,7 +38548,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38574,7 +38574,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38600,7 +38600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1387" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38626,7 +38626,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1388" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38652,7 +38652,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1389" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38756,7 +38756,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>522</v>
+        <v>601</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -68040,7 +68040,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.531099537</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>1000</v>
@@ -68061,6 +68061,32 @@
         <v>726</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.4519560185</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>1930</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544274330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552562236786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831963062286</t>
+    <t xml:space="preserve">1.12615478038788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12544286251068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831974983215</t>
   </si>
   <si>
     <t xml:space="preserve">1.0962381362915</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">1.10407340526581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09053981304169</t>
+    <t xml:space="preserve">1.09053957462311</t>
   </si>
   <si>
     <t xml:space="preserve">1.08412873744965</t>
@@ -74,124 +74,124 @@
     <t xml:space="preserve">1.00007677078247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943804800510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925996959209442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925371170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01004922389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492413043976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213059902191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711664676666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02571988105774</t>
+    <t xml:space="preserve">0.943804681301117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925997018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993666291236877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925359249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01004898548126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859676837921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492424964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213047981262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711676597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02571976184845</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0207337141037</t>
+    <t xml:space="preserve">1.02643191814423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073383331299</t>
   </si>
   <si>
     <t xml:space="preserve">0.947366237640381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900354087352753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530909061432</t>
+    <t xml:space="preserve">0.900354027748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91602486371994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530968666077</t>
   </si>
   <si>
     <t xml:space="preserve">0.985830783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970159888267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612403392792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324440479279</t>
+    <t xml:space="preserve">0.970160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612224578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324559688568</t>
   </si>
   <si>
     <t xml:space="preserve">1.00435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997939884662628</t>
+    <t xml:space="preserve">0.997939765453339</t>
   </si>
   <si>
     <t xml:space="preserve">0.989392459392548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991528987884521</t>
+    <t xml:space="preserve">0.991529047489166</t>
   </si>
   <si>
     <t xml:space="preserve">0.979419946670532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990816712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967610359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227549552917</t>
+    <t xml:space="preserve">0.9908167719841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967669963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227668762207</t>
   </si>
   <si>
     <t xml:space="preserve">1.01717221736908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01503527164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078892707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02215826511383</t>
+    <t xml:space="preserve">1.0150351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078904628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02215814590454</t>
   </si>
   <si>
     <t xml:space="preserve">1.00577533245087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00648748874664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076114177704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00221383571625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984406054019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00791227817535</t>
+    <t xml:space="preserve">1.00648760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076138019562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00221359729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984406173229218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00791203975677</t>
   </si>
   <si>
     <t xml:space="preserve">1.03284275531769</t>
@@ -200,37 +200,37 @@
     <t xml:space="preserve">1.01930904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996598720551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979963302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10051190853119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484101295471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982729911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18171465396881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16818082332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185322284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968849182129</t>
+    <t xml:space="preserve">1.03996610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979951381683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1005117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084841132164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1817147731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1681809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185346126556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968873023987</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393483638763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689496040344</t>
+    <t xml:space="preserve">1.11689507961273</t>
   </si>
   <si>
     <t xml:space="preserve">1.09766268730164</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">1.15963327884674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14752399921417</t>
+    <t xml:space="preserve">1.14752411842346</t>
   </si>
   <si>
     <t xml:space="preserve">1.13683950901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612711429596</t>
+    <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
     <t xml:space="preserve">1.12900412082672</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">1.1703177690506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18100249767303</t>
+    <t xml:space="preserve">1.18100237846375</t>
   </si>
   <si>
     <t xml:space="preserve">1.197385430336</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">1.2109192609787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163153648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20593297481537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22089147567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19596076011658</t>
+    <t xml:space="preserve">1.21163129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20593309402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302854061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2208913564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19596099853516</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548436164856</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">1.22670149803162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18937349319458</t>
+    <t xml:space="preserve">1.18937337398529</t>
   </si>
   <si>
     <t xml:space="preserve">1.1879096031189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1630243062973</t>
+    <t xml:space="preserve">1.16302442550659</t>
   </si>
   <si>
     <t xml:space="preserve">1.16595208644867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16229236125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16375613212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570509433746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911782741547</t>
+    <t xml:space="preserve">1.16229248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16375625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570497512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911794662476</t>
   </si>
   <si>
     <t xml:space="preserve">1.15424120426178</t>
@@ -329,61 +329,61 @@
     <t xml:space="preserve">1.10154283046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520231723785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934711456299</t>
+    <t xml:space="preserve">1.10520243644714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0993469953537</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12935590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12203669548035</t>
+    <t xml:space="preserve">1.1293557882309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12203657627106</t>
   </si>
   <si>
     <t xml:space="preserve">1.12716007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07226598262787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13081967830658</t>
+    <t xml:space="preserve">1.07226610183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860649585724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">1.12423241138458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15716898441315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18717789649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205404281616</t>
+    <t xml:space="preserve">1.15716886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18717765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767140388489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839467525482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401203632355</t>
+    <t xml:space="preserve">1.17839455604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401191711426</t>
   </si>
   <si>
     <t xml:space="preserve">1.18351817131042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2047438621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17473495006561</t>
+    <t xml:space="preserve">1.20474374294281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1747350692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.18571388721466</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">1.21499085426331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20693969726562</t>
+    <t xml:space="preserve">1.20693957805634</t>
   </si>
   <si>
     <t xml:space="preserve">1.21425890922546</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">1.22962927818298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23328876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22450590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524628162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232765197754</t>
+    <t xml:space="preserve">1.2332888841629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22450578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524640083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232753276825</t>
   </si>
   <si>
     <t xml:space="preserve">1.31745982170105</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">1.30208957195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29550218582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184257984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866816520691</t>
+    <t xml:space="preserve">1.29550230503082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2918426990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890600681305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354454994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963795185089</t>
+    <t xml:space="preserve">1.25890612602234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354443073273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2596378326416</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26256585121155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26915287971497</t>
+    <t xml:space="preserve">1.26256573200226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26915299892426</t>
   </si>
   <si>
     <t xml:space="preserve">1.23694849014282</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">1.23109304904938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26402938365936</t>
+    <t xml:space="preserve">1.26402950286865</t>
   </si>
   <si>
     <t xml:space="preserve">1.24719548225403</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">1.22304201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21938240528107</t>
+    <t xml:space="preserve">1.21938252449036</t>
   </si>
   <si>
     <t xml:space="preserve">1.1996203660965</t>
@@ -488,34 +488,34 @@
     <t xml:space="preserve">1.19669270515442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19376492500305</t>
+    <t xml:space="preserve">1.19376504421234</t>
   </si>
   <si>
     <t xml:space="preserve">1.17766273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19742465019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20620763301849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230127334595</t>
+    <t xml:space="preserve">1.19742453098297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20620775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230115413666</t>
   </si>
   <si>
     <t xml:space="preserve">1.18059051036835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16521990299225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15643715858459</t>
+    <t xml:space="preserve">1.16522002220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15643727779388</t>
   </si>
   <si>
     <t xml:space="preserve">1.16887962818146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693090438843</t>
+    <t xml:space="preserve">1.17693078517914</t>
   </si>
   <si>
     <t xml:space="preserve">1.19522893428802</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">1.18498194217682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17400300502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107534408569</t>
+    <t xml:space="preserve">1.17400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107546329498</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814780235291</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">1.1125214099884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13447940349579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325371265411</t>
+    <t xml:space="preserve">1.1344792842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984074115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
   </si>
   <si>
     <t xml:space="preserve">1.10593438148499</t>
@@ -560,34 +560,34 @@
     <t xml:space="preserve">1.10007905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12276864051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032593250275</t>
+    <t xml:space="preserve">1.12276840209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032581329346</t>
   </si>
   <si>
     <t xml:space="preserve">1.1161812543869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13960289955139</t>
+    <t xml:space="preserve">1.1396027803421</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14399433135986</t>
+    <t xml:space="preserve">1.14399445056915</t>
   </si>
   <si>
     <t xml:space="preserve">1.14179861545563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13521122932434</t>
+    <t xml:space="preserve">1.13521111011505</t>
   </si>
   <si>
     <t xml:space="preserve">1.13813889026642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14253044128418</t>
+    <t xml:space="preserve">1.14253056049347</t>
   </si>
   <si>
     <t xml:space="preserve">1.19449698925018</t>
@@ -599,55 +599,55 @@
     <t xml:space="preserve">1.17253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17912650108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887095451355</t>
+    <t xml:space="preserve">1.17912662029266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887083530426</t>
   </si>
   <si>
     <t xml:space="preserve">1.13374757766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12350034713745</t>
+    <t xml:space="preserve">1.12350046634674</t>
   </si>
   <si>
     <t xml:space="preserve">1.12569630146027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11910903453827</t>
+    <t xml:space="preserve">1.11910891532898</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12642812728882</t>
+    <t xml:space="preserve">1.12642824649811</t>
   </si>
   <si>
     <t xml:space="preserve">1.15936458110809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15277755260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741597652435</t>
+    <t xml:space="preserve">1.15277767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741585731506</t>
   </si>
   <si>
     <t xml:space="preserve">1.22377383708954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22596967220306</t>
+    <t xml:space="preserve">1.22596955299377</t>
   </si>
   <si>
     <t xml:space="preserve">1.2567104101181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24792730808258</t>
+    <t xml:space="preserve">1.24792742729187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060809612274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26622521877289</t>
+    <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
     <t xml:space="preserve">1.2684211730957</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">1.29769802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30867683887482</t>
+    <t xml:space="preserve">1.30867671966553</t>
   </si>
   <si>
     <t xml:space="preserve">1.29403829574585</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">1.3284387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29037857055664</t>
+    <t xml:space="preserve">1.29037868976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135774612427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30282127857208</t>
+    <t xml:space="preserve">1.30282139778137</t>
   </si>
   <si>
     <t xml:space="preserve">1.31526410579681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32624292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137533187866</t>
+    <t xml:space="preserve">1.32624304294586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137521266937</t>
   </si>
   <si>
     <t xml:space="preserve">1.33941745758057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34673678874969</t>
+    <t xml:space="preserve">1.34673666954041</t>
   </si>
   <si>
     <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36869442462921</t>
+    <t xml:space="preserve">1.36869466304779</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772439956665</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">1.35991132259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37454974651337</t>
+    <t xml:space="preserve">1.37454986572266</t>
   </si>
   <si>
     <t xml:space="preserve">1.40529048442841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39065194129944</t>
+    <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
     <t xml:space="preserve">1.39650762081146</t>
@@ -725,40 +725,40 @@
     <t xml:space="preserve">1.41114592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38186895847321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.371621966362</t>
+    <t xml:space="preserve">1.3818690776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162208557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884562253952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41927742958069</t>
+    <t xml:space="preserve">1.41927754878998</t>
   </si>
   <si>
     <t xml:space="preserve">1.45009875297546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50046503543854</t>
+    <t xml:space="preserve">1.50046515464783</t>
   </si>
   <si>
     <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56361067295074</t>
+    <t xml:space="preserve">1.56361079216003</t>
   </si>
   <si>
     <t xml:space="preserve">1.58616280555725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60570812225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5170031785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51098942756653</t>
+    <t xml:space="preserve">1.60570800304413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51700294017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51098930835724</t>
   </si>
   <si>
     <t xml:space="preserve">1.48693382740021</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814024448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964383125305</t>
+    <t xml:space="preserve">1.46814012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964371204376</t>
   </si>
   <si>
     <t xml:space="preserve">1.44333302974701</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">1.43882274627686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4320570230484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43581569194794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40574622154236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836794376373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45911943912506</t>
+    <t xml:space="preserve">1.43205690383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43581557273865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40574645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836782455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45911931991577</t>
   </si>
   <si>
     <t xml:space="preserve">1.47189903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4531055688858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42829823493958</t>
+    <t xml:space="preserve">1.45310544967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
     <t xml:space="preserve">1.41852569580078</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">1.42604303359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702222824097</t>
+    <t xml:space="preserve">1.41702234745026</t>
   </si>
   <si>
     <t xml:space="preserve">1.42529141902924</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">1.44408488273621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47716104984283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219584465027</t>
+    <t xml:space="preserve">1.47716128826141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219596385956</t>
   </si>
   <si>
     <t xml:space="preserve">1.46663677692413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46588504314423</t>
+    <t xml:space="preserve">1.46588516235352</t>
   </si>
   <si>
     <t xml:space="preserve">1.49144399166107</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">1.48843717575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850664615631</t>
+    <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
     <t xml:space="preserve">1.50948572158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50347197055817</t>
+    <t xml:space="preserve">1.50347208976746</t>
   </si>
   <si>
     <t xml:space="preserve">1.48167169094086</t>
@@ -869,34 +869,34 @@
     <t xml:space="preserve">1.50497555732727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52151358127594</t>
+    <t xml:space="preserve">1.52151370048523</t>
   </si>
   <si>
     <t xml:space="preserve">1.49369943141937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49896168708801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602398395538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49670624732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5079824924469</t>
+    <t xml:space="preserve">1.49896156787872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602410316467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.496706366539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798225402832</t>
   </si>
   <si>
     <t xml:space="preserve">1.5485759973526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48242318630219</t>
+    <t xml:space="preserve">1.48242342472076</t>
   </si>
   <si>
     <t xml:space="preserve">1.47039556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47941648960114</t>
+    <t xml:space="preserve">1.47941660881042</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203809261322</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">1.67637121677399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65682590007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69140601158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644056797028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997201442719</t>
+    <t xml:space="preserve">1.65682601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69140589237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644068717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997213363647</t>
   </si>
   <si>
     <t xml:space="preserve">1.65381920337677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67937803268433</t>
+    <t xml:space="preserve">1.67937791347504</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735029220581</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">1.66885387897491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67787480354309</t>
+    <t xml:space="preserve">1.6778746843338</t>
   </si>
   <si>
     <t xml:space="preserve">1.67035710811615</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">1.67186105251312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6883989572525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689560890198</t>
+    <t xml:space="preserve">1.68839883804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68689548969269</t>
   </si>
   <si>
     <t xml:space="preserve">1.65983307361603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63878440856934</t>
+    <t xml:space="preserve">1.63878464698792</t>
   </si>
   <si>
     <t xml:space="preserve">1.64630174636841</t>
@@ -977,46 +977,46 @@
     <t xml:space="preserve">1.80115938186646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81318700313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213869571686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965579509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175312519073</t>
+    <t xml:space="preserve">1.81318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213881492615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965567588806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175300598145</t>
   </si>
   <si>
     <t xml:space="preserve">1.86430513858795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8387463092804</t>
+    <t xml:space="preserve">1.83874619007111</t>
   </si>
   <si>
     <t xml:space="preserve">1.76657950878143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7124547958374</t>
+    <t xml:space="preserve">1.71245467662811</t>
   </si>
   <si>
     <t xml:space="preserve">1.66133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76206922531128</t>
+    <t xml:space="preserve">1.76206910610199</t>
   </si>
   <si>
     <t xml:space="preserve">1.77560031414032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83423554897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8056697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220792770386</t>
+    <t xml:space="preserve">1.83423566818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220780849457</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899270057678</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">1.7410204410553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72598564624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.751544713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297894954681</t>
+    <t xml:space="preserve">1.72598576545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75154483318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
     <t xml:space="preserve">1.70193016529083</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">1.69441282749176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68388855457306</t>
+    <t xml:space="preserve">1.68388843536377</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">1.66434347629547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72448229789734</t>
+    <t xml:space="preserve">1.72448217868805</t>
   </si>
   <si>
     <t xml:space="preserve">1.71846854686737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75755858421326</t>
+    <t xml:space="preserve">1.75755870342255</t>
   </si>
   <si>
     <t xml:space="preserve">1.73500669002533</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">1.73951697349548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73651003837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71395802497864</t>
+    <t xml:space="preserve">1.73651015758514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71395790576935</t>
   </si>
   <si>
     <t xml:space="preserve">1.78161418437958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75906205177307</t>
+    <t xml:space="preserve">1.75906193256378</t>
   </si>
   <si>
     <t xml:space="preserve">1.81920099258423</t>
@@ -1082,34 +1082,34 @@
     <t xml:space="preserve">1.8267183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416631698608</t>
+    <t xml:space="preserve">1.80416619777679</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685750961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168353557587</t>
+    <t xml:space="preserve">1.88685762882233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168377399445</t>
   </si>
   <si>
     <t xml:space="preserve">1.7966490983963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77409684658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678803920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701069355011</t>
+    <t xml:space="preserve">1.77409696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913176059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678815841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927070140839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870108127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.89468145370483</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">1.8486567735672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86399829387665</t>
+    <t xml:space="preserve">1.86399841308594</t>
   </si>
   <si>
     <t xml:space="preserve">1.81797361373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.810302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235221385956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331525325775</t>
+    <t xml:space="preserve">1.81030285358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331513404846</t>
   </si>
   <si>
     <t xml:space="preserve">1.80263209342957</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">1.75660729408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70291221141815</t>
+    <t xml:space="preserve">1.70291209220886</t>
   </si>
   <si>
     <t xml:space="preserve">1.76427829265594</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">1.6798996925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69524133205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222905158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74893641471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688741207123</t>
+    <t xml:space="preserve">1.69524121284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222893238068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74893653392792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688753128052</t>
   </si>
   <si>
     <t xml:space="preserve">1.64154601097107</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">1.66455817222595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62620425224304</t>
+    <t xml:space="preserve">1.62620437145233</t>
   </si>
   <si>
     <t xml:space="preserve">1.57250893115997</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">1.51497805118561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53031957149506</t>
+    <t xml:space="preserve">1.53031969070435</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813033103943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4152580499649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41142272949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306880950928</t>
+    <t xml:space="preserve">1.41525793075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4114226102829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
     <t xml:space="preserve">1.35005629062653</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">1.380739569664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39224576950073</t>
+    <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923336982727</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">1.39991641044617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35772716999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35389173030853</t>
+    <t xml:space="preserve">1.35772728919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35389184951782</t>
   </si>
   <si>
     <t xml:space="preserve">1.34238564968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30403172969818</t>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101944923401</t>
@@ -1247,34 +1247,34 @@
     <t xml:space="preserve">1.29252552986145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31937336921692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786728858948</t>
+    <t xml:space="preserve">1.31937325000763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786716938019</t>
   </si>
   <si>
     <t xml:space="preserve">1.33087944984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33855009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471488952637</t>
+    <t xml:space="preserve">1.33855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471477031708</t>
   </si>
   <si>
     <t xml:space="preserve">1.31553781032562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39608108997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
+    <t xml:space="preserve">1.39608097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457465171814</t>
   </si>
   <si>
     <t xml:space="preserve">1.40375185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36156260967255</t>
+    <t xml:space="preserve">1.36156249046326</t>
   </si>
   <si>
     <t xml:space="preserve">1.36539781093597</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">1.43443489074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37690401077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38841021060944</t>
+    <t xml:space="preserve">1.37690412998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38841009140015</t>
   </si>
   <si>
     <t xml:space="preserve">1.34622097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32704389095306</t>
+    <t xml:space="preserve">1.32704401016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.27334868907928</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">1.32320880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37706005573273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38903450965881</t>
+    <t xml:space="preserve">1.37706017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38903474807739</t>
   </si>
   <si>
     <t xml:space="preserve">1.36109435558319</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.32916235923767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311126708984</t>
+    <t xml:space="preserve">1.35311138629913</t>
   </si>
   <si>
     <t xml:space="preserve">1.3451281785965</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">1.41298341751099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4010089635849</t>
+    <t xml:space="preserve">1.40100908279419</t>
   </si>
   <si>
     <t xml:space="preserve">1.40899205207825</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">1.46886420249939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4968044757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877892971039</t>
+    <t xml:space="preserve">1.49680459499359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877904891968</t>
   </si>
   <si>
     <t xml:space="preserve">1.51277041435242</t>
@@ -1355,31 +1355,31 @@
     <t xml:space="preserve">1.46487271785736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50079607963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44491529464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45289838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495787143707</t>
+    <t xml:space="preserve">1.50079596042633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44491517543793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45289826393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693244457245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495799064636</t>
   </si>
   <si>
     <t xml:space="preserve">1.42096638679504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40500044822693</t>
+    <t xml:space="preserve">1.40500056743622</t>
   </si>
   <si>
     <t xml:space="preserve">1.39302611351013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38504326343536</t>
+    <t xml:space="preserve">1.38504314422607</t>
   </si>
   <si>
     <t xml:space="preserve">1.42894947528839</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">1.35710287094116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34912002086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48483002185822</t>
+    <t xml:space="preserve">1.3491199016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4848301410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.47684705257416</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">1.46088123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48882174491882</t>
+    <t xml:space="preserve">1.48882162570953</t>
   </si>
   <si>
     <t xml:space="preserve">1.52075326442719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51676189899445</t>
+    <t xml:space="preserve">1.51676177978516</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659159183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56465971469879</t>
+    <t xml:space="preserve">1.59659147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56465983390808</t>
   </si>
   <si>
     <t xml:space="preserve">1.54071080684662</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52873635292053</t>
+    <t xml:space="preserve">1.52873647212982</t>
   </si>
   <si>
     <t xml:space="preserve">1.58860850334167</t>
@@ -1436,28 +1436,28 @@
     <t xml:space="preserve">1.55667674541473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54869401454926</t>
+    <t xml:space="preserve">1.54869389533997</t>
   </si>
   <si>
     <t xml:space="preserve">1.53671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470217227936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55268526077271</t>
+    <t xml:space="preserve">1.54470241069794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55268514156342</t>
   </si>
   <si>
     <t xml:space="preserve">1.5247448682785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264256477356</t>
+    <t xml:space="preserve">1.57264268398285</t>
   </si>
   <si>
     <t xml:space="preserve">1.67642092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801195144653</t>
+    <t xml:space="preserve">1.86801218986511</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397812843323</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">1.94784164428711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15539860725403</t>
+    <t xml:space="preserve">2.15539836883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.05960297584534</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329618453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926236152649</t>
+    <t xml:space="preserve">2.20329642295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926212310791</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23522782325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11548399925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98775625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82011425495148</t>
+    <t xml:space="preserve">2.23522806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9877564907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82011437416077</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809722423553</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.91590988636017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86002933979034</t>
+    <t xml:space="preserve">1.86002922058105</t>
   </si>
   <si>
     <t xml:space="preserve">1.63650631904602</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">1.44890677928925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59260010719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72431886196136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62852334976196</t>
+    <t xml:space="preserve">1.5925999879837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72431898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62852323055267</t>
   </si>
   <si>
     <t xml:space="preserve">1.64448916912079</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">1.60457444190979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6604551076889</t>
+    <t xml:space="preserve">1.66045498847961</t>
   </si>
   <si>
     <t xml:space="preserve">1.65247225761414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74826753139496</t>
+    <t xml:space="preserve">1.74826741218567</t>
   </si>
   <si>
     <t xml:space="preserve">1.71633589267731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62054026126862</t>
+    <t xml:space="preserve">1.62054038047791</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843807697296</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238686561584</t>
+    <t xml:space="preserve">1.69238710403442</t>
   </si>
   <si>
     <t xml:space="preserve">1.7562507390976</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">1.76423370838165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792715549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582497119904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92389285564423</t>
+    <t xml:space="preserve">1.9079270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389297485352</t>
   </si>
   <si>
     <t xml:space="preserve">1.94757223129272</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">1.79077613353729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75776660442352</t>
+    <t xml:space="preserve">1.75776648521423</t>
   </si>
   <si>
     <t xml:space="preserve">1.79902851581573</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">1.74126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78252363204956</t>
+    <t xml:space="preserve">1.78252375125885</t>
   </si>
   <si>
     <t xml:space="preserve">1.73300898075104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74951386451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
+    <t xml:space="preserve">1.7495139837265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650409698486</t>
   </si>
   <si>
     <t xml:space="preserve">1.69999933242798</t>
@@ -1631,40 +1631,40 @@
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
   </si>
   <si>
     <t xml:space="preserve">1.69174695014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72475671768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985372543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60922265052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8980575799942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582449436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660129547119</t>
+    <t xml:space="preserve">1.7247565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048480033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398015499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572765350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985384464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60922276973724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582461357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660105705261</t>
   </si>
   <si>
     <t xml:space="preserve">1.96407699584961</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">1.9393196105957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87330043315887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88980495929718</t>
+    <t xml:space="preserve">1.87330031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155281543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88980507850647</t>
   </si>
   <si>
     <t xml:space="preserve">1.86504781246185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9228150844574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106722831726</t>
+    <t xml:space="preserve">1.92281496524811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106734752655</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359152793884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883438110352</t>
+    <t xml:space="preserve">1.98883450031281</t>
   </si>
   <si>
     <t xml:space="preserve">1.97232961654663</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17038774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213512420654</t>
+    <t xml:space="preserve">2.17038750648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213488578796</t>
   </si>
   <si>
     <t xml:space="preserve">2.14563035964966</t>
@@ -68115,7 +68115,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6912037037</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>2130</v>
@@ -68136,6 +68136,32 @@
         <v>725</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6197222222</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>6656</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.12615489959717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12544250488281</t>
+    <t xml:space="preserve">1.1254426240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.09552574157715</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">1.11831951141357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09623789787292</t>
+    <t xml:space="preserve">1.09623801708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695029258728</t>
@@ -68,58 +68,58 @@
     <t xml:space="preserve">1.0905396938324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08412873744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007700920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943804800510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925997018814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666112422943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925347328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01004910469055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492413043976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213047981262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711664676666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02571976184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495191574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02643215656281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073347568512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354027748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91602486371994</t>
+    <t xml:space="preserve">1.08412885665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007677078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943804740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925996899604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993665933609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925359249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01004898548126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859676837921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492424964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213036060333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711676597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572000026703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495203495026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02643227577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073359489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366178035736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354087352753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024744510651</t>
   </si>
   <si>
     <t xml:space="preserve">0.922435462474823</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">0.939530968666077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98583060503006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612403392792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324619293213</t>
+    <t xml:space="preserve">0.985830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160126686096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324559688568</t>
   </si>
   <si>
     <t xml:space="preserve">1.00435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997940003871918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991528987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419946670532</t>
+    <t xml:space="preserve">0.997939765453339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392340183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529047489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419827461243</t>
   </si>
   <si>
     <t xml:space="preserve">0.99081689119339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987967550754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227549552917</t>
+    <t xml:space="preserve">0.987967669963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227668762207</t>
   </si>
   <si>
     <t xml:space="preserve">1.01717221736908</t>
@@ -170,121 +170,121 @@
     <t xml:space="preserve">1.01503503322601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00078892707825</t>
+    <t xml:space="preserve">1.00078904628754</t>
   </si>
   <si>
     <t xml:space="preserve">1.02215826511383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00577509403229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648748874664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076126098633</t>
+    <t xml:space="preserve">1.00577521324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076138019562</t>
   </si>
   <si>
     <t xml:space="preserve">1.00221371650696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984405994415283</t>
+    <t xml:space="preserve">0.984406173229218</t>
   </si>
   <si>
     <t xml:space="preserve">1.00791215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03284275531769</t>
+    <t xml:space="preserve">1.03284287452698</t>
   </si>
   <si>
     <t xml:space="preserve">1.01930904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996574878693</t>
+    <t xml:space="preserve">1.03996586799622</t>
   </si>
   <si>
     <t xml:space="preserve">1.09979963302612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1005117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084841132164</t>
+    <t xml:space="preserve">1.10051190853119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484125137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.08982741832733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1817147731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185334205627</t>
+    <t xml:space="preserve">1.18171489238739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818106174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185322284698</t>
   </si>
   <si>
     <t xml:space="preserve">1.13968873023987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15393459796906</t>
+    <t xml:space="preserve">1.15393495559692</t>
   </si>
   <si>
     <t xml:space="preserve">1.11689496040344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09766256809235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16105794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15963327884674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14752411842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683950901031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612711429596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12900424003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316710948944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17031788825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18100261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.197385430336</t>
+    <t xml:space="preserve">1.09766268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16105771064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15963315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612723350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12900400161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467489719391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316699028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1703177690506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18100249767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19738554954529</t>
   </si>
   <si>
     <t xml:space="preserve">1.2109192609787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163141727448</t>
+    <t xml:space="preserve">1.21163153648376</t>
   </si>
   <si>
     <t xml:space="preserve">1.20593309402466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22302854061127</t>
+    <t xml:space="preserve">1.22302842140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089147567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596099853516</t>
+    <t xml:space="preserve">1.19596076011658</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548436164856</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">1.22670149803162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18937349319458</t>
+    <t xml:space="preserve">1.18937361240387</t>
   </si>
   <si>
     <t xml:space="preserve">1.18790972232819</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">1.16302418708801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16595184803009</t>
+    <t xml:space="preserve">1.16595196723938</t>
   </si>
   <si>
     <t xml:space="preserve">1.16229236125946</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">1.16375637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15570497512817</t>
+    <t xml:space="preserve">1.15570521354675</t>
   </si>
   <si>
     <t xml:space="preserve">1.14911770820618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15424132347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1410665512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11837708950043</t>
+    <t xml:space="preserve">1.15424144268036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14106667041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11837697029114</t>
   </si>
   <si>
     <t xml:space="preserve">1.10154271125793</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">1.09934711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14545810222626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12935602664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12203657627106</t>
+    <t xml:space="preserve">1.14545822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1293557882309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12203669548035</t>
   </si>
   <si>
     <t xml:space="preserve">1.12716007232666</t>
@@ -350,103 +350,103 @@
     <t xml:space="preserve">1.07226598262787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06860637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13081955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12423253059387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15716886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18717765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205428123474</t>
+    <t xml:space="preserve">1.06860625743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13081967830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12423241138458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15716898441315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18717789649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767140388489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839479446411</t>
+    <t xml:space="preserve">1.17839455604553</t>
   </si>
   <si>
     <t xml:space="preserve">1.20401191711426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18351817131042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20474374294281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17473518848419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571388721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546701431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1930330991745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035207271576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888865947723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693957805634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21425879001617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22230982780457</t>
+    <t xml:space="preserve">1.18351805210114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20474398136139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17473530769348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546689510345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19303297996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035243034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888854026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499073505402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21425902843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22231006622314</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962915897369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23328876495361</t>
+    <t xml:space="preserve">1.2332888841629</t>
   </si>
   <si>
     <t xml:space="preserve">1.22450566291809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25524640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745994091034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208957195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550218582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2918426990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866780757904</t>
+    <t xml:space="preserve">1.25524663925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208945274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550194740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29184246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866792678833</t>
   </si>
   <si>
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890600681305</t>
+    <t xml:space="preserve">1.25890612602234</t>
   </si>
   <si>
     <t xml:space="preserve">1.27354454994202</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">1.26915287971497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23694860935211</t>
+    <t xml:space="preserve">1.23694837093353</t>
   </si>
   <si>
     <t xml:space="preserve">1.23109304904938</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">1.21938228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19962048530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669270515442</t>
+    <t xml:space="preserve">1.1996203660965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669282436371</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376504421234</t>
@@ -494,16 +494,16 @@
     <t xml:space="preserve">1.17766273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19742465019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20620763301849</t>
+    <t xml:space="preserve">1.19742476940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20620775222778</t>
   </si>
   <si>
     <t xml:space="preserve">1.19230127334595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18059051036835</t>
+    <t xml:space="preserve">1.18059039115906</t>
   </si>
   <si>
     <t xml:space="preserve">1.16522014141083</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">1.15643703937531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16887974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693078517914</t>
+    <t xml:space="preserve">1.16887962818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693090438843</t>
   </si>
   <si>
     <t xml:space="preserve">1.19522881507874</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">1.17985844612122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18498194217682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17400288581848</t>
+    <t xml:space="preserve">1.18498182296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17400300502777</t>
   </si>
   <si>
     <t xml:space="preserve">1.17107546329498</t>
@@ -536,34 +536,34 @@
     <t xml:space="preserve">1.16814768314362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14618992805481</t>
+    <t xml:space="preserve">1.1461900472641</t>
   </si>
   <si>
     <t xml:space="preserve">1.14326238632202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11252152919769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1344792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325371265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1059342622757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276840209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032605171204</t>
+    <t xml:space="preserve">1.11252164840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13447916507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984097957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593438148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007882118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12276864051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032593250275</t>
   </si>
   <si>
     <t xml:space="preserve">1.1161812543869</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14399445056915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14179849624634</t>
+    <t xml:space="preserve">1.14399433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14179861545563</t>
   </si>
   <si>
     <t xml:space="preserve">1.13521111011505</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">1.13813900947571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14253044128418</t>
+    <t xml:space="preserve">1.14253056049347</t>
   </si>
   <si>
     <t xml:space="preserve">1.19449687004089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1813223361969</t>
+    <t xml:space="preserve">1.18132245540619</t>
   </si>
   <si>
     <t xml:space="preserve">1.17253923416138</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">1.17912650108337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13887071609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13374733924866</t>
+    <t xml:space="preserve">1.13887083530426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
     <t xml:space="preserve">1.12350046634674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12569618225098</t>
+    <t xml:space="preserve">1.12569630146027</t>
   </si>
   <si>
     <t xml:space="preserve">1.11910903453827</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">1.12642812728882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15936458110809</t>
+    <t xml:space="preserve">1.15936470031738</t>
   </si>
   <si>
     <t xml:space="preserve">1.15277743339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16741573810577</t>
+    <t xml:space="preserve">1.16741585731506</t>
   </si>
   <si>
     <t xml:space="preserve">1.22377383708954</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">1.22596967220306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2567104101181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792730808258</t>
+    <t xml:space="preserve">1.25671029090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792742729187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060797691345</t>
@@ -650,43 +650,43 @@
     <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2684211730957</t>
+    <t xml:space="preserve">1.26842093467712</t>
   </si>
   <si>
     <t xml:space="preserve">1.29769802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30867683887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403817653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3101407289505</t>
+    <t xml:space="preserve">1.30867671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3247789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404696941376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014060974121</t>
   </si>
   <si>
     <t xml:space="preserve">1.3284387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29037880897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135762691498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30282139778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31526410579681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32624304294586</t>
+    <t xml:space="preserve">1.29037868976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135750770569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30282151699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3152642250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32624292373657</t>
   </si>
   <si>
     <t xml:space="preserve">1.36137521266937</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">1.3869925737381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36869442462921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772428035736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35991144180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37454962730408</t>
+    <t xml:space="preserve">1.36869418621063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772439956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35991132259369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37454986572266</t>
   </si>
   <si>
     <t xml:space="preserve">1.40529048442841</t>
@@ -719,37 +719,37 @@
     <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39650738239288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114604473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3818690776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37162220478058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845610618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927742958069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45009875297546</t>
+    <t xml:space="preserve">1.39650726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114580631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38186895847321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38845646381378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927754878998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45009863376617</t>
   </si>
   <si>
     <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53654825687408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56361067295074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58616280555725</t>
+    <t xml:space="preserve">1.53654837608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56361055374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58616268634796</t>
   </si>
   <si>
     <t xml:space="preserve">1.60570800304413</t>
@@ -761,28 +761,28 @@
     <t xml:space="preserve">1.51098942756653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48693370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866451740265</t>
+    <t xml:space="preserve">1.48693406581879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866463661194</t>
   </si>
   <si>
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814024448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964383125305</t>
+    <t xml:space="preserve">1.46814036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964406967163</t>
   </si>
   <si>
     <t xml:space="preserve">1.44333302974701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882262706757</t>
+    <t xml:space="preserve">1.4448367357254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882274627686</t>
   </si>
   <si>
     <t xml:space="preserve">1.4320570230484</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">1.40574622154236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45836794376373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45911943912506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189891338348</t>
+    <t xml:space="preserve">1.45836782455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45911967754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189903259277</t>
   </si>
   <si>
     <t xml:space="preserve">1.4531055688858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42829823493958</t>
+    <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
     <t xml:space="preserve">1.41852581501007</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">1.4207808971405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42604303359985</t>
+    <t xml:space="preserve">1.42604315280914</t>
   </si>
   <si>
     <t xml:space="preserve">1.41702222824097</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">1.47716104984283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49219596385956</t>
+    <t xml:space="preserve">1.49219584465027</t>
   </si>
   <si>
     <t xml:space="preserve">1.46663677692413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46588492393494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144399166107</t>
+    <t xml:space="preserve">1.46588528156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144411087036</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843717575073</t>
@@ -854,34 +854,34 @@
     <t xml:space="preserve">1.50948572158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50347197055817</t>
+    <t xml:space="preserve">1.50347208976746</t>
   </si>
   <si>
     <t xml:space="preserve">1.48167157173157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49595475196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51249277591705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497555732727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151358127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49369931221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49896156787872</t>
+    <t xml:space="preserve">1.4959545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51249265670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497543811798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369943141937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49896168708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602398395538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.496706366539</t>
+    <t xml:space="preserve">1.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">1.5079824924469</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">1.5485759973526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48242318630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941648960114</t>
+    <t xml:space="preserve">1.48242354393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039544582367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941637039185</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903079986572</t>
+    <t xml:space="preserve">1.52903091907501</t>
   </si>
   <si>
     <t xml:space="preserve">1.51399624347687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55158305168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511425971985</t>
+    <t xml:space="preserve">1.55158281326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511437892914</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609333515167</t>
@@ -920,70 +920,70 @@
     <t xml:space="preserve">1.63126718997955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67637145519257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682590007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69140601158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644044876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997201442719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381896495819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937827110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735029220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66885411739349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787492275238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035734653473</t>
+    <t xml:space="preserve">1.6763710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65682601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69140589237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644056797028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381920337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6673504114151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885387897491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67787480354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035698890686</t>
   </si>
   <si>
     <t xml:space="preserve">1.67186069488525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68839907646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689560890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983307361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878452777863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64630162715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74402737617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115938186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318700313568</t>
+    <t xml:space="preserve">1.68839919567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68689548969269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983295440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64630174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402749538422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115950107574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318712234497</t>
   </si>
   <si>
     <t xml:space="preserve">1.79213857650757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79965591430664</t>
+    <t xml:space="preserve">1.79965579509735</t>
   </si>
   <si>
     <t xml:space="preserve">1.84175312519073</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">1.86430513858795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8387463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657950878143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245443820953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206922531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77560019493103</t>
+    <t xml:space="preserve">1.83874619007111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133666038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206934452057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7756005525589</t>
   </si>
   <si>
     <t xml:space="preserve">1.83423578739166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80566954612732</t>
+    <t xml:space="preserve">1.8056697845459</t>
   </si>
   <si>
     <t xml:space="preserve">1.82220816612244</t>
@@ -1022,25 +1022,25 @@
     <t xml:space="preserve">1.72899270057678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74102056026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598564624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.751544713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297894954681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70193016529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441270828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388843536377</t>
+    <t xml:space="preserve">1.7410204410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598588466644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75154483318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7229790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70193028450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388855457306</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">1.66434335708618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72448229789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71846842765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500657081604</t>
+    <t xml:space="preserve">1.72448217868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846854686737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755870342255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500680923462</t>
   </si>
   <si>
     <t xml:space="preserve">1.73951697349548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73651015758514</t>
+    <t xml:space="preserve">1.73651003837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395826339722</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">1.75906217098236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81920099258423</t>
+    <t xml:space="preserve">1.81920123100281</t>
   </si>
   <si>
     <t xml:space="preserve">1.8267183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416631698608</t>
+    <t xml:space="preserve">1.80416655540466</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">1.88685703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81168377399445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409672737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678803920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8492705821991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701069355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865701198578</t>
+    <t xml:space="preserve">1.81168365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409684658051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913176059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927022457123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88701057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468133449554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865689277649</t>
   </si>
   <si>
     <t xml:space="preserve">1.86399829387665</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">1.81797385215759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.810302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235209465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331525325775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263209342957</t>
+    <t xml:space="preserve">1.81030285358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235221385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331549167633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263197422028</t>
   </si>
   <si>
     <t xml:space="preserve">1.75660753250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70291233062744</t>
+    <t xml:space="preserve">1.70291209220886</t>
   </si>
   <si>
     <t xml:space="preserve">1.76427829265594</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">1.6798996925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69524121284485</t>
+    <t xml:space="preserve">1.69524145126343</t>
   </si>
   <si>
     <t xml:space="preserve">1.67222905158997</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">1.7489367723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65688741207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154601097107</t>
+    <t xml:space="preserve">1.65688753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154589176178</t>
   </si>
   <si>
     <t xml:space="preserve">1.58017957210541</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">1.57250893115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5149781703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031957149506</t>
+    <t xml:space="preserve">1.51497805118561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031969070435</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813045024872</t>
@@ -1190,226 +1190,229 @@
     <t xml:space="preserve">1.4114226102829</t>
   </si>
   <si>
+    <t xml:space="preserve">1.37306869029999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35005640983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.380739569664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39224565029144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36923336982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39991641044617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35772716999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35389184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3423855304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28101933002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26951324939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25417172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2465010881424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25800704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29636096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019652843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252552986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937348842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786716938019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471477031708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3155380487442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39608108997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40375173091888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36156249046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443500995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37690412998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38841021060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3462210893631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704412937164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334868907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320868968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706005573273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3890346288681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3610942363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32916224002838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35311138629913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3451281785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39701759815216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41298341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40100908279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40899205207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4169750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46886420249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49680471420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877892971039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51277053356171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49281299114227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487283706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50079596042633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44491529464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45289838314056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693220615387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495787143707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096650600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500056743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39302623271942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894923686981</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.37306880950928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35005640983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.380739569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39224565029144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36923336982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39991641044617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35772716999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35389173030853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34238564968109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403172969818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28101944923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26951324939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25417184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24650096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25800704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29636096954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869020938873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019640922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252552986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937325000763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786728858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087944984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855020999908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471500873566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31553781032562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39608120918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40375173091888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36156260967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539793014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37690401077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38841021060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34622097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320868968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706017494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3890346288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36109435558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32916235923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3451281785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508584022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39701771736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41298341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4010089635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40899205207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4169750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46886420249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49680459499359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877892971039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51277053356171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49281299114227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487271785736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50079607963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44491529464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45289838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495799064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096638679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500044822693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39302611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4289493560791</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
     <t xml:space="preserve">1.35710287094116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34912002086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48483002185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47684705257416</t>
+    <t xml:space="preserve">1.3491199016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4848301410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47684717178345</t>
   </si>
   <si>
     <t xml:space="preserve">1.46088123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48882174491882</t>
+    <t xml:space="preserve">1.48882150650024</t>
   </si>
   <si>
     <t xml:space="preserve">1.52075338363647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51676189899445</t>
+    <t xml:space="preserve">1.51676177978516</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
@@ -1418,7 +1421,7 @@
     <t xml:space="preserve">1.59659159183502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56465971469879</t>
+    <t xml:space="preserve">1.56465983390808</t>
   </si>
   <si>
     <t xml:space="preserve">1.54071068763733</t>
@@ -1427,7 +1430,7 @@
     <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52873635292053</t>
+    <t xml:space="preserve">1.52873623371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.58860850334167</t>
@@ -1442,7 +1445,7 @@
     <t xml:space="preserve">1.53671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470229148865</t>
+    <t xml:space="preserve">1.54470217227936</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268526077271</t>
@@ -1451,22 +1454,22 @@
     <t xml:space="preserve">1.5247448682785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264256477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801195144653</t>
+    <t xml:space="preserve">1.57264268398285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801183223724</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397789001465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94784164428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539884567261</t>
+    <t xml:space="preserve">1.9478417634964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539836883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.05960297584534</t>
@@ -1475,7 +1478,7 @@
     <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329618453979</t>
+    <t xml:space="preserve">2.20329642295837</t>
   </si>
   <si>
     <t xml:space="preserve">2.21926212310791</t>
@@ -1496,37 +1499,37 @@
     <t xml:space="preserve">1.98775625228882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011425495148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91590988636017</t>
+    <t xml:space="preserve">1.82011413574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809746265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91591012477875</t>
   </si>
   <si>
     <t xml:space="preserve">1.86002910137177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63650631904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890677928925</t>
+    <t xml:space="preserve">1.63650619983673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890689849854</t>
   </si>
   <si>
     <t xml:space="preserve">1.59260010719299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72431886196136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62852334976196</t>
+    <t xml:space="preserve">1.72431910037994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62852323055267</t>
   </si>
   <si>
     <t xml:space="preserve">1.64448916912079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68440401554108</t>
+    <t xml:space="preserve">1.68440389633179</t>
   </si>
   <si>
     <t xml:space="preserve">1.60457456111908</t>
@@ -1538,289 +1541,286 @@
     <t xml:space="preserve">1.65247225761414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74826765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633589267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054038047791</t>
+    <t xml:space="preserve">1.74826776981354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633577346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054026126862</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843807697296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61255741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69238686561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75625050067902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76423346996307</t>
+    <t xml:space="preserve">1.61255729198456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69238698482513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625085830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76423370838165</t>
   </si>
   <si>
     <t xml:space="preserve">1.90792691707611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95582473278046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92389285564423</t>
+    <t xml:space="preserve">1.95582449436188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389273643494</t>
   </si>
   <si>
     <t xml:space="preserve">1.94757199287415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91456234455109</t>
+    <t xml:space="preserve">1.91456246376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679566860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84029042720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81553339958191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077613353729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75776648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902863502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427113056183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76601886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126136302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495139837265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650421619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69999933242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68349432945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67524218559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66698968410492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174695014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72475671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048491954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398003578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572753429413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985384464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60922265052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9640771150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931949138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88980519771576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86504781246185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92281484603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106710910797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232937812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98058211803436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06310606002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19514489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17864036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17038750648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563012123108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566035270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863988876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18715023994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906766891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08502650260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09353685379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06800580024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03396463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254545211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247522354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05098533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482043266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184089660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95737171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98290276527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439253330231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0765163898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11055755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05949568748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992311000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9914128780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843358039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01694393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204696655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12757802009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14459872245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16161918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13608837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9658819437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94035112857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89779949188232</t>
   </si>
   <si>
     <t xml:space="preserve">1.90631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8567955493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84029066562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81553316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.790776014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75776660442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902863502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427124977112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76601886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74951386451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69999933242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6834944486618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67524218559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66698968410492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174695014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72475671768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985372543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60922265052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8980575799942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582449436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96407699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9393196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330043315887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88980519771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86504781246185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92281484603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106722831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232937812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98058187961578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06310606002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19514489173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17038750648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864012718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310883522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906766891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08502650260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09353685379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06800580024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03396463394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02545428276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247498512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05098533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482031345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184101581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95737183094025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98290276527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11055755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05949568748474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992334842682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99141299724579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843358039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01694393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204720497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12757802009583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14459872245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16161942481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13608837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96588218212128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94035112857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630972385406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226855754852</t>
+    <t xml:space="preserve">1.8722687959671</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">1.94886159896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07243394851685</t>
+    <t xml:space="preserve">2.07243418693542</t>
   </si>
   <si>
     <t xml:space="preserve">2.08129048347473</t>
@@ -1850,55 +1850,55 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9750120639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99272513389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95729875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94844222068787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86873316764832</t>
+    <t xml:space="preserve">1.93958556652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97501194477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99272501468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95729887485504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94844233989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8687332868576</t>
   </si>
   <si>
     <t xml:space="preserve">1.92187261581421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91301608085632</t>
+    <t xml:space="preserve">1.9130163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775897026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93072938919067</t>
+    <t xml:space="preserve">1.93072926998138</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90415954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89530313014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8244503736496</t>
+    <t xml:space="preserve">1.96615540981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90415966510773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89530301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82445049285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673730373383</t>
+    <t xml:space="preserve">1.80673742294312</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
@@ -1910,52 +1910,52 @@
     <t xml:space="preserve">1.70488691329956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77131116390228</t>
+    <t xml:space="preserve">1.77131128311157</t>
   </si>
   <si>
     <t xml:space="preserve">1.815593957901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74474143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85102021694183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016781806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85987651348114</t>
+    <t xml:space="preserve">1.74474155902863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85102009773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84216368198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016769886017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85987663269043</t>
   </si>
   <si>
     <t xml:space="preserve">1.75802636146545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7624546289444</t>
+    <t xml:space="preserve">1.76245474815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75359809398651</t>
+    <t xml:space="preserve">1.7535982131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.71817195415497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7093151807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72702836990356</t>
+    <t xml:space="preserve">1.70931529998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72702848911285</t>
   </si>
   <si>
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295209407806</t>
+    <t xml:space="preserve">1.88295221328735</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988074302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142035007477</t>
+    <t xml:space="preserve">1.79988086223602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142046928406</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526966571808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988884449005</t>
+    <t xml:space="preserve">1.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757925510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66142845153809</t>
+    <t xml:space="preserve">1.6614283323288</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9752539396286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833291530609</t>
+    <t xml:space="preserve">1.97525370121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833303451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526180267334</t>
+    <t xml:space="preserve">1.81372606754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526168346405</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89218235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910301685333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064262390137</t>
+    <t xml:space="preserve">1.8921822309494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910277843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064250469208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371409416199</t>
+    <t xml:space="preserve">1.99371421337128</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -27212,7 +27212,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27238,7 +27238,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G950" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27290,7 +27290,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G952" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27316,7 +27316,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27394,7 +27394,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G956" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27420,7 +27420,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G957" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27472,7 +27472,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27498,7 +27498,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27550,7 +27550,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G962" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27576,7 +27576,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G963" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27602,7 +27602,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27628,7 +27628,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27654,7 +27654,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27680,7 +27680,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27706,7 +27706,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G968" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27732,7 +27732,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G969" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27758,7 +27758,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27784,7 +27784,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27810,7 +27810,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27862,7 +27862,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G974" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27914,7 +27914,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27940,7 +27940,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28018,7 +28018,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G980" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28044,7 +28044,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G981" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28070,7 +28070,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28174,7 +28174,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28200,7 +28200,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28330,7 +28330,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G992" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28356,7 +28356,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28408,7 +28408,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G995" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28434,7 +28434,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G996" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28486,7 +28486,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G998" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28512,7 +28512,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28538,7 +28538,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1000" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28564,7 +28564,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1001" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28616,7 +28616,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1003" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28694,7 +28694,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1006" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28720,7 +28720,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1007" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28772,7 +28772,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1009" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28798,7 +28798,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28824,7 +28824,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1011" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28850,7 +28850,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1012" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28902,7 +28902,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1014" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28928,7 +28928,7 @@
         <v>2</v>
       </c>
       <c r="G1015" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28954,7 +28954,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1016" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28980,7 +28980,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1017" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29006,7 +29006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1018" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29084,7 +29084,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1021" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29110,7 +29110,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29136,7 +29136,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1023" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29162,7 +29162,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1024" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29188,7 +29188,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1025" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29214,7 +29214,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29240,7 +29240,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1027" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29266,7 +29266,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1028" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29292,7 +29292,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1029" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29318,7 +29318,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1030" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29344,7 +29344,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1031" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29370,7 +29370,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1032" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29396,7 +29396,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1033" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29422,7 +29422,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1034" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29448,7 +29448,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1035" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29474,7 +29474,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1036" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29500,7 +29500,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1037" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29526,7 +29526,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1038" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29552,7 +29552,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1039" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29578,7 +29578,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29604,7 +29604,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1041" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29630,7 +29630,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1042" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29656,7 +29656,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1043" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29682,7 +29682,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1044" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29708,7 +29708,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1045" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29734,7 +29734,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1046" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29760,7 +29760,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29786,7 +29786,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1048" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29812,7 +29812,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29838,7 +29838,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1050" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29864,7 +29864,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1051" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29890,7 +29890,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29916,7 +29916,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1053" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29942,7 +29942,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1054" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29968,7 +29968,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1055" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29994,7 +29994,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1056" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30020,7 +30020,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1057" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30046,7 +30046,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1058" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30072,7 +30072,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30098,7 +30098,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30124,7 +30124,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1061" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30150,7 +30150,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1062" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30228,7 +30228,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1065" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30254,7 +30254,7 @@
         <v>2</v>
       </c>
       <c r="G1066" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30280,7 +30280,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1067" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30332,7 +30332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30358,7 +30358,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1070" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30384,7 +30384,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1071" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30514,7 +30514,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1076" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30540,7 +30540,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1077" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30644,7 +30644,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1081" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30670,7 +30670,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1082" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30696,7 +30696,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1083" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30722,7 +30722,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1084" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30748,7 +30748,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30774,7 +30774,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1086" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30800,7 +30800,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1087" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30826,7 +30826,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30852,7 +30852,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1089" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30878,7 +30878,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30904,7 +30904,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1091" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30930,7 +30930,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1092" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30956,7 +30956,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30982,7 +30982,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1094" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31008,7 +31008,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1095" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31034,7 +31034,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1096" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31060,7 +31060,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31086,7 +31086,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1098" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31112,7 +31112,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31138,7 +31138,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31164,7 +31164,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1101" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31190,7 +31190,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31216,7 +31216,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1103" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31242,7 +31242,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1104" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31268,7 +31268,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1105" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31294,7 +31294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1106" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31320,7 +31320,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1107" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31346,7 +31346,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1108" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31372,7 +31372,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1109" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31398,7 +31398,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31424,7 +31424,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1111" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31450,7 +31450,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1112" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31476,7 +31476,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1113" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31502,7 +31502,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31528,7 +31528,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1115" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31554,7 +31554,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1116" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31580,7 +31580,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31606,7 +31606,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1118" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31632,7 +31632,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1119" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31658,7 +31658,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1120" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31684,7 +31684,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31710,7 +31710,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1122" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31736,7 +31736,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31762,7 +31762,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31788,7 +31788,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1125" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31814,7 +31814,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31840,7 +31840,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1127" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31866,7 +31866,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1128" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31892,7 +31892,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31918,7 +31918,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1130" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31944,7 +31944,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1131" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31970,7 +31970,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31996,7 +31996,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1133" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32022,7 +32022,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1134" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32048,7 +32048,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1135" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32074,7 +32074,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1136" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32100,7 +32100,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32126,7 +32126,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1138" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32152,7 +32152,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32178,7 +32178,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1140" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32204,7 +32204,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1141" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32230,7 +32230,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32256,7 +32256,7 @@
         <v>2.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32282,7 +32282,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32308,7 +32308,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32334,7 +32334,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32360,7 +32360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32386,7 +32386,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1148" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32412,7 +32412,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32438,7 +32438,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1150" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32464,7 +32464,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32490,7 +32490,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32516,7 +32516,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1153" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32542,7 +32542,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1154" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32568,7 +32568,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1155" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32594,7 +32594,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1156" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32620,7 +32620,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1157" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32646,7 +32646,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1158" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32672,7 +32672,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1159" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32698,7 +32698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1160" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32724,7 +32724,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1161" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32750,7 +32750,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1162" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32776,7 +32776,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1163" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32802,7 +32802,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1164" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32828,7 +32828,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1165" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32854,7 +32854,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1166" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32880,7 +32880,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1167" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32906,7 +32906,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1168" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32932,7 +32932,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1169" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32958,7 +32958,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1170" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32984,7 +32984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1171" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33010,7 +33010,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33036,7 +33036,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1173" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33062,7 +33062,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33088,7 +33088,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1175" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33114,7 +33114,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1176" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33140,7 +33140,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1177" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33166,7 +33166,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1178" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33192,7 +33192,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1179" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33218,7 +33218,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1180" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33244,7 +33244,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1181" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33270,7 +33270,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1182" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33296,7 +33296,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1183" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33322,7 +33322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1184" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33348,7 +33348,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1185" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33374,7 +33374,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1186" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33400,7 +33400,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1187" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33426,7 +33426,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1188" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33452,7 +33452,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1189" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33478,7 +33478,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1190" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33504,7 +33504,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33530,7 +33530,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1192" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33556,7 +33556,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1193" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33582,7 +33582,7 @@
         <v>2</v>
       </c>
       <c r="G1194" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33608,7 +33608,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1195" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33634,7 +33634,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33660,7 +33660,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1197" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33686,7 +33686,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33712,7 +33712,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1199" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33738,7 +33738,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1200" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33764,7 +33764,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33790,7 +33790,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33816,7 +33816,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33842,7 +33842,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33868,7 +33868,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33894,7 +33894,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1206" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33920,7 +33920,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1207" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33946,7 +33946,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1208" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33972,7 +33972,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1209" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33998,7 +33998,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34024,7 +34024,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34050,7 +34050,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34076,7 +34076,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1213" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34102,7 +34102,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1214" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34128,7 +34128,7 @@
         <v>2</v>
       </c>
       <c r="G1215" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34154,7 +34154,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34180,7 +34180,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1217" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34206,7 +34206,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1218" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34232,7 +34232,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34258,7 +34258,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1220" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34284,7 +34284,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34310,7 +34310,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34336,7 +34336,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34362,7 +34362,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34388,7 +34388,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1225" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34414,7 +34414,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1226" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34440,7 +34440,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34466,7 +34466,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1228" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34492,7 +34492,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1229" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34518,7 +34518,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34544,7 +34544,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1231" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34570,7 +34570,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34596,7 +34596,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34622,7 +34622,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34648,7 +34648,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1235" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34674,7 +34674,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34700,7 +34700,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34726,7 +34726,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34752,7 +34752,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34778,7 +34778,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1240" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34804,7 +34804,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1241" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34830,7 +34830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1242" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34856,7 +34856,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1243" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34882,7 +34882,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1244" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34908,7 +34908,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1245" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34934,7 +34934,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34960,7 +34960,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34986,7 +34986,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35012,7 +35012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1249" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35038,7 +35038,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1250" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35064,7 +35064,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35090,7 +35090,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1252" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35116,7 +35116,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35168,7 +35168,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35246,7 +35246,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1258" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35324,7 +35324,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1261" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35350,7 +35350,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1262" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35714,7 +35714,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1276" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35766,7 +35766,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1278" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35792,7 +35792,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35818,7 +35818,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1280" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35844,7 +35844,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1281" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35870,7 +35870,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1282" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35896,7 +35896,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1283" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35922,7 +35922,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1284" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36104,7 +36104,7 @@
         <v>2.25</v>
       </c>
       <c r="G1291" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36130,7 +36130,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1292" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36182,7 +36182,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1294" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36234,7 +36234,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1296" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36286,7 +36286,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1298" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36390,7 +36390,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1302" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36416,7 +36416,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1303" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36442,7 +36442,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1304" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36494,7 +36494,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36520,7 +36520,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36546,7 +36546,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36598,7 +36598,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36624,7 +36624,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1311" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36650,7 +36650,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1312" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36676,7 +36676,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1313" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36702,7 +36702,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36728,7 +36728,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1315" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36936,7 +36936,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1323" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36962,7 +36962,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1324" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36988,7 +36988,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37222,7 +37222,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1334" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37248,7 +37248,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1335" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37274,7 +37274,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1336" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37352,7 +37352,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1339" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37378,7 +37378,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1340" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37404,7 +37404,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1341" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37430,7 +37430,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1342" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37456,7 +37456,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37482,7 +37482,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1344" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37534,7 +37534,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37560,7 +37560,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1347" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37612,7 +37612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37664,7 +37664,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1351" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37690,7 +37690,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1352" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37820,7 +37820,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1357" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38002,7 +38002,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1364" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -68248,7 +68248,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6909837963</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>6511</v>
@@ -68269,6 +68269,32 @@
         <v>725</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.681712963</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>13133</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681160449982</t>
+    <t xml:space="preserve">1.14681172370911</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1254426240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552574157715</t>
+    <t xml:space="preserve">1.12615501880646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12544250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552562236786</t>
   </si>
   <si>
     <t xml:space="preserve">1.11831951141357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09623801708221</t>
+    <t xml:space="preserve">1.0962381362915</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695029258728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407328605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0905396938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412885665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007677078247</t>
+    <t xml:space="preserve">1.10407340526581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09053981304169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412873744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007665157318</t>
   </si>
   <si>
     <t xml:space="preserve">0.943804740905762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925996899604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993665933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925359249115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01004898548126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859676837921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492424964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213036060333</t>
+    <t xml:space="preserve">0.925997018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993665993213654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925371170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01004910469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492436885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213059902191</t>
   </si>
   <si>
     <t xml:space="preserve">1.03711676597595</t>
@@ -107,58 +107,58 @@
     <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643227577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073359489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366178035736</t>
+    <t xml:space="preserve">1.02643203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073383331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94736635684967</t>
   </si>
   <si>
     <t xml:space="preserve">0.900354087352753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916024744510651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530968666077</t>
+    <t xml:space="preserve">0.916024923324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435343265533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530849456787</t>
   </si>
   <si>
     <t xml:space="preserve">0.985830783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970160126686096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324559688568</t>
+    <t xml:space="preserve">0.970159947872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612284183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324678897858</t>
   </si>
   <si>
     <t xml:space="preserve">1.00435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997939765453339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392340183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529047489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419827461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99081689119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967669963837</t>
+    <t xml:space="preserve">0.997939884662628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392161369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529285907745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419946670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990816950798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967431545258</t>
   </si>
   <si>
     <t xml:space="preserve">0.997227668762207</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">1.01717221736908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01503503322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078904628754</t>
+    <t xml:space="preserve">1.01503527164459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078916549683</t>
   </si>
   <si>
     <t xml:space="preserve">1.02215826511383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00577521324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648760795593</t>
+    <t xml:space="preserve">1.005774974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648736953735</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076138019562</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">1.00221371650696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984406173229218</t>
+    <t xml:space="preserve">0.984406113624573</t>
   </si>
   <si>
     <t xml:space="preserve">1.00791215896606</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">1.03284287452698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01930904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979963302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10051190853119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982741832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18171489238739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16818106174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185322284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968873023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15393495559692</t>
+    <t xml:space="preserve">1.01930916309357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996598720551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979939460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1005117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484137058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1817147731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1681809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185334205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968884944916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15393471717834</t>
   </si>
   <si>
     <t xml:space="preserve">1.11689496040344</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16105771064758</t>
+    <t xml:space="preserve">1.16105794906616</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963315963745</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">1.13683938980103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612723350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12900400161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467489719391</t>
+    <t xml:space="preserve">1.13612711429596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12900424003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467477798462</t>
   </si>
   <si>
     <t xml:space="preserve">1.17316699028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1703177690506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18100249767303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19738554954529</t>
+    <t xml:space="preserve">1.17031764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18100225925446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.197385430336</t>
   </si>
   <si>
     <t xml:space="preserve">1.2109192609787</t>
@@ -275,31 +275,31 @@
     <t xml:space="preserve">1.21163153648376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20593309402466</t>
+    <t xml:space="preserve">1.20593297481537</t>
   </si>
   <si>
     <t xml:space="preserve">1.22302842140198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22089147567749</t>
+    <t xml:space="preserve">1.22089159488678</t>
   </si>
   <si>
     <t xml:space="preserve">1.19596076011658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23548436164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22670149803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937361240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790972232819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16302418708801</t>
+    <t xml:space="preserve">1.23548448085785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2267017364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937337398529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1879096031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1630243062973</t>
   </si>
   <si>
     <t xml:space="preserve">1.16595196723938</t>
@@ -308,40 +308,40 @@
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570521354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911770820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424144268036</t>
+    <t xml:space="preserve">1.16375613212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570509433746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911782741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424120426178</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11837697029114</t>
+    <t xml:space="preserve">1.11837708950043</t>
   </si>
   <si>
     <t xml:space="preserve">1.10154271125793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520243644714</t>
+    <t xml:space="preserve">1.10520231723785</t>
   </si>
   <si>
     <t xml:space="preserve">1.09934711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14545822143555</t>
+    <t xml:space="preserve">1.14545810222626</t>
   </si>
   <si>
     <t xml:space="preserve">1.1293557882309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12203669548035</t>
+    <t xml:space="preserve">1.12203657627106</t>
   </si>
   <si>
     <t xml:space="preserve">1.12716007232666</t>
@@ -350,58 +350,58 @@
     <t xml:space="preserve">1.07226598262787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06860625743866</t>
+    <t xml:space="preserve">1.06860637664795</t>
   </si>
   <si>
     <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423241138458</t>
+    <t xml:space="preserve">1.12423253059387</t>
   </si>
   <si>
     <t xml:space="preserve">1.15716898441315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18717789649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205416202545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20767140388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17839455604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401191711426</t>
+    <t xml:space="preserve">1.18717765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205428123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20767152309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17839467525482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401167869568</t>
   </si>
   <si>
     <t xml:space="preserve">1.18351805210114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20474398136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17473530769348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571400642395</t>
+    <t xml:space="preserve">1.2047438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1747350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571388721466</t>
   </si>
   <si>
     <t xml:space="preserve">1.17546689510345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19303297996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035243034363</t>
+    <t xml:space="preserve">1.1930330991745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035231113434</t>
   </si>
   <si>
     <t xml:space="preserve">1.19888854026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21499073505402</t>
+    <t xml:space="preserve">1.21499061584473</t>
   </si>
   <si>
     <t xml:space="preserve">1.20693969726562</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">1.21425902843475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22231006622314</t>
+    <t xml:space="preserve">1.22230994701385</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962915897369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2332888841629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22450566291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524663925171</t>
+    <t xml:space="preserve">1.23328900337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22450578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524640083313</t>
   </si>
   <si>
     <t xml:space="preserve">1.28232765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31745982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208945274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550194740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184246063232</t>
+    <t xml:space="preserve">1.31745970249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208957195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550206661224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2918426990509</t>
   </si>
   <si>
     <t xml:space="preserve">1.27866792678833</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">1.25963795185089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26183366775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26256561279297</t>
+    <t xml:space="preserve">1.26183378696442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26256573200226</t>
   </si>
   <si>
     <t xml:space="preserve">1.26915287971497</t>
@@ -467,34 +467,34 @@
     <t xml:space="preserve">1.23694837093353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23109304904938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402962207794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24719548225403</t>
+    <t xml:space="preserve">1.23109292984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24719536304474</t>
   </si>
   <si>
     <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21938228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1996203660965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669282436371</t>
+    <t xml:space="preserve">1.21938252449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962048530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669258594513</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376504421234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742476940155</t>
+    <t xml:space="preserve">1.17766261100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742465019226</t>
   </si>
   <si>
     <t xml:space="preserve">1.20620775222778</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">1.18059039115906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16522014141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15643703937531</t>
+    <t xml:space="preserve">1.16522002220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15643692016602</t>
   </si>
   <si>
     <t xml:space="preserve">1.16887962818146</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">1.17693090438843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19522881507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985844612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498182296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17400300502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107546329498</t>
+    <t xml:space="preserve">1.19522893428802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985856533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498206138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107570171356</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814768314362</t>
@@ -542,34 +542,34 @@
     <t xml:space="preserve">1.14326238632202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11252164840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13447916507721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984097957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325359344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593438148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007882118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276864051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032593250275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1161812543869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13960289955139</t>
+    <t xml:space="preserve">1.11252176761627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13447940349579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984086036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325371265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593450069427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007905960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1227685213089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11618113517761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1396027803421</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278920173645</t>
@@ -578,37 +578,37 @@
     <t xml:space="preserve">1.14399433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14179861545563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13521111011505</t>
+    <t xml:space="preserve">1.14179849624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13521122932434</t>
   </si>
   <si>
     <t xml:space="preserve">1.13813900947571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14253056049347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19449687004089</t>
+    <t xml:space="preserve">1.14253044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19449698925018</t>
   </si>
   <si>
     <t xml:space="preserve">1.18132245540619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17253923416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912650108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887083530426</t>
+    <t xml:space="preserve">1.17253935337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912662029266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887095451355</t>
   </si>
   <si>
     <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12350046634674</t>
+    <t xml:space="preserve">1.12350058555603</t>
   </si>
   <si>
     <t xml:space="preserve">1.12569630146027</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12496435642242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12642812728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936470031738</t>
+    <t xml:space="preserve">1.12496411800385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12642824649811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936458110809</t>
   </si>
   <si>
     <t xml:space="preserve">1.15277743339539</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">1.22377383708954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22596967220306</t>
+    <t xml:space="preserve">1.22596943378448</t>
   </si>
   <si>
     <t xml:space="preserve">1.25671029090881</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">1.24792742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24060797691345</t>
+    <t xml:space="preserve">1.24060809612274</t>
   </si>
   <si>
     <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26842093467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29769802093506</t>
+    <t xml:space="preserve">1.26842105388641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29769778251648</t>
   </si>
   <si>
     <t xml:space="preserve">1.30867671966553</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">1.3247789144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32404696941376</t>
+    <t xml:space="preserve">1.32404720783234</t>
   </si>
   <si>
     <t xml:space="preserve">1.31014060974121</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">1.29037868976593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30135750770569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30282151699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3152642250061</t>
+    <t xml:space="preserve">1.30135762691498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30282127857208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31526410579681</t>
   </si>
   <si>
     <t xml:space="preserve">1.32624292373657</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">1.34673678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3869925737381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36869418621063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772439956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35991132259369</t>
+    <t xml:space="preserve">1.38699245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36869442462921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772463798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35991144180298</t>
   </si>
   <si>
     <t xml:space="preserve">1.37454986572266</t>
@@ -716,37 +716,37 @@
     <t xml:space="preserve">1.40529048442841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39065206050873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39650726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114580631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38186895847321</t>
+    <t xml:space="preserve">1.39065194129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39650738239288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114592552185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3818690776825</t>
   </si>
   <si>
     <t xml:space="preserve">1.37162208557129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38845646381378</t>
+    <t xml:space="preserve">1.38845634460449</t>
   </si>
   <si>
     <t xml:space="preserve">1.41927754878998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45009863376617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046503543854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53654837608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56361055374146</t>
+    <t xml:space="preserve">1.45009875297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046491622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53654825687408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56361079216003</t>
   </si>
   <si>
     <t xml:space="preserve">1.58616268634796</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51098942756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693406581879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866463661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49069249629974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46814036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964406967163</t>
+    <t xml:space="preserve">1.51098930835724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4869339466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866451740265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49069237709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46814024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964383125305</t>
   </si>
   <si>
     <t xml:space="preserve">1.44333302974701</t>
@@ -782,25 +782,25 @@
     <t xml:space="preserve">1.4448367357254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43882274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4320570230484</t>
+    <t xml:space="preserve">1.43882262706757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43205690383911</t>
   </si>
   <si>
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574622154236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836782455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45911967754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189903259277</t>
+    <t xml:space="preserve">1.40574634075165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836770534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45911955833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189891338348</t>
   </si>
   <si>
     <t xml:space="preserve">1.4531055688858</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41852581501007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42980170249939</t>
+    <t xml:space="preserve">1.41852569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
     <t xml:space="preserve">1.4207808971405</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">1.42604315280914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702222824097</t>
+    <t xml:space="preserve">1.41702210903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.42529141902924</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">1.44408476352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47716104984283</t>
+    <t xml:space="preserve">1.47716116905212</t>
   </si>
   <si>
     <t xml:space="preserve">1.49219584465027</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">1.46663677692413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46588528156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144411087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48843717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850664615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347208976746</t>
+    <t xml:space="preserve">1.46588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144423007965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48843729496002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948584079742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347185134888</t>
   </si>
   <si>
     <t xml:space="preserve">1.48167157173157</t>
@@ -863,55 +863,55 @@
     <t xml:space="preserve">1.4959545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51249265670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497543811798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49369943141937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49896168708801</t>
+    <t xml:space="preserve">1.51249289512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497555732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151358127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369931221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49896156787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602398395538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49670648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5079824924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5485759973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242354393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039544582367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941637039185</t>
+    <t xml:space="preserve">1.496706366539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798237323761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54857611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039568424225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941648960114</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903091907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51399624347687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158281326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511437892914</t>
+    <t xml:space="preserve">1.52903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51399612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158293247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511414051056</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609333515167</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">1.63126718997955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6763710975647</t>
+    <t xml:space="preserve">1.67637133598328</t>
   </si>
   <si>
     <t xml:space="preserve">1.65682601928711</t>
@@ -929,28 +929,28 @@
     <t xml:space="preserve">1.69140589237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70644056797028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381920337677</t>
+    <t xml:space="preserve">1.70644068717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997177600861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381896495819</t>
   </si>
   <si>
     <t xml:space="preserve">1.67937803268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6673504114151</t>
+    <t xml:space="preserve">1.66735017299652</t>
   </si>
   <si>
     <t xml:space="preserve">1.66885387897491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67787480354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035698890686</t>
+    <t xml:space="preserve">1.6778746843338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035722732544</t>
   </si>
   <si>
     <t xml:space="preserve">1.67186069488525</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">1.68839919567108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68689548969269</t>
+    <t xml:space="preserve">1.6868953704834</t>
   </si>
   <si>
     <t xml:space="preserve">1.65983295440674</t>
@@ -971,67 +971,67 @@
     <t xml:space="preserve">1.64630174636841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74402749538422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115950107574</t>
+    <t xml:space="preserve">1.74402737617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115914344788</t>
   </si>
   <si>
     <t xml:space="preserve">1.81318712234497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79213857650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965579509735</t>
+    <t xml:space="preserve">1.79213869571686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965615272522</t>
   </si>
   <si>
     <t xml:space="preserve">1.84175312519073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86430513858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83874619007111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133666038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206934452057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7756005525589</t>
+    <t xml:space="preserve">1.86430537700653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874642848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71245467662811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133630275726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206922531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77560031414032</t>
   </si>
   <si>
     <t xml:space="preserve">1.83423578739166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8056697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220816612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72899270057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7410204410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598588466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75154483318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7229790687561</t>
+    <t xml:space="preserve">1.80566990375519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220804691315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72899258136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74102056026459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598576545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.751544713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
     <t xml:space="preserve">1.70193028450012</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">1.69441294670105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68388855457306</t>
+    <t xml:space="preserve">1.68388831615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728082180023</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">1.66434335708618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72448217868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71846854686737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755870342255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500680923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951697349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73651003837585</t>
+    <t xml:space="preserve">1.72448229789734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846842765808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755894184113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500669002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951685428619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73650991916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395826339722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78161430358887</t>
+    <t xml:space="preserve">1.78161406517029</t>
   </si>
   <si>
     <t xml:space="preserve">1.75906217098236</t>
@@ -1079,40 +1079,40 @@
     <t xml:space="preserve">1.81920123100281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8267183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416655540466</t>
+    <t xml:space="preserve">1.82671844959259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416619777679</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409684658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913176059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678780078888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927022457123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468133449554</t>
+    <t xml:space="preserve">1.88685727119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168377399445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664885997772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409672737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678803920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927034378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88701045513153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468169212341</t>
   </si>
   <si>
     <t xml:space="preserve">1.84865689277649</t>
@@ -1121,274 +1121,274 @@
     <t xml:space="preserve">1.86399829387665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81797385215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81030285358429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235221385956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331549167633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263197422028</t>
+    <t xml:space="preserve">1.81797349452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.810302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331513404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263221263885</t>
   </si>
   <si>
     <t xml:space="preserve">1.75660753250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427829265594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6798996925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524145126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222905158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7489367723465</t>
+    <t xml:space="preserve">1.70291221141815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427817344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989981174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524109363556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222893238068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74893701076508</t>
   </si>
   <si>
     <t xml:space="preserve">1.65688753128052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64154589176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58017957210541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455817222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620425224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250893115997</t>
+    <t xml:space="preserve">1.64154601097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5801796913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455829143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620413303375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250881195068</t>
   </si>
   <si>
     <t xml:space="preserve">1.51497805118561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53031969070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48813045024872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4152580499649</t>
+    <t xml:space="preserve">1.53031957149506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48813033103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41525816917419</t>
   </si>
   <si>
     <t xml:space="preserve">1.4114226102829</t>
   </si>
   <si>
+    <t xml:space="preserve">1.3730685710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35005629062653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.380739569664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39224565029144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36923325061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39991641044617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35772716999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35389196872711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34238576889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403172969818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2810195684433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26951324939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25417172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24650084972382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25800716876984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29636096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28869020938873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019640922546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252552986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937325000763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30786716938019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087956905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31553792953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39608097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40375196933746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36156260967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443500995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37690412998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38841021060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34622097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704412937164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334845066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320868968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38903474807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36109435558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32916247844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34512829780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508572101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39701759815216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41298353672028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4010089635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40899205207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41697490215302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46886420249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4968044757843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877904891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51277041435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49281299114227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487271785736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50079596042633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44491529464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45289838314056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495799064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096650600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500044822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39302611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4289493560791</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35005640983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.380739569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39224565029144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36923336982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39991641044617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35772716999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35389184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3423855304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403184890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28101933002472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26951324939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25417172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2465010881424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25800704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29636096954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869009017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019652843475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252552986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937348842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30786716938019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087944984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855020999908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471477031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3155380487442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39608108997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40375173091888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36156249046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539793014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443500995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37690412998199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38841021060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3462210893631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704412937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334868907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320868968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706005573273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3890346288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3610942363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32916224002838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35311138629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3451281785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508584022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39701759815216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41298341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40100908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40899205207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4169750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46886420249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49680471420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877892971039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51277053356171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49281299114227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487283706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50079596042633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44491529464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45289838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693220615387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096650600433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500056743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39302623271942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894923686981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306880950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907720565796</t>
+    <t xml:space="preserve">1.36907732486725</t>
   </si>
   <si>
     <t xml:space="preserve">1.35710287094116</t>
@@ -1400,49 +1400,49 @@
     <t xml:space="preserve">1.4848301410675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47684717178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46088123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48882150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075338363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51676177978516</t>
+    <t xml:space="preserve">1.47684729099274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46088135242462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48882162570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075326442719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51676201820374</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659159183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56465983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54071068763733</t>
+    <t xml:space="preserve">1.59659147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56465971469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54071080684662</t>
   </si>
   <si>
     <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52873623371124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58860850334167</t>
+    <t xml:space="preserve">1.52873635292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58860862255096</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54869401454926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53671932220459</t>
+    <t xml:space="preserve">1.54869377613068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470217227936</t>
@@ -1451,82 +1451,82 @@
     <t xml:space="preserve">1.55268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5247448682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264268398285</t>
+    <t xml:space="preserve">1.52474498748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264280319214</t>
   </si>
   <si>
     <t xml:space="preserve">1.67642104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801183223724</t>
+    <t xml:space="preserve">1.86801207065582</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397789001465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9478417634964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05960297584534</t>
+    <t xml:space="preserve">1.94784152507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539860725403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05960321426392</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329642295837</t>
+    <t xml:space="preserve">2.20329618453979</t>
   </si>
   <si>
     <t xml:space="preserve">2.21926212310791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22724533081055</t>
+    <t xml:space="preserve">2.22724485397339</t>
   </si>
   <si>
     <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23522782325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11548399925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98775625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82011413574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809746265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91591012477875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002910137177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650619983673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260010719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72431910037994</t>
+    <t xml:space="preserve">2.2352283000946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9877564907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82011437416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91591000556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002898216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650643825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890677928925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5925999879837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72431898117065</t>
   </si>
   <si>
     <t xml:space="preserve">1.62852323055267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64448916912079</t>
+    <t xml:space="preserve">1.64448928833008</t>
   </si>
   <si>
     <t xml:space="preserve">1.68440389633179</t>
@@ -1538,70 +1538,70 @@
     <t xml:space="preserve">1.6604551076889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65247225761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826776981354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633577346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054026126862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843807697296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61255729198456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69238698482513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75625085830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76423370838165</t>
+    <t xml:space="preserve">1.65247213840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633613109589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054038047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843819618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61255741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69238686561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625061988831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
     <t xml:space="preserve">1.90792691707611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95582449436188</t>
+    <t xml:space="preserve">1.95582485198975</t>
   </si>
   <si>
     <t xml:space="preserve">1.92389273643494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94757199287415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456246376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679566860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84029042720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81553339958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79077613353729</t>
+    <t xml:space="preserve">1.94757211208344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456270217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630996227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8567955493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84029066562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81553328037262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.790776014328</t>
   </si>
   <si>
     <t xml:space="preserve">1.75776648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79902863502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427113056183</t>
+    <t xml:space="preserve">1.79902851581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7742714881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.76601886749268</t>
@@ -1610,70 +1610,73 @@
     <t xml:space="preserve">1.74126136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78252387046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300909996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7495139837265</t>
+    <t xml:space="preserve">1.78252375125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74951386451721</t>
   </si>
   <si>
     <t xml:space="preserve">1.71650421619415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69999933242798</t>
+    <t xml:space="preserve">1.69999945163727</t>
   </si>
   <si>
     <t xml:space="preserve">1.68349432945251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67524218559265</t>
+    <t xml:space="preserve">1.67524206638336</t>
   </si>
   <si>
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174695014954</t>
+    <t xml:space="preserve">1.65873742103577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825171470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174706935883</t>
   </si>
   <si>
     <t xml:space="preserve">1.72475671768188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985384464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60922265052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9640771150589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93931949138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330031394958</t>
+    <t xml:space="preserve">1.65048480033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398015499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572765350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985372543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60922276973724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805734157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582437515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660153388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96407687664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9393196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330007553101</t>
   </si>
   <si>
     <t xml:space="preserve">1.88155269622803</t>
@@ -1682,31 +1685,31 @@
     <t xml:space="preserve">1.88980519771576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86504781246185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92281484603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106710910797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232937812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98058211803436</t>
+    <t xml:space="preserve">1.86504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92281472682953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106722831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359152793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883426189423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232949733734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98058199882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.06310606002808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19514489173889</t>
+    <t xml:space="preserve">2.19514513015747</t>
   </si>
   <si>
     <t xml:space="preserve">2.17864036560059</t>
@@ -1715,19 +1718,19 @@
     <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16213512420654</t>
+    <t xml:space="preserve">2.16213488578796</t>
   </si>
   <si>
     <t xml:space="preserve">2.14563012123108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19566035270691</t>
+    <t xml:space="preserve">2.19566059112549</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18715023994446</t>
+    <t xml:space="preserve">2.18715000152588</t>
   </si>
   <si>
     <t xml:space="preserve">2.15310907363892</t>
@@ -1736,7 +1739,7 @@
     <t xml:space="preserve">2.11906766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08502650260925</t>
+    <t xml:space="preserve">2.08502674102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.09353685379028</t>
@@ -1745,34 +1748,34 @@
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396463394165</t>
+    <t xml:space="preserve">2.03396487236023</t>
   </si>
   <si>
     <t xml:space="preserve">2.0254545211792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04247522354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05098533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482043266296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184089660645</t>
+    <t xml:space="preserve">2.04247498512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05098509788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482031345367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184077739716</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290276527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439253330231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0765163898468</t>
+    <t xml:space="preserve">1.98290252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439241409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07651615142822</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
@@ -1781,10 +1784,10 @@
     <t xml:space="preserve">2.05949568748474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99992311000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9914128780365</t>
+    <t xml:space="preserve">1.99992334842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99141311645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.00843358039856</t>
@@ -1793,13 +1796,13 @@
     <t xml:space="preserve">2.01694393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10204696655273</t>
+    <t xml:space="preserve">2.10204720497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14459872245789</t>
+    <t xml:space="preserve">2.14459848403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.16161918640137</t>
@@ -1811,28 +1814,25 @@
     <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94035112857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89779949188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90631008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722687959671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92333054542542</t>
+    <t xml:space="preserve">1.94035124778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977997303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87226867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9233306646347</t>
   </si>
   <si>
     <t xml:space="preserve">1.94886159896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07243418693542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08129048347473</t>
+    <t xml:space="preserve">2.07243394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08129072189331</t>
   </si>
   <si>
     <t xml:space="preserve">2.05472087860107</t>
@@ -1850,46 +1850,46 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958556652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97501194477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99272501468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95729887485504</t>
+    <t xml:space="preserve">1.93958580493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9750120639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99272525310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95729875564575</t>
   </si>
   <si>
     <t xml:space="preserve">1.94844233989716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8687332868576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92187261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9130163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775897026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072926998138</t>
+    <t xml:space="preserve">1.86873316764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9218727350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91301620006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87758982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072903156281</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615540981293</t>
+    <t xml:space="preserve">1.96615552902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.90415966510773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89530301094055</t>
+    <t xml:space="preserve">1.89530313014984</t>
   </si>
   <si>
     <t xml:space="preserve">1.82445049285889</t>
@@ -1904,37 +1904,37 @@
     <t xml:space="preserve">1.79788088798523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70045864582062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70488691329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131128311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.815593957901</t>
+    <t xml:space="preserve">1.70045876502991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70488703250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131116390228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81559383869171</t>
   </si>
   <si>
     <t xml:space="preserve">1.74474155902863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85102009773254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84216368198395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016769886017</t>
+    <t xml:space="preserve">1.85102021694183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84216356277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016781806946</t>
   </si>
   <si>
     <t xml:space="preserve">1.85987663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75802636146545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76245474815369</t>
+    <t xml:space="preserve">1.75802648067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76245450973511</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">1.7535982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71817195415497</t>
+    <t xml:space="preserve">1.71817183494568</t>
   </si>
   <si>
     <t xml:space="preserve">1.70931529998779</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295221328735</t>
+    <t xml:space="preserve">1.88295209407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988086223602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142046928406</t>
+    <t xml:space="preserve">1.79988074302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142035007477</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757925510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988872528076</t>
+    <t xml:space="preserve">1.73526966571808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757913589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988884449005</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6614283323288</t>
+    <t xml:space="preserve">1.66142845153809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97525370121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833303451538</t>
+    <t xml:space="preserve">1.9752539396286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833291530609</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372606754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526168346405</t>
+    <t xml:space="preserve">1.81372594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526180267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8921822309494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910277843475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064250469208</t>
+    <t xml:space="preserve">1.89218235015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910301685333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371421337128</t>
+    <t xml:space="preserve">1.99371409416199</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -35116,7 +35116,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35142,7 +35142,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1256" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35220,7 +35220,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35272,7 +35272,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35298,7 +35298,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1260" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35376,7 +35376,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35402,7 +35402,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35428,7 +35428,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35454,7 +35454,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35480,7 +35480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35506,7 +35506,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35532,7 +35532,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1269" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35558,7 +35558,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1270" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35584,7 +35584,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1271" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35610,7 +35610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35636,7 +35636,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35662,7 +35662,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1274" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35688,7 +35688,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35740,7 +35740,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1277" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35948,7 +35948,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35974,7 +35974,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1286" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36000,7 +36000,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1287" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36026,7 +36026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1288" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36052,7 +36052,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36078,7 +36078,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36156,7 +36156,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36208,7 +36208,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36260,7 +36260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36312,7 +36312,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36338,7 +36338,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36468,7 +36468,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36572,7 +36572,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36754,7 +36754,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36780,7 +36780,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36806,7 +36806,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36832,7 +36832,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36858,7 +36858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1320" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36884,7 +36884,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1321" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36910,7 +36910,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1322" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37014,7 +37014,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1326" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37040,7 +37040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37066,7 +37066,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1328" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37092,7 +37092,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37118,7 +37118,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1330" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37144,7 +37144,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1331" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37170,7 +37170,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37196,7 +37196,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37300,7 +37300,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37326,7 +37326,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37508,7 +37508,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37586,7 +37586,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37638,7 +37638,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1350" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37794,7 +37794,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1356" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37846,7 +37846,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1358" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37872,7 +37872,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1359" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37898,7 +37898,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1360" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37924,7 +37924,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1361" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37976,7 +37976,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1363" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38028,7 +38028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1365" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38080,7 +38080,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1367" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38106,7 +38106,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1368" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38184,7 +38184,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38210,7 +38210,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1372" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38236,7 +38236,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38262,7 +38262,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1374" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38288,7 +38288,7 @@
         <v>2.5</v>
       </c>
       <c r="G1375" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38314,7 +38314,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38340,7 +38340,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1377" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38366,7 +38366,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38392,7 +38392,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38418,7 +38418,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38444,7 +38444,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1381" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38470,7 +38470,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1382" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38496,7 +38496,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1383" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38522,7 +38522,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1384" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38548,7 +38548,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38574,7 +38574,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38600,7 +38600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1387" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38626,7 +38626,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38652,7 +38652,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1389" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38756,7 +38756,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>601</v>
+        <v>522</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -68274,7 +68274,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.681712963</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>13133</v>
@@ -68295,6 +68295,32 @@
         <v>726</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.5464351852</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.1468118429184</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
@@ -50,142 +50,142 @@
     <t xml:space="preserve">1.12544250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09552562236786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0962381362915</t>
+    <t xml:space="preserve">1.09552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831963062286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09623801708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695029258728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407340526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09053981304169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412873744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007665157318</t>
+    <t xml:space="preserve">1.10407328605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09053957462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412897586823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007677078247</t>
   </si>
   <si>
     <t xml:space="preserve">0.943804740905762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925997018814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993665993213654</t>
+    <t xml:space="preserve">0.925997257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993666112422943</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004910469055</t>
+    <t xml:space="preserve">1.01004886627197</t>
   </si>
   <si>
     <t xml:space="preserve">1.01859664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05492436885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213059902191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711676597595</t>
+    <t xml:space="preserve">1.05492424964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213036060333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711664676666</t>
   </si>
   <si>
     <t xml:space="preserve">1.02572000026703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495203495026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02643203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94736635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354087352753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024923324585</t>
+    <t xml:space="preserve">1.04495215415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02643239498138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073359489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366237640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354146957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024804115295</t>
   </si>
   <si>
     <t xml:space="preserve">0.922435343265533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939530849456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324678897858</t>
+    <t xml:space="preserve">0.939530968666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830664634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612462997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324619293213</t>
   </si>
   <si>
     <t xml:space="preserve">1.00435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997939884662628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392161369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529285907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419946670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990816950798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967431545258</t>
+    <t xml:space="preserve">0.997939944267273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392220973969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529166698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99081689119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967729568481</t>
   </si>
   <si>
     <t xml:space="preserve">0.997227668762207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01717221736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01503527164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078916549683</t>
+    <t xml:space="preserve">1.01717209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0150351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078904628754</t>
   </si>
   <si>
     <t xml:space="preserve">1.02215826511383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.005774974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648736953735</t>
+    <t xml:space="preserve">1.00577509403229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648748874664</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076138019562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00221371650696</t>
+    <t xml:space="preserve">1.00221383571625</t>
   </si>
   <si>
     <t xml:space="preserve">0.984406113624573</t>
@@ -200,37 +200,37 @@
     <t xml:space="preserve">1.01930916309357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996598720551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979939460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1005117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484137058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982717990875</t>
+    <t xml:space="preserve">1.03996610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979963302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10051190853119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982729911804</t>
   </si>
   <si>
     <t xml:space="preserve">1.1817147731781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1681809425354</t>
+    <t xml:space="preserve">1.16818082332611</t>
   </si>
   <si>
     <t xml:space="preserve">1.13185334205627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13968884944916</t>
+    <t xml:space="preserve">1.13968861103058</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393471717834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689496040344</t>
+    <t xml:space="preserve">1.11689484119415</t>
   </si>
   <si>
     <t xml:space="preserve">1.09766268730164</t>
@@ -245,37 +245,37 @@
     <t xml:space="preserve">1.14752399921417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13683938980103</t>
+    <t xml:space="preserve">1.1368396282196</t>
   </si>
   <si>
     <t xml:space="preserve">1.13612711429596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12900424003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316699028015</t>
+    <t xml:space="preserve">1.12900400161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467489719391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316687107086</t>
   </si>
   <si>
     <t xml:space="preserve">1.17031764984131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18100225925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.197385430336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2109192609787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163153648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20593297481537</t>
+    <t xml:space="preserve">1.18100249767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19738554954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163165569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20593309402466</t>
   </si>
   <si>
     <t xml:space="preserve">1.22302842140198</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">1.22089159488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596076011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23548448085785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2267017364502</t>
+    <t xml:space="preserve">1.19596087932587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23548460006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22670149803162</t>
   </si>
   <si>
     <t xml:space="preserve">1.18937337398529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1879096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1630243062973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16595196723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16229236125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16375613212585</t>
+    <t xml:space="preserve">1.18790972232819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16302442550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16595208644867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16229248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16375637054443</t>
   </si>
   <si>
     <t xml:space="preserve">1.15570509433746</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">1.15424120426178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14106667041779</t>
+    <t xml:space="preserve">1.1410665512085</t>
   </si>
   <si>
     <t xml:space="preserve">1.11837708950043</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">1.10154271125793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520231723785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934711456299</t>
+    <t xml:space="preserve">1.10520243644714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934723377228</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545810222626</t>
@@ -350,34 +350,34 @@
     <t xml:space="preserve">1.07226598262787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06860637664795</t>
+    <t xml:space="preserve">1.06860649585724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423253059387</t>
+    <t xml:space="preserve">1.12423229217529</t>
   </si>
   <si>
     <t xml:space="preserve">1.15716898441315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18717765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205428123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20767152309418</t>
+    <t xml:space="preserve">1.18717753887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205440044403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20767140388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.17839467525482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20401167869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18351805210114</t>
+    <t xml:space="preserve">1.20401191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18351817131042</t>
   </si>
   <si>
     <t xml:space="preserve">1.2047438621521</t>
@@ -386,28 +386,28 @@
     <t xml:space="preserve">1.1747350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18571388721466</t>
+    <t xml:space="preserve">1.18571400642395</t>
   </si>
   <si>
     <t xml:space="preserve">1.17546689510345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1930330991745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035231113434</t>
+    <t xml:space="preserve">1.19303321838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035254955292</t>
   </si>
   <si>
     <t xml:space="preserve">1.19888854026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21499061584473</t>
+    <t xml:space="preserve">1.21499085426331</t>
   </si>
   <si>
     <t xml:space="preserve">1.20693969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21425902843475</t>
+    <t xml:space="preserve">1.21425890922546</t>
   </si>
   <si>
     <t xml:space="preserve">1.22230994701385</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">1.22962915897369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23328900337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22450578212738</t>
+    <t xml:space="preserve">1.23328876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22450566291809</t>
   </si>
   <si>
     <t xml:space="preserve">1.25524640083313</t>
@@ -428,31 +428,31 @@
     <t xml:space="preserve">1.28232765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31745970249176</t>
+    <t xml:space="preserve">1.31745994091034</t>
   </si>
   <si>
     <t xml:space="preserve">1.30208957195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29550206661224</t>
+    <t xml:space="preserve">1.29550218582153</t>
   </si>
   <si>
     <t xml:space="preserve">1.2918426990509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27866792678833</t>
+    <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890612602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354454994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963795185089</t>
+    <t xml:space="preserve">1.25890624523163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354466915131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25963807106018</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183378696442</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">1.26256573200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915287971497</t>
+    <t xml:space="preserve">1.26915311813354</t>
   </si>
   <si>
     <t xml:space="preserve">1.23694837093353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24719536304474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2230418920517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21938252449036</t>
+    <t xml:space="preserve">1.23109304904938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402962207794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24719548225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22304201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21938216686249</t>
   </si>
   <si>
     <t xml:space="preserve">1.19962048530579</t>
@@ -491,28 +491,28 @@
     <t xml:space="preserve">1.19376504421234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766261100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742465019226</t>
+    <t xml:space="preserve">1.17766273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742453098297</t>
   </si>
   <si>
     <t xml:space="preserve">1.20620775222778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19230127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522002220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15643692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16887962818146</t>
+    <t xml:space="preserve">1.19230115413666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059051036835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522014141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15643703937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16887986660004</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693090438843</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">1.17400312423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17107570171356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16814768314362</t>
+    <t xml:space="preserve">1.17107558250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16814780235291</t>
   </si>
   <si>
     <t xml:space="preserve">1.1461900472641</t>
@@ -545,37 +545,37 @@
     <t xml:space="preserve">1.11252176761627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13447940349579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325371265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593450069427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007905960083</t>
+    <t xml:space="preserve">1.1344792842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984097957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325347423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1059342622757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007917881012</t>
   </si>
   <si>
     <t xml:space="preserve">1.1227685213089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11032581329346</t>
+    <t xml:space="preserve">1.11032605171204</t>
   </si>
   <si>
     <t xml:space="preserve">1.11618113517761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1396027803421</t>
+    <t xml:space="preserve">1.13960289955139</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14399433135986</t>
+    <t xml:space="preserve">1.14399421215057</t>
   </si>
   <si>
     <t xml:space="preserve">1.14179849624634</t>
@@ -584,64 +584,64 @@
     <t xml:space="preserve">1.13521122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13813900947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14253044128418</t>
+    <t xml:space="preserve">1.13813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14253056049347</t>
   </si>
   <si>
     <t xml:space="preserve">1.19449698925018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18132245540619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17253935337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912662029266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887095451355</t>
+    <t xml:space="preserve">1.1813223361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17253923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912650108337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887071609497</t>
   </si>
   <si>
     <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12350058555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569630146027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11910903453827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12496411800385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12642824649811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936458110809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277743339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741585731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22377383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596943378448</t>
+    <t xml:space="preserve">1.12350046634674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569618225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11910891532898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12496423721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12642812728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15277755260468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741597652435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22377395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596967220306</t>
   </si>
   <si>
     <t xml:space="preserve">1.25671029090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24792742729187</t>
+    <t xml:space="preserve">1.24792718887329</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060809612274</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26842105388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29769778251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3247789144516</t>
+    <t xml:space="preserve">1.26842129230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29769790172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867683887482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403841495514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477903366089</t>
   </si>
   <si>
     <t xml:space="preserve">1.32404720783234</t>
@@ -671,25 +671,25 @@
     <t xml:space="preserve">1.31014060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3284387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037868976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135762691498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30282127857208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31526410579681</t>
+    <t xml:space="preserve">1.32843863964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037892818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135774612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30282139778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31526398658752</t>
   </si>
   <si>
     <t xml:space="preserve">1.32624292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36137521266937</t>
+    <t xml:space="preserve">1.36137509346008</t>
   </si>
   <si>
     <t xml:space="preserve">1.33941757678986</t>
@@ -698,46 +698,46 @@
     <t xml:space="preserve">1.34673678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38699245452881</t>
+    <t xml:space="preserve">1.38699269294739</t>
   </si>
   <si>
     <t xml:space="preserve">1.36869442462921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38772463798523</t>
+    <t xml:space="preserve">1.38772451877594</t>
   </si>
   <si>
     <t xml:space="preserve">1.35991144180298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37454986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40529048442841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39065194129944</t>
+    <t xml:space="preserve">1.37454998493195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4052906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
     <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114592552185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3818690776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37162208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927754878998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45009875297546</t>
+    <t xml:space="preserve">1.41114580631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38186919689178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.371621966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3884562253952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927766799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45009863376617</t>
   </si>
   <si>
     <t xml:space="preserve">1.50046491622925</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56361079216003</t>
+    <t xml:space="preserve">1.56361067295074</t>
   </si>
   <si>
     <t xml:space="preserve">1.58616268634796</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">1.60570800304413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51700305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51098930835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4869339466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866451740265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49069237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46814024448395</t>
+    <t xml:space="preserve">1.51700294017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51098918914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693382740021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866475582123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49069261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46814036369324</t>
   </si>
   <si>
     <t xml:space="preserve">1.46964383125305</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">1.44333302974701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4448367357254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882262706757</t>
+    <t xml:space="preserve">1.44483649730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882250785828</t>
   </si>
   <si>
     <t xml:space="preserve">1.43205690383911</t>
@@ -791,49 +791,49 @@
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574634075165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836770534515</t>
+    <t xml:space="preserve">1.40574622154236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836782455444</t>
   </si>
   <si>
     <t xml:space="preserve">1.45911955833435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189891338348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4531055688858</t>
+    <t xml:space="preserve">1.47189903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45310544967651</t>
   </si>
   <si>
     <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41852569580078</t>
+    <t xml:space="preserve">1.41852581501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4207808971405</t>
+    <t xml:space="preserve">1.42078101634979</t>
   </si>
   <si>
     <t xml:space="preserve">1.42604315280914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41702210903168</t>
+    <t xml:space="preserve">1.41702222824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.42529141902924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44408476352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716116905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219584465027</t>
+    <t xml:space="preserve">1.44408488273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716128826141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219608306885</t>
   </si>
   <si>
     <t xml:space="preserve">1.46663677692413</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">1.46588516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49144423007965</t>
+    <t xml:space="preserve">1.49144434928894</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843729496002</t>
@@ -851,49 +851,49 @@
     <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948584079742</t>
+    <t xml:space="preserve">1.50948560237885</t>
   </si>
   <si>
     <t xml:space="preserve">1.50347185134888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48167157173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4959545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51249289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497555732727</t>
+    <t xml:space="preserve">1.48167145252228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49595463275909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51249277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497543811798</t>
   </si>
   <si>
     <t xml:space="preserve">1.52151358127594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49369931221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49896156787872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602398395538</t>
+    <t xml:space="preserve">1.49369943141937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49896132946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602410316467</t>
   </si>
   <si>
     <t xml:space="preserve">1.496706366539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50798237323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54857611656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47039568424225</t>
+    <t xml:space="preserve">1.5079824924469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5485759973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242342472076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47039544582367</t>
   </si>
   <si>
     <t xml:space="preserve">1.47941648960114</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">1.52903079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51399612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158293247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511414051056</t>
+    <t xml:space="preserve">1.51399600505829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158305168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511425971985</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609333515167</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">1.63126718997955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67637133598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682601928711</t>
+    <t xml:space="preserve">1.67637145519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6568261384964</t>
   </si>
   <si>
     <t xml:space="preserve">1.69140589237213</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">1.71997177600861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65381896495819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937803268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735017299652</t>
+    <t xml:space="preserve">1.65381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937827110291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6673504114151</t>
   </si>
   <si>
     <t xml:space="preserve">1.66885387897491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778746843338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035722732544</t>
+    <t xml:space="preserve">1.67787492275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035734653473</t>
   </si>
   <si>
     <t xml:space="preserve">1.67186069488525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68839919567108</t>
+    <t xml:space="preserve">1.6883989572525</t>
   </si>
   <si>
     <t xml:space="preserve">1.6868953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65983295440674</t>
+    <t xml:space="preserve">1.65983271598816</t>
   </si>
   <si>
     <t xml:space="preserve">1.63878440856934</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">1.64630174636841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74402737617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213869571686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965615272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175312519073</t>
+    <t xml:space="preserve">1.74402713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115926265717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318747997284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213857650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175324440002</t>
   </si>
   <si>
     <t xml:space="preserve">1.86430537700653</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">1.83874642848969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76657950878143</t>
+    <t xml:space="preserve">1.76657974720001</t>
   </si>
   <si>
     <t xml:space="preserve">1.71245467662811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66133630275726</t>
+    <t xml:space="preserve">1.66133642196655</t>
   </si>
   <si>
     <t xml:space="preserve">1.76206922531128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77560031414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83423578739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80566990375519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220804691315</t>
+    <t xml:space="preserve">1.77560043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83423590660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220780849457</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899258136749</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70193028450012</t>
+    <t xml:space="preserve">1.70193016529083</t>
   </si>
   <si>
     <t xml:space="preserve">1.69441294670105</t>
@@ -1043,43 +1043,43 @@
     <t xml:space="preserve">1.68388831615448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63728082180023</t>
+    <t xml:space="preserve">1.63728094100952</t>
   </si>
   <si>
     <t xml:space="preserve">1.66434335708618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72448229789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71846842765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755894184113</t>
+    <t xml:space="preserve">1.72448217868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846830844879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755858421326</t>
   </si>
   <si>
     <t xml:space="preserve">1.73500669002533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73951685428619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73650991916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71395826339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161406517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906217098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920123100281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82671844959259</t>
+    <t xml:space="preserve">1.73951709270477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73651015758514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71395814418793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161418437958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82671856880188</t>
   </si>
   <si>
     <t xml:space="preserve">1.80416619777679</t>
@@ -1088,73 +1088,73 @@
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168377399445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664885997772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409672737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678803920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927034378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701045513153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468169212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865689277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399829387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797349452972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.810302734375</t>
+    <t xml:space="preserve">1.88685739040375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168389320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7966490983963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409684658051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913176059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927046298981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870108127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81030285358429</t>
   </si>
   <si>
     <t xml:space="preserve">1.90235233306885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83331513404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263221263885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660753250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291221141815</t>
+    <t xml:space="preserve">1.83331537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263233184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660729408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291209220886</t>
   </si>
   <si>
     <t xml:space="preserve">1.76427817344666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67989981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524109363556</t>
+    <t xml:space="preserve">1.6798996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524121284485</t>
   </si>
   <si>
     <t xml:space="preserve">1.67222893238068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74893701076508</t>
+    <t xml:space="preserve">1.74893689155579</t>
   </si>
   <si>
     <t xml:space="preserve">1.65688753128052</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">1.64154601097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5801796913147</t>
+    <t xml:space="preserve">1.58017957210541</t>
   </si>
   <si>
     <t xml:space="preserve">1.66455829143524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62620413303375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51497805118561</t>
+    <t xml:space="preserve">1.62620425224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250893115997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5149781703949</t>
   </si>
   <si>
     <t xml:space="preserve">1.53031957149506</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">1.48813033103943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41525816917419</t>
+    <t xml:space="preserve">1.41525793075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.4114226102829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3730685710907</t>
+    <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
     <t xml:space="preserve">1.35005629062653</t>
@@ -1199,61 +1199,61 @@
     <t xml:space="preserve">1.380739569664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39224565029144</t>
+    <t xml:space="preserve">1.39224553108215</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39991641044617</t>
+    <t xml:space="preserve">1.39991652965546</t>
   </si>
   <si>
     <t xml:space="preserve">1.35772716999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35389196872711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34238576889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403172969818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2810195684433</t>
+    <t xml:space="preserve">1.35389184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34238564968109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28101944923401</t>
   </si>
   <si>
     <t xml:space="preserve">1.26951324939728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25417172908783</t>
+    <t xml:space="preserve">1.25417160987854</t>
   </si>
   <si>
     <t xml:space="preserve">1.24650084972382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25800716876984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29636096954346</t>
+    <t xml:space="preserve">1.25800728797913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29636085033417</t>
   </si>
   <si>
     <t xml:space="preserve">1.28869020938873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30019640922546</t>
+    <t xml:space="preserve">1.30019652843475</t>
   </si>
   <si>
     <t xml:space="preserve">1.29252552986145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31937325000763</t>
+    <t xml:space="preserve">1.31937336921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.30786716938019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33087956905365</t>
+    <t xml:space="preserve">1.33087944984436</t>
   </si>
   <si>
     <t xml:space="preserve">1.33855020999908</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">1.33471488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31553792953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39608097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
+    <t xml:space="preserve">1.31553781032562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39608108997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457477092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.40375196933746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36156260967255</t>
+    <t xml:space="preserve">1.36156249046326</t>
   </si>
   <si>
     <t xml:space="preserve">1.36539793014526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43443500995636</t>
+    <t xml:space="preserve">1.43443489074707</t>
   </si>
   <si>
     <t xml:space="preserve">1.37690412998199</t>
@@ -1289,61 +1289,61 @@
     <t xml:space="preserve">1.38841021060944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34622097015381</t>
+    <t xml:space="preserve">1.3462210893631</t>
   </si>
   <si>
     <t xml:space="preserve">1.32704412937164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27334845066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320868968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706017494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38903474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36109435558319</t>
+    <t xml:space="preserve">1.27334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320880889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706029415131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3890346288681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3610942363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916247844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34512829780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508572101593</t>
+    <t xml:space="preserve">1.35311138629913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3451281785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508560180664</t>
   </si>
   <si>
     <t xml:space="preserve">1.39701759815216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41298353672028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4010089635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40899205207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41697490215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46886420249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4968044757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877904891968</t>
+    <t xml:space="preserve">1.41298341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40100908279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40899193286896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4169750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46886432170868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49680459499359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877892971039</t>
   </si>
   <si>
     <t xml:space="preserve">1.51277041435242</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.49281299114227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46487271785736</t>
+    <t xml:space="preserve">1.46487283706665</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079596042633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44491529464722</t>
+    <t xml:space="preserve">1.44491517543793</t>
   </si>
   <si>
     <t xml:space="preserve">1.45289838314056</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">1.42495799064636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42096650600433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500044822693</t>
+    <t xml:space="preserve">1.42096638679504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500056743622</t>
   </si>
   <si>
     <t xml:space="preserve">1.39302611351013</t>
@@ -1385,9 +1385,6 @@
     <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37306869029999</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.36907732486725</t>
   </si>
   <si>
@@ -1397,19 +1394,19 @@
     <t xml:space="preserve">1.3491199016571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4848301410675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47684729099274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46088135242462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48882162570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075326442719</t>
+    <t xml:space="preserve">1.48483002185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47684717178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46088123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48882150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075338363647</t>
   </si>
   <si>
     <t xml:space="preserve">1.51676201820374</t>
@@ -1418,22 +1415,22 @@
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659147262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56465971469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54071080684662</t>
+    <t xml:space="preserve">1.59659159183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5646595954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54071068763733</t>
   </si>
   <si>
     <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52873635292053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58860862255096</t>
+    <t xml:space="preserve">1.52873623371124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58860850334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
@@ -1445,13 +1442,13 @@
     <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470217227936</t>
+    <t xml:space="preserve">1.54470241069794</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52474498748779</t>
+    <t xml:space="preserve">1.52474474906921</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264280319214</t>
@@ -1460,28 +1457,28 @@
     <t xml:space="preserve">1.67642104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801207065582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88397789001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784152507782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539860725403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05960321426392</t>
+    <t xml:space="preserve">1.86801195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88397812843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478417634964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539836883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05960273742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329618453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926212310791</t>
+    <t xml:space="preserve">2.20329642295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926236152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724485397339</t>
@@ -1490,22 +1487,22 @@
     <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2352283000946</t>
+    <t xml:space="preserve">2.23522806167603</t>
   </si>
   <si>
     <t xml:space="preserve">2.11548376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9877564907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82011437416077</t>
+    <t xml:space="preserve">1.98775660991669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82011449337006</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809734344482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91591000556946</t>
+    <t xml:space="preserve">1.91590988636017</t>
   </si>
   <si>
     <t xml:space="preserve">1.86002898216248</t>
@@ -1517,22 +1514,22 @@
     <t xml:space="preserve">1.44890677928925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5925999879837</t>
+    <t xml:space="preserve">1.59260010719299</t>
   </si>
   <si>
     <t xml:space="preserve">1.72431898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62852323055267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448928833008</t>
+    <t xml:space="preserve">1.62852334976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64448916912079</t>
   </si>
   <si>
     <t xml:space="preserve">1.68440389633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60457456111908</t>
+    <t xml:space="preserve">1.60457444190979</t>
   </si>
   <si>
     <t xml:space="preserve">1.6604551076889</t>
@@ -1541,58 +1538,58 @@
     <t xml:space="preserve">1.65247213840485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74826765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633613109589</t>
+    <t xml:space="preserve">1.74826776981354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633589267731</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843819618225</t>
+    <t xml:space="preserve">1.66843807697296</t>
   </si>
   <si>
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238686561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75625061988831</t>
+    <t xml:space="preserve">1.69238698482513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625097751617</t>
   </si>
   <si>
     <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792691707611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92389273643494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757211208344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456270217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8567955493927</t>
+    <t xml:space="preserve">1.9079270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582461357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389309406281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757223129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456258296967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679543018341</t>
   </si>
   <si>
     <t xml:space="preserve">1.84029066562653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81553328037262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.790776014328</t>
+    <t xml:space="preserve">1.81553363800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077625274658</t>
   </si>
   <si>
     <t xml:space="preserve">1.75776648521423</t>
@@ -1601,7 +1598,7 @@
     <t xml:space="preserve">1.79902851581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7742714881897</t>
+    <t xml:space="preserve">1.77427124977112</t>
   </si>
   <si>
     <t xml:space="preserve">1.76601886749268</t>
@@ -1610,22 +1607,22 @@
     <t xml:space="preserve">1.74126136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78252375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74951386451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69999945163727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68349432945251</t>
+    <t xml:space="preserve">1.78252387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495139837265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69999933242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6834944486618</t>
   </si>
   <si>
     <t xml:space="preserve">1.67524206638336</t>
@@ -1634,94 +1631,94 @@
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873742103577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
   </si>
   <si>
     <t xml:space="preserve">1.69174706935883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72475671768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048480033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398015499115</t>
+    <t xml:space="preserve">1.7247565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048491954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398003578186</t>
   </si>
   <si>
     <t xml:space="preserve">1.62572765350342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62985372543335</t>
+    <t xml:space="preserve">1.62985384464264</t>
   </si>
   <si>
     <t xml:space="preserve">1.60922276973724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89805734157562</t>
+    <t xml:space="preserve">1.89805769920349</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582437515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04660153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96407687664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9393196105957</t>
+    <t xml:space="preserve">2.04660129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96407699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931949138641</t>
   </si>
   <si>
     <t xml:space="preserve">1.87330007553101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88155269622803</t>
+    <t xml:space="preserve">1.88155281543732</t>
   </si>
   <si>
     <t xml:space="preserve">1.88980519771576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86504793167114</t>
+    <t xml:space="preserve">1.86504781246185</t>
   </si>
   <si>
     <t xml:space="preserve">1.92281472682953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93106722831726</t>
+    <t xml:space="preserve">1.93106710910797</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359152793884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883426189423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232949733734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98058199882507</t>
+    <t xml:space="preserve">1.98883450031281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232961654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98058187961578</t>
   </si>
   <si>
     <t xml:space="preserve">2.06310606002808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19514513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864036560059</t>
+    <t xml:space="preserve">2.19514489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
     <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16213488578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563012123108</t>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563035964966</t>
   </si>
   <si>
     <t xml:space="preserve">2.19566059112549</t>
@@ -1730,7 +1727,7 @@
     <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18715000152588</t>
+    <t xml:space="preserve">2.18715023994446</t>
   </si>
   <si>
     <t xml:space="preserve">2.15310907363892</t>
@@ -1742,7 +1739,7 @@
     <t xml:space="preserve">2.08502674102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09353685379028</t>
+    <t xml:space="preserve">2.0935366153717</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800580024719</t>
@@ -1751,31 +1748,31 @@
     <t xml:space="preserve">2.03396487236023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0254545211792</t>
+    <t xml:space="preserve">2.02545428276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05098509788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482031345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184077739716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95737171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651615142822</t>
+    <t xml:space="preserve">2.05098533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184101581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95737183094025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98290276527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9743926525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0765163898468</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
@@ -1784,13 +1781,13 @@
     <t xml:space="preserve">2.05949568748474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99992334842682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99141311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843358039856</t>
+    <t xml:space="preserve">1.99992311000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99141299724579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843381881714</t>
   </si>
   <si>
     <t xml:space="preserve">2.01694393157959</t>
@@ -1802,10 +1799,10 @@
     <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14459848403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16161918640137</t>
+    <t xml:space="preserve">2.14459872245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16161942481995</t>
   </si>
   <si>
     <t xml:space="preserve">2.13608837127686</t>
@@ -1814,16 +1811,19 @@
     <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94035124778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9233306646347</t>
+    <t xml:space="preserve">1.94035112857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89779961109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722687959671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92333054542542</t>
   </si>
   <si>
     <t xml:space="preserve">1.94886159896851</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">2.07243394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08129072189331</t>
+    <t xml:space="preserve">2.08129048347473</t>
   </si>
   <si>
     <t xml:space="preserve">2.05472087860107</t>
@@ -1850,34 +1850,34 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958580493927</t>
+    <t xml:space="preserve">1.93958568572998</t>
   </si>
   <si>
     <t xml:space="preserve">1.9750120639801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99272525310516</t>
+    <t xml:space="preserve">1.99272513389587</t>
   </si>
   <si>
     <t xml:space="preserve">1.95729875564575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94844233989716</t>
+    <t xml:space="preserve">1.94844222068787</t>
   </si>
   <si>
     <t xml:space="preserve">1.86873316764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9218727350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91301620006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87758982181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072903156281</t>
+    <t xml:space="preserve">1.92187261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91301608085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775897026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072938919067</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
@@ -1886,37 +1886,37 @@
     <t xml:space="preserve">1.96615552902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90415966510773</t>
+    <t xml:space="preserve">1.90415954589844</t>
   </si>
   <si>
     <t xml:space="preserve">1.89530313014984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82445049285889</t>
+    <t xml:space="preserve">1.8244503736496</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673742294312</t>
+    <t xml:space="preserve">1.80673730373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70045876502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70488703250885</t>
+    <t xml:space="preserve">1.70045864582062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70488691329956</t>
   </si>
   <si>
     <t xml:space="preserve">1.77131116390228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81559383869171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74474155902863</t>
+    <t xml:space="preserve">1.815593957901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74474143981934</t>
   </si>
   <si>
     <t xml:space="preserve">1.85102021694183</t>
@@ -1928,28 +1928,28 @@
     <t xml:space="preserve">1.78016781806946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85987663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75802648067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76245450973511</t>
+    <t xml:space="preserve">1.85987651348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75802636146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7624546289444</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7535982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71817183494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70931529998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72702848911285</t>
+    <t xml:space="preserve">1.75359809398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71817195415497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7093151807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72702836990356</t>
   </si>
   <si>
     <t xml:space="preserve">1.90141236782074</t>
@@ -27212,7 +27212,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27238,7 +27238,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G950" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27290,7 +27290,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G952" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27316,7 +27316,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27394,7 +27394,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G956" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27420,7 +27420,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G957" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27472,7 +27472,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27498,7 +27498,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27550,7 +27550,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G962" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27576,7 +27576,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G963" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27602,7 +27602,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27628,7 +27628,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27654,7 +27654,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27680,7 +27680,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27706,7 +27706,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G968" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27732,7 +27732,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G969" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27758,7 +27758,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27784,7 +27784,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27810,7 +27810,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27862,7 +27862,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G974" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27914,7 +27914,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27940,7 +27940,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28018,7 +28018,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G980" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28044,7 +28044,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G981" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28070,7 +28070,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28174,7 +28174,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28200,7 +28200,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28330,7 +28330,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G992" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28356,7 +28356,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28408,7 +28408,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G995" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28434,7 +28434,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G996" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28486,7 +28486,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G998" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28512,7 +28512,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28538,7 +28538,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1000" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28564,7 +28564,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1001" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28616,7 +28616,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1003" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28694,7 +28694,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1006" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28720,7 +28720,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1007" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28772,7 +28772,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1009" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28798,7 +28798,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28824,7 +28824,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1011" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28850,7 +28850,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1012" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28902,7 +28902,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1014" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28928,7 +28928,7 @@
         <v>2</v>
       </c>
       <c r="G1015" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28954,7 +28954,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1016" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28980,7 +28980,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1017" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29006,7 +29006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1018" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29084,7 +29084,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1021" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29110,7 +29110,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29136,7 +29136,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1023" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29162,7 +29162,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1024" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29188,7 +29188,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1025" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29214,7 +29214,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29240,7 +29240,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1027" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29266,7 +29266,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1028" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29292,7 +29292,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1029" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29318,7 +29318,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1030" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29344,7 +29344,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1031" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29370,7 +29370,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1032" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29396,7 +29396,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1033" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29422,7 +29422,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1034" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29448,7 +29448,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1035" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29474,7 +29474,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1036" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29500,7 +29500,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1037" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29526,7 +29526,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1038" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29552,7 +29552,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1039" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29578,7 +29578,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29604,7 +29604,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1041" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29630,7 +29630,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1042" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29656,7 +29656,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1043" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29682,7 +29682,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1044" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29708,7 +29708,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1045" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29734,7 +29734,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1046" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29760,7 +29760,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29786,7 +29786,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1048" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29812,7 +29812,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29838,7 +29838,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1050" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29864,7 +29864,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1051" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29890,7 +29890,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29916,7 +29916,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1053" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29942,7 +29942,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1054" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29968,7 +29968,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1055" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29994,7 +29994,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1056" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30020,7 +30020,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1057" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30046,7 +30046,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1058" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30072,7 +30072,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30098,7 +30098,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30124,7 +30124,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1061" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30150,7 +30150,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1062" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30228,7 +30228,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1065" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30254,7 +30254,7 @@
         <v>2</v>
       </c>
       <c r="G1066" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30280,7 +30280,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1067" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30332,7 +30332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30358,7 +30358,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1070" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30384,7 +30384,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1071" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30514,7 +30514,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1076" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30540,7 +30540,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1077" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30644,7 +30644,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1081" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30670,7 +30670,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1082" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30696,7 +30696,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1083" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30722,7 +30722,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1084" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30748,7 +30748,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30774,7 +30774,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1086" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30800,7 +30800,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1087" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30826,7 +30826,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30852,7 +30852,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1089" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30878,7 +30878,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30904,7 +30904,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1091" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30930,7 +30930,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1092" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30956,7 +30956,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30982,7 +30982,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1094" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31008,7 +31008,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1095" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31034,7 +31034,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1096" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31060,7 +31060,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31086,7 +31086,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1098" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31112,7 +31112,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31138,7 +31138,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31164,7 +31164,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1101" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31190,7 +31190,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31216,7 +31216,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1103" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31242,7 +31242,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1104" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31268,7 +31268,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31294,7 +31294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1106" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31320,7 +31320,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1107" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31346,7 +31346,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1108" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31372,7 +31372,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1109" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31398,7 +31398,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31424,7 +31424,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1111" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31450,7 +31450,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1112" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31476,7 +31476,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1113" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31502,7 +31502,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31528,7 +31528,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1115" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31554,7 +31554,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1116" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31580,7 +31580,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31606,7 +31606,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1118" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31632,7 +31632,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1119" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31658,7 +31658,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1120" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31684,7 +31684,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31710,7 +31710,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1122" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31736,7 +31736,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31762,7 +31762,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31788,7 +31788,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1125" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31814,7 +31814,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31840,7 +31840,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31866,7 +31866,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1128" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31892,7 +31892,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31918,7 +31918,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1130" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31944,7 +31944,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31970,7 +31970,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1132" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31996,7 +31996,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1133" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32022,7 +32022,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1134" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32048,7 +32048,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1135" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32074,7 +32074,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1136" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32100,7 +32100,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32126,7 +32126,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1138" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32152,7 +32152,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32178,7 +32178,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1140" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32204,7 +32204,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1141" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32230,7 +32230,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32256,7 +32256,7 @@
         <v>2.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32282,7 +32282,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32308,7 +32308,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32334,7 +32334,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32360,7 +32360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32386,7 +32386,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1148" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32412,7 +32412,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32438,7 +32438,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1150" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32464,7 +32464,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32490,7 +32490,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32516,7 +32516,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1153" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32542,7 +32542,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1154" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32568,7 +32568,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1155" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32594,7 +32594,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1156" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32620,7 +32620,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1157" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32646,7 +32646,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1158" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32672,7 +32672,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1159" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32698,7 +32698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1160" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32724,7 +32724,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1161" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32750,7 +32750,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1162" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32776,7 +32776,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1163" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32802,7 +32802,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1164" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32828,7 +32828,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1165" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32854,7 +32854,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1166" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32880,7 +32880,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1167" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32906,7 +32906,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1168" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32932,7 +32932,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1169" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32958,7 +32958,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1170" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32984,7 +32984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1171" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33010,7 +33010,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33036,7 +33036,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1173" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33062,7 +33062,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33088,7 +33088,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1175" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33114,7 +33114,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1176" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33140,7 +33140,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1177" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33166,7 +33166,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1178" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33192,7 +33192,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1179" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33218,7 +33218,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1180" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33244,7 +33244,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1181" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33270,7 +33270,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1182" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33296,7 +33296,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1183" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33322,7 +33322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33348,7 +33348,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1185" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33374,7 +33374,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1186" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33400,7 +33400,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1187" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33426,7 +33426,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1188" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33452,7 +33452,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1189" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33478,7 +33478,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1190" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33504,7 +33504,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33530,7 +33530,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1192" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33556,7 +33556,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1193" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33582,7 +33582,7 @@
         <v>2</v>
       </c>
       <c r="G1194" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33608,7 +33608,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1195" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33634,7 +33634,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33660,7 +33660,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1197" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33686,7 +33686,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33712,7 +33712,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1199" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33738,7 +33738,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1200" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33764,7 +33764,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33790,7 +33790,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33816,7 +33816,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33842,7 +33842,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33868,7 +33868,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33894,7 +33894,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1206" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33920,7 +33920,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1207" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33946,7 +33946,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1208" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33972,7 +33972,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1209" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33998,7 +33998,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34024,7 +34024,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34050,7 +34050,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34076,7 +34076,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1213" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34102,7 +34102,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1214" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34128,7 +34128,7 @@
         <v>2</v>
       </c>
       <c r="G1215" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34154,7 +34154,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34180,7 +34180,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1217" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34206,7 +34206,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1218" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34232,7 +34232,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34258,7 +34258,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1220" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34284,7 +34284,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34310,7 +34310,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34336,7 +34336,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34362,7 +34362,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34388,7 +34388,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1225" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34414,7 +34414,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1226" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34440,7 +34440,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34466,7 +34466,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1228" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34492,7 +34492,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1229" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34518,7 +34518,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34544,7 +34544,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1231" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34570,7 +34570,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34596,7 +34596,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34622,7 +34622,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34648,7 +34648,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1235" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34674,7 +34674,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34700,7 +34700,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34726,7 +34726,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34752,7 +34752,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34778,7 +34778,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1240" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34804,7 +34804,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1241" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34830,7 +34830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1242" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34856,7 +34856,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1243" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34882,7 +34882,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1244" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34908,7 +34908,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1245" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34934,7 +34934,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34960,7 +34960,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34986,7 +34986,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35012,7 +35012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1249" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35038,7 +35038,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1250" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35064,7 +35064,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35090,7 +35090,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1252" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35116,7 +35116,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35142,7 +35142,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35168,7 +35168,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1256" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35220,7 +35220,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35246,7 +35246,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1258" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35272,7 +35272,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35298,7 +35298,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1260" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35324,7 +35324,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1261" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35350,7 +35350,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1262" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35376,7 +35376,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35402,7 +35402,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35428,7 +35428,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35454,7 +35454,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35480,7 +35480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35506,7 +35506,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1268" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35532,7 +35532,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1269" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35558,7 +35558,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1270" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35584,7 +35584,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1271" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35610,7 +35610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35636,7 +35636,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35662,7 +35662,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1274" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35688,7 +35688,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35714,7 +35714,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1276" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35740,7 +35740,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1277" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35766,7 +35766,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1278" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35792,7 +35792,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35818,7 +35818,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1280" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35844,7 +35844,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1281" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35870,7 +35870,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1282" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35896,7 +35896,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1283" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35922,7 +35922,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1284" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35948,7 +35948,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35974,7 +35974,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1286" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36000,7 +36000,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1287" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36026,7 +36026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1288" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36052,7 +36052,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36078,7 +36078,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36104,7 +36104,7 @@
         <v>2.25</v>
       </c>
       <c r="G1291" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36130,7 +36130,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1292" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36156,7 +36156,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36182,7 +36182,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1294" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36208,7 +36208,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36234,7 +36234,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1296" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36260,7 +36260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36286,7 +36286,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1298" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36312,7 +36312,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36338,7 +36338,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36390,7 +36390,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1302" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36416,7 +36416,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1303" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36442,7 +36442,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1304" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36468,7 +36468,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36494,7 +36494,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36520,7 +36520,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36546,7 +36546,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36572,7 +36572,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36598,7 +36598,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36624,7 +36624,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1311" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36650,7 +36650,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1312" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36676,7 +36676,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1313" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36702,7 +36702,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36728,7 +36728,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1315" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36754,7 +36754,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36780,7 +36780,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36806,7 +36806,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36832,7 +36832,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36858,7 +36858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1320" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36884,7 +36884,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1321" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36910,7 +36910,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1322" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36936,7 +36936,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1323" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36962,7 +36962,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1324" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36988,7 +36988,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37014,7 +37014,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1326" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37040,7 +37040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37066,7 +37066,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1328" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37092,7 +37092,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37118,7 +37118,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1330" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37144,7 +37144,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1331" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37170,7 +37170,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37196,7 +37196,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37222,7 +37222,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1334" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37248,7 +37248,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1335" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37274,7 +37274,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1336" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37300,7 +37300,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37326,7 +37326,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37352,7 +37352,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1339" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37378,7 +37378,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1340" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37404,7 +37404,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1341" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37430,7 +37430,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1342" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37456,7 +37456,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37482,7 +37482,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1344" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37508,7 +37508,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37534,7 +37534,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37560,7 +37560,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1347" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37586,7 +37586,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37612,7 +37612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37638,7 +37638,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1350" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37664,7 +37664,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1351" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37690,7 +37690,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1352" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37794,7 +37794,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1356" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37820,7 +37820,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1357" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37846,7 +37846,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1358" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37872,7 +37872,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1359" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37898,7 +37898,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1360" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37924,7 +37924,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1361" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37976,7 +37976,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1363" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38002,7 +38002,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1364" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38028,7 +38028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1365" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38080,7 +38080,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1367" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38106,7 +38106,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1368" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38184,7 +38184,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38210,7 +38210,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1372" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38236,7 +38236,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38262,7 +38262,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1374" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38288,7 +38288,7 @@
         <v>2.5</v>
       </c>
       <c r="G1375" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38314,7 +38314,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38340,7 +38340,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1377" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38366,7 +38366,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38392,7 +38392,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38418,7 +38418,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38444,7 +38444,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1381" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38470,7 +38470,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1382" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38496,7 +38496,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1383" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38522,7 +38522,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1384" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38548,7 +38548,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38574,7 +38574,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38600,7 +38600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1387" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38626,7 +38626,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1388" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38652,7 +38652,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1389" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38756,7 +38756,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>522</v>
+        <v>601</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -68300,7 +68300,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.5464351852</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>1650</v>
@@ -68321,6 +68321,32 @@
         <v>725</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.5705787037</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>12479</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1468118429184</t>
+    <t xml:space="preserve">1.14681172370911</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615501880646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544274330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09623825550079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09695017337799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407328605652</t>
+    <t xml:space="preserve">1.12615489959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1254426240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552597999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831963062286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09623801708221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09695029258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407340526581</t>
   </si>
   <si>
     <t xml:space="preserve">1.09053957462311</t>
@@ -71,70 +71,70 @@
     <t xml:space="preserve">1.08412885665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00007688999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943804740905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925996959209442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666112422943</t>
+    <t xml:space="preserve">1.00007677078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943804681301117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925997078418732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993666231632233</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004910469055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859676837921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492424964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213059902191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711664676666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02571988105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02643239498138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073359489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354087352753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91602486371994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435581684113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530849456787</t>
+    <t xml:space="preserve">1.01004898548126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492436885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213047981262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711676597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572000026703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495203495026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02643227577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0207337141037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94736635684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354146957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024804115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530909061432</t>
   </si>
   <si>
     <t xml:space="preserve">0.985830664634705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970160007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612343788147</t>
+    <t xml:space="preserve">0.970160126686096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612462997437</t>
   </si>
   <si>
     <t xml:space="preserve">0.962324619293213</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">1.00435054302216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997939944267273</t>
+    <t xml:space="preserve">0.997939825057983</t>
   </si>
   <si>
     <t xml:space="preserve">0.989392220973969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991529047489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419767856598</t>
+    <t xml:space="preserve">0.991529166698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979420006275177</t>
   </si>
   <si>
     <t xml:space="preserve">0.99081689119339</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">0.997227549552917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01717221736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01503527164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00078916549683</t>
+    <t xml:space="preserve">1.01717209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0150351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00078904628754</t>
   </si>
   <si>
     <t xml:space="preserve">1.02215826511383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00577521324158</t>
+    <t xml:space="preserve">1.00577509403229</t>
   </si>
   <si>
     <t xml:space="preserve">1.00648748874664</t>
@@ -185,67 +185,67 @@
     <t xml:space="preserve">1.01076149940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00221371650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984406113624573</t>
+    <t xml:space="preserve">1.00221383571625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984406232833862</t>
   </si>
   <si>
     <t xml:space="preserve">1.00791215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03284275531769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01930916309357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979963302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10051202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084841132164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982729911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18171453475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1681809425354</t>
+    <t xml:space="preserve">1.03284299373627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01930904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979975223541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10051190853119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982741832733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18171465396881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818070411682</t>
   </si>
   <si>
     <t xml:space="preserve">1.13185334205627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13968861103058</t>
+    <t xml:space="preserve">1.13968873023987</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393471717834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689496040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09766268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16105794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15963351726532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683938980103</t>
+    <t xml:space="preserve">1.11689484119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09766280651093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16105782985687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15963315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14752388000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683950901031</t>
   </si>
   <si>
     <t xml:space="preserve">1.13612723350525</t>
@@ -254,31 +254,31 @@
     <t xml:space="preserve">1.12900412082672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14467489719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316687107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1703177690506</t>
+    <t xml:space="preserve">1.14467477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316699028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17031764984131</t>
   </si>
   <si>
     <t xml:space="preserve">1.18100237846375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19738554954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2109192609787</t>
+    <t xml:space="preserve">1.197385430336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091938018799</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163153648376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20593309402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302842140198</t>
+    <t xml:space="preserve">1.20593297481537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302854061127</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089147567749</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">1.19596087932587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23548460006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22670161724091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790948390961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1630243062973</t>
+    <t xml:space="preserve">1.23548448085785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22670137882233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937337398529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1879096031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16302418708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.16595208644867</t>
@@ -308,37 +308,37 @@
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375625133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570509433746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911782741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424120426178</t>
+    <t xml:space="preserve">1.16375648975372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570521354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911770820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424132347107</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11837708950043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10154283046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10520243644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0993469953537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545810222626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1293557882309</t>
+    <t xml:space="preserve">1.11837697029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10154271125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10520231723785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545834064484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12935590744019</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203669548035</t>
@@ -350,28 +350,28 @@
     <t xml:space="preserve">1.07226598262787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06860625743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13081979751587</t>
+    <t xml:space="preserve">1.06860637664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
     <t xml:space="preserve">1.12423241138458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15716898441315</t>
+    <t xml:space="preserve">1.15716886520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.18717777729034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18205416202545</t>
+    <t xml:space="preserve">1.18205428123474</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839479446411</t>
+    <t xml:space="preserve">1.17839467525482</t>
   </si>
   <si>
     <t xml:space="preserve">1.20401191711426</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">1.1747350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18571388721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546689510345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19303321838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035243034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888854026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2149909734726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2069399356842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21425867080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22231018543243</t>
+    <t xml:space="preserve">1.18571364879608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1930330991745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035231113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888842105865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499073505402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693957805634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21425902843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22230994701385</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962915897369</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">1.22450578212738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25524640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745994091034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208957195282</t>
+    <t xml:space="preserve">1.25524652004242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232741355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745970249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208969116211</t>
   </si>
   <si>
     <t xml:space="preserve">1.29550218582153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29184257984161</t>
+    <t xml:space="preserve">1.29184246063232</t>
   </si>
   <si>
     <t xml:space="preserve">1.27866804599762</t>
@@ -446,73 +446,73 @@
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354466915131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963795185089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26183378696442</t>
+    <t xml:space="preserve">1.25890600681305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354443073273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2596378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26183366775513</t>
   </si>
   <si>
     <t xml:space="preserve">1.26256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915299892426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694849014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109316825867</t>
+    <t xml:space="preserve">1.26915287971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694837093353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109304904938</t>
   </si>
   <si>
     <t xml:space="preserve">1.26402950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24719524383545</t>
+    <t xml:space="preserve">1.24719536304474</t>
   </si>
   <si>
     <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21938228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19962048530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669258594513</t>
+    <t xml:space="preserve">1.21938252449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962060451508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669282436371</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376516342163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766261100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742453098297</t>
+    <t xml:space="preserve">1.17766273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742465019226</t>
   </si>
   <si>
     <t xml:space="preserve">1.20620775222778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19230103492737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059051036835</t>
+    <t xml:space="preserve">1.19230115413666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059039115906</t>
   </si>
   <si>
     <t xml:space="preserve">1.16522014141083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15643715858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16887962818146</t>
+    <t xml:space="preserve">1.15643703937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16887974739075</t>
   </si>
   <si>
     <t xml:space="preserve">1.17693078517914</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.17985844612122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18498194217682</t>
+    <t xml:space="preserve">1.18498182296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.17400312423706</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">1.16814768314362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1461900472641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14326238632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11252152919769</t>
+    <t xml:space="preserve">1.14619028568268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14326250553131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11252164840698</t>
   </si>
   <si>
     <t xml:space="preserve">1.1344792842865</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.10593450069427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10007905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1227685213089</t>
+    <t xml:space="preserve">1.10007917881012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12276864051819</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032593250275</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">1.11618113517761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13960289955139</t>
+    <t xml:space="preserve">1.1396027803421</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278920173645</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.14399433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14179861545563</t>
+    <t xml:space="preserve">1.14179849624634</t>
   </si>
   <si>
     <t xml:space="preserve">1.13521134853363</t>
@@ -590,25 +590,25 @@
     <t xml:space="preserve">1.14253044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1944967508316</t>
+    <t xml:space="preserve">1.19449687004089</t>
   </si>
   <si>
     <t xml:space="preserve">1.1813223361969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17253935337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912650108337</t>
+    <t xml:space="preserve">1.17253923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912662029266</t>
   </si>
   <si>
     <t xml:space="preserve">1.13887083530426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13374745845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350046634674</t>
+    <t xml:space="preserve">1.13374733924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350058555603</t>
   </si>
   <si>
     <t xml:space="preserve">1.12569630146027</t>
@@ -617,46 +617,46 @@
     <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12496435642242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1264283657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936458110809</t>
+    <t xml:space="preserve">1.12496423721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12642824649811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936481952667</t>
   </si>
   <si>
     <t xml:space="preserve">1.15277743339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16741585731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22377395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596943378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25671029090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792730808258</t>
+    <t xml:space="preserve">1.16741597652435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22377383708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596955299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25671017169952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792742729187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060809612274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26622557640076</t>
+    <t xml:space="preserve">1.26622533798218</t>
   </si>
   <si>
     <t xml:space="preserve">1.2684211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29769802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867671966553</t>
+    <t xml:space="preserve">1.29769790172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867683887482</t>
   </si>
   <si>
     <t xml:space="preserve">1.29403841495514</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">1.32477915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32404708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3101407289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3284387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037868976593</t>
+    <t xml:space="preserve">1.32404720783234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32843863964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037880897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135762691498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30282163619995</t>
+    <t xml:space="preserve">1.30282139778137</t>
   </si>
   <si>
     <t xml:space="preserve">1.31526410579681</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">1.32624292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36137533187866</t>
+    <t xml:space="preserve">1.36137509346008</t>
   </si>
   <si>
     <t xml:space="preserve">1.33941769599915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34673678874969</t>
+    <t xml:space="preserve">1.34673666954041</t>
   </si>
   <si>
     <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3686945438385</t>
+    <t xml:space="preserve">1.36869430541992</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772439956665</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">1.40529048442841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39065217971802</t>
+    <t xml:space="preserve">1.39065194129944</t>
   </si>
   <si>
     <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114592552185</t>
+    <t xml:space="preserve">1.41114580631256</t>
   </si>
   <si>
     <t xml:space="preserve">1.38186883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37162220478058</t>
+    <t xml:space="preserve">1.371621966362</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884562253952</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">1.41927742958069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45009875297546</t>
+    <t xml:space="preserve">1.45009863376617</t>
   </si>
   <si>
     <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53654837608337</t>
+    <t xml:space="preserve">1.53654825687408</t>
   </si>
   <si>
     <t xml:space="preserve">1.56361079216003</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">1.58616280555725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60570800304413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51700305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51098930835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693370819092</t>
+    <t xml:space="preserve">1.60570812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5170031785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51098918914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693382740021</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866463661194</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814036369324</t>
+    <t xml:space="preserve">1.46814024448395</t>
   </si>
   <si>
     <t xml:space="preserve">1.46964395046234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44333291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483649730682</t>
+    <t xml:space="preserve">1.44333302974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483637809753</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882262706757</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574634075165</t>
+    <t xml:space="preserve">1.40574610233307</t>
   </si>
   <si>
     <t xml:space="preserve">1.45836770534515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45911943912506</t>
+    <t xml:space="preserve">1.45911955833435</t>
   </si>
   <si>
     <t xml:space="preserve">1.47189891338348</t>
@@ -809,28 +809,28 @@
     <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41852569580078</t>
+    <t xml:space="preserve">1.41852581501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4207808971405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42604303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41702246665955</t>
+    <t xml:space="preserve">1.42078101634979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42604315280914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41702222824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.42529153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44408476352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716128826141</t>
+    <t xml:space="preserve">1.44408464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716116905212</t>
   </si>
   <si>
     <t xml:space="preserve">1.49219596385956</t>
@@ -854,109 +854,109 @@
     <t xml:space="preserve">1.50948572158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50347173213959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167157173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4959545135498</t>
+    <t xml:space="preserve">1.50347185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167145252228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49595463275909</t>
   </si>
   <si>
     <t xml:space="preserve">1.51249289512634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497555732727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49369943141937</t>
+    <t xml:space="preserve">1.50497543811798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151334285736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369955062866</t>
   </si>
   <si>
     <t xml:space="preserve">1.49896144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602398395538</t>
+    <t xml:space="preserve">1.52602386474609</t>
   </si>
   <si>
     <t xml:space="preserve">1.496706366539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50798225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5485759973526</t>
+    <t xml:space="preserve">1.50798237323761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54857623577118</t>
   </si>
   <si>
     <t xml:space="preserve">1.48242342472076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47039544582367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941637039185</t>
+    <t xml:space="preserve">1.47039556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941648960114</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903091907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51399612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158293247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511437892914</t>
+    <t xml:space="preserve">1.52903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51399624347687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158281326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511425971985</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609345436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126707077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67637097835541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682590007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69140589237213</t>
+    <t xml:space="preserve">1.63126718997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6763710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65682601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69140565395355</t>
   </si>
   <si>
     <t xml:space="preserve">1.70644068717957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71997213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937815189362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735017299652</t>
+    <t xml:space="preserve">1.71997177600861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381896495819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735029220581</t>
   </si>
   <si>
     <t xml:space="preserve">1.66885375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67787504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839919567108</t>
+    <t xml:space="preserve">1.67787480354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035698890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186081409454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839907646179</t>
   </si>
   <si>
     <t xml:space="preserve">1.68689548969269</t>
@@ -968,67 +968,67 @@
     <t xml:space="preserve">1.63878440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64630174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74402713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115926265717</t>
+    <t xml:space="preserve">1.6463018655777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402737617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115914344788</t>
   </si>
   <si>
     <t xml:space="preserve">1.81318700313568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79213857650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965615272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430501937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8387463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245455741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133677959442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7620689868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77560019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83423578739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80567002296448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220804691315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72899258136749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74102056026459</t>
+    <t xml:space="preserve">1.79213833808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175312519073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430513858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874619007111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71245467662811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133654117584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206922531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77560043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83423566818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80566966533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72899270057678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7410204410553</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598576545715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75154495239258</t>
+    <t xml:space="preserve">1.75154483318329</t>
   </si>
   <si>
     <t xml:space="preserve">1.72297871112823</t>
@@ -1037,118 +1037,115 @@
     <t xml:space="preserve">1.70193028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69441282749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388867378235</t>
+    <t xml:space="preserve">1.69441270828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388843536377</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434335708618</t>
+    <t xml:space="preserve">1.66434323787689</t>
   </si>
   <si>
     <t xml:space="preserve">1.72448217868805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71846842765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500669002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951697349548</t>
+    <t xml:space="preserve">1.71846854686737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755894184113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500680923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951721191406</t>
   </si>
   <si>
     <t xml:space="preserve">1.73651003837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71395814418793</t>
+    <t xml:space="preserve">1.71395790576935</t>
   </si>
   <si>
     <t xml:space="preserve">1.78161418437958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75906193256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920087337494</t>
+    <t xml:space="preserve">1.75906229019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920111179352</t>
   </si>
   <si>
     <t xml:space="preserve">1.82671844959259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416667461395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87933993339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685703277588</t>
+    <t xml:space="preserve">1.80416643619537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87934005260468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88685727119446</t>
   </si>
   <si>
     <t xml:space="preserve">1.81168377399445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79664897918701</t>
+    <t xml:space="preserve">1.79664885997772</t>
   </si>
   <si>
     <t xml:space="preserve">1.77409696578979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78913164138794</t>
+    <t xml:space="preserve">1.78913176059723</t>
   </si>
   <si>
     <t xml:space="preserve">1.85678791999817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84927034378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87933969497681</t>
+    <t xml:space="preserve">1.84927022457123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870108127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.89468145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84865689277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179737329483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81030309200287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235209465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263209342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660753250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291197299957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427805423737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67989981174469</t>
+    <t xml:space="preserve">1.84865713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399829387665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81030285358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235221385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331513404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8026317358017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660741329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427817344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67989945411682</t>
   </si>
   <si>
     <t xml:space="preserve">1.69524145126343</t>
@@ -1157,10 +1154,10 @@
     <t xml:space="preserve">1.67222905158997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74893689155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688741207123</t>
+    <t xml:space="preserve">1.74893665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688753128052</t>
   </si>
   <si>
     <t xml:space="preserve">1.64154589176178</t>
@@ -1169,28 +1166,28 @@
     <t xml:space="preserve">1.58017957210541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66455817222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620425224304</t>
+    <t xml:space="preserve">1.66455829143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620413303375</t>
   </si>
   <si>
     <t xml:space="preserve">1.57250893115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5149781703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031969070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48813033103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41525793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4114226102829</t>
+    <t xml:space="preserve">1.51497805118561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031945228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48813045024872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4152580499649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41142272949219</t>
   </si>
   <si>
     <t xml:space="preserve">1.37306869029999</t>
@@ -1202,25 +1199,25 @@
     <t xml:space="preserve">1.380739569664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39224576950073</t>
+    <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39991664886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35772705078125</t>
+    <t xml:space="preserve">1.39991641044617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35772728919983</t>
   </si>
   <si>
     <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34238564968109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403184890747</t>
+    <t xml:space="preserve">1.34238576889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403172969818</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101944923401</t>
@@ -1235,13 +1232,13 @@
     <t xml:space="preserve">1.24650096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25800716876984</t>
+    <t xml:space="preserve">1.25800704956055</t>
   </si>
   <si>
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869009017944</t>
+    <t xml:space="preserve">1.28869020938873</t>
   </si>
   <si>
     <t xml:space="preserve">1.30019640922546</t>
@@ -1253,10 +1250,10 @@
     <t xml:space="preserve">1.31937336921692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30786716938019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33087944984436</t>
+    <t xml:space="preserve">1.30786728858948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33087933063507</t>
   </si>
   <si>
     <t xml:space="preserve">1.33855020999908</t>
@@ -1268,40 +1265,40 @@
     <t xml:space="preserve">1.31553792953491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39608108997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38457489013672</t>
+    <t xml:space="preserve">1.39608120918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38457477092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.40375185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36156260967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539804935455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443500995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37690401077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38841032981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3462210893631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704424858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334868907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320868968964</t>
+    <t xml:space="preserve">1.36156272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37690412998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38841021060944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34622085094452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704412937164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320880889893</t>
   </si>
   <si>
     <t xml:space="preserve">1.37706029415131</t>
@@ -1310,7 +1307,7 @@
     <t xml:space="preserve">1.3890346288681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3610942363739</t>
+    <t xml:space="preserve">1.36109435558319</t>
   </si>
   <si>
     <t xml:space="preserve">1.32916235923767</t>
@@ -1322,22 +1319,22 @@
     <t xml:space="preserve">1.3451281785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36508584022522</t>
+    <t xml:space="preserve">1.36508572101593</t>
   </si>
   <si>
     <t xml:space="preserve">1.39701759815216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41298341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40100908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40899205207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41697478294373</t>
+    <t xml:space="preserve">1.41298353672028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4010089635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40899193286896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41697490215302</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886432170868</t>
@@ -1349,19 +1346,19 @@
     <t xml:space="preserve">1.50877892971039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51277041435242</t>
+    <t xml:space="preserve">1.51277029514313</t>
   </si>
   <si>
     <t xml:space="preserve">1.49281311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46487283706665</t>
+    <t xml:space="preserve">1.46487271785736</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079596042633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44491529464722</t>
+    <t xml:space="preserve">1.44491517543793</t>
   </si>
   <si>
     <t xml:space="preserve">1.45289838314056</t>
@@ -1370,13 +1367,13 @@
     <t xml:space="preserve">1.43693232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42495787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096650600433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500068664551</t>
+    <t xml:space="preserve">1.42495799064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096638679504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500056743622</t>
   </si>
   <si>
     <t xml:space="preserve">1.39302611351013</t>
@@ -1388,6 +1385,9 @@
     <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
+    <t xml:space="preserve">1.37306880950928</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">1.46088123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48882150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075338363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51676189899445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56066811084747</t>
+    <t xml:space="preserve">1.48882162570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075350284576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51676201820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56066834926605</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659159183502</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58860862255096</t>
+    <t xml:space="preserve">1.58860850334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">1.54869389533997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53671932220459</t>
+    <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470229148865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55268537998199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52474498748779</t>
+    <t xml:space="preserve">1.55268526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5247448682785</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264268398285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801183223724</t>
+    <t xml:space="preserve">1.67642092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801195144653</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397789001465</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">2.15539860725403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05960321426392</t>
+    <t xml:space="preserve">2.05960297584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338133811951</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">2.20329642295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926236152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22724533081055</t>
+    <t xml:space="preserve">2.21926212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22724509239197</t>
   </si>
   <si>
     <t xml:space="preserve">2.1793475151062</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">1.98775637149811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011425495148</t>
+    <t xml:space="preserve">1.82011437416077</t>
   </si>
   <si>
     <t xml:space="preserve">1.82809722423553</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">1.91591000556946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86002898216248</t>
+    <t xml:space="preserve">1.86002910137177</t>
   </si>
   <si>
     <t xml:space="preserve">1.63650631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5925999879837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72431874275208</t>
+    <t xml:space="preserve">1.44890677928925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59259986877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72431898117065</t>
   </si>
   <si>
     <t xml:space="preserve">1.62852334976196</t>
@@ -1529,31 +1529,31 @@
     <t xml:space="preserve">1.64448916912079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68440389633179</t>
+    <t xml:space="preserve">1.68440401554108</t>
   </si>
   <si>
     <t xml:space="preserve">1.60457444190979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6604551076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65247237682343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826776981354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7163360118866</t>
+    <t xml:space="preserve">1.66045522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65247213840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633577346802</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843795776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61255753040314</t>
+    <t xml:space="preserve">1.66843807697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
     <t xml:space="preserve">1.69238698482513</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">1.7562507390976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76423382759094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90792679786682</t>
+    <t xml:space="preserve">1.76423370838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90792667865753</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582461357117</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">1.92389285564423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94757199287415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456246376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679566860199</t>
+    <t xml:space="preserve">1.94757223129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456258296967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85679543018341</t>
   </si>
   <si>
     <t xml:space="preserve">1.84029066562653</t>
@@ -1592,37 +1592,37 @@
     <t xml:space="preserve">1.81553339958191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.790776014328</t>
+    <t xml:space="preserve">1.79077613353729</t>
   </si>
   <si>
     <t xml:space="preserve">1.75776648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79902839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77427136898041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76601874828339</t>
+    <t xml:space="preserve">1.79902863502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77427113056183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76601886749268</t>
   </si>
   <si>
     <t xml:space="preserve">1.74126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78252375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300909996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74951386451721</t>
+    <t xml:space="preserve">1.78252387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300898075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495139837265</t>
   </si>
   <si>
     <t xml:space="preserve">1.71650421619415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69999945163727</t>
+    <t xml:space="preserve">1.69999933242798</t>
   </si>
   <si>
     <t xml:space="preserve">1.6834944486618</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">1.66698980331421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
   </si>
   <si>
     <t xml:space="preserve">1.69174695014954</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">1.7247565984726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65048480033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
+    <t xml:space="preserve">1.65048491954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398015499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572765350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.62985384464264</t>
@@ -1667,43 +1667,43 @@
     <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96407723426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9393196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8733001947403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88980519771576</t>
+    <t xml:space="preserve">1.96407675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931949138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155281543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88980507850647</t>
   </si>
   <si>
     <t xml:space="preserve">1.86504781246185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92281496524811</t>
+    <t xml:space="preserve">1.92281472682953</t>
   </si>
   <si>
     <t xml:space="preserve">1.93106710910797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883426189423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232961654663</t>
+    <t xml:space="preserve">2.01359152793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883450031281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232937812805</t>
   </si>
   <si>
     <t xml:space="preserve">1.98058187961578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06310629844666</t>
+    <t xml:space="preserve">2.06310606002808</t>
   </si>
   <si>
     <t xml:space="preserve">2.19514489173889</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17038774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563012123108</t>
+    <t xml:space="preserve">2.17038750648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213488578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563035964966</t>
   </si>
   <si>
     <t xml:space="preserve">2.19566059112549</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18715000152588</t>
+    <t xml:space="preserve">2.18715023994446</t>
   </si>
   <si>
     <t xml:space="preserve">2.15310883522034</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">2.11906766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08502626419067</t>
+    <t xml:space="preserve">2.08502674102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.09353685379028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800603866577</t>
+    <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
     <t xml:space="preserve">2.03396487236023</t>
@@ -1757,76 +1757,76 @@
     <t xml:space="preserve">2.05098533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91482031345367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184077739716</t>
+    <t xml:space="preserve">1.91482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184101581573</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737183094025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290276527405</t>
+    <t xml:space="preserve">1.98290300369263</t>
   </si>
   <si>
     <t xml:space="preserve">1.97439241409302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0765163898468</t>
+    <t xml:space="preserve">2.07651615142822</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949544906616</t>
+    <t xml:space="preserve">2.05949568748474</t>
   </si>
   <si>
     <t xml:space="preserve">1.99992334842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99141323566437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843358039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01694369316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204696655273</t>
+    <t xml:space="preserve">1.99141299724579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843381881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01694393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204744338989</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14459872245789</t>
+    <t xml:space="preserve">2.14459848403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.16161942481995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13608837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96588218212128</t>
+    <t xml:space="preserve">2.13608860969543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.94035112857819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977997303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226855754852</t>
+    <t xml:space="preserve">1.89779984951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722687959671</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94886159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07243418693542</t>
+    <t xml:space="preserve">1.94886136054993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07243394851685</t>
   </si>
   <si>
     <t xml:space="preserve">2.08129048347473</t>
@@ -1856,37 +1856,37 @@
     <t xml:space="preserve">1.99272513389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95729899406433</t>
+    <t xml:space="preserve">1.95729875564575</t>
   </si>
   <si>
     <t xml:space="preserve">1.94844222068787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8687332868576</t>
+    <t xml:space="preserve">1.86873316764832</t>
   </si>
   <si>
     <t xml:space="preserve">1.92187261581421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91301620006561</t>
+    <t xml:space="preserve">1.91301608085632</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775897026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93072915077209</t>
+    <t xml:space="preserve">1.93072938919067</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615529060364</t>
+    <t xml:space="preserve">1.96615552902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.90415954589844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89530289173126</t>
+    <t xml:space="preserve">1.89530313014984</t>
   </si>
   <si>
     <t xml:space="preserve">1.8244503736496</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673742294312</t>
+    <t xml:space="preserve">1.80673730373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
@@ -1910,22 +1910,22 @@
     <t xml:space="preserve">1.77131116390228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81559383869171</t>
+    <t xml:space="preserve">1.815593957901</t>
   </si>
   <si>
     <t xml:space="preserve">1.74474143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85101997852325</t>
+    <t xml:space="preserve">1.85102021694183</t>
   </si>
   <si>
     <t xml:space="preserve">1.84216356277466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78016769886017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85987663269043</t>
+    <t xml:space="preserve">1.78016781806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85987651348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.75802636146545</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">1.71817195415497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70931529998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72702848911285</t>
+    <t xml:space="preserve">1.7093151807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72702836990356</t>
   </si>
   <si>
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295221328735</t>
+    <t xml:space="preserve">1.88295209407806</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988086223602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142046928406</t>
+    <t xml:space="preserve">1.79988074302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142035007477</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757925510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988872528076</t>
+    <t xml:space="preserve">1.73526966571808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757913589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988884449005</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6614283323288</t>
+    <t xml:space="preserve">1.66142845153809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97525370121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833303451538</t>
+    <t xml:space="preserve">1.9752539396286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833291530609</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2048,28 +2048,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372606754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526168346405</t>
+    <t xml:space="preserve">1.81372594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526180267334</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8921822309494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910277843475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064250469208</t>
+    <t xml:space="preserve">1.89218235015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910301685333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371421337128</t>
+    <t xml:space="preserve">1.99371409416199</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -19019,7 +19019,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G634" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19045,7 +19045,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G635" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19071,7 +19071,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G636" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19097,7 +19097,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19123,7 +19123,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19227,7 +19227,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G642" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19253,7 +19253,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19305,7 +19305,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G645" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19331,7 +19331,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G646" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19357,7 +19357,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G647" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19383,7 +19383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G648" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19409,7 +19409,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G649" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19435,7 +19435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G650" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19461,7 +19461,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G651" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19513,7 +19513,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G653" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19539,7 +19539,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G654" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19695,7 +19695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G660" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19721,7 +19721,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G661" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19747,7 +19747,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G662" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19799,7 +19799,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G664" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19825,7 +19825,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G665" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -19929,7 +19929,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G669" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -19981,7 +19981,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20163,7 +20163,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G678" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20293,7 +20293,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20319,7 +20319,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G684" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20345,7 +20345,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G685" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20371,7 +20371,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G686" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20397,7 +20397,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G687" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20605,7 +20605,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G695" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20631,7 +20631,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G696" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20839,7 +20839,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20943,7 +20943,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G708" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -20969,7 +20969,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21125,7 +21125,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G715" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21151,7 +21151,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G716" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21177,7 +21177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21203,7 +21203,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G718" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21229,7 +21229,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G719" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21255,7 +21255,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G720" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21281,7 +21281,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G721" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21307,7 +21307,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G722" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21333,7 +21333,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G723" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21359,7 +21359,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21385,7 +21385,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G725" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21411,7 +21411,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21437,7 +21437,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G727" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21463,7 +21463,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G728" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21489,7 +21489,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G729" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21515,7 +21515,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G730" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21541,7 +21541,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21567,7 +21567,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G732" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21593,7 +21593,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21619,7 +21619,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21645,7 +21645,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G735" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21671,7 +21671,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G736" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21697,7 +21697,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G737" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21723,7 +21723,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G738" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21749,7 +21749,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G739" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21775,7 +21775,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G740" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21801,7 +21801,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G741" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21827,7 +21827,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G742" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -21853,7 +21853,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G743" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21879,7 +21879,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G744" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21905,7 +21905,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21931,7 +21931,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G746" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21957,7 +21957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G747" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21983,7 +21983,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G748" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22009,7 +22009,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G749" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22035,7 +22035,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22061,7 +22061,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G751" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22087,7 +22087,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G752" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22113,7 +22113,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G753" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22139,7 +22139,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G754" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22165,7 +22165,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G755" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22191,7 +22191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G756" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22217,7 +22217,7 @@
         <v>1.75</v>
       </c>
       <c r="G757" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22243,7 +22243,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G758" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22269,7 +22269,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G759" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22295,7 +22295,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G760" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22321,7 +22321,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G761" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22347,7 +22347,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G762" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22373,7 +22373,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22399,7 +22399,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G764" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22425,7 +22425,7 @@
         <v>1.625</v>
       </c>
       <c r="G765" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22451,7 +22451,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G766" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22477,7 +22477,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G767" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22503,7 +22503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G768" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22529,7 +22529,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G769" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22555,7 +22555,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G770" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22581,7 +22581,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G771" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22607,7 +22607,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G772" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22633,7 +22633,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G773" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22659,7 +22659,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G774" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22685,7 +22685,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G775" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22711,7 +22711,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22737,7 +22737,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G777" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22763,7 +22763,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G778" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22789,7 +22789,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G779" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22815,7 +22815,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G780" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22841,7 +22841,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G781" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22867,7 +22867,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G782" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22893,7 +22893,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G783" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22919,7 +22919,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G784" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22945,7 +22945,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G785" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22971,7 +22971,7 @@
         <v>1.75</v>
       </c>
       <c r="G786" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22997,7 +22997,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G787" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23023,7 +23023,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G788" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23049,7 +23049,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G789" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23075,7 +23075,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G790" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23101,7 +23101,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G791" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23127,7 +23127,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G792" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23153,7 +23153,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G793" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23179,7 +23179,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G794" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23205,7 +23205,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G795" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23231,7 +23231,7 @@
         <v>1.75</v>
       </c>
       <c r="G796" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23257,7 +23257,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G797" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23283,7 +23283,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G798" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23309,7 +23309,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G799" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23335,7 +23335,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G800" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23361,7 +23361,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G801" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23387,7 +23387,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G802" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23413,7 +23413,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G803" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23439,7 +23439,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G804" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23465,7 +23465,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G805" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23491,7 +23491,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G806" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23517,7 +23517,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G807" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23543,7 +23543,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G808" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23569,7 +23569,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G809" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23595,7 +23595,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G810" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23621,7 +23621,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G811" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23647,7 +23647,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23673,7 +23673,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G813" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23699,7 +23699,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23725,7 +23725,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G815" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23751,7 +23751,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G816" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23777,7 +23777,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G817" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23803,7 +23803,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G818" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23829,7 +23829,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G819" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23855,7 +23855,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G820" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23881,7 +23881,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23907,7 +23907,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23933,7 +23933,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G823" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23959,7 +23959,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G824" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23985,7 +23985,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G825" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24011,7 +24011,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24037,7 +24037,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24063,7 +24063,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G828" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24089,7 +24089,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24115,7 +24115,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G830" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24141,7 +24141,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G831" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24167,7 +24167,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G832" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24193,7 +24193,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G833" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24219,7 +24219,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G834" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24245,7 +24245,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G835" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24271,7 +24271,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G836" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24297,7 +24297,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G837" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24323,7 +24323,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G838" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24349,7 +24349,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G839" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24375,7 +24375,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G840" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24401,7 +24401,7 @@
         <v>1.75</v>
       </c>
       <c r="G841" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24427,7 +24427,7 @@
         <v>1.75</v>
       </c>
       <c r="G842" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24453,7 +24453,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G843" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24479,7 +24479,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24505,7 +24505,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24531,7 +24531,7 @@
         <v>1.75</v>
       </c>
       <c r="G846" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24557,7 +24557,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G847" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24583,7 +24583,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G848" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24609,7 +24609,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G849" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24635,7 +24635,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G850" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24661,7 +24661,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G851" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24687,7 +24687,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G852" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24713,7 +24713,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G853" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24739,7 +24739,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G854" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24765,7 +24765,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24791,7 +24791,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G856" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24817,7 +24817,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24843,7 +24843,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G858" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24869,7 +24869,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G859" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24895,7 +24895,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G860" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24921,7 +24921,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G861" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24947,7 +24947,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G862" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24973,7 +24973,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G863" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24999,7 +24999,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G864" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25025,7 +25025,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G865" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25051,7 +25051,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G866" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25077,7 +25077,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G867" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25103,7 +25103,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G868" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25129,7 +25129,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G869" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25155,7 +25155,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G870" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25181,7 +25181,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25207,7 +25207,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G872" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25233,7 +25233,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G873" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25259,7 +25259,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25285,7 +25285,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G875" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25311,7 +25311,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G876" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25337,7 +25337,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G877" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25363,7 +25363,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G878" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25389,7 +25389,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G879" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25415,7 +25415,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G880" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25441,7 +25441,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G881" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25467,7 +25467,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G882" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25493,7 +25493,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25519,7 +25519,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25545,7 +25545,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25571,7 +25571,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25597,7 +25597,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25623,7 +25623,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G888" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25649,7 +25649,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G889" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25675,7 +25675,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G890" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25701,7 +25701,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25727,7 +25727,7 @@
         <v>1.75</v>
       </c>
       <c r="G892" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25753,7 +25753,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G893" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25779,7 +25779,7 @@
         <v>1.75</v>
       </c>
       <c r="G894" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25805,7 +25805,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G895" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25831,7 +25831,7 @@
         <v>1.75</v>
       </c>
       <c r="G896" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25857,7 +25857,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G897" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25883,7 +25883,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G898" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25909,7 +25909,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G899" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25935,7 +25935,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G900" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25961,7 +25961,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G901" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25987,7 +25987,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G902" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26013,7 +26013,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G903" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26039,7 +26039,7 @@
         <v>1.875</v>
       </c>
       <c r="G904" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26065,7 +26065,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G905" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26091,7 +26091,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G906" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26117,7 +26117,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G907" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26143,7 +26143,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G908" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26169,7 +26169,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G909" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26195,7 +26195,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G910" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26221,7 +26221,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26247,7 +26247,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G912" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26273,7 +26273,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G913" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26299,7 +26299,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G914" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26325,7 +26325,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G915" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26351,7 +26351,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G916" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26377,7 +26377,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G917" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26403,7 +26403,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G918" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26429,7 +26429,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G919" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26455,7 +26455,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G920" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26481,7 +26481,7 @@
         <v>1.75</v>
       </c>
       <c r="G921" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26507,7 +26507,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G922" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26533,7 +26533,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G923" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26559,7 +26559,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G924" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26585,7 +26585,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G925" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26611,7 +26611,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G926" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26637,7 +26637,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G927" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26663,7 +26663,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G928" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26689,7 +26689,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G929" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26715,7 +26715,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26741,7 +26741,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G931" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26767,7 +26767,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G932" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26793,7 +26793,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G933" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26819,7 +26819,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26845,7 +26845,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G935" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26871,7 +26871,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G936" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26897,7 +26897,7 @@
         <v>1.75</v>
       </c>
       <c r="G937" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26923,7 +26923,7 @@
         <v>1.75</v>
       </c>
       <c r="G938" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26949,7 +26949,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G939" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26975,7 +26975,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G940" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27001,7 +27001,7 @@
         <v>1.75</v>
       </c>
       <c r="G941" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27027,7 +27027,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G942" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27053,7 +27053,7 @@
         <v>1.75</v>
       </c>
       <c r="G943" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27079,7 +27079,7 @@
         <v>1.75</v>
       </c>
       <c r="G944" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27105,7 +27105,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27131,7 +27131,7 @@
         <v>1.75</v>
       </c>
       <c r="G946" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27157,7 +27157,7 @@
         <v>1.75</v>
       </c>
       <c r="G947" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27183,7 +27183,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G948" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27209,7 +27209,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27261,7 +27261,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G951" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27313,7 +27313,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27339,7 +27339,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27365,7 +27365,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G955" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27443,7 +27443,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27469,7 +27469,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27495,7 +27495,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27521,7 +27521,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G961" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27599,7 +27599,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27625,7 +27625,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27651,7 +27651,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27677,7 +27677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27755,7 +27755,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27781,7 +27781,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27807,7 +27807,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27833,7 +27833,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G973" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27885,7 +27885,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G975" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27911,7 +27911,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27937,7 +27937,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27963,7 +27963,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27989,7 +27989,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G979" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28067,7 +28067,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28093,7 +28093,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G983" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28119,7 +28119,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G984" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28145,7 +28145,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G985" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28223,7 +28223,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28249,7 +28249,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G989" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28275,7 +28275,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28301,7 +28301,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28379,7 +28379,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G994" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28457,7 +28457,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G997" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28587,7 +28587,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1002" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28639,7 +28639,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1004" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28665,7 +28665,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1005" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28743,7 +28743,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1008" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28873,7 +28873,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1013" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29029,7 +29029,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1019" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29055,7 +29055,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30173,7 +30173,7 @@
         <v>1.75</v>
       </c>
       <c r="G1063" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30199,7 +30199,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1064" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30303,7 +30303,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1068" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30407,7 +30407,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1072" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30433,7 +30433,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30459,7 +30459,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1074" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30485,7 +30485,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1075" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30563,7 +30563,7 @@
         <v>1.75</v>
       </c>
       <c r="G1078" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30589,7 +30589,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1079" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30615,7 +30615,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1080" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -68396,6 +68396,58 @@
         <v>727</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.3333333333</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6797453704</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>14496</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681160449982</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">1.1254426240921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09552597999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831963062286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09623801708221</t>
+    <t xml:space="preserve">1.09552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0962381362915</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695029258728</t>
@@ -65,49 +65,49 @@
     <t xml:space="preserve">1.10407340526581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09053957462311</t>
+    <t xml:space="preserve">1.0905396938324</t>
   </si>
   <si>
     <t xml:space="preserve">1.08412885665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00007677078247</t>
+    <t xml:space="preserve">1.00007665157318</t>
   </si>
   <si>
     <t xml:space="preserve">0.943804681301117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925997078418732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666231632233</t>
+    <t xml:space="preserve">0.925996959209442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993666112422943</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004898548126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492436885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03213047981262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03711676597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02572000026703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495203495026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02643227577209</t>
+    <t xml:space="preserve">1.01004910469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859652996063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492424964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03213059902191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03711652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02571988105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495215415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02643215656281</t>
   </si>
   <si>
     <t xml:space="preserve">1.0207337141037</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">0.94736635684967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900354146957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024804115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435522079468</t>
+    <t xml:space="preserve">0.900354087352753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91602486371994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435462474823</t>
   </si>
   <si>
     <t xml:space="preserve">0.939530909061432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985830664634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970160126686096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612462997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00435054302216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997939825057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392220973969</t>
+    <t xml:space="preserve">0.985830545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612403392792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324678897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997939884662628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392161369324</t>
   </si>
   <si>
     <t xml:space="preserve">0.991529166698456</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">0.979420006275177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99081689119339</t>
+    <t xml:space="preserve">0.990816831588745</t>
   </si>
   <si>
     <t xml:space="preserve">0.987967610359192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997227549552917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717209815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0150351524353</t>
+    <t xml:space="preserve">0.997227609157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717221736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01503527164459</t>
   </si>
   <si>
     <t xml:space="preserve">1.00078904628754</t>
@@ -185,55 +185,55 @@
     <t xml:space="preserve">1.01076149940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00221383571625</t>
+    <t xml:space="preserve">1.00221359729767</t>
   </si>
   <si>
     <t xml:space="preserve">0.984406232833862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00791215896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03284299373627</t>
+    <t xml:space="preserve">1.00791203975677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03284287452698</t>
   </si>
   <si>
     <t xml:space="preserve">1.01930904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996610641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979975223541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10051190853119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982741832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18171465396881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16818070411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185334205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968873023987</t>
+    <t xml:space="preserve">1.03996598720551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979963302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1005117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084841132164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18171453475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818106174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185346126556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968861103058</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393471717834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689484119415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09766280651093</t>
+    <t xml:space="preserve">1.11689496040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
     <t xml:space="preserve">1.16105782985687</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">1.14752388000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13683950901031</t>
+    <t xml:space="preserve">1.13683938980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12900412082672</t>
+    <t xml:space="preserve">1.12900400161743</t>
   </si>
   <si>
     <t xml:space="preserve">1.14467477798462</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">1.17316699028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17031764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18100237846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.197385430336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21091938018799</t>
+    <t xml:space="preserve">1.17031788825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18100249767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19738531112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091914176941</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163153648376</t>
@@ -278,28 +278,28 @@
     <t xml:space="preserve">1.20593297481537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22302854061127</t>
+    <t xml:space="preserve">1.22302830219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.22089147567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596087932587</t>
+    <t xml:space="preserve">1.19596099853516</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548448085785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22670137882233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937337398529</t>
+    <t xml:space="preserve">1.22670149803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937349319458</t>
   </si>
   <si>
     <t xml:space="preserve">1.1879096031189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16302418708801</t>
+    <t xml:space="preserve">1.1630243062973</t>
   </si>
   <si>
     <t xml:space="preserve">1.16595208644867</t>
@@ -308,52 +308,52 @@
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375648975372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570521354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911770820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424132347107</t>
+    <t xml:space="preserve">1.16375625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570497512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911782741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424108505249</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11837697029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10154271125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10520231723785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545834064484</t>
+    <t xml:space="preserve">1.11837708950043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10154283046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10520267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0993469953537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545822143555</t>
   </si>
   <si>
     <t xml:space="preserve">1.12935590744019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12715995311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07226598262787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13081967830658</t>
+    <t xml:space="preserve">1.12203657627106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12716007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07226586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860649585724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13081955909729</t>
   </si>
   <si>
     <t xml:space="preserve">1.12423241138458</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">1.15716886520386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18717777729034</t>
+    <t xml:space="preserve">1.18717765808105</t>
   </si>
   <si>
     <t xml:space="preserve">1.18205428123474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20767152309418</t>
+    <t xml:space="preserve">1.20767140388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.17839467525482</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">1.20401191711426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18351805210114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20474374294281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1747350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571364879608</t>
+    <t xml:space="preserve">1.18351817131042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20474398136139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17473495006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571388721466</t>
   </si>
   <si>
     <t xml:space="preserve">1.17546701431274</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">1.1930330991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20035231113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888842105865</t>
+    <t xml:space="preserve">1.20035243034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888830184937</t>
   </si>
   <si>
     <t xml:space="preserve">1.21499073505402</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">1.20693957805634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21425902843475</t>
+    <t xml:space="preserve">1.21425879001617</t>
   </si>
   <si>
     <t xml:space="preserve">1.22230994701385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962915897369</t>
+    <t xml:space="preserve">1.22962927818298</t>
   </si>
   <si>
     <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22450578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524652004242</t>
+    <t xml:space="preserve">1.22450566291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524640083313</t>
   </si>
   <si>
     <t xml:space="preserve">1.28232741355896</t>
@@ -431,43 +431,43 @@
     <t xml:space="preserve">1.31745970249176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30208969116211</t>
+    <t xml:space="preserve">1.30208945274353</t>
   </si>
   <si>
     <t xml:space="preserve">1.29550218582153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29184246063232</t>
+    <t xml:space="preserve">1.2918426990509</t>
   </si>
   <si>
     <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24426770210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25890600681305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354443073273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2596378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26183366775513</t>
+    <t xml:space="preserve">1.24426758289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25890624523163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354454994202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25963807106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26183378696442</t>
   </si>
   <si>
     <t xml:space="preserve">1.26256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915287971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694837093353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109304904938</t>
+    <t xml:space="preserve">1.26915299892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694849014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109316825867</t>
   </si>
   <si>
     <t xml:space="preserve">1.26402950286865</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">1.24719536304474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2230418920517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21938252449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19962060451508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669282436371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17766273021698</t>
+    <t xml:space="preserve">1.22304177284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21938240528107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962048530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669270515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376504421234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17766284942627</t>
   </si>
   <si>
     <t xml:space="preserve">1.19742465019226</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">1.17693078517914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19522881507874</t>
+    <t xml:space="preserve">1.19522905349731</t>
   </si>
   <si>
     <t xml:space="preserve">1.17985844612122</t>
@@ -527,46 +527,46 @@
     <t xml:space="preserve">1.18498182296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17400312423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107546329498</t>
+    <t xml:space="preserve">1.17400300502777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107534408569</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814768314362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14619028568268</t>
+    <t xml:space="preserve">1.14619016647339</t>
   </si>
   <si>
     <t xml:space="preserve">1.14326250553131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11252164840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1344792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325371265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593450069427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007917881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276864051819</t>
+    <t xml:space="preserve">1.11252152919769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13447940349579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984074115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593438148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007894039154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1227685213089</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032593250275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11618113517761</t>
+    <t xml:space="preserve">1.11618149280548</t>
   </si>
   <si>
     <t xml:space="preserve">1.1396027803421</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14399433135986</t>
+    <t xml:space="preserve">1.14399421215057</t>
   </si>
   <si>
     <t xml:space="preserve">1.14179849624634</t>
@@ -584,67 +584,67 @@
     <t xml:space="preserve">1.13521134853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13813889026642</t>
+    <t xml:space="preserve">1.13813877105713</t>
   </si>
   <si>
     <t xml:space="preserve">1.14253044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19449687004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1813223361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17253923416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912662029266</t>
+    <t xml:space="preserve">1.19449698925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18132245540619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17253935337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912650108337</t>
   </si>
   <si>
     <t xml:space="preserve">1.13887083530426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13374733924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350058555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569630146027</t>
+    <t xml:space="preserve">1.13374757766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350046634674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569618225098</t>
   </si>
   <si>
     <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12496423721313</t>
+    <t xml:space="preserve">1.12496435642242</t>
   </si>
   <si>
     <t xml:space="preserve">1.12642824649811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15936481952667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277743339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741597652435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22377383708954</t>
+    <t xml:space="preserve">1.15936470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15277755260468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741585731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22377395629883</t>
   </si>
   <si>
     <t xml:space="preserve">1.22596955299377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25671017169952</t>
+    <t xml:space="preserve">1.25671029090881</t>
   </si>
   <si>
     <t xml:space="preserve">1.24792742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24060809612274</t>
+    <t xml:space="preserve">1.24060821533203</t>
   </si>
   <si>
     <t xml:space="preserve">1.26622533798218</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">1.29769790172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30867683887482</t>
+    <t xml:space="preserve">1.30867671966553</t>
   </si>
   <si>
     <t xml:space="preserve">1.29403841495514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32477915287018</t>
+    <t xml:space="preserve">1.32477903366089</t>
   </si>
   <si>
     <t xml:space="preserve">1.32404720783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32843863964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037880897522</t>
+    <t xml:space="preserve">1.3101407289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3284387588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037868976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135762691498</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">1.32624292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36137509346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941769599915</t>
+    <t xml:space="preserve">1.36137521266937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941781520844</t>
   </si>
   <si>
     <t xml:space="preserve">1.34673666954041</t>
@@ -701,40 +701,40 @@
     <t xml:space="preserve">1.38699245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36869430541992</t>
+    <t xml:space="preserve">1.36869442462921</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772439956665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35991132259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37454974651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40529048442841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39065194129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39650738239288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114580631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38186883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.371621966362</t>
+    <t xml:space="preserve">1.3599112033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37454986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40529036521912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39065217971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39650726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114592552185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3818690776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162208557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884562253952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41927742958069</t>
+    <t xml:space="preserve">1.41927754878998</t>
   </si>
   <si>
     <t xml:space="preserve">1.45009863376617</t>
@@ -743,25 +743,25 @@
     <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53654825687408</t>
+    <t xml:space="preserve">1.53654837608337</t>
   </si>
   <si>
     <t xml:space="preserve">1.56361079216003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58616280555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60570812225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5170031785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51098918914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693382740021</t>
+    <t xml:space="preserve">1.58616268634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60570800304413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51700305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51098930835724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693370819092</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866463661194</t>
@@ -770,79 +770,79 @@
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814024448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964395046234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44333302974701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483637809753</t>
+    <t xml:space="preserve">1.46814036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964371204376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44333291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483661651611</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882262706757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4320570230484</t>
+    <t xml:space="preserve">1.43205690383911</t>
   </si>
   <si>
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574610233307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45836770534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45911955833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189891338348</t>
+    <t xml:space="preserve">1.40574622154236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45836794376373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45911943912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189903259277</t>
   </si>
   <si>
     <t xml:space="preserve">1.4531055688858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42829835414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41852581501007</t>
+    <t xml:space="preserve">1.42829847335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41852569580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42078101634979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42604315280914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41702222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42529153823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44408464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716116905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219596385956</t>
+    <t xml:space="preserve">1.4207808971405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42604303359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41702234745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42529141902924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44408488273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4771614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219584465027</t>
   </si>
   <si>
     <t xml:space="preserve">1.46663689613342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46588528156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144423007965</t>
+    <t xml:space="preserve">1.46588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144411087036</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843729496002</t>
@@ -851,34 +851,34 @@
     <t xml:space="preserve">1.51850664615631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167145252228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49595463275909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51249289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497543811798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52151334285736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49369955062866</t>
+    <t xml:space="preserve">1.50948584079742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347197055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167157173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4959545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51249277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497555732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52151346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369931221008</t>
   </si>
   <si>
     <t xml:space="preserve">1.49896144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602386474609</t>
+    <t xml:space="preserve">1.52602410316467</t>
   </si>
   <si>
     <t xml:space="preserve">1.496706366539</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">1.50798237323761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54857623577118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242342472076</t>
+    <t xml:space="preserve">1.54857611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242330551147</t>
   </si>
   <si>
     <t xml:space="preserve">1.47039556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47941648960114</t>
+    <t xml:space="preserve">1.47941637039185</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203797340393</t>
@@ -905,103 +905,103 @@
     <t xml:space="preserve">1.52903079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51399624347687</t>
+    <t xml:space="preserve">1.51399612426758</t>
   </si>
   <si>
     <t xml:space="preserve">1.55158281326294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56511425971985</t>
+    <t xml:space="preserve">1.56511414051056</t>
   </si>
   <si>
     <t xml:space="preserve">1.55609345436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126718997955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
+    <t xml:space="preserve">1.63126707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637133598328</t>
   </si>
   <si>
     <t xml:space="preserve">1.65682601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69140565395355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644068717957</t>
+    <t xml:space="preserve">1.69140577316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644056797028</t>
   </si>
   <si>
     <t xml:space="preserve">1.71997177600861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65381896495819</t>
+    <t xml:space="preserve">1.65381932258606</t>
   </si>
   <si>
     <t xml:space="preserve">1.67937803268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66735029220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66885375976562</t>
+    <t xml:space="preserve">1.66735053062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885364055634</t>
   </si>
   <si>
     <t xml:space="preserve">1.67787480354309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67035698890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186081409454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839907646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6463018655777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74402737617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115914344788</t>
+    <t xml:space="preserve">1.67035722732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186093330383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6883989572525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68689525127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983283519745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878428936005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64630174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402725696564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115926265717</t>
   </si>
   <si>
     <t xml:space="preserve">1.81318700313568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79213833808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965591430664</t>
+    <t xml:space="preserve">1.79213869571686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965603351593</t>
   </si>
   <si>
     <t xml:space="preserve">1.84175312519073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86430513858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83874619007111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657950878143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245467662811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133654117584</t>
+    <t xml:space="preserve">1.86430525779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657927036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133666038513</t>
   </si>
   <si>
     <t xml:space="preserve">1.76206922531128</t>
@@ -1010,61 +1010,61 @@
     <t xml:space="preserve">1.77560043334961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83423566818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80566966533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220792770386</t>
+    <t xml:space="preserve">1.83423578739166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80567002296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220816612244</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899270057678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7410204410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598576545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75154483318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297871112823</t>
+    <t xml:space="preserve">1.74102067947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598564624786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.751544713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72297894954681</t>
   </si>
   <si>
     <t xml:space="preserve">1.70193028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69441270828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388843536377</t>
+    <t xml:space="preserve">1.69441282749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388855457306</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434323787689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72448217868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71846854686737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75755894184113</t>
+    <t xml:space="preserve">1.66434335708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72448229789734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71846842765808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75755858421326</t>
   </si>
   <si>
     <t xml:space="preserve">1.73500680923462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73951721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73651003837585</t>
+    <t xml:space="preserve">1.73951697349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73651027679443</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395790576935</t>
@@ -1076,46 +1076,46 @@
     <t xml:space="preserve">1.75906229019165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81920111179352</t>
+    <t xml:space="preserve">1.81920087337494</t>
   </si>
   <si>
     <t xml:space="preserve">1.82671844959259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416643619537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87934005260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168377399445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664885997772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913176059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678791999817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927022457123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8870108127594</t>
+    <t xml:space="preserve">1.80416655540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87933969497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88685739040375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168389320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7966490983963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409684658051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8492705821991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88701057434082</t>
   </si>
   <si>
     <t xml:space="preserve">1.89468145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84865713119507</t>
+    <t xml:space="preserve">1.84865701198578</t>
   </si>
   <si>
     <t xml:space="preserve">1.86399829387665</t>
@@ -1124,46 +1124,46 @@
     <t xml:space="preserve">1.81797361373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81030285358429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235221385956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331513404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8026317358017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660741329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291209220886</t>
+    <t xml:space="preserve">1.81030261516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235245227814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263197422028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660729408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291197299957</t>
   </si>
   <si>
     <t xml:space="preserve">1.76427817344666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67989945411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524145126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222905158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74893665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154589176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58017957210541</t>
+    <t xml:space="preserve">1.67989981174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524133205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222893238068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74893653392792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688741207123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154601097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58017945289612</t>
   </si>
   <si>
     <t xml:space="preserve">1.66455829143524</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">1.57250893115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031945228577</t>
+    <t xml:space="preserve">1.5149781703949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031957149506</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813045024872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4152580499649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41142272949219</t>
+    <t xml:space="preserve">1.41525793075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4114226102829</t>
   </si>
   <si>
     <t xml:space="preserve">1.37306869029999</t>
@@ -1196,28 +1196,28 @@
     <t xml:space="preserve">1.35005629062653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.380739569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39224565029144</t>
+    <t xml:space="preserve">1.38073933124542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39224576950073</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39991641044617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35772728919983</t>
+    <t xml:space="preserve">1.39991652965546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35772716999054</t>
   </si>
   <si>
     <t xml:space="preserve">1.35389173030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34238576889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30403172969818</t>
+    <t xml:space="preserve">1.34238564968109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101944923401</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">1.26951324939728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25417160987854</t>
+    <t xml:space="preserve">1.25417172908783</t>
   </si>
   <si>
     <t xml:space="preserve">1.24650096893311</t>
@@ -1244,28 +1244,28 @@
     <t xml:space="preserve">1.30019640922546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29252552986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937336921692</t>
+    <t xml:space="preserve">1.29252541065216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937325000763</t>
   </si>
   <si>
     <t xml:space="preserve">1.30786728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33087933063507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855020999908</t>
+    <t xml:space="preserve">1.33087944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855032920837</t>
   </si>
   <si>
     <t xml:space="preserve">1.33471488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31553792953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39608120918274</t>
+    <t xml:space="preserve">1.31553781032562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39608108997345</t>
   </si>
   <si>
     <t xml:space="preserve">1.38457477092743</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">1.40375185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36156272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539793014526</t>
+    <t xml:space="preserve">1.36156249046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539804935455</t>
   </si>
   <si>
     <t xml:space="preserve">1.43443489074707</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">1.37690412998199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38841021060944</t>
+    <t xml:space="preserve">1.38841032981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.34622085094452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32704412937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320880889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706029415131</t>
+    <t xml:space="preserve">1.32704401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334868907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320868968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706017494202</t>
   </si>
   <si>
     <t xml:space="preserve">1.3890346288681</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">1.36109435558319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32916235923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3451281785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508572101593</t>
+    <t xml:space="preserve">1.32916247844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35311138629913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34512829780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508595943451</t>
   </si>
   <si>
     <t xml:space="preserve">1.39701759815216</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.46886432170868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4968044757843</t>
+    <t xml:space="preserve">1.49680459499359</t>
   </si>
   <si>
     <t xml:space="preserve">1.50877892971039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51277029514313</t>
+    <t xml:space="preserve">1.51277041435242</t>
   </si>
   <si>
     <t xml:space="preserve">1.49281311035156</t>
@@ -1358,36 +1358,33 @@
     <t xml:space="preserve">1.50079596042633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44491517543793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45289838314056</t>
+    <t xml:space="preserve">1.44491529464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45289826393127</t>
   </si>
   <si>
     <t xml:space="preserve">1.43693232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42495799064636</t>
+    <t xml:space="preserve">1.42495787143707</t>
   </si>
   <si>
     <t xml:space="preserve">1.42096638679504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40500056743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39302611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504314422607</t>
+    <t xml:space="preserve">1.40500044822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39302599430084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504302501678</t>
   </si>
   <si>
     <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37306880950928</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
@@ -1397,34 +1394,34 @@
     <t xml:space="preserve">1.3491199016571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4848301410675</t>
+    <t xml:space="preserve">1.48483026027679</t>
   </si>
   <si>
     <t xml:space="preserve">1.47684717178345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46088123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48882162570953</t>
+    <t xml:space="preserve">1.46088135242462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48882150650024</t>
   </si>
   <si>
     <t xml:space="preserve">1.52075350284576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51676201820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56066834926605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59659159183502</t>
+    <t xml:space="preserve">1.51676189899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56066823005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59659147262573</t>
   </si>
   <si>
     <t xml:space="preserve">1.56465971469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54071080684662</t>
+    <t xml:space="preserve">1.54071068763733</t>
   </si>
   <si>
     <t xml:space="preserve">1.53272783756256</t>
@@ -1433,7 +1430,7 @@
     <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58860850334167</t>
+    <t xml:space="preserve">1.58860862255096</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
@@ -1442,34 +1439,34 @@
     <t xml:space="preserve">1.54869389533997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5367192029953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54470229148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55268526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5247448682785</t>
+    <t xml:space="preserve">1.53671932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54470241069794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55268549919128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52474474906921</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264268398285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801195144653</t>
+    <t xml:space="preserve">1.67642104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801207065582</t>
   </si>
   <si>
     <t xml:space="preserve">1.88397789001465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9478417634964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539860725403</t>
+    <t xml:space="preserve">1.94784152507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539836883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.05960297584534</t>
@@ -1478,10 +1475,10 @@
     <t xml:space="preserve">2.16338133811951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329642295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926212310791</t>
+    <t xml:space="preserve">2.20329618453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926188468933</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
@@ -1490,64 +1487,64 @@
     <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2352283000946</t>
+    <t xml:space="preserve">2.23522806167603</t>
   </si>
   <si>
     <t xml:space="preserve">2.11548376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98775637149811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82011437416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91591000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002910137177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650631904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44890677928925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59259986877441</t>
+    <t xml:space="preserve">1.9877564907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82011425495148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91590988636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650619983673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44890689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59260010719299</t>
   </si>
   <si>
     <t xml:space="preserve">1.72431898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62852334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448916912079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68440401554108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457444190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66045522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65247213840485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633577346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054038047791</t>
+    <t xml:space="preserve">1.62852323055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6444890499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68440389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457456111908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604551076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65247225761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826776981354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71633589267731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054026126862</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843807697296</t>
@@ -1556,7 +1553,7 @@
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238698482513</t>
+    <t xml:space="preserve">1.69238686561584</t>
   </si>
   <si>
     <t xml:space="preserve">1.7562507390976</t>
@@ -1565,19 +1562,19 @@
     <t xml:space="preserve">1.76423370838165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792667865753</t>
+    <t xml:space="preserve">1.90792691707611</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582461357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92389285564423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757223129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456258296967</t>
+    <t xml:space="preserve">1.92389273643494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757199287415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9145622253418</t>
   </si>
   <si>
     <t xml:space="preserve">1.90630984306335</t>
@@ -1586,22 +1583,22 @@
     <t xml:space="preserve">1.85679543018341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84029066562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81553339958191</t>
+    <t xml:space="preserve">1.84029054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81553328037262</t>
   </si>
   <si>
     <t xml:space="preserve">1.79077613353729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75776648521423</t>
+    <t xml:space="preserve">1.75776636600494</t>
   </si>
   <si>
     <t xml:space="preserve">1.79902863502502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77427113056183</t>
+    <t xml:space="preserve">1.77427124977112</t>
   </si>
   <si>
     <t xml:space="preserve">1.76601886749268</t>
@@ -1610,16 +1607,16 @@
     <t xml:space="preserve">1.74126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78252387046814</t>
+    <t xml:space="preserve">1.78252375125885</t>
   </si>
   <si>
     <t xml:space="preserve">1.73300898075104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7495139837265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
+    <t xml:space="preserve">1.74951386451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650409698486</t>
   </si>
   <si>
     <t xml:space="preserve">1.69999933242798</t>
@@ -1628,10 +1625,10 @@
     <t xml:space="preserve">1.6834944486618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67524206638336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66698980331421</t>
+    <t xml:space="preserve">1.67524230480194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
     <t xml:space="preserve">1.65873730182648</t>
@@ -1640,16 +1637,16 @@
     <t xml:space="preserve">1.70825183391571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69174695014954</t>
+    <t xml:space="preserve">1.69174706935883</t>
   </si>
   <si>
     <t xml:space="preserve">1.7247565984726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398015499115</t>
+    <t xml:space="preserve">1.65048480033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398003578186</t>
   </si>
   <si>
     <t xml:space="preserve">1.62572765350342</t>
@@ -1658,49 +1655,52 @@
     <t xml:space="preserve">1.62985384464264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60922276973724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805746078491</t>
+    <t xml:space="preserve">1.60922288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805769920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582437515259</t>
   </si>
   <si>
     <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96407675743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93931949138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155281543732</t>
+    <t xml:space="preserve">1.96407735347748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93931972980499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8733001947403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155269622803</t>
   </si>
   <si>
     <t xml:space="preserve">1.88980507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86504781246185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92281472682953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106710910797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883450031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232937812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98058187961578</t>
+    <t xml:space="preserve">1.86504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92281484603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106734752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232949733734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98058176040649</t>
   </si>
   <si>
     <t xml:space="preserve">2.06310606002808</t>
@@ -1715,40 +1715,40 @@
     <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16213488578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566059112549</t>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563012123108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566035270691</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18715023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310883522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906766891479</t>
+    <t xml:space="preserve">2.18715000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906790733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.08502674102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09353685379028</t>
+    <t xml:space="preserve">2.09353709220886</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396487236023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02545428276062</t>
+    <t xml:space="preserve">2.03396463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254545211792</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">2.05098533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91482019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184101581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95737183094025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98290300369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439241409302</t>
+    <t xml:space="preserve">1.91482043266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184089660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95737171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98290252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439253330231</t>
   </si>
   <si>
     <t xml:space="preserve">2.07651615142822</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">1.99992334842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99141299724579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843381881714</t>
+    <t xml:space="preserve">1.9914128780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843358039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.01694393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10204744338989</t>
+    <t xml:space="preserve">2.10204720497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14459848403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16161942481995</t>
+    <t xml:space="preserve">2.14459872245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16161918640137</t>
   </si>
   <si>
     <t xml:space="preserve">2.13608860969543</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">1.94035112857819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89779984951019</t>
+    <t xml:space="preserve">1.89779961109161</t>
   </si>
   <si>
     <t xml:space="preserve">1.8722687959671</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">1.92333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94886136054993</t>
+    <t xml:space="preserve">1.94886147975922</t>
   </si>
   <si>
     <t xml:space="preserve">2.07243394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08129048347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05472087860107</t>
+    <t xml:space="preserve">2.08129072189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05472111701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.04586434364319</t>
@@ -1847,49 +1847,49 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9750120639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99272513389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95729875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94844222068787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86873316764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92187261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91301608085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775897026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072938919067</t>
+    <t xml:space="preserve">1.93958580493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97501194477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99272525310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95729887485504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94844233989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86873304843903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92187285423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91301620006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87758982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90415954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89530313014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8244503736496</t>
+    <t xml:space="preserve">1.96615540981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90415978431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89530301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82445049285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
@@ -1907,25 +1907,25 @@
     <t xml:space="preserve">1.70488691329956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77131116390228</t>
+    <t xml:space="preserve">1.77131128311157</t>
   </si>
   <si>
     <t xml:space="preserve">1.815593957901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74474143981934</t>
+    <t xml:space="preserve">1.74474155902863</t>
   </si>
   <si>
     <t xml:space="preserve">1.85102021694183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016781806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85987651348114</t>
+    <t xml:space="preserve">1.84216368198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016769886017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85987663269043</t>
   </si>
   <si>
     <t xml:space="preserve">1.75802636146545</t>
@@ -1937,22 +1937,22 @@
     <t xml:space="preserve">1.73588502407074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75359809398651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71817195415497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7093151807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72702836990356</t>
+    <t xml:space="preserve">1.7535982131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71817183494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70931529998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72702848911285</t>
   </si>
   <si>
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295209407806</t>
+    <t xml:space="preserve">1.88295221328735</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988074302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142035007477</t>
+    <t xml:space="preserve">1.79988086223602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142046928406</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526966571808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988884449005</t>
+    <t xml:space="preserve">1.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757925510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66142845153809</t>
+    <t xml:space="preserve">1.6614283323288</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9752539396286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833291530609</t>
+    <t xml:space="preserve">1.97525370121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833303451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2048,28 +2048,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526180267334</t>
+    <t xml:space="preserve">1.81372606754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526168346405</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89218235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910301685333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064262390137</t>
+    <t xml:space="preserve">1.8921822309494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910277843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064250469208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371409416199</t>
+    <t xml:space="preserve">1.99371421337128</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -27209,7 +27209,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27235,7 +27235,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G950" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27287,7 +27287,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G952" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27313,7 +27313,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27391,7 +27391,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G956" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27417,7 +27417,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G957" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27469,7 +27469,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27495,7 +27495,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27547,7 +27547,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G962" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27573,7 +27573,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G963" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27599,7 +27599,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27625,7 +27625,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27651,7 +27651,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27677,7 +27677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27703,7 +27703,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G968" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27729,7 +27729,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G969" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27755,7 +27755,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27781,7 +27781,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27807,7 +27807,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27859,7 +27859,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G974" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27911,7 +27911,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27937,7 +27937,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27963,7 +27963,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28015,7 +28015,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G980" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28041,7 +28041,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G981" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28067,7 +28067,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28171,7 +28171,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28197,7 +28197,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28327,7 +28327,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G992" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28353,7 +28353,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28405,7 +28405,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G995" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28431,7 +28431,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G996" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28483,7 +28483,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G998" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28509,7 +28509,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28535,7 +28535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1000" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28561,7 +28561,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1001" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28613,7 +28613,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1003" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28691,7 +28691,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1006" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28717,7 +28717,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1007" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28769,7 +28769,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1009" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28795,7 +28795,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28821,7 +28821,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1011" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28847,7 +28847,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1012" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28899,7 +28899,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1014" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28925,7 +28925,7 @@
         <v>2</v>
       </c>
       <c r="G1015" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28951,7 +28951,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1016" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28977,7 +28977,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1017" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29003,7 +29003,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1018" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29081,7 +29081,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1021" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29107,7 +29107,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29133,7 +29133,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1023" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29159,7 +29159,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1024" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29185,7 +29185,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1025" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29211,7 +29211,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29237,7 +29237,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1027" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29263,7 +29263,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1028" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29289,7 +29289,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1029" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29315,7 +29315,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1030" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29341,7 +29341,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1031" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29367,7 +29367,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1032" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29393,7 +29393,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1033" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29419,7 +29419,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1034" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29445,7 +29445,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1035" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29471,7 +29471,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1036" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29497,7 +29497,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1037" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29523,7 +29523,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1038" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29549,7 +29549,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1039" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29575,7 +29575,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29601,7 +29601,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1041" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29627,7 +29627,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1042" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29653,7 +29653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1043" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29679,7 +29679,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1044" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29705,7 +29705,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1045" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29731,7 +29731,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1046" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29757,7 +29757,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29783,7 +29783,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1048" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29809,7 +29809,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29835,7 +29835,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1050" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29861,7 +29861,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1051" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29887,7 +29887,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29913,7 +29913,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1053" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29939,7 +29939,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1054" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29965,7 +29965,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1055" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29991,7 +29991,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1056" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30017,7 +30017,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1057" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30043,7 +30043,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1058" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30069,7 +30069,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30095,7 +30095,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30121,7 +30121,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1061" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30147,7 +30147,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1062" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30225,7 +30225,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1065" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30251,7 +30251,7 @@
         <v>2</v>
       </c>
       <c r="G1066" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30277,7 +30277,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1067" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30329,7 +30329,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30355,7 +30355,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1070" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30381,7 +30381,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1071" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30511,7 +30511,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1076" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30537,7 +30537,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1077" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30641,7 +30641,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1081" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30667,7 +30667,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1082" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30693,7 +30693,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1083" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30719,7 +30719,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1084" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30745,7 +30745,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30771,7 +30771,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1086" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30797,7 +30797,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1087" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30823,7 +30823,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30849,7 +30849,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1089" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30875,7 +30875,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30901,7 +30901,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1091" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30927,7 +30927,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1092" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30953,7 +30953,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30979,7 +30979,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1094" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31005,7 +31005,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1095" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31031,7 +31031,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1096" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31057,7 +31057,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31083,7 +31083,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1098" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31109,7 +31109,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31135,7 +31135,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31161,7 +31161,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1101" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31187,7 +31187,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31213,7 +31213,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1103" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31239,7 +31239,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1104" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31265,7 +31265,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31291,7 +31291,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1106" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31317,7 +31317,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1107" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31343,7 +31343,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1108" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31369,7 +31369,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1109" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31395,7 +31395,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31421,7 +31421,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1111" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31447,7 +31447,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1112" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31473,7 +31473,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1113" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31499,7 +31499,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31525,7 +31525,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1115" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31551,7 +31551,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1116" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31577,7 +31577,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31603,7 +31603,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1118" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31629,7 +31629,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1119" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31655,7 +31655,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1120" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31681,7 +31681,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31707,7 +31707,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1122" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31733,7 +31733,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31759,7 +31759,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31785,7 +31785,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1125" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31811,7 +31811,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31837,7 +31837,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31863,7 +31863,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1128" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31889,7 +31889,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31915,7 +31915,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1130" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31941,7 +31941,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31967,7 +31967,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1132" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31993,7 +31993,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1133" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32019,7 +32019,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1134" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32045,7 +32045,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1135" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32071,7 +32071,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1136" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32097,7 +32097,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32123,7 +32123,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1138" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32149,7 +32149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32175,7 +32175,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1140" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32201,7 +32201,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1141" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32227,7 +32227,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32253,7 +32253,7 @@
         <v>2.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32279,7 +32279,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32305,7 +32305,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32331,7 +32331,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32357,7 +32357,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32383,7 +32383,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1148" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32409,7 +32409,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32435,7 +32435,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1150" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32461,7 +32461,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32487,7 +32487,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32513,7 +32513,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1153" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32539,7 +32539,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1154" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32565,7 +32565,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1155" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32591,7 +32591,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1156" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32617,7 +32617,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1157" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32643,7 +32643,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1158" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32669,7 +32669,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1159" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32695,7 +32695,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1160" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32721,7 +32721,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1161" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32747,7 +32747,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1162" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32773,7 +32773,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1163" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32799,7 +32799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1164" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32825,7 +32825,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1165" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32851,7 +32851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1166" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32877,7 +32877,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1167" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32903,7 +32903,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1168" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32929,7 +32929,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1169" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32955,7 +32955,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1170" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32981,7 +32981,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1171" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33007,7 +33007,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33033,7 +33033,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1173" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33059,7 +33059,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33085,7 +33085,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1175" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33111,7 +33111,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1176" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33137,7 +33137,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1177" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33163,7 +33163,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1178" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33189,7 +33189,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1179" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33215,7 +33215,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1180" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33241,7 +33241,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1181" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33267,7 +33267,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1182" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33293,7 +33293,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1183" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33319,7 +33319,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33345,7 +33345,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1185" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33371,7 +33371,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1186" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33397,7 +33397,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1187" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33423,7 +33423,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1188" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33449,7 +33449,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1189" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33475,7 +33475,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1190" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33501,7 +33501,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33527,7 +33527,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1192" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33553,7 +33553,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1193" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33579,7 +33579,7 @@
         <v>2</v>
       </c>
       <c r="G1194" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33605,7 +33605,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1195" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33631,7 +33631,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33657,7 +33657,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1197" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33683,7 +33683,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33709,7 +33709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1199" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33735,7 +33735,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1200" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33761,7 +33761,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33787,7 +33787,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33813,7 +33813,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33839,7 +33839,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33865,7 +33865,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33891,7 +33891,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1206" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33917,7 +33917,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1207" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33943,7 +33943,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1208" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33969,7 +33969,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1209" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33995,7 +33995,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34021,7 +34021,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34047,7 +34047,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34073,7 +34073,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1213" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34099,7 +34099,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1214" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34125,7 +34125,7 @@
         <v>2</v>
       </c>
       <c r="G1215" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34151,7 +34151,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34177,7 +34177,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1217" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34203,7 +34203,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1218" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34229,7 +34229,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34255,7 +34255,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1220" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34281,7 +34281,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34307,7 +34307,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34333,7 +34333,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34359,7 +34359,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34385,7 +34385,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1225" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34411,7 +34411,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1226" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34437,7 +34437,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34463,7 +34463,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1228" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34489,7 +34489,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1229" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34515,7 +34515,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34541,7 +34541,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1231" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34567,7 +34567,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34593,7 +34593,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34619,7 +34619,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34645,7 +34645,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1235" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34671,7 +34671,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34697,7 +34697,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34723,7 +34723,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34749,7 +34749,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34775,7 +34775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1240" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34801,7 +34801,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1241" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34827,7 +34827,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1242" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34853,7 +34853,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1243" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34879,7 +34879,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1244" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34905,7 +34905,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1245" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34931,7 +34931,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34957,7 +34957,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34983,7 +34983,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35009,7 +35009,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1249" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35035,7 +35035,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1250" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35061,7 +35061,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35087,7 +35087,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1252" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35113,7 +35113,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35165,7 +35165,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35243,7 +35243,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1258" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35321,7 +35321,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1261" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35347,7 +35347,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1262" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35711,7 +35711,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1276" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35763,7 +35763,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1278" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35789,7 +35789,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35815,7 +35815,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1280" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35841,7 +35841,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1281" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35867,7 +35867,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1282" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35893,7 +35893,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1283" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35919,7 +35919,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1284" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36101,7 +36101,7 @@
         <v>2.25</v>
       </c>
       <c r="G1291" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36127,7 +36127,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1292" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36179,7 +36179,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1294" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36231,7 +36231,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1296" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36283,7 +36283,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1298" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36361,7 +36361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36387,7 +36387,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1302" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36413,7 +36413,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1303" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36439,7 +36439,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1304" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36491,7 +36491,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36517,7 +36517,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36543,7 +36543,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36595,7 +36595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36621,7 +36621,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1311" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36647,7 +36647,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1312" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36673,7 +36673,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1313" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36699,7 +36699,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36725,7 +36725,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1315" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36933,7 +36933,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1323" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36959,7 +36959,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1324" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36985,7 +36985,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37219,7 +37219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1334" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37245,7 +37245,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1335" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37271,7 +37271,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1336" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37349,7 +37349,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1339" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37375,7 +37375,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1340" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37401,7 +37401,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1341" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37427,7 +37427,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1342" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37453,7 +37453,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37479,7 +37479,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1344" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37531,7 +37531,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37557,7 +37557,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1347" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37609,7 +37609,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37661,7 +37661,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1351" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37687,7 +37687,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1352" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37713,7 +37713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37739,7 +37739,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37765,7 +37765,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37817,7 +37817,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1357" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37947,7 +37947,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37999,7 +37999,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1364" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38051,7 +38051,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38129,7 +38129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38155,7 +38155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -43355,7 +43355,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -68427,7 +68427,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6797453704</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>14496</v>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -44,52 +44,52 @@
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552562236786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831963062286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09623825550079</t>
+    <t xml:space="preserve">1.12615478038788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1254426240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831974983215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09623801708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695041179657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407340526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0905396938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412885665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943804740905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925997138023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666052818298</t>
+    <t xml:space="preserve">1.10407316684723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09053957462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412873744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007688999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943804919719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925996899604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993666172027588</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925359249115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01004922389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859664916992</t>
+    <t xml:space="preserve">1.01004910469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859676837921</t>
   </si>
   <si>
     <t xml:space="preserve">1.05492436885834</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">1.03213059902191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03711676597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02571988105774</t>
+    <t xml:space="preserve">1.03711664676666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572000026703</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643191814423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073359489441</t>
+    <t xml:space="preserve">1.02643203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073383331299</t>
   </si>
   <si>
     <t xml:space="preserve">0.947366237640381</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">0.900354087352753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435581684113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530909061432</t>
+    <t xml:space="preserve">0.916024744510651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530849456787</t>
   </si>
   <si>
     <t xml:space="preserve">0.985830664634705</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">0.970160007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961612284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324559688568</t>
+    <t xml:space="preserve">0.961612343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324678897858</t>
   </si>
   <si>
     <t xml:space="preserve">1.00435078144073</t>
@@ -146,184 +146,184 @@
     <t xml:space="preserve">0.997939884662628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989392340183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529107093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979420185089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990816831588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717209815979</t>
+    <t xml:space="preserve">0.989392459392548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529047489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419946670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9908167719841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967669963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227489948273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717245578766</t>
   </si>
   <si>
     <t xml:space="preserve">1.0150351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00078916549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02215826511383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577521324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648736953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076149940491</t>
+    <t xml:space="preserve">1.00078904628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02215814590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577533245087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0107616186142</t>
   </si>
   <si>
     <t xml:space="preserve">1.00221359729767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984406054019928</t>
+    <t xml:space="preserve">0.984406173229218</t>
   </si>
   <si>
     <t xml:space="preserve">1.00791215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03284287452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01930916309357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979975223541</t>
+    <t xml:space="preserve">1.03284275531769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01930904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979963302612</t>
   </si>
   <si>
     <t xml:space="preserve">1.10051190853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08484125137329</t>
+    <t xml:space="preserve">1.08484101295471</t>
   </si>
   <si>
     <t xml:space="preserve">1.08982729911804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18171465396881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13185334205627</t>
+    <t xml:space="preserve">1.18171453475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818082332611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13185346126556</t>
   </si>
   <si>
     <t xml:space="preserve">1.13968884944916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15393495559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11689484119415</t>
+    <t xml:space="preserve">1.15393471717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11689496040344</t>
   </si>
   <si>
     <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16105782985687</t>
+    <t xml:space="preserve">1.16105794906616</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963327884674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612711429596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12900412082672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467489719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316699028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17031788825989</t>
+    <t xml:space="preserve">1.14752423763275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683950901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612723350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12900424003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1703177690506</t>
   </si>
   <si>
     <t xml:space="preserve">1.18100225925446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.197385430336</t>
+    <t xml:space="preserve">1.19738531112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.21091914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21163165569305</t>
+    <t xml:space="preserve">1.21163153648376</t>
   </si>
   <si>
     <t xml:space="preserve">1.20593297481537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22302854061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22089147567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19596076011658</t>
+    <t xml:space="preserve">1.22302842140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22089159488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19596087932587</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548448085785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22670161724091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18937337398529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790984153748</t>
+    <t xml:space="preserve">1.22670149803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18937349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18790972232819</t>
   </si>
   <si>
     <t xml:space="preserve">1.16302442550659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16595196723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16229248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16375613212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570509433746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911782741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424132347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14106667041779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11837708950043</t>
+    <t xml:space="preserve">1.16595208644867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16229236125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16375625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570521354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424120426178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1410665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11837697029114</t>
   </si>
   <si>
     <t xml:space="preserve">1.10154271125793</t>
@@ -335,31 +335,31 @@
     <t xml:space="preserve">1.0993469953537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14545822143555</t>
+    <t xml:space="preserve">1.14545810222626</t>
   </si>
   <si>
     <t xml:space="preserve">1.1293557882309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12716007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07226598262787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860637664795</t>
+    <t xml:space="preserve">1.12203681468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12716019153595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07226586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860649585724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423229217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15716898441315</t>
+    <t xml:space="preserve">1.12423241138458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15716886520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.18717765808105</t>
@@ -368,67 +368,67 @@
     <t xml:space="preserve">1.18205428123474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20767164230347</t>
+    <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
     <t xml:space="preserve">1.17839455604553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20401191711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18351805210114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2047438621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17473483085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571388721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546689510345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1930330991745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035231113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888854026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499085426331</t>
+    <t xml:space="preserve">1.20401179790497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18351793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20474374294281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1747350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571376800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546677589417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19303321838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035219192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888842105865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499073505402</t>
   </si>
   <si>
     <t xml:space="preserve">1.20693957805634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21425879001617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22231006622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2296290397644</t>
+    <t xml:space="preserve">1.21425867080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22230994701385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962915897369</t>
   </si>
   <si>
     <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22450578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745994091034</t>
+    <t xml:space="preserve">1.2245055437088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524652004242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232741355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745970249176</t>
   </si>
   <si>
     <t xml:space="preserve">1.30208957195282</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">1.29550230503082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2918426990509</t>
+    <t xml:space="preserve">1.29184257984161</t>
   </si>
   <si>
     <t xml:space="preserve">1.27866804599762</t>
@@ -446,112 +446,112 @@
     <t xml:space="preserve">1.24426758289337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890600681305</t>
+    <t xml:space="preserve">1.25890612602234</t>
   </si>
   <si>
     <t xml:space="preserve">1.27354454994202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25963807106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26183390617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26256573200226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26915287971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694860935211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109304904938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24719548225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2230418920517</t>
+    <t xml:space="preserve">1.25963795185089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26183378696442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26256549358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26915299892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694849014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109292984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402974128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24719536304474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22304201126099</t>
   </si>
   <si>
     <t xml:space="preserve">1.21938228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1996203660965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669282436371</t>
+    <t xml:space="preserve">1.19962048530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669270515442</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376492500305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742453098297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2062075138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19230115413666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059051036835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522014141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15643715858459</t>
+    <t xml:space="preserve">1.17766273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742465019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20620775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19230091571808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059039115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16521990299225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15643703937531</t>
   </si>
   <si>
     <t xml:space="preserve">1.16887974739075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693078517914</t>
+    <t xml:space="preserve">1.17693090438843</t>
   </si>
   <si>
     <t xml:space="preserve">1.19522893428802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17985856533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498182296753</t>
+    <t xml:space="preserve">1.17985868453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498194217682</t>
   </si>
   <si>
     <t xml:space="preserve">1.17400312423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17107546329498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16814768314362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14619028568268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14326238632202</t>
+    <t xml:space="preserve">1.17107558250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16814780235291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14619016647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14326226711273</t>
   </si>
   <si>
     <t xml:space="preserve">1.11252164840698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13447940349579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984074115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325347423553</t>
+    <t xml:space="preserve">1.13447904586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984086036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325359344482</t>
   </si>
   <si>
     <t xml:space="preserve">1.10593438148499</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">1.1227685213089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11032593250275</t>
+    <t xml:space="preserve">1.11032581329346</t>
   </si>
   <si>
     <t xml:space="preserve">1.1161812543869</t>
@@ -572,67 +572,67 @@
     <t xml:space="preserve">1.13960289955139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12789189815521</t>
+    <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
     <t xml:space="preserve">1.14399433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14179849624634</t>
+    <t xml:space="preserve">1.14179861545563</t>
   </si>
   <si>
     <t xml:space="preserve">1.13521122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13813889026642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14253044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19449687004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18132245540619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17253911495209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912650108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887071609497</t>
+    <t xml:space="preserve">1.138139128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14253067970276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19449698925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1813223361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17253923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887095451355</t>
   </si>
   <si>
     <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12350046634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12569618225098</t>
+    <t xml:space="preserve">1.12350034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12569630146027</t>
   </si>
   <si>
     <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12496435642242</t>
+    <t xml:space="preserve">1.12496423721313</t>
   </si>
   <si>
     <t xml:space="preserve">1.12642812728882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15936458110809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277743339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741597652435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22377395629883</t>
+    <t xml:space="preserve">1.15936470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15277755260468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741585731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22377383708954</t>
   </si>
   <si>
     <t xml:space="preserve">1.22596967220306</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">1.25671029090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24792730808258</t>
+    <t xml:space="preserve">1.24792742729187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060809612274</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">1.2684211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29769802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867683887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403841495514</t>
+    <t xml:space="preserve">1.29769790172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403829574585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3247789144516</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">1.32404720783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014060974121</t>
+    <t xml:space="preserve">1.3101407289505</t>
   </si>
   <si>
     <t xml:space="preserve">1.3284387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29037868976593</t>
+    <t xml:space="preserve">1.29037880897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135750770569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30282151699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3152642250061</t>
+    <t xml:space="preserve">1.30282139778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31526398658752</t>
   </si>
   <si>
     <t xml:space="preserve">1.32624292373657</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">1.33941745758057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34673666954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3869925737381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36869430541992</t>
+    <t xml:space="preserve">1.34673690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38699245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3686945438385</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772439956665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35991132259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37454986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40529036521912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39065217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39650750160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114580631256</t>
+    <t xml:space="preserve">1.35991144180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37454974651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40529048442841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39065194129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39650738239288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114592552185</t>
   </si>
   <si>
     <t xml:space="preserve">1.3818690776825</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">1.37162208557129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38845634460449</t>
+    <t xml:space="preserve">1.3884562253952</t>
   </si>
   <si>
     <t xml:space="preserve">1.41927754878998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45009875297546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046491622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53654825687408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56361067295074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58616256713867</t>
+    <t xml:space="preserve">1.45009887218475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046515464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53654837608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56361079216003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58616280555725</t>
   </si>
   <si>
     <t xml:space="preserve">1.60570800304413</t>
@@ -758,40 +758,40 @@
     <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51098954677582</t>
+    <t xml:space="preserve">1.51098930835724</t>
   </si>
   <si>
     <t xml:space="preserve">1.48693382740021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47866463661194</t>
+    <t xml:space="preserve">1.47866451740265</t>
   </si>
   <si>
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46964371204376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44333291053772</t>
+    <t xml:space="preserve">1.46814024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964395046234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44333302974701</t>
   </si>
   <si>
     <t xml:space="preserve">1.44483649730682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43882262706757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43205678462982</t>
+    <t xml:space="preserve">1.43882274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43205690383911</t>
   </si>
   <si>
     <t xml:space="preserve">1.43581569194794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40574610233307</t>
+    <t xml:space="preserve">1.40574634075165</t>
   </si>
   <si>
     <t xml:space="preserve">1.45836770534515</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">1.47189903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45310544967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42829847335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41852557659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42980170249939</t>
+    <t xml:space="preserve">1.4531055688858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42829823493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41852569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42980182170868</t>
   </si>
   <si>
     <t xml:space="preserve">1.4207808971405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42604315280914</t>
+    <t xml:space="preserve">1.42604303359985</t>
   </si>
   <si>
     <t xml:space="preserve">1.41702234745026</t>
@@ -827,76 +827,76 @@
     <t xml:space="preserve">1.42529141902924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44408476352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716116905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219572544098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46663665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46588516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144411087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48843717575073</t>
+    <t xml:space="preserve">1.44408488273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716128826141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219596385956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46663689613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46588528156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144399166107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48843729496002</t>
   </si>
   <si>
     <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948560237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167169094086</t>
+    <t xml:space="preserve">1.50948584079742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347197055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167157173157</t>
   </si>
   <si>
     <t xml:space="preserve">1.4959545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51249277591705</t>
+    <t xml:space="preserve">1.51249289512634</t>
   </si>
   <si>
     <t xml:space="preserve">1.50497531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52151358127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49369943141937</t>
+    <t xml:space="preserve">1.52151346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369931221008</t>
   </si>
   <si>
     <t xml:space="preserve">1.49896156787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602398395538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.496706366539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5079824924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5485759973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48242330551147</t>
+    <t xml:space="preserve">1.52602410316467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49670624732971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798213481903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54857611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48242318630219</t>
   </si>
   <si>
     <t xml:space="preserve">1.47039556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47941625118256</t>
+    <t xml:space="preserve">1.47941637039185</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203797340393</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">1.52903079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.513995885849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158293247223</t>
+    <t xml:space="preserve">1.51399624347687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158305168152</t>
   </si>
   <si>
     <t xml:space="preserve">1.56511425971985</t>
@@ -917,28 +917,28 @@
     <t xml:space="preserve">1.55609333515167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126695156097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682590007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69140601158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644056797028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381932258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937827110291</t>
+    <t xml:space="preserve">1.63126707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637121677399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65682578086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69140565395355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644068717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381920337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937803268433</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735029220581</t>
@@ -947,52 +947,52 @@
     <t xml:space="preserve">1.66885387897491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778746843338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67186081409454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839919567108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
+    <t xml:space="preserve">1.67787456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67186105251312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6883989572525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6868953704834</t>
   </si>
   <si>
     <t xml:space="preserve">1.65983295440674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63878440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64630174636841</t>
+    <t xml:space="preserve">1.63878452777863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6463018655777</t>
   </si>
   <si>
     <t xml:space="preserve">1.74402737617493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80115914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318700313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79213869571686</t>
+    <t xml:space="preserve">1.80115926265717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318736076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79213857650757</t>
   </si>
   <si>
     <t xml:space="preserve">1.79965603351593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84175312519073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430537700653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83874607086182</t>
+    <t xml:space="preserve">1.84175300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430525779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874619007111</t>
   </si>
   <si>
     <t xml:space="preserve">1.76657962799072</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">1.66133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76206910610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77560043334961</t>
+    <t xml:space="preserve">1.76206922531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77560019493103</t>
   </si>
   <si>
     <t xml:space="preserve">1.83423590660095</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">1.8056697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82220804691315</t>
+    <t xml:space="preserve">1.82220780849457</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899270057678</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">1.74102056026459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72598576545715</t>
+    <t xml:space="preserve">1.72598588466644</t>
   </si>
   <si>
     <t xml:space="preserve">1.751544713974</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">1.72297883033752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70193028450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441306591034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728082180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434335708618</t>
+    <t xml:space="preserve">1.70193016529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388855457306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728070259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434323787689</t>
   </si>
   <si>
     <t xml:space="preserve">1.72448241710663</t>
@@ -1061,112 +1061,109 @@
     <t xml:space="preserve">1.73500669002533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73951697349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73650991916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71395826339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161418437958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906193256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920099258423</t>
+    <t xml:space="preserve">1.73951685428619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73651003837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71395790576935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161406517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906217098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920111179352</t>
   </si>
   <si>
     <t xml:space="preserve">1.8267183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8041660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87934005260468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88685762882233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81168353557587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664885997772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409684658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78913164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678780078888</t>
+    <t xml:space="preserve">1.80416631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87933993339539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88685703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81168377399445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409672737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78913176059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678791999817</t>
   </si>
   <si>
     <t xml:space="preserve">1.8492705821991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88701093196869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8793398141861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865653514862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399829387665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797361373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81030285358429</t>
+    <t xml:space="preserve">1.8870108127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865689277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399817466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797349452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81030297279358</t>
   </si>
   <si>
     <t xml:space="preserve">1.90235233306885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83331513404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263209342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660741329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291221141815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427829265594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67989981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69524121284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222893238068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74893689155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65688741207123</t>
+    <t xml:space="preserve">1.83331537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263221263885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660753250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291197299957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427817344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6798996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69524133205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222881317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74893665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65688753128052</t>
   </si>
   <si>
     <t xml:space="preserve">1.64154589176178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5801796913147</t>
+    <t xml:space="preserve">1.58017957210541</t>
   </si>
   <si>
     <t xml:space="preserve">1.66455817222595</t>
@@ -1175,7 +1172,7 @@
     <t xml:space="preserve">1.62620437145233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57250893115997</t>
+    <t xml:space="preserve">1.57250869274139</t>
   </si>
   <si>
     <t xml:space="preserve">1.51497805118561</t>
@@ -1193,22 +1190,22 @@
     <t xml:space="preserve">1.41142249107361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37306869029999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35005629062653</t>
+    <t xml:space="preserve">1.3730685710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35005640983582</t>
   </si>
   <si>
     <t xml:space="preserve">1.38073945045471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39224576950073</t>
+    <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.36923325061798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39991652965546</t>
+    <t xml:space="preserve">1.39991641044617</t>
   </si>
   <si>
     <t xml:space="preserve">1.35772716999054</t>
@@ -1220,19 +1217,19 @@
     <t xml:space="preserve">1.34238576889038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30403172969818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28101933002472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26951324939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25417184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24650096893311</t>
+    <t xml:space="preserve">1.30403184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28101921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25417172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24650084972382</t>
   </si>
   <si>
     <t xml:space="preserve">1.25800704956055</t>
@@ -1247,25 +1244,25 @@
     <t xml:space="preserve">1.30019640922546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29252564907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937325000763</t>
+    <t xml:space="preserve">1.29252552986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937336921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.30786716938019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33087944984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855020999908</t>
+    <t xml:space="preserve">1.33087956905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855032920837</t>
   </si>
   <si>
     <t xml:space="preserve">1.33471488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31553792953491</t>
+    <t xml:space="preserve">1.3155380487442</t>
   </si>
   <si>
     <t xml:space="preserve">1.39608097076416</t>
@@ -1274,7 +1271,7 @@
     <t xml:space="preserve">1.38457477092743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40375185012817</t>
+    <t xml:space="preserve">1.40375196933746</t>
   </si>
   <si>
     <t xml:space="preserve">1.36156260967255</t>
@@ -1289,22 +1286,22 @@
     <t xml:space="preserve">1.37690412998199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38841021060944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34622097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32704412937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27334868907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320857048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37706005573273</t>
+    <t xml:space="preserve">1.38840997219086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3462210893631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32704424858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27334845066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320868968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37706017494202</t>
   </si>
   <si>
     <t xml:space="preserve">1.3890346288681</t>
@@ -1313,10 +1310,10 @@
     <t xml:space="preserve">1.36109435558319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32916235923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35311126708984</t>
+    <t xml:space="preserve">1.32916247844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35311138629913</t>
   </si>
   <si>
     <t xml:space="preserve">1.34512829780579</t>
@@ -1325,16 +1322,16 @@
     <t xml:space="preserve">1.36508572101593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39701771736145</t>
+    <t xml:space="preserve">1.39701759815216</t>
   </si>
   <si>
     <t xml:space="preserve">1.41298353672028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4010089635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40899217128754</t>
+    <t xml:space="preserve">1.40100908279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40899205207825</t>
   </si>
   <si>
     <t xml:space="preserve">1.4169750213623</t>
@@ -1343,25 +1340,25 @@
     <t xml:space="preserve">1.4688640832901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4968044757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877904891968</t>
+    <t xml:space="preserve">1.49680459499359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877892971039</t>
   </si>
   <si>
     <t xml:space="preserve">1.51277053356171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49281299114227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487271785736</t>
+    <t xml:space="preserve">1.49281311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487259864807</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079607963562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44491529464722</t>
+    <t xml:space="preserve">1.44491517543793</t>
   </si>
   <si>
     <t xml:space="preserve">1.45289826393127</t>
@@ -1370,10 +1367,10 @@
     <t xml:space="preserve">1.43693232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42495787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096650600433</t>
+    <t xml:space="preserve">1.42495799064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096638679504</t>
   </si>
   <si>
     <t xml:space="preserve">1.40500044822693</t>
@@ -1382,13 +1379,16 @@
     <t xml:space="preserve">1.39302611351013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38504326343536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4289493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907720565796</t>
+    <t xml:space="preserve">1.38504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894923686981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37306880950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907732486725</t>
   </si>
   <si>
     <t xml:space="preserve">1.35710275173187</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">1.3491199016571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48483002185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47684717178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46088123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48882162570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075326442719</t>
+    <t xml:space="preserve">1.48482990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47684729099274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46088147163391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48882150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075338363647</t>
   </si>
   <si>
     <t xml:space="preserve">1.51676189899445</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659159183502</t>
+    <t xml:space="preserve">1.59659147262573</t>
   </si>
   <si>
     <t xml:space="preserve">1.56465971469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54071080684662</t>
+    <t xml:space="preserve">1.54071092605591</t>
   </si>
   <si>
     <t xml:space="preserve">1.53272783756256</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">1.52873635292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58860838413239</t>
+    <t xml:space="preserve">1.58860850334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.55667674541473</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">1.54869389533997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53671932220459</t>
+    <t xml:space="preserve">1.5367192029953</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470229148865</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">1.52474498748779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264280319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801183223724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88397800922394</t>
+    <t xml:space="preserve">1.57264256477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88397812843323</t>
   </si>
   <si>
     <t xml:space="preserve">1.94784164428711</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">2.15539836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05960321426392</t>
+    <t xml:space="preserve">2.05960273742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338157653809</t>
@@ -1490,73 +1490,73 @@
     <t xml:space="preserve">2.1793475151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23522782325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11548399925232</t>
+    <t xml:space="preserve">2.23522806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11548376083374</t>
   </si>
   <si>
     <t xml:space="preserve">1.9877564907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82011449337006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91590964794159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002898216248</t>
+    <t xml:space="preserve">1.82011425495148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82809722423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91591000556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002886295319</t>
   </si>
   <si>
     <t xml:space="preserve">1.63650631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44890689849854</t>
+    <t xml:space="preserve">1.44890677928925</t>
   </si>
   <si>
     <t xml:space="preserve">1.5925999879837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72431898117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62852334976196</t>
+    <t xml:space="preserve">1.72431886196136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62852323055267</t>
   </si>
   <si>
     <t xml:space="preserve">1.64448916912079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6844037771225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457468032837</t>
+    <t xml:space="preserve">1.68440389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457444190979</t>
   </si>
   <si>
     <t xml:space="preserve">1.6604551076889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65247213840485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826788902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71633613109589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054038047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843819618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61255729198456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69238698482513</t>
+    <t xml:space="preserve">1.65247225761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7163360118866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054049968719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843807697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61255741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69238710403442</t>
   </si>
   <si>
     <t xml:space="preserve">1.7562507390976</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792679786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582449436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92389261722565</t>
+    <t xml:space="preserve">1.90792691707611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92389285564423</t>
   </si>
   <si>
     <t xml:space="preserve">1.94757223129272</t>
@@ -1580,43 +1580,43 @@
     <t xml:space="preserve">1.91456246376038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90630996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679566860199</t>
+    <t xml:space="preserve">1.90630984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8567955493927</t>
   </si>
   <si>
     <t xml:space="preserve">1.84029054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81553328037262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79077625274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75776660442352</t>
+    <t xml:space="preserve">1.81553339958191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79077613353729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75776636600494</t>
   </si>
   <si>
     <t xml:space="preserve">1.79902839660645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7742714881897</t>
+    <t xml:space="preserve">1.77427136898041</t>
   </si>
   <si>
     <t xml:space="preserve">1.76601874828339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74126124382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74951386451721</t>
+    <t xml:space="preserve">1.74126136302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495139837265</t>
   </si>
   <si>
     <t xml:space="preserve">1.71650421619415</t>
@@ -1625,37 +1625,37 @@
     <t xml:space="preserve">1.69999933242798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68349432945251</t>
+    <t xml:space="preserve">1.6834944486618</t>
   </si>
   <si>
     <t xml:space="preserve">1.67524218559265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66698956489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
+    <t xml:space="preserve">1.66698968410492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
   </si>
   <si>
     <t xml:space="preserve">1.69174695014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72475671768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048491954803</t>
+    <t xml:space="preserve">1.7247565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048480033875</t>
   </si>
   <si>
     <t xml:space="preserve">1.63398003578186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62572765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985384464264</t>
+    <t xml:space="preserve">1.62572753429413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985372543335</t>
   </si>
   <si>
     <t xml:space="preserve">1.60922276973724</t>
@@ -1664,6 +1664,9 @@
     <t xml:space="preserve">1.89805746078491</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95582437515259</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
@@ -1673,7 +1676,7 @@
     <t xml:space="preserve">1.93931972980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87330031394958</t>
+    <t xml:space="preserve">1.8733001947403</t>
   </si>
   <si>
     <t xml:space="preserve">1.88155269622803</t>
@@ -1682,10 +1685,10 @@
     <t xml:space="preserve">1.88980507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86504781246185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92281472682953</t>
+    <t xml:space="preserve">1.86504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92281460762024</t>
   </si>
   <si>
     <t xml:space="preserve">1.93106710910797</t>
@@ -1694,13 +1697,13 @@
     <t xml:space="preserve">2.01359152793884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883414268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97232961654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98058187961578</t>
+    <t xml:space="preserve">1.98883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97232949733734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98058199882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.06310606002808</t>
@@ -1709,7 +1712,7 @@
     <t xml:space="preserve">2.19514489173889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17864036560059</t>
+    <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
     <t xml:space="preserve">2.17038750648499</t>
@@ -1721,31 +1724,31 @@
     <t xml:space="preserve">2.14563012123108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19566059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17864012718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310883522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906766891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08502650260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09353685379028</t>
+    <t xml:space="preserve">2.19566035270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863988876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18715000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906790733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09353709220886</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396487236023</t>
+    <t xml:space="preserve">2.03396463394165</t>
   </si>
   <si>
     <t xml:space="preserve">2.0254545211792</t>
@@ -1754,7 +1757,7 @@
     <t xml:space="preserve">2.04247498512268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05098509788513</t>
+    <t xml:space="preserve">2.05098533630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.91482043266296</t>
@@ -1766,7 +1769,7 @@
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290264606476</t>
+    <t xml:space="preserve">1.98290252685547</t>
   </si>
   <si>
     <t xml:space="preserve">1.97439253330231</t>
@@ -1778,16 +1781,16 @@
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949544906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992346763611</t>
+    <t xml:space="preserve">2.05949568748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992334842682</t>
   </si>
   <si>
     <t xml:space="preserve">1.9914128780365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00843381881714</t>
+    <t xml:space="preserve">2.00843358039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.01694393157959</t>
@@ -1808,7 +1811,7 @@
     <t xml:space="preserve">2.13608860969543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96588206291199</t>
+    <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.94035112857819</t>
@@ -1817,10 +1820,7 @@
     <t xml:space="preserve">1.89779961109161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90630984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226867675781</t>
+    <t xml:space="preserve">1.8722687959671</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
@@ -19022,7 +19022,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G634" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G635" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19074,7 +19074,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G636" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19100,7 +19100,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19230,7 +19230,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G642" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19256,7 +19256,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G643" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19308,7 +19308,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G645" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19334,7 +19334,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G646" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19360,7 +19360,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G647" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19386,7 +19386,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G648" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19412,7 +19412,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G649" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19438,7 +19438,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G650" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19464,7 +19464,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G651" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G653" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G654" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G660" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19724,7 +19724,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G661" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G662" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19802,7 +19802,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G664" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G665" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G669" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20166,7 +20166,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G678" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20296,7 +20296,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20322,7 +20322,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G684" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20348,7 +20348,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G685" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20374,7 +20374,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G686" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20400,7 +20400,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G687" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20608,7 +20608,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G695" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20634,7 +20634,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G696" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20842,7 +20842,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20946,7 +20946,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G708" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -20972,7 +20972,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21128,7 +21128,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G715" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21154,7 +21154,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G716" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21180,7 +21180,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21206,7 +21206,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G718" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21232,7 +21232,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G719" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21258,7 +21258,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G720" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21284,7 +21284,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G721" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21310,7 +21310,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G722" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21336,7 +21336,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G723" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21362,7 +21362,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21388,7 +21388,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G725" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21414,7 +21414,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21440,7 +21440,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G727" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21466,7 +21466,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G728" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21492,7 +21492,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G729" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21518,7 +21518,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G730" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21544,7 +21544,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21570,7 +21570,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G732" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21596,7 +21596,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21622,7 +21622,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21648,7 +21648,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G735" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21674,7 +21674,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G736" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21700,7 +21700,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G737" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21726,7 +21726,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G738" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21752,7 +21752,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G739" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21778,7 +21778,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G740" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21804,7 +21804,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G741" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21830,7 +21830,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G742" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -21856,7 +21856,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G743" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21882,7 +21882,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G744" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21908,7 +21908,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21934,7 +21934,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G746" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21960,7 +21960,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G747" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21986,7 +21986,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G748" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22012,7 +22012,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G749" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22038,7 +22038,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22064,7 +22064,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G751" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22090,7 +22090,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G752" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22116,7 +22116,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G753" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22142,7 +22142,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G754" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22168,7 +22168,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G755" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22194,7 +22194,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G756" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22220,7 +22220,7 @@
         <v>1.75</v>
       </c>
       <c r="G757" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22246,7 +22246,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G758" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22272,7 +22272,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G759" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22298,7 +22298,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G760" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22324,7 +22324,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G761" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22350,7 +22350,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G762" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22376,7 +22376,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22402,7 +22402,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G764" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22428,7 +22428,7 @@
         <v>1.625</v>
       </c>
       <c r="G765" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22454,7 +22454,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G766" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22480,7 +22480,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G767" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22506,7 +22506,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G768" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22532,7 +22532,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G769" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22558,7 +22558,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G770" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22584,7 +22584,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G771" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22610,7 +22610,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G772" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22636,7 +22636,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G773" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22662,7 +22662,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G774" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22688,7 +22688,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G775" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22714,7 +22714,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22740,7 +22740,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G777" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22766,7 +22766,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G778" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22792,7 +22792,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G779" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22818,7 +22818,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G780" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22844,7 +22844,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G781" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22870,7 +22870,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G782" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22896,7 +22896,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G783" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22922,7 +22922,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G784" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22948,7 +22948,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G785" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22974,7 +22974,7 @@
         <v>1.75</v>
       </c>
       <c r="G786" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23000,7 +23000,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G787" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23026,7 +23026,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G788" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23052,7 +23052,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G789" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23078,7 +23078,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G790" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23104,7 +23104,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G791" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23130,7 +23130,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G792" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23156,7 +23156,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G793" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23182,7 +23182,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G794" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23208,7 +23208,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G795" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23234,7 +23234,7 @@
         <v>1.75</v>
       </c>
       <c r="G796" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23260,7 +23260,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G797" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23286,7 +23286,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G798" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23312,7 +23312,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G799" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23338,7 +23338,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G800" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23364,7 +23364,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G801" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23390,7 +23390,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G802" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23416,7 +23416,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G803" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23442,7 +23442,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G804" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23468,7 +23468,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G805" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23494,7 +23494,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G806" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23520,7 +23520,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G807" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23546,7 +23546,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G808" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23572,7 +23572,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G809" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23598,7 +23598,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G810" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23624,7 +23624,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G811" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23650,7 +23650,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23676,7 +23676,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G813" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23702,7 +23702,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23728,7 +23728,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G815" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23754,7 +23754,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G816" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23780,7 +23780,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G817" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23806,7 +23806,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G818" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23832,7 +23832,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G819" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23858,7 +23858,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G820" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23884,7 +23884,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23910,7 +23910,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23936,7 +23936,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G823" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23962,7 +23962,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G824" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23988,7 +23988,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G825" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24014,7 +24014,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24040,7 +24040,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24066,7 +24066,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G828" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24092,7 +24092,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24118,7 +24118,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G830" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24144,7 +24144,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G831" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24170,7 +24170,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G832" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24196,7 +24196,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G833" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24222,7 +24222,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G834" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24248,7 +24248,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G835" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24274,7 +24274,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G836" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24300,7 +24300,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G837" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24326,7 +24326,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G838" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24352,7 +24352,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G839" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24378,7 +24378,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G840" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24404,7 +24404,7 @@
         <v>1.75</v>
       </c>
       <c r="G841" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24430,7 +24430,7 @@
         <v>1.75</v>
       </c>
       <c r="G842" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24456,7 +24456,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G843" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24482,7 +24482,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24508,7 +24508,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24534,7 +24534,7 @@
         <v>1.75</v>
       </c>
       <c r="G846" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24560,7 +24560,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G847" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24586,7 +24586,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G848" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24612,7 +24612,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G849" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24638,7 +24638,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G850" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24664,7 +24664,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G851" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24690,7 +24690,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G852" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24716,7 +24716,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G853" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24742,7 +24742,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G854" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24768,7 +24768,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24794,7 +24794,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G856" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24820,7 +24820,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24846,7 +24846,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G858" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24872,7 +24872,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G859" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24898,7 +24898,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G860" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24924,7 +24924,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G861" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24950,7 +24950,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G862" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24976,7 +24976,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G863" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25002,7 +25002,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G864" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25028,7 +25028,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G865" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25054,7 +25054,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G866" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25080,7 +25080,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G867" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25106,7 +25106,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G868" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G869" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25158,7 +25158,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G870" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25184,7 +25184,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25210,7 +25210,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G872" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25236,7 +25236,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G873" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25262,7 +25262,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25288,7 +25288,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G875" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25314,7 +25314,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G876" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25340,7 +25340,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G877" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25366,7 +25366,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G878" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25392,7 +25392,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G879" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25418,7 +25418,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G880" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25444,7 +25444,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G881" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25470,7 +25470,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G882" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25496,7 +25496,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25522,7 +25522,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25548,7 +25548,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25574,7 +25574,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G886" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25600,7 +25600,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25626,7 +25626,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G888" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25652,7 +25652,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G889" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25678,7 +25678,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G890" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25704,7 +25704,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25730,7 +25730,7 @@
         <v>1.75</v>
       </c>
       <c r="G892" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25756,7 +25756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G893" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25782,7 +25782,7 @@
         <v>1.75</v>
       </c>
       <c r="G894" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25808,7 +25808,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G895" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25834,7 +25834,7 @@
         <v>1.75</v>
       </c>
       <c r="G896" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25860,7 +25860,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G897" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25886,7 +25886,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G898" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25912,7 +25912,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G899" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25938,7 +25938,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G900" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25964,7 +25964,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G901" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25990,7 +25990,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G902" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26016,7 +26016,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G903" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26042,7 +26042,7 @@
         <v>1.875</v>
       </c>
       <c r="G904" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26068,7 +26068,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G905" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26094,7 +26094,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G906" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26120,7 +26120,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G907" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26146,7 +26146,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G908" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26172,7 +26172,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G909" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26198,7 +26198,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G910" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26224,7 +26224,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26250,7 +26250,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G912" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26276,7 +26276,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G913" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26302,7 +26302,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G914" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26328,7 +26328,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G915" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26354,7 +26354,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G916" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26380,7 +26380,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G917" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26406,7 +26406,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G918" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26432,7 +26432,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G919" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26458,7 +26458,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G920" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26484,7 +26484,7 @@
         <v>1.75</v>
       </c>
       <c r="G921" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26510,7 +26510,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G922" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26536,7 +26536,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G923" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26562,7 +26562,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G924" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26588,7 +26588,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G925" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26614,7 +26614,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G926" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26640,7 +26640,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G927" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26666,7 +26666,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G928" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26692,7 +26692,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G929" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26718,7 +26718,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G930" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26744,7 +26744,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G931" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26770,7 +26770,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G932" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26796,7 +26796,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G933" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26822,7 +26822,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26848,7 +26848,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G935" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26874,7 +26874,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G936" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26900,7 +26900,7 @@
         <v>1.75</v>
       </c>
       <c r="G937" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26926,7 +26926,7 @@
         <v>1.75</v>
       </c>
       <c r="G938" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26952,7 +26952,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G939" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26978,7 +26978,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G940" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27004,7 +27004,7 @@
         <v>1.75</v>
       </c>
       <c r="G941" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27030,7 +27030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G942" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27056,7 +27056,7 @@
         <v>1.75</v>
       </c>
       <c r="G943" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27082,7 +27082,7 @@
         <v>1.75</v>
       </c>
       <c r="G944" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27108,7 +27108,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27134,7 +27134,7 @@
         <v>1.75</v>
       </c>
       <c r="G946" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27160,7 +27160,7 @@
         <v>1.75</v>
       </c>
       <c r="G947" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27186,7 +27186,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G948" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27212,7 +27212,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27264,7 +27264,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G951" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27316,7 +27316,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27342,7 +27342,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27368,7 +27368,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G955" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27446,7 +27446,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27472,7 +27472,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27498,7 +27498,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27524,7 +27524,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G961" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27602,7 +27602,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27628,7 +27628,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27654,7 +27654,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27680,7 +27680,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27758,7 +27758,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27784,7 +27784,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27810,7 +27810,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27836,7 +27836,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G973" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27888,7 +27888,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G975" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27914,7 +27914,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27940,7 +27940,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27992,7 +27992,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G979" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28070,7 +28070,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28096,7 +28096,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G983" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28122,7 +28122,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G984" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28148,7 +28148,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G985" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28226,7 +28226,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28252,7 +28252,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G989" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28278,7 +28278,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28304,7 +28304,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28382,7 +28382,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G994" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28460,7 +28460,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G997" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28590,7 +28590,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1002" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28642,7 +28642,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1004" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28668,7 +28668,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1005" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28746,7 +28746,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1008" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28876,7 +28876,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1013" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29032,7 +29032,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1019" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29058,7 +29058,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1020" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30176,7 +30176,7 @@
         <v>1.75</v>
       </c>
       <c r="G1063" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30202,7 +30202,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1064" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30306,7 +30306,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1068" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30410,7 +30410,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1072" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30436,7 +30436,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30462,7 +30462,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1074" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30488,7 +30488,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1075" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30566,7 +30566,7 @@
         <v>1.75</v>
       </c>
       <c r="G1078" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30592,7 +30592,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1079" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30618,7 +30618,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1080" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -35116,7 +35116,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35142,7 +35142,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1256" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35220,7 +35220,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35272,7 +35272,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35298,7 +35298,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1260" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35376,7 +35376,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35402,7 +35402,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35428,7 +35428,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35454,7 +35454,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35480,7 +35480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35506,7 +35506,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35532,7 +35532,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1269" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35558,7 +35558,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1270" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35584,7 +35584,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1271" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35610,7 +35610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35636,7 +35636,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35662,7 +35662,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1274" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35688,7 +35688,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35740,7 +35740,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1277" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35948,7 +35948,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35974,7 +35974,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1286" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36000,7 +36000,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1287" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36026,7 +36026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1288" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36052,7 +36052,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36078,7 +36078,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36156,7 +36156,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36208,7 +36208,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36260,7 +36260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36312,7 +36312,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36338,7 +36338,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36468,7 +36468,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36572,7 +36572,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36754,7 +36754,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36780,7 +36780,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36806,7 +36806,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36832,7 +36832,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36858,7 +36858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1320" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36884,7 +36884,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1321" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36910,7 +36910,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1322" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37014,7 +37014,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1326" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37040,7 +37040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37066,7 +37066,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1328" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37092,7 +37092,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37118,7 +37118,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1330" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37144,7 +37144,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1331" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37170,7 +37170,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37196,7 +37196,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37300,7 +37300,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37326,7 +37326,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37508,7 +37508,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37586,7 +37586,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37638,7 +37638,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1350" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37794,7 +37794,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1356" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37846,7 +37846,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1358" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37872,7 +37872,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1359" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37898,7 +37898,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1360" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37924,7 +37924,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1361" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37976,7 +37976,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1363" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38028,7 +38028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1365" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38080,7 +38080,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1367" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38106,7 +38106,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1368" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38184,7 +38184,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38210,7 +38210,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1372" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38236,7 +38236,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38262,7 +38262,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1374" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38288,7 +38288,7 @@
         <v>2.5</v>
       </c>
       <c r="G1375" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38314,7 +38314,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38340,7 +38340,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1377" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38366,7 +38366,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38392,7 +38392,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38418,7 +38418,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38444,7 +38444,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1381" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38470,7 +38470,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1382" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38496,7 +38496,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1383" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38522,7 +38522,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1384" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38548,7 +38548,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38574,7 +38574,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38600,7 +38600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1387" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38626,7 +38626,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38652,7 +38652,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1389" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1392" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38756,7 +38756,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1394" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1395" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1396" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1398" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1399" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1400" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1401" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1403" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1404" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1405" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1406" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1407" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1408" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>2.25</v>
       </c>
       <c r="G1409" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1410" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1411" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1412" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1413" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1415" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1417" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1418" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1419" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1420" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1421" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1422" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1424" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1426" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1427" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1428" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1429" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1430" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1433" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1434" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1437" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1438" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1439" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1440" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1443" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1444" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1446" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1447" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1448" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1450" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1451" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1453" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1455" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1456" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1457" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1458" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1459" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1460" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1461" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>2.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1463" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1465" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1468" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1471" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1473" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1476" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1477" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1478" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1479" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1480" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>2.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1484" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1485" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1486" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1487" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1488" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1489" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1490" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1491" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1492" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1494" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1495" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1497" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1498" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1500" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1501" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1502" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1504" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1505" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1507" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1508" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1509" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1510" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1511" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1513" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1515" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1516" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1517" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1518" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1519" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1523" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1524" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1526" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1527" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1528" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>2.5</v>
       </c>
       <c r="G1529" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1532" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1533" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1536" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1537" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1539" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1540" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1541" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1544" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1545" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1546" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1547" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1548" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1550" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1551" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1552" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1553" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1554" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1555" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1558" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1559" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1560" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1561" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1563" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1564" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1565" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1566" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1568" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>601</v>
+        <v>522</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>2.25</v>
       </c>
       <c r="G1575" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>2.25</v>
       </c>
       <c r="G1576" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1577" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1578" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1581" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1582" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1583" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1584" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1585" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1587" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1588" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1589" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1593" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1596" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1598" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1599" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>2.25</v>
       </c>
       <c r="G1601" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1605" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1611" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1612" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1613" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1614" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1617" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1619" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1620" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1621" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1622" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1623" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1624" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1626" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1627" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1628" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1629" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1630" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1631" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1632" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1633" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1635" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1637" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1638" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1639" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1640" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1641" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1642" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1643" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1468118429184</t>
+    <t xml:space="preserve">1.14681172370911</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">1.12615489959717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12544274330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09552562236786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831974983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09623801708221</t>
+    <t xml:space="preserve">1.1254426240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09552586078644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831963062286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0962381362915</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695041179657</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">1.0905396938324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08412873744965</t>
+    <t xml:space="preserve">1.08412885665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.00007700920105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943804621696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925996959209442</t>
+    <t xml:space="preserve">0.943804800510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925997078418732</t>
   </si>
   <si>
     <t xml:space="preserve">0.993665993213654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03925347328186</t>
+    <t xml:space="preserve">1.03925359249115</t>
   </si>
   <si>
     <t xml:space="preserve">1.01004898548126</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">1.01859676837921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05492413043976</t>
+    <t xml:space="preserve">1.05492424964905</t>
   </si>
   <si>
     <t xml:space="preserve">1.03213047981262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03711676597595</t>
+    <t xml:space="preserve">1.03711664676666</t>
   </si>
   <si>
     <t xml:space="preserve">1.02571988105774</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">1.04495203495026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02073383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366178035736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354146957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024625301361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435641288757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530909061432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830724239349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
+    <t xml:space="preserve">1.02643215656281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073347568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366297245026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354087352753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024744510651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435402870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939531028270721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970159888267517</t>
   </si>
   <si>
     <t xml:space="preserve">0.961612403392792</t>
@@ -143,73 +143,73 @@
     <t xml:space="preserve">1.00435078144073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997939884662628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392340183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529107093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419946670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990817010402679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717221736908</t>
+    <t xml:space="preserve">0.997939765453339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529166698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979419887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9908167719841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967610359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227489948273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717209815979</t>
   </si>
   <si>
     <t xml:space="preserve">1.0150351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00078892707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02215826511383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577533245087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648748874664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076126098633</t>
+    <t xml:space="preserve">1.00078916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02215814590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577521324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076138019562</t>
   </si>
   <si>
     <t xml:space="preserve">1.00221371650696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984405875205994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00791215896606</t>
+    <t xml:space="preserve">0.984406113624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00791203975677</t>
   </si>
   <si>
     <t xml:space="preserve">1.03284287452698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01930916309357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03996610641479</t>
+    <t xml:space="preserve">1.01930892467499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03996598720551</t>
   </si>
   <si>
     <t xml:space="preserve">1.09979963302612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1005117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484125137329</t>
+    <t xml:space="preserve">1.10051190853119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084841132164</t>
   </si>
   <si>
     <t xml:space="preserve">1.08982741832733</t>
@@ -221,61 +221,61 @@
     <t xml:space="preserve">1.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13185322284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13968873023987</t>
+    <t xml:space="preserve">1.13185334205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13968861103058</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393483638763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689496040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09766268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16105782985687</t>
+    <t xml:space="preserve">1.11689472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09766280651093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16105771064758</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963327884674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14752388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13683938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12900424003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467489719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17316710948944</t>
+    <t xml:space="preserve">1.14752376079559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683950901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612735271454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12900400161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467465877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17316699028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.1703177690506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18100249767303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19738554954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21091949939728</t>
+    <t xml:space="preserve">1.18100237846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.197385430336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091914176941</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163153648376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20593297481537</t>
+    <t xml:space="preserve">1.20593321323395</t>
   </si>
   <si>
     <t xml:space="preserve">1.22302842140198</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">1.22089147567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19596087932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23548448085785</t>
+    <t xml:space="preserve">1.19596099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23548460006714</t>
   </si>
   <si>
     <t xml:space="preserve">1.22670149803162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18937349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18790984153748</t>
+    <t xml:space="preserve">1.18937361240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1879096031189</t>
   </si>
   <si>
     <t xml:space="preserve">1.16302418708801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16595208644867</t>
+    <t xml:space="preserve">1.16595196723938</t>
   </si>
   <si>
     <t xml:space="preserve">1.16229236125946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16375613212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570485591888</t>
+    <t xml:space="preserve">1.16375625133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570509433746</t>
   </si>
   <si>
     <t xml:space="preserve">1.14911782741547</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">1.15424132347107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14106643199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11837708950043</t>
+    <t xml:space="preserve">1.1410665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11837685108185</t>
   </si>
   <si>
     <t xml:space="preserve">1.10154283046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520255565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0993469953537</t>
+    <t xml:space="preserve">1.10520243644714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934687614441</t>
   </si>
   <si>
     <t xml:space="preserve">1.14545822143555</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">1.12935602664948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12203669548035</t>
+    <t xml:space="preserve">1.12203657627106</t>
   </si>
   <si>
     <t xml:space="preserve">1.12716019153595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07226598262787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860649585724</t>
+    <t xml:space="preserve">1.07226586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860637664795</t>
   </si>
   <si>
     <t xml:space="preserve">1.13081967830658</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20767152309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17839467525482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401179790497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18351817131042</t>
+    <t xml:space="preserve">1.20767140388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17839479446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18351829051971</t>
   </si>
   <si>
     <t xml:space="preserve">1.20474374294281</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">1.1747350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18571388721466</t>
+    <t xml:space="preserve">1.18571400642395</t>
   </si>
   <si>
     <t xml:space="preserve">1.17546689510345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19303297996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20035243034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888842105865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499073505402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20693981647491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21425902843475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22230982780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962927818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23328852653503</t>
+    <t xml:space="preserve">1.1930330991745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20035231113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888854026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499085426331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20693957805634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21425890922546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22230994701385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962915897369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
     <t xml:space="preserve">1.22450578212738</t>
@@ -425,52 +425,52 @@
     <t xml:space="preserve">1.25524640083313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28232753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745994091034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208957195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184246063232</t>
+    <t xml:space="preserve">1.28232741355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550218582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29184257984161</t>
   </si>
   <si>
     <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24426782131195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25890624523163</t>
+    <t xml:space="preserve">1.24426770210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25890600681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.27354454994202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25963795185089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26183378696442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26256549358368</t>
+    <t xml:space="preserve">1.25963807106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26183366775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26256573200226</t>
   </si>
   <si>
     <t xml:space="preserve">1.26915311813354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23694837093353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109304904938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26402950286865</t>
+    <t xml:space="preserve">1.23694860935211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109316825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26402962207794</t>
   </si>
   <si>
     <t xml:space="preserve">1.24719536304474</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">1.21938228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19962048530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669258594513</t>
+    <t xml:space="preserve">1.19962060451508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669270515442</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376504421234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17766273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19742453098297</t>
+    <t xml:space="preserve">1.17766284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19742476940155</t>
   </si>
   <si>
     <t xml:space="preserve">1.20620763301849</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.16522002220154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15643692016602</t>
+    <t xml:space="preserve">1.15643715858459</t>
   </si>
   <si>
     <t xml:space="preserve">1.16887962818146</t>
@@ -518,148 +518,148 @@
     <t xml:space="preserve">1.17693078517914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19522893428802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985832691193</t>
+    <t xml:space="preserve">1.19522881507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985844612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.18498194217682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17400312423706</t>
+    <t xml:space="preserve">1.17400300502777</t>
   </si>
   <si>
     <t xml:space="preserve">1.17107546329498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16814756393433</t>
+    <t xml:space="preserve">1.16814768314362</t>
   </si>
   <si>
     <t xml:space="preserve">1.1461900472641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14326238632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11252176761627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13447940349579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1198410987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11325359344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593450069427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007894039154</t>
+    <t xml:space="preserve">1.14326250553131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11252152919769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1344792842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984097957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11325371265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593438148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007917881012</t>
   </si>
   <si>
     <t xml:space="preserve">1.12276864051819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11032581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11618113517761</t>
+    <t xml:space="preserve">1.11032593250275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11618137359619</t>
   </si>
   <si>
     <t xml:space="preserve">1.13960289955139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12789189815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14399433135986</t>
+    <t xml:space="preserve">1.12789213657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14399409294128</t>
   </si>
   <si>
     <t xml:space="preserve">1.14179861545563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13521122932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13813889026642</t>
+    <t xml:space="preserve">1.13521134853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13813877105713</t>
   </si>
   <si>
     <t xml:space="preserve">1.14253044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1944967508316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18132221698761</t>
+    <t xml:space="preserve">1.19449687004089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1813223361969</t>
   </si>
   <si>
     <t xml:space="preserve">1.17253935337067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17912650108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887083530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13374733924866</t>
+    <t xml:space="preserve">1.17912638187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887107372284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
     <t xml:space="preserve">1.12350046634674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12569618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11910903453827</t>
+    <t xml:space="preserve">1.12569630146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11910891532898</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12642800807953</t>
+    <t xml:space="preserve">1.12642824649811</t>
   </si>
   <si>
     <t xml:space="preserve">1.15936470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15277743339539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16741561889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22377383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596943378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25671029090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24792718887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24060797691345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26622533798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2684211730957</t>
+    <t xml:space="preserve">1.15277755260468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16741597652435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22377371788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596955299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25671052932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24792730808258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24060821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26622545719147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26842105388641</t>
   </si>
   <si>
     <t xml:space="preserve">1.29769802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30867660045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29403841495514</t>
+    <t xml:space="preserve">1.30867671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29403829574585</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477903366089</t>
@@ -668,37 +668,37 @@
     <t xml:space="preserve">1.32404720783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014049053192</t>
+    <t xml:space="preserve">1.3101407289505</t>
   </si>
   <si>
     <t xml:space="preserve">1.3284387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29037880897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135750770569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30282127857208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31526398658752</t>
+    <t xml:space="preserve">1.29037857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135762691498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30282151699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3152642250061</t>
   </si>
   <si>
     <t xml:space="preserve">1.32624292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36137521266937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941757678986</t>
+    <t xml:space="preserve">1.36137533187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941769599915</t>
   </si>
   <si>
     <t xml:space="preserve">1.34673678874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38699233531952</t>
+    <t xml:space="preserve">1.3869925737381</t>
   </si>
   <si>
     <t xml:space="preserve">1.36869442462921</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">1.38772451877594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35991132259369</t>
+    <t xml:space="preserve">1.35991144180298</t>
   </si>
   <si>
     <t xml:space="preserve">1.37454986572266</t>
@@ -716,52 +716,52 @@
     <t xml:space="preserve">1.40529036521912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39065206050873</t>
+    <t xml:space="preserve">1.39065217971802</t>
   </si>
   <si>
     <t xml:space="preserve">1.39650762081146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114592552185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3818690776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37162208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3884562253952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41927754878998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45009875297546</t>
+    <t xml:space="preserve">1.41114580631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38186883926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162220478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38845634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41927742958069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45009851455688</t>
   </si>
   <si>
     <t xml:space="preserve">1.50046503543854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53654837608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56361079216003</t>
+    <t xml:space="preserve">1.53654825687408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56361067295074</t>
   </si>
   <si>
     <t xml:space="preserve">1.58616268634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60570812225342</t>
+    <t xml:space="preserve">1.60570776462555</t>
   </si>
   <si>
     <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51098918914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693370819092</t>
+    <t xml:space="preserve">1.51098930835724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693382740021</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866463661194</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">1.49069249629974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46814024448395</t>
+    <t xml:space="preserve">1.46814036369324</t>
   </si>
   <si>
     <t xml:space="preserve">1.46964383125305</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">1.43205690383911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43581569194794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40574634075165</t>
+    <t xml:space="preserve">1.43581557273865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40574622154236</t>
   </si>
   <si>
     <t xml:space="preserve">1.45836782455444</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">1.45911931991577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189903259277</t>
+    <t xml:space="preserve">1.47189891338348</t>
   </si>
   <si>
     <t xml:space="preserve">1.45310568809509</t>
@@ -809,64 +809,64 @@
     <t xml:space="preserve">1.42829835414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41852581501007</t>
+    <t xml:space="preserve">1.41852569580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.42980170249939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42078101634979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42604315280914</t>
+    <t xml:space="preserve">1.4207808971405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42604303359985</t>
   </si>
   <si>
     <t xml:space="preserve">1.41702222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42529153823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44408464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47716116905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49219608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46663677692413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46588516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144423007965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48843705654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850664615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948584079742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50347197055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48167169094086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4959545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51249265670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497543811798</t>
+    <t xml:space="preserve">1.42529141902924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44408476352692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47716128826141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49219584465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46663701534271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46588504314423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144411087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48843729496002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948548316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50347185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48167157173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49595439434052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51249289512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497555732727</t>
   </si>
   <si>
     <t xml:space="preserve">1.52151346206665</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">1.49369931221008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49896144866943</t>
+    <t xml:space="preserve">1.49896168708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602398395538</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">1.496706366539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5079824924469</t>
+    <t xml:space="preserve">1.50798237323761</t>
   </si>
   <si>
     <t xml:space="preserve">1.5485759973526</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">1.48242342472076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47039556503296</t>
+    <t xml:space="preserve">1.47039568424225</t>
   </si>
   <si>
     <t xml:space="preserve">1.47941648960114</t>
@@ -902,25 +902,25 @@
     <t xml:space="preserve">1.53203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903091907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51399612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55158305168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511414051056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55609333515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126695156097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6763710975647</t>
+    <t xml:space="preserve">1.52903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51399624347687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55158293247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55609357357025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126718997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637121677399</t>
   </si>
   <si>
     <t xml:space="preserve">1.6568261384964</t>
@@ -929,124 +929,124 @@
     <t xml:space="preserve">1.69140589237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70644068717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937827110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735017299652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6688539981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778746843338</t>
+    <t xml:space="preserve">1.70644044876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71997213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65381944179535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735029220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885387897491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67787456512451</t>
   </si>
   <si>
     <t xml:space="preserve">1.67035722732544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67186081409454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839871883392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6868953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878452777863</t>
+    <t xml:space="preserve">1.67186057567596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839907646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68689560890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983307361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878440856934</t>
   </si>
   <si>
     <t xml:space="preserve">1.64630174636841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74402737617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115926265717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81318712234497</t>
+    <t xml:space="preserve">1.74402761459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81318736076355</t>
   </si>
   <si>
     <t xml:space="preserve">1.79213845729828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79965579509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84175324440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86430501937866</t>
+    <t xml:space="preserve">1.79965591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84175336360931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86430549621582</t>
   </si>
   <si>
     <t xml:space="preserve">1.8387463092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76657962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245467662811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206910610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77560019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83423566818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80566966533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82220792770386</t>
+    <t xml:space="preserve">1.76657927036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71245455741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133654117584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206922531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77560043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83423578739166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8056697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82220780849457</t>
   </si>
   <si>
     <t xml:space="preserve">1.72899258136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7410204410553</t>
+    <t xml:space="preserve">1.74102032184601</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598576545715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75154483318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7229790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70193016529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441282749176</t>
+    <t xml:space="preserve">1.751544713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72297883033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70192992687225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441294670105</t>
   </si>
   <si>
     <t xml:space="preserve">1.68388867378235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63728082180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434359550476</t>
+    <t xml:space="preserve">1.63728094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434347629547</t>
   </si>
   <si>
     <t xml:space="preserve">1.72448205947876</t>
@@ -1055,64 +1055,64 @@
     <t xml:space="preserve">1.71846854686737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75755870342255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73500669002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951685428619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73651027679443</t>
+    <t xml:space="preserve">1.75755858421326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73500657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951709270477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73651015758514</t>
   </si>
   <si>
     <t xml:space="preserve">1.71395802497864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78161442279816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906193256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81920111179352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82671809196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80416631698608</t>
+    <t xml:space="preserve">1.78161406517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906205177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920123100281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80416655540466</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88685727119446</t>
+    <t xml:space="preserve">1.88685715198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.81168389320374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79664897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77409648895264</t>
+    <t xml:space="preserve">1.79664885997772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77409672737122</t>
   </si>
   <si>
     <t xml:space="preserve">1.78913164138794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85678791999817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927034378052</t>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927046298981</t>
   </si>
   <si>
     <t xml:space="preserve">1.88701057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87934005260468</t>
+    <t xml:space="preserve">1.87934017181396</t>
   </si>
   <si>
     <t xml:space="preserve">1.89468145370483</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">1.84865701198578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86399805545807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81797385215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81030261516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235209465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83331525325775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80263209342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75660741329193</t>
+    <t xml:space="preserve">1.86399841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797349452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.810302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235257148743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83331513404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80263197422028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75660753250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.70291209220886</t>
@@ -1151,43 +1151,43 @@
     <t xml:space="preserve">1.6798996925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69524121284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222905158997</t>
+    <t xml:space="preserve">1.69524133205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222893238068</t>
   </si>
   <si>
     <t xml:space="preserve">1.7489367723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65688741207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64154601097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58017957210541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455805301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620413303375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031957149506</t>
+    <t xml:space="preserve">1.65688753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64154613018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58017945289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620425224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57250893115997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5149781703949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031969070435</t>
   </si>
   <si>
     <t xml:space="preserve">1.48813033103943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4152580499649</t>
+    <t xml:space="preserve">1.41525793075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.41142272949219</t>
@@ -1196,58 +1196,58 @@
     <t xml:space="preserve">1.37306869029999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35005640983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.380739569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39224576950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36923325061798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39991641044617</t>
+    <t xml:space="preserve">1.35005629062653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38073933124542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39224565029144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36923313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39991652965546</t>
   </si>
   <si>
     <t xml:space="preserve">1.35772716999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35389173030853</t>
+    <t xml:space="preserve">1.35389184951782</t>
   </si>
   <si>
     <t xml:space="preserve">1.34238564968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30403196811676</t>
+    <t xml:space="preserve">1.30403184890747</t>
   </si>
   <si>
     <t xml:space="preserve">1.28101933002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26951313018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25417160987854</t>
+    <t xml:space="preserve">1.26951324939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25417172908783</t>
   </si>
   <si>
     <t xml:space="preserve">1.24650096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25800716876984</t>
+    <t xml:space="preserve">1.25800704956055</t>
   </si>
   <si>
     <t xml:space="preserve">1.29636096954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869020938873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30019629001617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252541065216</t>
+    <t xml:space="preserve">1.28869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30019640922546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252564907074</t>
   </si>
   <si>
     <t xml:space="preserve">1.31937336921692</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">1.33087944984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33855009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471488952637</t>
+    <t xml:space="preserve">1.33855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471477031708</t>
   </si>
   <si>
     <t xml:space="preserve">1.31553792953491</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">1.38457489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40375196933746</t>
+    <t xml:space="preserve">1.40375173091888</t>
   </si>
   <si>
     <t xml:space="preserve">1.36156249046326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36539793014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43443500995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37690412998199</t>
+    <t xml:space="preserve">1.36539804935455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43443489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37690401077271</t>
   </si>
   <si>
     <t xml:space="preserve">1.38841021060944</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.32320857048035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37706005573273</t>
+    <t xml:space="preserve">1.37706017494202</t>
   </si>
   <si>
     <t xml:space="preserve">1.3890346288681</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">1.32916235923767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3451281785965</t>
+    <t xml:space="preserve">1.35311138629913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34512841701508</t>
   </si>
   <si>
     <t xml:space="preserve">1.36508584022522</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">1.4010089635849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40899193286896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41697490215302</t>
+    <t xml:space="preserve">1.40899205207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4169750213623</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886432170868</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">1.49680459499359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50877904891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51277041435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49281311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46487271785736</t>
+    <t xml:space="preserve">1.50877892971039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51277053356171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49281299114227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46487283706665</t>
   </si>
   <si>
     <t xml:space="preserve">1.50079596042633</t>
@@ -1364,40 +1364,37 @@
     <t xml:space="preserve">1.44491529464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45289838314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693244457245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495787143707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42096638679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40500056743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39302599430084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38504314422607</t>
+    <t xml:space="preserve">1.45289826393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693220615387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495775222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42096650600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40500044822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39302611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38504302501678</t>
   </si>
   <si>
     <t xml:space="preserve">1.4289493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37306880950928</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.36907720565796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35710299015045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34911978244781</t>
+    <t xml:space="preserve">1.35710287094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3491199016571</t>
   </si>
   <si>
     <t xml:space="preserve">1.4848301410675</t>
@@ -1406,31 +1403,31 @@
     <t xml:space="preserve">1.47684717178345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46088135242462</t>
+    <t xml:space="preserve">1.46088123321533</t>
   </si>
   <si>
     <t xml:space="preserve">1.48882162570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52075326442719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51676189899445</t>
+    <t xml:space="preserve">1.52075338363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51676201820374</t>
   </si>
   <si>
     <t xml:space="preserve">1.56066823005676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659147262573</t>
+    <t xml:space="preserve">1.59659135341644</t>
   </si>
   <si>
     <t xml:space="preserve">1.56465971469879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54071080684662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53272771835327</t>
+    <t xml:space="preserve">1.54071068763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
     <t xml:space="preserve">1.52873635292053</t>
@@ -1439,22 +1436,22 @@
     <t xml:space="preserve">1.58860850334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55667674541473</t>
+    <t xml:space="preserve">1.55667662620544</t>
   </si>
   <si>
     <t xml:space="preserve">1.54869377613068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5367192029953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54470229148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55268526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52474498748779</t>
+    <t xml:space="preserve">1.53671932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54470241069794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55268537998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52474474906921</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264268398285</t>
@@ -1463,40 +1460,40 @@
     <t xml:space="preserve">1.67642092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801183223724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88397765159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94784152507782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15539884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05960273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16338157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20329642295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926259994507</t>
+    <t xml:space="preserve">1.86801195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88397777080536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478417634964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15539836883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05960297584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16338133811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20329618453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926188468933</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17934727668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2352283000946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11548376083374</t>
+    <t xml:space="preserve">2.1793475151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23522806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11548399925232</t>
   </si>
   <si>
     <t xml:space="preserve">1.9877564907074</t>
@@ -1505,70 +1502,70 @@
     <t xml:space="preserve">1.82011437416077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82809722423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91590976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63650619983673</t>
+    <t xml:space="preserve">1.82809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91591000556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002898216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63650631904602</t>
   </si>
   <si>
     <t xml:space="preserve">1.44890689849854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5925999879837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72431886196136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62852334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448916912079</t>
+    <t xml:space="preserve">1.59260010719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72431910037994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62852323055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6444890499115</t>
   </si>
   <si>
     <t xml:space="preserve">1.68440389633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60457444190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66045522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65247213840485</t>
+    <t xml:space="preserve">1.60457456111908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66045498847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65247225761414</t>
   </si>
   <si>
     <t xml:space="preserve">1.74826765060425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71633589267731</t>
+    <t xml:space="preserve">1.7163360118866</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843819618225</t>
+    <t xml:space="preserve">1.66843807697296</t>
   </si>
   <si>
     <t xml:space="preserve">1.61255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69238686561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75625061988831</t>
+    <t xml:space="preserve">1.69238698482513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625097751617</t>
   </si>
   <si>
     <t xml:space="preserve">1.76423358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90792691707611</t>
+    <t xml:space="preserve">1.90792679786682</t>
   </si>
   <si>
     <t xml:space="preserve">1.95582485198975</t>
@@ -1577,28 +1574,28 @@
     <t xml:space="preserve">1.92389297485352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94757211208344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456234455109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90630984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85679543018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84029078483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81553339958191</t>
+    <t xml:space="preserve">1.94757199287415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91456258296967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630996227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8567955493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84029054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8155335187912</t>
   </si>
   <si>
     <t xml:space="preserve">1.79077613353729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75776660442352</t>
+    <t xml:space="preserve">1.75776648521423</t>
   </si>
   <si>
     <t xml:space="preserve">1.79902851581573</t>
@@ -1607,22 +1604,22 @@
     <t xml:space="preserve">1.77427124977112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76601898670197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78252375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73300898075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74951386451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71650421619415</t>
+    <t xml:space="preserve">1.76601886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126136302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78252387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73300909996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495139837265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71650409698486</t>
   </si>
   <si>
     <t xml:space="preserve">1.69999933242798</t>
@@ -1631,58 +1628,58 @@
     <t xml:space="preserve">1.6834944486618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67524206638336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66698956489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873730182648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825171470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174695014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72475671768188</t>
+    <t xml:space="preserve">1.67524218559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66698968410492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873742103577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174706935883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7247565984726</t>
   </si>
   <si>
     <t xml:space="preserve">1.65048480033875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63398015499115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62572753429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62985384464264</t>
+    <t xml:space="preserve">1.63398003578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62572765350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62985396385193</t>
   </si>
   <si>
     <t xml:space="preserve">1.60922276973724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89805746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95582461357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660105705261</t>
+    <t xml:space="preserve">1.89805734157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582437515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660153388977</t>
   </si>
   <si>
     <t xml:space="preserve">1.9640771150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93931972980499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87330031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88155269622803</t>
+    <t xml:space="preserve">1.93931949138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87330007553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88155281543732</t>
   </si>
   <si>
     <t xml:space="preserve">1.88980507850647</t>
@@ -1691,16 +1688,16 @@
     <t xml:space="preserve">1.86504793167114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92281496524811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93106722831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883450031281</t>
+    <t xml:space="preserve">1.92281484603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93106710910797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.97232949733734</t>
@@ -1709,16 +1706,16 @@
     <t xml:space="preserve">1.98058199882507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0631058216095</t>
+    <t xml:space="preserve">2.06310606002808</t>
   </si>
   <si>
     <t xml:space="preserve">2.19514489173889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17863988876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17038774490356</t>
+    <t xml:space="preserve">2.17864036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17038750648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.16213488578796</t>
@@ -1727,31 +1724,34 @@
     <t xml:space="preserve">2.14563035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19566059112549</t>
+    <t xml:space="preserve">2.19566035270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
     <t xml:space="preserve">2.18715023994446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15310883522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906766891479</t>
+    <t xml:space="preserve">2.15310907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906790733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.08502674102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09353709220886</t>
+    <t xml:space="preserve">2.09353685379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396487236023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02545428276062</t>
+    <t xml:space="preserve">2.03396463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0254545211792</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247498512268</t>
@@ -1760,34 +1760,34 @@
     <t xml:space="preserve">2.05098533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91482019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184101581573</t>
+    <t xml:space="preserve">1.91482031345367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184065818787</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290300369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439229488373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07651591300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11055731773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05949568748474</t>
+    <t xml:space="preserve">1.98290252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439253330231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0765163898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11055755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05949592590332</t>
   </si>
   <si>
     <t xml:space="preserve">1.99992334842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99141311645508</t>
+    <t xml:space="preserve">1.9914128780365</t>
   </si>
   <si>
     <t xml:space="preserve">2.00843358039856</t>
@@ -1796,49 +1796,49 @@
     <t xml:space="preserve">2.01694393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10204744338989</t>
+    <t xml:space="preserve">2.10204696655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14459848403931</t>
+    <t xml:space="preserve">2.14459872245789</t>
   </si>
   <si>
     <t xml:space="preserve">2.16161918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13608860969543</t>
+    <t xml:space="preserve">2.13608837127686</t>
   </si>
   <si>
     <t xml:space="preserve">1.9658819437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94035124778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89779984951019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722687959671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92333042621613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94886136054993</t>
+    <t xml:space="preserve">1.94035112857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977997303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87226891517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92333054542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94886159896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.07243394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08129048347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05472087860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04586458206177</t>
+    <t xml:space="preserve">2.08129072189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05472111701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04586434364319</t>
   </si>
   <si>
     <t xml:space="preserve">2.00158166885376</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">1.93958580493927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9750120639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99272501468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95729899406433</t>
+    <t xml:space="preserve">1.97501194477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99272525310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95729887485504</t>
   </si>
   <si>
     <t xml:space="preserve">1.94844233989716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8687332868576</t>
+    <t xml:space="preserve">1.86873304843903</t>
   </si>
   <si>
     <t xml:space="preserve">1.92187285423279</t>
@@ -1874,43 +1874,43 @@
     <t xml:space="preserve">1.91301620006561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8775897026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072926998138</t>
+    <t xml:space="preserve">1.87758982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96615552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90415954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89530313014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8244503736496</t>
+    <t xml:space="preserve">1.96615540981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90415978431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89530301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82445049285889</t>
   </si>
   <si>
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673742294312</t>
+    <t xml:space="preserve">1.80673730373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70045876502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70488703250885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131116390228</t>
+    <t xml:space="preserve">1.70045864582062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70488691329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131128311157</t>
   </si>
   <si>
     <t xml:space="preserve">1.815593957901</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">1.85102021694183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78016781806946</t>
+    <t xml:space="preserve">1.84216368198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78016769886017</t>
   </si>
   <si>
     <t xml:space="preserve">1.85987663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75802648067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76245450973511</t>
+    <t xml:space="preserve">1.75802636146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7624546289444</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">1.7535982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71817195415497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7093151807785</t>
+    <t xml:space="preserve">1.71817183494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70931529998779</t>
   </si>
   <si>
     <t xml:space="preserve">1.72702848911285</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">1.90141236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88295209407806</t>
+    <t xml:space="preserve">1.88295221328735</t>
   </si>
   <si>
     <t xml:space="preserve">1.91987276077271</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">1.84603154659271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79988074302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78142035007477</t>
+    <t xml:space="preserve">1.79988086223602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78142046928406</t>
   </si>
   <si>
     <t xml:space="preserve">1.77219021320343</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">1.74449980258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73526966571808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70757913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67988884449005</t>
+    <t xml:space="preserve">1.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70757925510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">1.61527764797211</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">1.7168093919754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66142845153809</t>
+    <t xml:space="preserve">1.6614283323288</t>
   </si>
   <si>
     <t xml:space="preserve">1.65219819545746</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.95679330825806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9752539396286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93833291530609</t>
+    <t xml:space="preserve">1.97525370121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833303451538</t>
   </si>
   <si>
     <t xml:space="preserve">1.80449593067169</t>
@@ -2051,28 +2051,28 @@
     <t xml:space="preserve">1.84141647815704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81372594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85526180267334</t>
+    <t xml:space="preserve">1.81372606754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85526168346405</t>
   </si>
   <si>
     <t xml:space="preserve">1.87372207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89218235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92910301685333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91064262390137</t>
+    <t xml:space="preserve">1.8921822309494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92910277843475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91064250469208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218634128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99371409416199</t>
+    <t xml:space="preserve">1.99371421337128</t>
   </si>
   <si>
     <t xml:space="preserve">1.98448395729065</t>
@@ -27212,7 +27212,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27238,7 +27238,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G950" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27290,7 +27290,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G952" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27316,7 +27316,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27394,7 +27394,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G956" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27420,7 +27420,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G957" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27472,7 +27472,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27498,7 +27498,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27550,7 +27550,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G962" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27576,7 +27576,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G963" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27602,7 +27602,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27628,7 +27628,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27654,7 +27654,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27680,7 +27680,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27706,7 +27706,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G968" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27732,7 +27732,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G969" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27758,7 +27758,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27784,7 +27784,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27810,7 +27810,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27862,7 +27862,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G974" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27914,7 +27914,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27940,7 +27940,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28018,7 +28018,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G980" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28044,7 +28044,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G981" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28070,7 +28070,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28174,7 +28174,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28200,7 +28200,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28330,7 +28330,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G992" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28356,7 +28356,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28408,7 +28408,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G995" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28434,7 +28434,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G996" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28486,7 +28486,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G998" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28512,7 +28512,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28538,7 +28538,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1000" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28564,7 +28564,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1001" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28616,7 +28616,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1003" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28694,7 +28694,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1006" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28720,7 +28720,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1007" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28772,7 +28772,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1009" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28798,7 +28798,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28824,7 +28824,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1011" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28850,7 +28850,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1012" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28902,7 +28902,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1014" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28928,7 +28928,7 @@
         <v>2</v>
       </c>
       <c r="G1015" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28954,7 +28954,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1016" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28980,7 +28980,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1017" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29006,7 +29006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1018" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29084,7 +29084,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1021" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29110,7 +29110,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29136,7 +29136,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1023" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29162,7 +29162,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1024" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29188,7 +29188,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1025" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29214,7 +29214,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29240,7 +29240,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1027" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29266,7 +29266,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1028" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29292,7 +29292,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1029" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29318,7 +29318,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1030" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29344,7 +29344,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1031" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29370,7 +29370,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1032" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29396,7 +29396,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1033" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29422,7 +29422,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1034" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29448,7 +29448,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1035" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29474,7 +29474,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1036" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29500,7 +29500,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1037" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29526,7 +29526,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1038" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29552,7 +29552,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1039" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29578,7 +29578,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29604,7 +29604,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1041" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29630,7 +29630,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1042" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29656,7 +29656,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1043" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29682,7 +29682,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1044" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29708,7 +29708,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1045" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29734,7 +29734,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1046" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29760,7 +29760,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29786,7 +29786,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1048" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29812,7 +29812,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29838,7 +29838,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1050" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29864,7 +29864,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1051" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29890,7 +29890,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29916,7 +29916,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1053" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29942,7 +29942,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1054" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29968,7 +29968,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1055" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29994,7 +29994,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1056" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30020,7 +30020,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1057" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30046,7 +30046,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1058" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30072,7 +30072,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30098,7 +30098,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30124,7 +30124,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1061" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30150,7 +30150,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1062" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30228,7 +30228,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1065" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30254,7 +30254,7 @@
         <v>2</v>
       </c>
       <c r="G1066" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30280,7 +30280,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1067" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30332,7 +30332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30358,7 +30358,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1070" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30384,7 +30384,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1071" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30514,7 +30514,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1076" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30540,7 +30540,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1077" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30644,7 +30644,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1081" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30670,7 +30670,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1082" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30696,7 +30696,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1083" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30722,7 +30722,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1084" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30748,7 +30748,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30774,7 +30774,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1086" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30800,7 +30800,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1087" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30826,7 +30826,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30852,7 +30852,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1089" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30878,7 +30878,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30904,7 +30904,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1091" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30930,7 +30930,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1092" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30956,7 +30956,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30982,7 +30982,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1094" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31008,7 +31008,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1095" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31034,7 +31034,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1096" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31060,7 +31060,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31086,7 +31086,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1098" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31112,7 +31112,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31138,7 +31138,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31164,7 +31164,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1101" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31190,7 +31190,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31216,7 +31216,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1103" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31242,7 +31242,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1104" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31268,7 +31268,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1105" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31294,7 +31294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1106" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31320,7 +31320,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1107" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31346,7 +31346,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1108" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31372,7 +31372,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1109" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31398,7 +31398,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31424,7 +31424,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1111" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31450,7 +31450,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31476,7 +31476,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1113" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31502,7 +31502,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31528,7 +31528,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1115" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31554,7 +31554,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1116" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31580,7 +31580,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31606,7 +31606,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1118" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31632,7 +31632,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1119" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31658,7 +31658,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1120" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31684,7 +31684,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31710,7 +31710,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1122" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31736,7 +31736,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31762,7 +31762,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31788,7 +31788,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1125" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31814,7 +31814,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31840,7 +31840,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1127" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31866,7 +31866,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1128" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31892,7 +31892,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31918,7 +31918,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1130" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31944,7 +31944,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1131" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31970,7 +31970,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1132" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31996,7 +31996,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1133" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32022,7 +32022,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1134" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32048,7 +32048,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1135" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32074,7 +32074,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1136" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32100,7 +32100,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32126,7 +32126,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1138" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32152,7 +32152,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32178,7 +32178,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1140" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32204,7 +32204,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1141" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32230,7 +32230,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32256,7 +32256,7 @@
         <v>2.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32282,7 +32282,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32308,7 +32308,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32334,7 +32334,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32360,7 +32360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32386,7 +32386,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1148" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32412,7 +32412,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32438,7 +32438,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1150" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32464,7 +32464,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32490,7 +32490,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32516,7 +32516,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1153" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32542,7 +32542,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1154" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32568,7 +32568,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1155" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32594,7 +32594,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1156" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32620,7 +32620,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1157" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32646,7 +32646,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1158" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32672,7 +32672,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1159" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32698,7 +32698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1160" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32724,7 +32724,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1161" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32750,7 +32750,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1162" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32776,7 +32776,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1163" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32802,7 +32802,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1164" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32828,7 +32828,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1165" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32854,7 +32854,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1166" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32880,7 +32880,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1167" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32906,7 +32906,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1168" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32932,7 +32932,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1169" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32958,7 +32958,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1170" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32984,7 +32984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1171" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33010,7 +33010,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33036,7 +33036,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1173" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33062,7 +33062,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33088,7 +33088,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1175" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33114,7 +33114,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1176" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33140,7 +33140,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1177" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33166,7 +33166,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1178" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33192,7 +33192,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1179" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33218,7 +33218,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1180" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33244,7 +33244,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1181" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33270,7 +33270,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1182" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33296,7 +33296,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1183" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33322,7 +33322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1184" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33348,7 +33348,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1185" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33374,7 +33374,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1186" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33400,7 +33400,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1187" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33426,7 +33426,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1188" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33452,7 +33452,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1189" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33478,7 +33478,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1190" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33504,7 +33504,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33530,7 +33530,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1192" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33556,7 +33556,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1193" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33582,7 +33582,7 @@
         <v>2</v>
       </c>
       <c r="G1194" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33608,7 +33608,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1195" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33634,7 +33634,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33660,7 +33660,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1197" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33686,7 +33686,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33712,7 +33712,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1199" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33738,7 +33738,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1200" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33764,7 +33764,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33790,7 +33790,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33816,7 +33816,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33842,7 +33842,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33868,7 +33868,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33894,7 +33894,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1206" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33920,7 +33920,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1207" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33946,7 +33946,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1208" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33972,7 +33972,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1209" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33998,7 +33998,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34024,7 +34024,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34050,7 +34050,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34076,7 +34076,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1213" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34102,7 +34102,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1214" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34128,7 +34128,7 @@
         <v>2</v>
       </c>
       <c r="G1215" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34154,7 +34154,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34180,7 +34180,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1217" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34206,7 +34206,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1218" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34232,7 +34232,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34258,7 +34258,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1220" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34284,7 +34284,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34310,7 +34310,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34336,7 +34336,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34362,7 +34362,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34388,7 +34388,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1225" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34414,7 +34414,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1226" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34440,7 +34440,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34466,7 +34466,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1228" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34492,7 +34492,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1229" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34518,7 +34518,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34544,7 +34544,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1231" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34570,7 +34570,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34596,7 +34596,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34622,7 +34622,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34648,7 +34648,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1235" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34674,7 +34674,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34700,7 +34700,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34726,7 +34726,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34752,7 +34752,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34778,7 +34778,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1240" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34804,7 +34804,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1241" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34830,7 +34830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1242" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34856,7 +34856,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1243" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34882,7 +34882,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1244" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34908,7 +34908,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1245" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34934,7 +34934,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34960,7 +34960,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34986,7 +34986,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35012,7 +35012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1249" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35038,7 +35038,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1250" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35064,7 +35064,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35090,7 +35090,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1252" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35116,7 +35116,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35142,7 +35142,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35168,7 +35168,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1256" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35220,7 +35220,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35246,7 +35246,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1258" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35272,7 +35272,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35298,7 +35298,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1260" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35324,7 +35324,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1261" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35350,7 +35350,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1262" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35376,7 +35376,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35402,7 +35402,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35428,7 +35428,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35454,7 +35454,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35480,7 +35480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35506,7 +35506,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1268" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35532,7 +35532,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1269" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35558,7 +35558,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1270" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35584,7 +35584,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1271" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35610,7 +35610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35636,7 +35636,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35662,7 +35662,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1274" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35688,7 +35688,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35714,7 +35714,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1276" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35740,7 +35740,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1277" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35766,7 +35766,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1278" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35792,7 +35792,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35818,7 +35818,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1280" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35844,7 +35844,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1281" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35870,7 +35870,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1282" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35896,7 +35896,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1283" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35922,7 +35922,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1284" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35948,7 +35948,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35974,7 +35974,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1286" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36000,7 +36000,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1287" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36026,7 +36026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1288" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36052,7 +36052,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36078,7 +36078,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36104,7 +36104,7 @@
         <v>2.25</v>
       </c>
       <c r="G1291" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36130,7 +36130,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1292" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36156,7 +36156,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36182,7 +36182,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1294" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36208,7 +36208,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36234,7 +36234,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1296" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36260,7 +36260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36286,7 +36286,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1298" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36312,7 +36312,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36338,7 +36338,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36390,7 +36390,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1302" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36416,7 +36416,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1303" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36442,7 +36442,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1304" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36468,7 +36468,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36494,7 +36494,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36520,7 +36520,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36546,7 +36546,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36572,7 +36572,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36598,7 +36598,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36624,7 +36624,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1311" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36650,7 +36650,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1312" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36676,7 +36676,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1313" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36702,7 +36702,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36728,7 +36728,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1315" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36754,7 +36754,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36780,7 +36780,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36806,7 +36806,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36832,7 +36832,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36858,7 +36858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1320" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36884,7 +36884,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1321" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36910,7 +36910,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1322" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36936,7 +36936,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1323" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36962,7 +36962,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1324" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36988,7 +36988,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37014,7 +37014,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1326" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37040,7 +37040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37066,7 +37066,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1328" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37092,7 +37092,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37118,7 +37118,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1330" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37144,7 +37144,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1331" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37170,7 +37170,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37196,7 +37196,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37222,7 +37222,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1334" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37248,7 +37248,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1335" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37274,7 +37274,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1336" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37300,7 +37300,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37326,7 +37326,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37352,7 +37352,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1339" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37378,7 +37378,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1340" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37404,7 +37404,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1341" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37430,7 +37430,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1342" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37456,7 +37456,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37482,7 +37482,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1344" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37508,7 +37508,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37534,7 +37534,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37560,7 +37560,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1347" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37586,7 +37586,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37612,7 +37612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37638,7 +37638,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1350" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37664,7 +37664,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1351" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37690,7 +37690,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1352" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37794,7 +37794,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1356" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37820,7 +37820,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1357" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37846,7 +37846,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1358" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37872,7 +37872,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1359" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37898,7 +37898,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1360" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37924,7 +37924,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1361" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37976,7 +37976,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1363" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38002,7 +38002,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1364" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38028,7 +38028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1365" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38080,7 +38080,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1367" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38106,7 +38106,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1368" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38184,7 +38184,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38210,7 +38210,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1372" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38236,7 +38236,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38262,7 +38262,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1374" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38288,7 +38288,7 @@
         <v>2.5</v>
       </c>
       <c r="G1375" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38314,7 +38314,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38340,7 +38340,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1377" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38366,7 +38366,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38392,7 +38392,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38418,7 +38418,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38444,7 +38444,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1381" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38470,7 +38470,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1382" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38496,7 +38496,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1383" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38522,7 +38522,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1384" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38548,7 +38548,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38574,7 +38574,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38600,7 +38600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1387" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38626,7 +38626,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1388" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38652,7 +38652,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1389" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38678,7 +38678,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1390" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1391" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38756,7 +38756,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -68560,7 +68560,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6911111111</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>3890</v>
@@ -68581,6 +68581,32 @@
         <v>727</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6856481482</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>5896</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>728</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14681172370911</t>
+    <t xml:space="preserve">1.14681148529053</t>
   </si>
   <si>
     <t xml:space="preserve">AC5.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12544274330139</t>
+    <t xml:space="preserve">1.12615501880646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12544250488281</t>
   </si>
   <si>
     <t xml:space="preserve">1.09552574157715</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">1.11831951141357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09623801708221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09695041179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407328605652</t>
+    <t xml:space="preserve">1.0962381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09695017337799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407340526581</t>
   </si>
   <si>
     <t xml:space="preserve">1.0905396938324</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">0.925997078418732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993665874004364</t>
+    <t xml:space="preserve">0.993665993213654</t>
   </si>
   <si>
     <t xml:space="preserve">1.03925359249115</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">1.01859664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05492424964905</t>
+    <t xml:space="preserve">1.05492448806763</t>
   </si>
   <si>
     <t xml:space="preserve">1.03213059902191</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">1.02571976184845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02643215656281</t>
+    <t xml:space="preserve">1.04495203495026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02643227577209</t>
   </si>
   <si>
     <t xml:space="preserve">1.0207337141037</t>
@@ -116,55 +116,55 @@
     <t xml:space="preserve">0.94736635684967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900354146957397</t>
+    <t xml:space="preserve">0.900353968143463</t>
   </si>
   <si>
     <t xml:space="preserve">0.91602486371994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530789852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830664634705</t>
+    <t xml:space="preserve">0.922435522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530968666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98583060503006</t>
   </si>
   <si>
     <t xml:space="preserve">0.970160126686096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961612403392792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962324678897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00435078144073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997939884662628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392161369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991529285907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419887065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990816831588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967610359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227609157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717221736908</t>
+    <t xml:space="preserve">0.961612224578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962324738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997939944267273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991528987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979420006275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990816950798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967669963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227549552917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717209815979</t>
   </si>
   <si>
     <t xml:space="preserve">1.01503527164459</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">1.00078916549683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02215838432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00577521324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648748874664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076149940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00221359729767</t>
+    <t xml:space="preserve">1.02215826511383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00577545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648760795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076138019562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00221371650696</t>
   </si>
   <si>
     <t xml:space="preserve">0.984406113624573</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">1.01930904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03996586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09979963302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1005117893219</t>
+    <t xml:space="preserve">1.03996598720551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09979951381683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10051202774048</t>
   </si>
   <si>
     <t xml:space="preserve">1.084841132164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08982729911804</t>
+    <t xml:space="preserve">1.08982717990875</t>
   </si>
   <si>
     <t xml:space="preserve">1.1817147731781</t>
@@ -224,73 +224,73 @@
     <t xml:space="preserve">1.13185334205627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13968861103058</t>
+    <t xml:space="preserve">1.13968873023987</t>
   </si>
   <si>
     <t xml:space="preserve">1.15393483638763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689472198486</t>
+    <t xml:space="preserve">1.11689484119415</t>
   </si>
   <si>
     <t xml:space="preserve">1.09766268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16105771064758</t>
+    <t xml:space="preserve">1.16105782985687</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14752388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1368396282196</t>
+    <t xml:space="preserve">1.14752411842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683950901031</t>
   </si>
   <si>
     <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12900412082672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14467489719391</t>
+    <t xml:space="preserve">1.12900424003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14467465877533</t>
   </si>
   <si>
     <t xml:space="preserve">1.17316699028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17031788825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18100237846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19738531112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2109192609787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21163141727448</t>
+    <t xml:space="preserve">1.1703177690506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18100249767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.197385430336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21091938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21163177490234</t>
   </si>
   <si>
     <t xml:space="preserve">1.20593297481537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22302830219269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22089159488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19596076011658</t>
+    <t xml:space="preserve">1.22302842140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22089147567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19596087932587</t>
   </si>
   <si>
     <t xml:space="preserve">1.23548460006714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22670161724091</t>
+    <t xml:space="preserve">1.22670149803162</t>
   </si>
   <si>
     <t xml:space="preserve">1.18937349319458</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">1.16595208644867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16229224205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16375625133514</t>
+    <t xml:space="preserve">1.16229248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16375613212585</t>
   </si>
   <si>
     <t xml:space="preserve">1.15570509433746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14911794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424132347107</t>
+    <t xml:space="preserve">1.14911782741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424120426178</t>
   </si>
   <si>
     <t xml:space="preserve">1.1410665512085</t>
@@ -326,37 +326,37 @@
     <t xml:space="preserve">1.11837708950043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10154271125793</t>
+    <t xml:space="preserve">1.10154294967651</t>
   </si>
   <si>
     <t xml:space="preserve">1.10520243644714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09934687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12935590744019</t>
+    <t xml:space="preserve">1.09934711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545810222626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1293557882309</t>
   </si>
   <si>
     <t xml:space="preserve">1.12203669548035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12715995311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07226586341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06860649585724</t>
+    <t xml:space="preserve">1.12716007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07226610183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06860637664795</t>
   </si>
   <si>
     <t xml:space="preserve">1.13081967830658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12423241138458</t>
+    <t xml:space="preserve">1.12423229217529</t>
   </si>
   <si>
     <t xml:space="preserve">1.15716898441315</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">1.18717777729034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18205428123474</t>
+    <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839467525482</t>
+    <t xml:space="preserve">1.17839443683624</t>
   </si>
   <si>
     <t xml:space="preserve">1.20401191711426</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">1.18351817131042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20474398136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1747350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546689510345</t>
+    <t xml:space="preserve">1.2047438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17473518848419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571388721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546677589417</t>
   </si>
   <si>
     <t xml:space="preserve">1.1930330991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20035243034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19888842105865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21499073505402</t>
+    <t xml:space="preserve">1.20035231113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19888854026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21499061584473</t>
   </si>
   <si>
     <t xml:space="preserve">1.20693957805634</t>
@@ -413,46 +413,46 @@
     <t xml:space="preserve">1.22230994701385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962915897369</t>
+    <t xml:space="preserve">1.2296290397644</t>
   </si>
   <si>
     <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22450566291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524652004242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208957195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550230503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866780757904</t>
+    <t xml:space="preserve">1.22450578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524663925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232777118683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745970249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208945274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550218582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29184257984161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866804599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.24426770210266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25890600681305</t>
+    <t xml:space="preserve">1.25890612602234</t>
   </si>
   <si>
     <t xml:space="preserve">1.27354454994202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25963795185089</t>
+    <t xml:space="preserve">1.25963807106018</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183378696442</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">1.26256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915299892426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694849014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23109292984009</t>
+    <t xml:space="preserve">1.26915287971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694837093353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23109316825867</t>
   </si>
   <si>
     <t xml:space="preserve">1.26402962207794</t>
@@ -479,58 +479,58 @@
     <t xml:space="preserve">1.2230418920517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21938240528107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1996203660965</t>
+    <t xml:space="preserve">1.21938228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962024688721</t>
   </si>
   <si>
     <t xml:space="preserve">1.19669258594513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19376516342163</t>
+    <t xml:space="preserve">1.19376492500305</t>
   </si>
   <si>
     <t xml:space="preserve">1.17766273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19742465019226</t>
+    <t xml:space="preserve">1.19742453098297</t>
   </si>
   <si>
     <t xml:space="preserve">1.20620775222778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19230103492737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18059051036835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522002220154</t>
+    <t xml:space="preserve">1.19230115413666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18059039115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522014141083</t>
   </si>
   <si>
     <t xml:space="preserve">1.15643703937531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16887974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17693078517914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19522893428802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17985844612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18498194217682</t>
+    <t xml:space="preserve">1.16887962818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17693090438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19522881507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17985856533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18498182296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.17400300502777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17107534408569</t>
+    <t xml:space="preserve">1.17107546329498</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814780235291</t>
@@ -539,31 +539,31 @@
     <t xml:space="preserve">1.1461900472641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14326250553131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11252176761627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13447940349579</t>
+    <t xml:space="preserve">1.14326226711273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1125214099884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1344792842865</t>
   </si>
   <si>
     <t xml:space="preserve">1.11984086036682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11325371265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10593450069427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10007905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12276875972748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032593250275</t>
+    <t xml:space="preserve">1.1132538318634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10593438148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10007894039154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1227685213089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032569408417</t>
   </si>
   <si>
     <t xml:space="preserve">1.11618137359619</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">1.1278920173645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14399421215057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14179849624634</t>
+    <t xml:space="preserve">1.14399433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14179861545563</t>
   </si>
   <si>
     <t xml:space="preserve">1.13521134853363</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">1.19449698925018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1813223361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17253923416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17912638187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13887083530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13374733924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12350034713745</t>
+    <t xml:space="preserve">1.18132221698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17253935337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17912650108337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13887095451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13374745845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12350046634674</t>
   </si>
   <si>
     <t xml:space="preserve">1.12569618225098</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">1.15936470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1527773141861</t>
+    <t xml:space="preserve">1.15277743339539</t>
   </si>
   <si>
     <t xml:space="preserve">1.16741585731506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22377407550812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22596955299377</t>
+    <t xml:space="preserve">1.22377395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22596967220306</t>
   </si>
   <si>
     <t xml:space="preserve">1.2567104101181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24792742729187</t>
+    <t xml:space="preserve">1.24792718887329</t>
   </si>
   <si>
     <t xml:space="preserve">1.24060809612274</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">1.26622521877289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26842105388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29769778251648</t>
+    <t xml:space="preserve">1.2684211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29769790172577</t>
   </si>
   <si>
     <t xml:space="preserve">1.30867683887482</t>
@@ -662,37 +662,37 @@
     <t xml:space="preserve">1.29403841495514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32477903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404720783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3101407289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3284387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037868976593</t>
+    <t xml:space="preserve">1.3247789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32843887805939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037880897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135762691498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30282139778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3152642250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32624292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137521266937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33941769599915</t>
+    <t xml:space="preserve">1.30282127857208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31526410579681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32624304294586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137509346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33941745758057</t>
   </si>
   <si>
     <t xml:space="preserve">1.34673678874969</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">1.38699233531952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36869442462921</t>
+    <t xml:space="preserve">1.36869430541992</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772439956665</t>
@@ -713,61 +713,61 @@
     <t xml:space="preserve">1.37454986572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40529048442841</t>
+    <t xml:space="preserve">1.40529036521912</t>
   </si>
   <si>
     <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39650750160217</t>
+    <t xml:space="preserve">1.39650738239288</t>
   </si>
   <si>
     <t xml:space="preserve">1.41114592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38186895847321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.371621966362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38845646381378</t>
+    <t xml:space="preserve">1.3818690776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37162208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38845634460449</t>
   </si>
   <si>
     <t xml:space="preserve">1.41927754878998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45009863376617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046503543854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53654813766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56361079216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58616292476654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60570800304413</t>
+    <t xml:space="preserve">1.45009875297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046515464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53654825687408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56361067295074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58616280555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60570788383484</t>
   </si>
   <si>
     <t xml:space="preserve">1.51700305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51098930835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48693370819092</t>
+    <t xml:space="preserve">1.51098918914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48693382740021</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49069261550903</t>
+    <t xml:space="preserve">1.49069237709045</t>
   </si>
   <si>
     <t xml:space="preserve">1.46814024448395</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">1.46964395046234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44333291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483649730682</t>
+    <t xml:space="preserve">1.44333302974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4448367357254</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882274627686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4320570230484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43581569194794</t>
+    <t xml:space="preserve">1.43205690383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43581557273865</t>
   </si>
   <si>
     <t xml:space="preserve">1.40574622154236</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">1.45911955833435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45310568809509</t>
+    <t xml:space="preserve">1.47189891338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45310544967651</t>
   </si>
   <si>
     <t xml:space="preserve">1.42829835414886</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">1.41852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42980182170868</t>
+    <t xml:space="preserve">1.42980170249939</t>
   </si>
   <si>
     <t xml:space="preserve">1.42078101634979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42604315280914</t>
+    <t xml:space="preserve">1.42604327201843</t>
   </si>
   <si>
     <t xml:space="preserve">1.41702222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42529129981995</t>
+    <t xml:space="preserve">1.42529141902924</t>
   </si>
   <si>
     <t xml:space="preserve">1.44408476352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47716116905212</t>
+    <t xml:space="preserve">1.47716104984283</t>
   </si>
   <si>
     <t xml:space="preserve">1.49219584465027</t>
@@ -839,52 +839,52 @@
     <t xml:space="preserve">1.46663689613342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46588528156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144411087036</t>
+    <t xml:space="preserve">1.46588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144423007965</t>
   </si>
   <si>
     <t xml:space="preserve">1.48843717575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850664615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948584079742</t>
+    <t xml:space="preserve">1.5185067653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948572158813</t>
   </si>
   <si>
     <t xml:space="preserve">1.50347197055817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48167145252228</t>
+    <t xml:space="preserve">1.48167157173157</t>
   </si>
   <si>
     <t xml:space="preserve">1.49595463275909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51249289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497543811798</t>
+    <t xml:space="preserve">1.51249301433563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497567653656</t>
   </si>
   <si>
     <t xml:space="preserve">1.52151346206665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49369931221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49896156787872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602410316467</t>
+    <t xml:space="preserve">1.49369955062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49896144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602386474609</t>
   </si>
   <si>
     <t xml:space="preserve">1.496706366539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50798237323761</t>
+    <t xml:space="preserve">1.50798225402832</t>
   </si>
   <si>
     <t xml:space="preserve">1.54857611656189</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">1.48242330551147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47039568424225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47941648960114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53203797340393</t>
+    <t xml:space="preserve">1.47039544582367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47941625118256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53203785419464</t>
   </si>
   <si>
     <t xml:space="preserve">1.52903091907501</t>
@@ -908,31 +908,31 @@
     <t xml:space="preserve">1.51399612426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55158293247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56511414051056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55609333515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126707077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67637121677399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65682601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69140601158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70644068717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71997201442719</t>
+    <t xml:space="preserve">1.55158305168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56511449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55609345436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126718997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67637145519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6568261384964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69140589237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70644056797028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7199718952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.65381908416748</t>
@@ -941,148 +941,148 @@
     <t xml:space="preserve">1.67937803268433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66735029220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66885375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787480354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67035698890686</t>
+    <t xml:space="preserve">1.6673504114151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66885387897491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6778746843338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67035746574402</t>
   </si>
   <si>
     <t xml:space="preserve">1.67186081409454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68839907646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68689548969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65983307361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63878464698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64630174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74402713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80115938186646</t>
+    <t xml:space="preserve">1.6883989572525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68689560890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65983283519745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63878452777863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6463018655777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74402749538422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80115926265717</t>
   </si>
   <si>
     <t xml:space="preserve">1.81318700313568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79213869571686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79965579509735</t>
+    <t xml:space="preserve">1.79213857650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79965603351593</t>
   </si>
   <si>
     <t xml:space="preserve">1.84175300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86430525779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8387463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76657962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71245443820953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66133654117584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7620689868927</t>
+    <t xml:space="preserve">1.86430490016937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83874642848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76657950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71245467662811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66133666038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206934452057</t>
   </si>
   <si>
     <t xml:space="preserve">1.77560031414032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83423566818237</t>
+    <t xml:space="preserve">1.83423590660095</t>
   </si>
   <si>
     <t xml:space="preserve">1.80566966533661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82220780849457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72899281978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74102079868317</t>
+    <t xml:space="preserve">1.82220804691315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72899258136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74102020263672</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598588466644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75154495239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72297859191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70193016529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69441270828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68388843536377</t>
+    <t xml:space="preserve">1.75154459476471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7229790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70193004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69441318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68388831615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434347629547</t>
+    <t xml:space="preserve">1.66434359550476</t>
   </si>
   <si>
     <t xml:space="preserve">1.72448241710663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71846854686737</t>
+    <t xml:space="preserve">1.71846842765808</t>
   </si>
   <si>
     <t xml:space="preserve">1.75755882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73500657081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73951697349548</t>
+    <t xml:space="preserve">1.73500669002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73951709270477</t>
   </si>
   <si>
     <t xml:space="preserve">1.73650991916656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71395778656006</t>
+    <t xml:space="preserve">1.71395802497864</t>
   </si>
   <si>
     <t xml:space="preserve">1.78161430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75906217098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8192013502121</t>
+    <t xml:space="preserve">1.75906193256378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81920111179352</t>
   </si>
   <si>
     <t xml:space="preserve">1.82671856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80416643619537</t>
+    <t xml:space="preserve">1.80416619777679</t>
   </si>
   <si>
     <t xml:space="preserve">1.87933993339539</t>
@@ -1094,67 +1094,67 @@
     <t xml:space="preserve">1.81168365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79664885997772</t>
+    <t xml:space="preserve">1.7966490983963</t>
   </si>
   <si>
     <t xml:space="preserve">1.77409672737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78913164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678803920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84927034378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88701057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865689277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86399805545807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179737329483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81030261516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90235221385956</t>
+    <t xml:space="preserve">1.78913187980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84927046298981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88701069355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89468133449554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865701198578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86399829387665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81797361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81030297279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90235209465027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83331537246704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80263209342957</t>
+    <t xml:space="preserve">1.80263197422028</t>
   </si>
   <si>
     <t xml:space="preserve">1.75660741329193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70291197299957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76427805423737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67989981174469</t>
+    <t xml:space="preserve">1.70291209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76427841186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6798996925354</t>
   </si>
   <si>
     <t xml:space="preserve">1.69524133205414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67222893238068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74893653392792</t>
+    <t xml:space="preserve">1.67222917079926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74893665313721</t>
   </si>
   <si>
     <t xml:space="preserve">1.65688741207123</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">1.64154589176178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58017945289612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66455829143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62620425224304</t>
+    <t xml:space="preserve">1.5801796913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66455817222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62620413303375</t>
   </si>
   <si>
     <t xml:space="preserve">1.57250893115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51497805118561</t>
+    <t xml:space="preserve">1.5149781703949</t>
   </si>
   <si>
     <t xml:space="preserve">1.53031957149506</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">1.39224565029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36923336982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39991652965546</t>
+    <t xml:space="preserve">1.36923325061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39991641044617</t>
   </si>
   <si>
     <t xml:space="preserve">1.35772716999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35389173030853</t>
+    <t xml:space="preserve">1.35389184951782</t>
   </si>
   <si>
     <t xml:space="preserve">1.34238564968109</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">1.30403172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28101933002472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26951324939728</t>
+    <t xml:space="preserve">1.28101944923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26951313018799</t>
   </si>
   <si>
     <t xml:space="preserve">1.25417172908783</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">1.25800704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29636096954346</t>
+    <t xml:space="preserve">1.29636108875275</t>
   </si>
   <si>
     <t xml:space="preserve">1.28869009017944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30019640922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252564907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31937336921692</t>
+    <t xml:space="preserve">1.30019629001617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252552986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31937325000763</t>
   </si>
   <si>
     <t xml:space="preserve">1.30786716938019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33087956905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855032920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33471477031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31553792953491</t>
+    <t xml:space="preserve">1.33087944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33471488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31553781032562</t>
   </si>
   <si>
     <t xml:space="preserve">1.39608108997345</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">1.38457489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40375173091888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36156249046326</t>
+    <t xml:space="preserve">1.40375185012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36156237125397</t>
   </si>
   <si>
     <t xml:space="preserve">1.36539793014526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43443500995636</t>
+    <t xml:space="preserve">1.43443512916565</t>
   </si>
   <si>
     <t xml:space="preserve">1.37690401077271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38841032981873</t>
+    <t xml:space="preserve">1.38841021060944</t>
   </si>
   <si>
     <t xml:space="preserve">1.34622097015381</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">1.32704401016235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27334868907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32320857048035</t>
+    <t xml:space="preserve">1.27334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32320868968964</t>
   </si>
   <si>
     <t xml:space="preserve">1.37706017494202</t>
@@ -1307,22 +1307,22 @@
     <t xml:space="preserve">1.3890346288681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3610942363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32916247844696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35311138629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34512841701508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36508595943451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39701759815216</t>
+    <t xml:space="preserve">1.36109435558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32916235923767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34512829780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36508584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39701771736145</t>
   </si>
   <si>
     <t xml:space="preserve">1.41298353672028</t>
@@ -1331,43 +1331,43 @@
     <t xml:space="preserve">1.40100908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40899193286896</t>
+    <t xml:space="preserve">1.40899205207825</t>
   </si>
   <si>
     <t xml:space="preserve">1.41697490215302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46886432170868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49680459499359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877892971039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51277053356171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49281311035156</t>
+    <t xml:space="preserve">1.4688640832901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4968044757843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877904891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51277041435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49281322956085</t>
   </si>
   <si>
     <t xml:space="preserve">1.46487271785736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50079607963562</t>
+    <t xml:space="preserve">1.50079596042633</t>
   </si>
   <si>
     <t xml:space="preserve">1.44491529464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45289826393127</t>
+    <t xml:space="preserve">1.45289838314056</t>
   </si>
   <si>
     <t xml:space="preserve">1.43693220615387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42495799064636</t>
+    <t xml:space="preserve">1.42495787143707</t>
   </si>
   <si>
     <t xml:space="preserve">1.42096638679504</t>
@@ -1382,10 +1382,7 @@
     <t xml:space="preserve">1.38504314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4289493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37306880950928</t>
+    <t xml:space="preserve">1.42894947528839</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907720565796</t>
@@ -1394,22 +1391,22 @@
     <t xml:space="preserve">1.35710275173187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3491199016571</t>
+    <t xml:space="preserve">1.34912002086639</t>
   </si>
   <si>
     <t xml:space="preserve">1.4848301410675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47684705257416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46088123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48882150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52075350284576</t>
+    <t xml:space="preserve">1.47684729099274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46088135242462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48882162570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52075338363647</t>
   </si>
   <si>
     <t xml:space="preserve">1.51676189899445</t>
@@ -1430,13 +1427,13 @@
     <t xml:space="preserve">1.53272783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52873635292053</t>
+    <t xml:space="preserve">1.52873623371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.58860862255096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55667674541473</t>
+    <t xml:space="preserve">1.55667686462402</t>
   </si>
   <si>
     <t xml:space="preserve">1.54869377613068</t>
@@ -1445,25 +1442,25 @@
     <t xml:space="preserve">1.53671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54470217227936</t>
+    <t xml:space="preserve">1.54470229148865</t>
   </si>
   <si>
     <t xml:space="preserve">1.55268537998199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52474474906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264268398285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642092704773</t>
+    <t xml:space="preserve">1.5247448682785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264256477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642104625702</t>
   </si>
   <si>
     <t xml:space="preserve">1.86801207065582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88397765159607</t>
+    <t xml:space="preserve">1.88397800922394</t>
   </si>
   <si>
     <t xml:space="preserve">1.9478417634964</t>
@@ -1472,7 +1469,7 @@
     <t xml:space="preserve">2.15539860725403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05960297584534</t>
+    <t xml:space="preserve">2.05960321426392</t>
   </si>
   <si>
     <t xml:space="preserve">2.16338133811951</t>
@@ -1481,7 +1478,7 @@
     <t xml:space="preserve">2.20329642295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926188468933</t>
+    <t xml:space="preserve">2.21926259994507</t>
   </si>
   <si>
     <t xml:space="preserve">2.22724509239197</t>
@@ -1493,7 +1490,7 @@
     <t xml:space="preserve">2.23522782325745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11548352241516</t>
+    <t xml:space="preserve">2.11548399925232</t>
   </si>
   <si>
     <t xml:space="preserve">1.9877564907074</t>
@@ -1505,28 +1502,28 @@
     <t xml:space="preserve">1.82809722423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91591000556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002898216248</t>
+    <t xml:space="preserve">1.91590976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002922058105</t>
   </si>
   <si>
     <t xml:space="preserve">1.63650631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260010719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72431898117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62852334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6444890499115</t>
+    <t xml:space="preserve">1.44890677928925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5925999879837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72431886196136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62852323055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64448928833008</t>
   </si>
   <si>
     <t xml:space="preserve">1.68440401554108</t>
@@ -1538,31 +1535,31 @@
     <t xml:space="preserve">1.6604551076889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65247225761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74826788902283</t>
+    <t xml:space="preserve">1.65247213840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74826776981354</t>
   </si>
   <si>
     <t xml:space="preserve">1.71633589267731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62054038047791</t>
+    <t xml:space="preserve">1.62054049968719</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843807697296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61255753040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69238698482513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7562507390976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76423358917236</t>
+    <t xml:space="preserve">1.61255741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69238686561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75625050067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76423370838165</t>
   </si>
   <si>
     <t xml:space="preserve">1.90792691707611</t>
@@ -1571,16 +1568,16 @@
     <t xml:space="preserve">1.95582461357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92389273643494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94757199287415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91456246376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90631008148193</t>
+    <t xml:space="preserve">1.92389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94757211208344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9145622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90630984306335</t>
   </si>
   <si>
     <t xml:space="preserve">1.85679543018341</t>
@@ -1592,13 +1589,13 @@
     <t xml:space="preserve">1.81553339958191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.790776014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75776636600494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902839660645</t>
+    <t xml:space="preserve">1.79077613353729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75776648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902863502502</t>
   </si>
   <si>
     <t xml:space="preserve">1.77427124977112</t>
@@ -1634,22 +1631,22 @@
     <t xml:space="preserve">1.66698968410492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70825183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69174706935883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7247565984726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65048491954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398003578186</t>
+    <t xml:space="preserve">1.65873730182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70825171470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69174695014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72475671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65048480033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63397991657257</t>
   </si>
   <si>
     <t xml:space="preserve">1.62572765350342</t>
@@ -1658,22 +1655,25 @@
     <t xml:space="preserve">1.62985384464264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60922276973724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805746078491</t>
+    <t xml:space="preserve">1.60922288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805769920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95582437515259</t>
   </si>
   <si>
     <t xml:space="preserve">2.04660129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9640771150589</t>
+    <t xml:space="preserve">1.96407723426819</t>
   </si>
   <si>
     <t xml:space="preserve">1.93931972980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8733001947403</t>
+    <t xml:space="preserve">1.87330031394958</t>
   </si>
   <si>
     <t xml:space="preserve">1.88155269622803</t>
@@ -1688,64 +1688,64 @@
     <t xml:space="preserve">1.92281484603882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93106734752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883414268494</t>
+    <t xml:space="preserve">1.93106722831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359152793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.97232949733734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98058176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06310606002808</t>
+    <t xml:space="preserve">1.98058187961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06310629844666</t>
   </si>
   <si>
     <t xml:space="preserve">2.19514489173889</t>
   </si>
   <si>
+    <t xml:space="preserve">2.17864036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17038750648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14563035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19566059112549</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.17864012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17038774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16213512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14563012123108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19566035270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863988876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18715000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15310907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11906790733337</t>
+    <t xml:space="preserve">2.18715023994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15310883522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11906766891479</t>
   </si>
   <si>
     <t xml:space="preserve">2.08502650260925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09353709220886</t>
+    <t xml:space="preserve">2.09353685379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800580024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03396463394165</t>
+    <t xml:space="preserve">2.03396487236023</t>
   </si>
   <si>
     <t xml:space="preserve">2.0254545211792</t>
@@ -1754,46 +1754,46 @@
     <t xml:space="preserve">2.04247498512268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05098533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91482019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93184065818787</t>
+    <t xml:space="preserve">2.05098509788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91482043266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93184089660645</t>
   </si>
   <si>
     <t xml:space="preserve">1.95737171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97439229488373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0765163898468</t>
+    <t xml:space="preserve">1.98290264606476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97439253330231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07651615142822</t>
   </si>
   <si>
     <t xml:space="preserve">2.11055755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05949568748474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99992311000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99141311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00843358039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01694369316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204696655273</t>
+    <t xml:space="preserve">2.05949544906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99992346763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9914128780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00843381881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01694393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204720497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.12757802009583</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">2.14459872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16161942481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13608837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9658819437027</t>
+    <t xml:space="preserve">2.16161918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13608860969543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96588206291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.94035112857819</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">1.89779961109161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8722687959671</t>
+    <t xml:space="preserve">1.87226867675781</t>
   </si>
   <si>
     <t xml:space="preserve">1.92333054542542</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">1.94886147975922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07243418693542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08129048347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05472087860107</t>
+    <t xml:space="preserve">2.07243394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08129072189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05472111701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.04586434364319</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">2.0370078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93958556652069</t>
+    <t xml:space="preserve">1.93958580493927</t>
   </si>
   <si>
     <t xml:space="preserve">1.97501194477081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99272501468658</t>
+    <t xml:space="preserve">1.99272525310516</t>
   </si>
   <si>
     <t xml:space="preserve">1.95729887485504</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">1.94844233989716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8687332868576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92187261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9130163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775897026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93072926998138</t>
+    <t xml:space="preserve">1.86873304843903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92187285423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91301620006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87758982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93072915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.88644659519196</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">1.96615540981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90415966510773</t>
+    <t xml:space="preserve">1.90415978431702</t>
   </si>
   <si>
     <t xml:space="preserve">1.89530301094055</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.78902423381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80673742294312</t>
+    <t xml:space="preserve">1.80673730373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.79788088798523</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">1.74474155902863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85102009773254</t>
+    <t xml:space="preserve">1.85102021694183</t>
   </si>
   <si>
     <t xml:space="preserve">1.84216368198395</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">1.75802636146545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76245474815369</t>
+    <t xml:space="preserve">1.7624546289444</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588502407074</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">1.7535982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71817195415497</t>
+    <t xml:space="preserve">1.71817183494568</t>
   </si>
   <si>
     <t xml:space="preserve">1.70931529998779</t>
@@ -27215,7 +27215,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G950" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G952" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G956" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G957" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27553,7 +27553,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G962" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G963" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G968" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G969" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G974" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G980" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G981" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G992" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G995" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G996" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G998" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1000" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1001" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1003" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1006" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1007" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1009" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1011" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1012" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1014" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>2</v>
       </c>
       <c r="G1015" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1016" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1017" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1018" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1021" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1023" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1024" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1025" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1027" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1028" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1029" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1030" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1031" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1032" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1033" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1034" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1035" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1036" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1037" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1038" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1039" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1040" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1041" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1042" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1043" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1044" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1045" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1046" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1048" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1050" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1051" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1053" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1054" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1055" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1056" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1057" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1058" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1061" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1062" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1065" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>2</v>
       </c>
       <c r="G1066" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1067" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1069" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1070" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1071" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1076" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1077" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1081" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1082" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1083" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1084" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1086" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1087" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1089" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1091" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1092" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1094" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1095" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1096" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1098" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1101" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1103" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1104" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1106" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1107" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1108" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1109" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1111" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1112" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1113" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1115" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1116" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1118" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1119" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1120" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31713,7 +31713,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1122" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31739,7 +31739,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31791,7 +31791,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1125" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1128" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1130" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1132" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1133" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1134" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1135" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32077,7 +32077,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1136" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1138" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32155,7 +32155,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1140" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1141" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32233,7 +32233,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>2.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1144" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32337,7 +32337,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32363,7 +32363,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1148" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1150" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32467,7 +32467,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32493,7 +32493,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32519,7 +32519,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1153" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32545,7 +32545,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1154" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32571,7 +32571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1155" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32597,7 +32597,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1156" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32623,7 +32623,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1157" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32649,7 +32649,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1158" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32675,7 +32675,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1159" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32701,7 +32701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1160" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32727,7 +32727,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1161" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32753,7 +32753,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1162" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32779,7 +32779,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1163" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32805,7 +32805,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1164" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32831,7 +32831,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1165" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32857,7 +32857,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1166" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32883,7 +32883,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1167" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32909,7 +32909,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1168" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1169" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1170" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32987,7 +32987,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1171" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1173" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1175" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1176" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1177" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1178" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1179" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1180" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1181" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1182" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1183" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1185" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1186" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1187" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1188" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1189" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1190" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1192" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1193" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>2</v>
       </c>
       <c r="G1194" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1195" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1197" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33715,7 +33715,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1199" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1200" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33767,7 +33767,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33819,7 +33819,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1206" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1207" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1208" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1209" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1213" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1214" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>2</v>
       </c>
       <c r="G1215" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1217" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1218" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34235,7 +34235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1220" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34313,7 +34313,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1225" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1226" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1228" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1229" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1231" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1235" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1240" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1241" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1242" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1243" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1244" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1245" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1249" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1250" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1252" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1258" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1261" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1262" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1276" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1278" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1280" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1281" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1282" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1283" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1284" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>2.25</v>
       </c>
       <c r="G1291" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36133,7 +36133,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1292" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36185,7 +36185,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1294" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1296" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1298" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36367,7 +36367,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36393,7 +36393,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1302" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36419,7 +36419,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1303" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36445,7 +36445,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1304" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36497,7 +36497,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36523,7 +36523,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1307" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36549,7 +36549,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36601,7 +36601,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36627,7 +36627,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1311" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36653,7 +36653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1312" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36679,7 +36679,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1313" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36705,7 +36705,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36731,7 +36731,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1315" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36939,7 +36939,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1323" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36965,7 +36965,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1324" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36991,7 +36991,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1325" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37225,7 +37225,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1334" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37251,7 +37251,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1335" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37277,7 +37277,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1336" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37355,7 +37355,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1339" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37381,7 +37381,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1340" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37407,7 +37407,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1341" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37433,7 +37433,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1342" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37459,7 +37459,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1343" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37485,7 +37485,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1344" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37537,7 +37537,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37563,7 +37563,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1347" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37615,7 +37615,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37667,7 +37667,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1351" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37693,7 +37693,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1352" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37719,7 +37719,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37745,7 +37745,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37771,7 +37771,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37823,7 +37823,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1357" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37953,7 +37953,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38005,7 +38005,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1364" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38057,7 +38057,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38135,7 +38135,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38161,7 +38161,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -43361,7 +43361,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1570" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -69057,7 +69057,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.533287037</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>1580</v>
@@ -69078,6 +69078,32 @@
         <v>729</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6911689815</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>1693</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">1.1254426240921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09552562236786</t>
+    <t xml:space="preserve">1.09552586078644</t>
   </si>
   <si>
     <t xml:space="preserve">1.11831951141357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0962381362915</t>
+    <t xml:space="preserve">1.09623801708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.09695041179657</t>
@@ -65,106 +65,106 @@
     <t xml:space="preserve">1.10407328605652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09053957462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08412897586823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00007688999176</t>
+    <t xml:space="preserve">1.0905396938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08412885665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007712841034</t>
   </si>
   <si>
     <t xml:space="preserve">0.943804681301117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925996899604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993666112422943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03925371170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01004910469055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05492448806763</t>
+    <t xml:space="preserve">0.925996959209442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993666052818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03925359249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01004922389984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01859676837921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05492424964905</t>
   </si>
   <si>
     <t xml:space="preserve">1.03213047981262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03711676597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02571976184845</t>
+    <t xml:space="preserve">1.03711652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572000026703</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02643227577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0207337141037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947366178035736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900354087352753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916024804115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922435522079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939530968666077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985830545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970159947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961612343788147</t>
+    <t xml:space="preserve">1.02643215656281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02073383331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947366237640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900354146957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916024625301361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922435700893402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939530849456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98583060503006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970160007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961612224578857</t>
   </si>
   <si>
     <t xml:space="preserve">0.962324619293213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00435066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997939944267273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989392101764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991528928279877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979419767856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99081689119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987967491149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997227668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01717221736908</t>
+    <t xml:space="preserve">1.00435078144073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997939825057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989392280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991529107093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979420065879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990816831588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987967669963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997227609157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01717209815979</t>
   </si>
   <si>
     <t xml:space="preserve">1.01503527164459</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">1.02215826511383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.005774974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00648760795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076149940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00221371650696</t>
+    <t xml:space="preserve">1.00577521324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00648748874664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00221383571625</t>
   </si>
   <si>
     <t xml:space="preserve">0.984405994415283</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.03284287452698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01930892467499</t>
+    <t xml:space="preserve">1.01930916309357</t>
   </si>
   <si>
     <t xml:space="preserve">1.03996598720551</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">1.09979951381683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1005117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084841132164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982729911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1817147731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1681809425354</t>
+    <t xml:space="preserve">1.10051214694977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982717990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18171453475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16818106174469</t>
   </si>
   <si>
     <t xml:space="preserve">1.13185334205627</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">1.15393483638763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11689496040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09766256809235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16105782985687</t>
+    <t xml:space="preserve">1.11689484119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09766268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16105771064758</t>
   </si>
   <si>
     <t xml:space="preserve">1.15963315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14752388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1368396282196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612711429596</t>
+    <t xml:space="preserve">1.14752411842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13683950901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612723350525</t>
   </si>
   <si>
     <t xml:space="preserve">1.12900412082672</t>
@@ -257,37 +257,37 @@
     <t xml:space="preserve">1.14467477798462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17316699028015</t>
+    <t xml:space="preserve">1.17316722869873</t>
   </si>
   <si>
     <t xml:space="preserve">1.1703177690506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18100237846375</t>
+    <t xml:space="preserve">1.18100249767303</t>
   </si>
   <si>
     <t xml:space="preserve">1.197385430336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21091938018799</t>
+    <t xml:space="preserve">1.2109192609787</t>
   </si>
   <si>
     <t xml:space="preserve">1.21163153648376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20593309402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22302830219269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22089147567749</t>
+    <t xml:space="preserve">1.20593321323395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22302842140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22089159488678</t>
   </si>
   <si>
     <t xml:space="preserve">1.19596087932587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23548448085785</t>
+    <t xml:space="preserve">1.23548460006714</t>
   </si>
   <si>
     <t xml:space="preserve">1.22670161724091</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">1.18937361240387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18790972232819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1630243062973</t>
+    <t xml:space="preserve">1.18790948390961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16302442550659</t>
   </si>
   <si>
     <t xml:space="preserve">1.16595208644867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16229236125946</t>
+    <t xml:space="preserve">1.16229248046875</t>
   </si>
   <si>
     <t xml:space="preserve">1.16375625133514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15570509433746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14911770820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15424144268036</t>
+    <t xml:space="preserve">1.15570497512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14911782741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15424132347107</t>
   </si>
   <si>
     <t xml:space="preserve">1.14106667041779</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">1.10154283046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10520255565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14545822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12935590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12716019153595</t>
+    <t xml:space="preserve">1.10520231723785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0993469953537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14545810222626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12935566902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12203681468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12715995311737</t>
   </si>
   <si>
     <t xml:space="preserve">1.07226598262787</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">1.06860649585724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13081955909729</t>
+    <t xml:space="preserve">1.13081979751587</t>
   </si>
   <si>
     <t xml:space="preserve">1.12423241138458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15716886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18717777729034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18205428123474</t>
+    <t xml:space="preserve">1.15716898441315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18717765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18205416202545</t>
   </si>
   <si>
     <t xml:space="preserve">1.20767152309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17839455604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20401191711426</t>
+    <t xml:space="preserve">1.17839467525482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20401203632355</t>
   </si>
   <si>
     <t xml:space="preserve">1.18351817131042</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">1.2047438621521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17473518848419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18571400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17546689510345</t>
+    <t xml:space="preserve">1.1747350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18571388721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17546677589417</t>
   </si>
   <si>
     <t xml:space="preserve">1.19303297996521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20035231113434</t>
+    <t xml:space="preserve">1.20035243034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.19888854026794</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">1.20693969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21425890922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22231006622314</t>
+    <t xml:space="preserve">1.21425867080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22230982780457</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962915897369</t>
@@ -419,40 +419,40 @@
     <t xml:space="preserve">1.23328876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22450566291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25524640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28232753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31745970249176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30208957195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29550218582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29184246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27866780757904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24426770210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25890612602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27354454994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25963795185089</t>
+    <t xml:space="preserve">1.22450578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25524652004242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28232765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31745994091034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30208945274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29550206661224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29184257984161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27866816520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24426782131195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25890636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27354443073273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25963807106018</t>
   </si>
   <si>
     <t xml:space="preserve">1.26183378696442</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">1.26256573200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26915311813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23694837093353</t>
+    <t xml:space="preserve">1.26915287971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23694849014282</t>
   </si>
   <si>
     <t xml:space="preserve">1.23109304904938</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">1.24719524383545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22304201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21938240528107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1996203660965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19669258594513</t>
+    <t xml:space="preserve">1.2230418920517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21938228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19962048530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19669270515442</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376504421234</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">1.19742476940155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20620763301849</t>
+    <t xml:space="preserve">1.20620775222778</t>
   </si>
   <si>
     <t xml:space="preserve">1.19230115413666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18059039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522002220154</t>
+    <t xml:space="preserve">1.18059051036835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522014141083</t>
   </si>
   <si>
     <t xml:space="preserve">1.15643703937531</t>
@@ -515,82 +515,82 @@
     <t xml:space="preserve">1.16887962818146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17693078517914</t>
+    <t xml:space="preserve">1.17693090438843</t>
   </si>
   <si>
     <t xml:space="preserve">1.19522893428802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17985856533051</t>
+    <t xml:space="preserve">1.17985832691193</t>
   </si>
   <si>
     <t xml:space="preserve">1.18498194217682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17400324344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17107558250427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16814792156219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14619016647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14326250553131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11252164840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13447940349579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11984086036682</t>
+    <t xml:space="preserve">1.17400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17107546329498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16814780235291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14618992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14326238632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11252176761627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1344792842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11984074115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.11325371265411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10593450069427</t>
+    <t xml:space="preserve">1.10593438148499</t>
   </si>
   <si>
     <t xml:space="preserve">1.10007894039154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1227685213089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032593250275</t>
+    <t xml:space="preserve">1.12276864051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032605171204</t>
   </si>
   <si>
     <t xml:space="preserve">1.1161812543869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13960289955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1278920173645</t>
+    <t xml:space="preserve">1.13960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12789213657379</t>
   </si>
   <si>
     <t xml:space="preserve">1.14399433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14179837703705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13521122932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13813889026642</t>
+    <t xml:space="preserve">1.14179861545563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13521111011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13813877105713</t>
   </si>
   <si>
     <t xml:space="preserve">1.14253044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1944967508316</t>
+    <t xml:space="preserve">1.19449698925018</t>
   </si>
   <si>
     <t xml:space="preserve">1.1813223361969</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">1.17253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17912638187408</t>
+    <t xml:space="preserve">1.17912662029266</t>
   </si>
   <si>
     <t xml:space="preserve">1.13887083530426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13374733924866</t>
+    <t xml:space="preserve">1.13374745845795</t>
   </si>
   <si>
     <t xml:space="preserve">1.12350058555603</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">1.12569630146027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11910915374756</t>
+    <t xml:space="preserve">1.11910903453827</t>
   </si>
   <si>
     <t xml:space="preserve">1.12496435642242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1264283657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15936458110809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15277755260468</t>
+    <t xml:space="preserve">1.12642800807953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15936470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15277743339539</t>
   </si>
   <si>
     <t xml:space="preserve">1.16741585731506</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">1.22377383708954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22596967220306</t>
+    <t xml:space="preserve">1.22596955299377</t>
   </si>
   <si>
     <t xml:space="preserve">1.25671029090881</t>
@@ -647,49 +647,49 @@
     <t xml:space="preserve">1.24060809612274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26622533798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2684211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29769802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30867683887482</t>
+    <t xml:space="preserve">1.26622521877289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26842105388641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29769790172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30867671966553</t>
   </si>
   <si>
     <t xml:space="preserve">1.29403829574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32477903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32404708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31014049053192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32843887805939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29037868976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135774612427</t>
+    <t xml:space="preserve">1.32477915287018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32404720783234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3284387588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29037892818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135762691498</t>
   </si>
   <si>
     <t xml:space="preserve">1.30282139778137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3152642250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32624280452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36137533187866</t>
+    <t xml:space="preserve">1.31526398658752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32624316215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36137521266937</t>
   </si>
   <si>
     <t xml:space="preserve">1.33941757678986</t>
@@ -704,22 +704,22 @@
     <t xml:space="preserve">1.36869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38772451877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35991144180298</t>
+    <t xml:space="preserve">1.38772439956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35991132259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.37454986572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40529036521912</t>
+    <t xml:space="preserve">1.4052906036377</t>
   </si>
   <si>
     <t xml:space="preserve">1.39065206050873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39650738239288</t>
+    <t xml:space="preserve">1.39650750160217</t>
   </si>
   <si>
     <t xml:space="preserve">1.41114592552185</t>
@@ -731,13 +